--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="375">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -535,6 +535,9 @@
   </si>
   <si>
     <t>Prior-Year ADA</t>
+  </si>
+  <si>
+    <t>Attendance Ratio (ADA ÷ ADM)</t>
   </si>
   <si>
     <t>Per-Pupil Rate</t>
@@ -1326,7 +1329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1355,6 +1358,7 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2044,7 +2048,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2076,25 +2080,25 @@
       <c r="A4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <v>120</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <v>200</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>300</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>400</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>500</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2106,19 +2110,19 @@
       <c r="A7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <v>969000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>1617850</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>2466200</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>3327850</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>4233200</v>
       </c>
     </row>
@@ -2126,19 +2130,19 @@
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <v>90000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>154500</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>238703</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>327818</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>422066</v>
       </c>
     </row>
@@ -2146,19 +2150,19 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <v>132000</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>226600</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>350097</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>480800</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>619030</v>
       </c>
     </row>
@@ -2166,19 +2170,19 @@
       <c r="A10" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <v>150000</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>154500</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>159135</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>163909</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>168826</v>
       </c>
     </row>
@@ -2186,19 +2190,19 @@
       <c r="A11" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <v>25000</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>25750</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>26523</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>27318</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>28138</v>
       </c>
     </row>
@@ -2206,59 +2210,59 @@
       <c r="A12" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <v>48000</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>82400</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>127308</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>174836</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>225102</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="25">
+        <v>207</v>
+      </c>
+      <c r="B13" s="26">
         <v>1414000</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>2261600</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>3367965</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>4502532</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>5696361</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B15" s="24">
+        <v>236</v>
+      </c>
+      <c r="B15" s="25">
         <v>11783</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>11308</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>11227</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>11256</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>11393</v>
       </c>
     </row>
@@ -2288,7 +2292,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2328,81 +2332,81 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B5" s="24">
+        <v>238</v>
+      </c>
+      <c r="B5" s="25">
         <v>278438</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>344149</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>354473</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>365107</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>376061</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="24">
+        <v>239</v>
+      </c>
+      <c r="B6" s="25">
         <v>59029</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>72960</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>75148</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>77403</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>79725</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="24">
+        <v>240</v>
+      </c>
+      <c r="B7" s="25">
         <v>87955</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>108712</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>111974</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>115333</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>118793</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B8" s="29">
+        <v>241</v>
+      </c>
+      <c r="B8" s="30">
         <v>425421</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>525821</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>541595</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>557843</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>574578</v>
       </c>
     </row>
@@ -2418,61 +2422,61 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B10" s="24">
+        <v>242</v>
+      </c>
+      <c r="B10" s="25">
         <v>116944</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>144542</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>148879</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>153345</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>157945</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B11" s="24">
+        <v>243</v>
+      </c>
+      <c r="B11" s="25">
         <v>91328</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>112881</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>116267</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>119755</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>123348</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="B12" s="29">
+        <v>244</v>
+      </c>
+      <c r="B12" s="30">
         <v>208271</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>257423</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>265146</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <v>273100</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <v>281293</v>
       </c>
     </row>
@@ -2488,41 +2492,41 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B14" s="24">
+        <v>245</v>
+      </c>
+      <c r="B14" s="25">
         <v>69053</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>85349</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>87909</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>90547</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>93263</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B15" s="29">
+        <v>246</v>
+      </c>
+      <c r="B15" s="30">
         <v>69053</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>85349</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>87909</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>90547</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>93263</v>
       </c>
     </row>
@@ -2538,61 +2542,61 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B17" s="24">
+        <v>247</v>
+      </c>
+      <c r="B17" s="25">
         <v>77790</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>96148</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>99033</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>102004</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>105064</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B18" s="29">
+        <v>248</v>
+      </c>
+      <c r="B18" s="30">
         <v>77790</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>96148</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>99033</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>102004</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>105064</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" s="25">
+        <v>249</v>
+      </c>
+      <c r="B20" s="26">
         <v>780535</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <v>964741</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <v>993683</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <v>1023494</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <v>1054199</v>
       </c>
     </row>
@@ -2622,7 +2626,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2652,7 +2656,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2662,147 +2666,147 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="B5" s="24">
+        <v>252</v>
+      </c>
+      <c r="B5" s="25">
         <v>807500</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>1617850</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>2466200</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>3327850</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>4233200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B6" s="24">
+        <v>253</v>
+      </c>
+      <c r="B6" s="25">
         <v>75000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>154500</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>238703</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>327818</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>422066</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="24">
+        <v>254</v>
+      </c>
+      <c r="B7" s="25">
         <v>110000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>226600</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>350097</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>480800</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>619030</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B8" s="24">
+        <v>255</v>
+      </c>
+      <c r="B8" s="25">
         <v>125000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>154500</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>159135</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>163909</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>168826</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B9" s="24">
+        <v>256</v>
+      </c>
+      <c r="B9" s="25">
         <v>20833</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>25750</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>26523</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>27318</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>28138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B10" s="24">
+        <v>257</v>
+      </c>
+      <c r="B10" s="25">
         <v>40000</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>82400</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>127308</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>174836</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>225102</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B11" s="29">
+        <v>258</v>
+      </c>
+      <c r="B11" s="30">
         <v>1178333</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>2261600</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>3367965</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>4502532</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>5696361</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2812,161 +2816,161 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B14" s="24">
+        <v>242</v>
+      </c>
+      <c r="B14" s="25">
         <v>116944</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>144542</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>148879</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>153345</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>157945</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B15" s="24">
+        <v>243</v>
+      </c>
+      <c r="B15" s="25">
         <v>91328</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>112881</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>116267</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>119755</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>123348</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B16" s="24">
+        <v>238</v>
+      </c>
+      <c r="B16" s="25">
         <v>278438</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>344149</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>354473</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>365107</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>376061</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B17" s="24">
+        <v>239</v>
+      </c>
+      <c r="B17" s="25">
         <v>59029</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>72960</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>75148</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>77403</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>79725</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="24">
+        <v>240</v>
+      </c>
+      <c r="B18" s="25">
         <v>87955</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <v>108712</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <v>111974</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <v>115333</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <v>118793</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" s="24">
+        <v>245</v>
+      </c>
+      <c r="B19" s="25">
         <v>69053</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>85349</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>87909</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>90547</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <v>93263</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B20" s="24">
+        <v>247</v>
+      </c>
+      <c r="B20" s="25">
         <v>77790</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <v>96148</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <v>99033</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <v>102004</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="25">
         <v>105064</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="29">
+        <v>211</v>
+      </c>
+      <c r="B21" s="30">
         <v>780535</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>964741</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>993683</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>1023494</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>1054199</v>
       </c>
     </row>
@@ -2981,228 +2985,228 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="32" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B25" s="24">
+        <v>260</v>
+      </c>
+      <c r="B25" s="25">
         <v>65000</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="25">
         <v>133900</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="25">
         <v>206875</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="25">
         <v>284109</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="25">
         <v>365790</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="32" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B27" s="24">
+        <v>261</v>
+      </c>
+      <c r="B27" s="25">
         <v>45000</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <v>92700</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="25">
         <v>143222</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <v>196691</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="25">
         <v>253239</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="32" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B29" s="24">
+        <v>262</v>
+      </c>
+      <c r="B29" s="25">
         <v>220000</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="25">
         <v>271920</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="25">
         <v>280078</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <v>288480</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="25">
         <v>297134</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B30" s="24">
+        <v>263</v>
+      </c>
+      <c r="B30" s="25">
         <v>30000</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="25">
         <v>37080</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="25">
         <v>38192</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <v>39338</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="25">
         <v>40518</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B31" s="24">
+        <v>264</v>
+      </c>
+      <c r="B31" s="25">
         <v>18333</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <v>22660</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <v>23340</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <v>24040</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="25">
         <v>24761</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="32" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B33" s="24">
+        <v>265</v>
+      </c>
+      <c r="B33" s="25">
         <v>25000</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="25">
         <v>30900</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="25">
         <v>31827</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <v>32782</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B34" s="24">
+        <v>266</v>
+      </c>
+      <c r="B34" s="25">
         <v>10000</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="25">
         <v>12360</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="25">
         <v>12731</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <v>13113</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="25">
         <v>13506</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B35" s="24">
+        <v>267</v>
+      </c>
+      <c r="B35" s="25">
         <v>15000</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="25">
         <v>18540</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="25">
         <v>19096</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="25">
         <v>19669</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="25">
         <v>20259</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B36" s="24">
+        <v>268</v>
+      </c>
+      <c r="B36" s="25">
         <v>75000</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="25">
         <v>154500</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="25">
         <v>238703</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="25">
         <v>327818</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="25">
         <v>422066</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B37" s="29">
+        <v>269</v>
+      </c>
+      <c r="B37" s="30">
         <v>503333</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <v>774560</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <v>994063</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <v>1226040</v>
       </c>
-      <c r="F37" s="29">
+      <c r="F37" s="30">
         <v>1471040</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -3212,61 +3216,61 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B40" s="24">
+        <v>271</v>
+      </c>
+      <c r="B40" s="25">
         <v>46629</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="25">
         <v>46629</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="25">
         <v>46629</v>
       </c>
-      <c r="E40" s="24">
+      <c r="E40" s="25">
         <v>46629</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="25">
         <v>46629</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B41" s="24">
+        <v>272</v>
+      </c>
+      <c r="B41" s="25">
         <v>60000</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="25">
         <v>20000</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="25">
         <v>25000</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="25">
         <v>10000</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="25">
         <v>10000</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B42" s="29">
+        <v>273</v>
+      </c>
+      <c r="B42" s="30">
         <v>106629</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <v>66629</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <v>71629</v>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="30">
         <v>56629</v>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="30">
         <v>56629</v>
       </c>
     </row>
@@ -3296,7 +3300,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3326,107 +3330,107 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B4" s="27">
+        <v>258</v>
+      </c>
+      <c r="B4" s="28">
         <v>1178333</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="28">
         <v>2261600</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="28">
         <v>3367965</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="28">
         <v>4502532</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <v>5696361</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="27">
+        <v>211</v>
+      </c>
+      <c r="B5" s="28">
         <v>780535</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <v>964741</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <v>993683</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <v>1023494</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <v>1054199</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="27">
+        <v>269</v>
+      </c>
+      <c r="B6" s="28">
         <v>503333</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <v>774560</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <v>994063</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <v>1226040</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <v>1471040</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B7" s="27">
+        <v>275</v>
+      </c>
+      <c r="B7" s="28">
         <v>106629</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <v>66629</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <v>71629</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="28">
         <v>56629</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <v>56629</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B8" s="29">
+        <v>276</v>
+      </c>
+      <c r="B8" s="30">
         <v>1390497</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>1805930</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>2059375</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>2306162</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>2581867</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3436,101 +3440,101 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B11" s="25">
+        <v>278</v>
+      </c>
+      <c r="B11" s="26">
         <v>-212164</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>455670</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>1308590</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>2196369</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>3114494</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B12" s="23">
+        <v>279</v>
+      </c>
+      <c r="B12" s="24">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="24">
         <v>0.20148130933167066</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <v>0.38854013963461814</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="24">
         <v>0.48780762672183775</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <v>0.54675147116204</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B13" s="24">
+        <v>280</v>
+      </c>
+      <c r="B13" s="25">
         <v>-212164</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>243507</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>1552096</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>3748465</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>6862959</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" s="24">
+        <v>236</v>
+      </c>
+      <c r="B14" s="25">
         <v>9819</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>11308</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>11227</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>11256</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>11393</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B15" s="24">
+        <v>281</v>
+      </c>
+      <c r="B15" s="25">
         <v>11587</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>9030</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>6865</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>5765</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>5164</v>
       </c>
     </row>
@@ -3561,7 +3565,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3582,48 +3586,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3641,51 +3645,51 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B4" s="29">
+        <v>258</v>
+      </c>
+      <c r="B4" s="30">
         <v>146500</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <v>146500</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>146500</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>146500</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>146500</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="30">
         <v>146500</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="30">
         <v>146500</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="30">
         <v>146500</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="30">
         <v>146500</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="30">
         <v>146500</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="30">
         <v>0</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="30">
         <v>0</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="30">
         <v>1465000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3703,139 +3707,139 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B7" s="24">
+        <v>297</v>
+      </c>
+      <c r="B7" s="25">
         <v>78054</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>78054</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>78054</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>78054</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>78054</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <v>78054</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="25">
         <v>78054</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="25">
         <v>78054</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="25">
         <v>78054</v>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="25">
         <v>78054</v>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="25">
         <v>0</v>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="25">
         <v>0</v>
       </c>
-      <c r="N7" s="24">
+      <c r="N7" s="25">
         <v>780535</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B8" s="24">
+        <v>298</v>
+      </c>
+      <c r="B8" s="25">
         <v>50333</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>50333</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>50333</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>50333</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>50333</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <v>50333</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <v>50333</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <v>50333</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <v>50333</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="25">
         <v>50333</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="25">
         <v>0</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="25">
         <v>0</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="25">
         <v>503333</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" s="24">
+        <v>299</v>
+      </c>
+      <c r="B9" s="25">
         <v>8886</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>8886</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>8886</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>8886</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>8886</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="25">
         <v>8886</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="25">
         <v>8886</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="25">
         <v>8886</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="25">
         <v>8886</v>
       </c>
-      <c r="K9" s="24">
+      <c r="K9" s="25">
         <v>8886</v>
       </c>
-      <c r="L9" s="24">
+      <c r="L9" s="25">
         <v>8886</v>
       </c>
-      <c r="M9" s="24">
+      <c r="M9" s="25">
         <v>8886</v>
       </c>
-      <c r="N9" s="24">
+      <c r="N9" s="25">
         <v>106629</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3853,139 +3857,139 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B12" s="27">
+        <v>276</v>
+      </c>
+      <c r="B12" s="28">
         <v>137273</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <v>137273</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <v>137273</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="28">
         <v>137273</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <v>137273</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="28">
         <v>137273</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="28">
         <v>137273</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="28">
         <v>137273</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="28">
         <v>137273</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="28">
         <v>137273</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="28">
         <v>8886</v>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="28">
         <v>8886</v>
       </c>
-      <c r="N12" s="27">
+      <c r="N12" s="28">
         <v>1390502</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B13" s="27">
+        <v>301</v>
+      </c>
+      <c r="B13" s="28">
         <v>9227</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <v>9227</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <v>9227</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <v>9227</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <v>9227</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="28">
         <v>9227</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="28">
         <v>9227</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="28">
         <v>9227</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="28">
         <v>9227</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="28">
         <v>9227</v>
       </c>
-      <c r="L13" s="27">
+      <c r="L13" s="28">
         <v>-8886</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="28">
         <v>-8886</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="28">
         <v>74498</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B14" s="32">
+        <v>302</v>
+      </c>
+      <c r="B14" s="33">
         <v>9227</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <v>18454</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <v>27681</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <v>36908</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <v>46135</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <v>55362</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="33">
         <v>64589</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="33">
         <v>73816</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="33">
         <v>83043</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="33">
         <v>92270</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="33">
         <v>83384</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="33">
         <v>74498</v>
       </c>
-      <c r="N14" s="25">
+      <c r="N14" s="26">
         <v>74498</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -3994,23 +3998,23 @@
       <c r="A17" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B18" s="32">
+        <v>304</v>
+      </c>
+      <c r="B18" s="33">
         <v>74498</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B19" s="24">
+        <v>305</v>
+      </c>
+      <c r="B19" s="25">
         <v>9227</v>
       </c>
     </row>
@@ -4040,7 +4044,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4070,7 +4074,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4079,22 +4083,22 @@
       <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="B5" s="29">
+      <c r="A5" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="B5" s="30">
         <v>1178333</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>2261600</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>3367965</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>4502532</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>5696361</v>
       </c>
     </row>
@@ -4110,7 +4114,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4120,81 +4124,81 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B8" s="27">
+        <v>297</v>
+      </c>
+      <c r="B8" s="28">
         <v>780535</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>964741</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <v>993683</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>1023494</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>1054199</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="27">
+        <v>298</v>
+      </c>
+      <c r="B9" s="28">
         <v>503333</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <v>774560</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <v>994063</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <v>1226040</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <v>1471040</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B10" s="27">
+        <v>307</v>
+      </c>
+      <c r="B10" s="28">
         <v>106629</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <v>66629</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <v>71629</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <v>56629</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <v>56629</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="29">
+      <c r="A11" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="30">
         <v>1390497</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>1805930</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>2059375</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="30">
         <v>2306162</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="30">
         <v>2581867</v>
       </c>
     </row>
@@ -4210,7 +4214,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4219,42 +4223,42 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B14" s="25">
+      <c r="A14" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="26">
         <v>-212164</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <v>455670</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <v>1308590</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>2196369</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>3114494</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B15" s="23">
+        <v>279</v>
+      </c>
+      <c r="B15" s="24">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="24">
         <v>0.20148130933167066</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <v>0.38854013963461814</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <v>0.48780762672183775</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <v>0.54675147116204</v>
       </c>
     </row>
@@ -4324,101 +4328,101 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B5" s="24">
+        <v>309</v>
+      </c>
+      <c r="B5" s="25">
         <v>350000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>323655</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>295685</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>265989</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>234462</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B6" s="24">
+        <v>310</v>
+      </c>
+      <c r="B6" s="25">
         <v>20283</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>18658</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>16933</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>15102</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>13157</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B7" s="24">
+        <v>311</v>
+      </c>
+      <c r="B7" s="25">
         <v>26345</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>27970</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>29695</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>31527</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>33471</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B8" s="27">
+        <v>312</v>
+      </c>
+      <c r="B8" s="28">
         <v>46629</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>46629</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <v>46629</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <v>46629</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>46629</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B9" s="32">
+        <v>313</v>
+      </c>
+      <c r="B9" s="33">
         <v>323655</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>295685</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <v>265989</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <v>234462</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <v>200991</v>
       </c>
     </row>
@@ -4448,7 +4452,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4478,7 +4482,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4488,107 +4492,107 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B5" s="34">
+        <v>316</v>
+      </c>
+      <c r="B5" s="35">
         <v>74498</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <v>530168</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <v>1838758</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="35">
         <v>4035127</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <v>7149621</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B6" s="24">
+        <v>317</v>
+      </c>
+      <c r="B6" s="25">
         <v>0</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>0</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>0</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>0</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B7" s="24">
+        <v>318</v>
+      </c>
+      <c r="B7" s="25">
         <v>0</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>0</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>0</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>0</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B8" s="24">
+        <v>319</v>
+      </c>
+      <c r="B8" s="25">
         <v>0</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>0</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>0</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>0</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B9" s="29">
+        <v>320</v>
+      </c>
+      <c r="B9" s="30">
         <v>74498</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>530168</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>1838758</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>4035127</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>7149621</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4598,67 +4602,67 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B12" s="24">
+        <v>322</v>
+      </c>
+      <c r="B12" s="25">
         <v>0</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>0</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>0</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>0</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B13" s="24">
+        <v>323</v>
+      </c>
+      <c r="B13" s="25">
         <v>323655</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>295685</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>265989</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>234462</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>200991</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B14" s="29">
+        <v>324</v>
+      </c>
+      <c r="B14" s="30">
         <v>323655</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>295685</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>265989</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>234462</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>200991</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4668,41 +4672,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B17" s="25">
+        <v>326</v>
+      </c>
+      <c r="B17" s="26">
         <v>-249157</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>234484</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>1572769</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>3800665</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>6948630</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B19" s="35">
+        <v>327</v>
+      </c>
+      <c r="B19" s="36">
         <v>0</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="37">
         <v>-1</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="36">
         <v>0</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="36">
         <v>0</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="36">
         <v>0</v>
       </c>
     </row>
@@ -4732,7 +4736,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4762,7 +4766,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4772,67 +4776,67 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B5" s="24">
+        <v>330</v>
+      </c>
+      <c r="B5" s="25">
         <v>-105535</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>522299</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>1380218</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>2252998</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>3171123</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B6" s="24">
+        <v>299</v>
+      </c>
+      <c r="B6" s="25">
         <v>46629</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>46629</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>46629</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>46629</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>46629</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B7" s="37">
+        <v>331</v>
+      </c>
+      <c r="B7" s="38">
         <v>-2.26</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="38">
         <v>11.2</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="38">
         <v>29.6</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="38">
         <v>48.32</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="38">
         <v>68.01</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -4842,87 +4846,87 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B10" s="24">
+        <v>333</v>
+      </c>
+      <c r="B10" s="25">
         <v>74498</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>530168</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>1838758</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>4035127</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>7149621</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B11" s="21">
+        <v>334</v>
+      </c>
+      <c r="B11" s="22">
         <v>20</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <v>108</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="22">
         <v>330</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <v>641</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>1015</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B12" s="28">
+        <v>335</v>
+      </c>
+      <c r="B12" s="29">
         <v>0.7</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <v>3.6</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <v>10.8</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <v>21.1</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <v>33.4</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="23">
+        <v>196</v>
+      </c>
+      <c r="B13" s="24">
         <v>0.2</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="24">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <v>0.5</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -4932,87 +4936,87 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B16" s="24">
+        <v>236</v>
+      </c>
+      <c r="B16" s="25">
         <v>9819</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>11308</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>11227</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>11256</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>11393</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B17" s="24">
+        <v>337</v>
+      </c>
+      <c r="B17" s="25">
         <v>827164</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>1011370</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>1040312</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>1070123</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>1100827</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B18" s="24">
+        <v>338</v>
+      </c>
+      <c r="B18" s="25">
         <v>4194</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <v>3873</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <v>3314</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <v>3065</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <v>2942</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B19" s="38">
+        <v>339</v>
+      </c>
+      <c r="B19" s="39">
         <v>148</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="39">
         <v>137</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="39">
         <v>132</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="39">
         <v>131</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="39">
         <v>131</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -5022,102 +5026,102 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B22" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="B22" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="D22" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="F22" s="40" t="s">
-        <v>342</v>
+      <c r="C22" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C23" s="41" t="s">
         <v>343</v>
       </c>
-      <c r="B23" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="D23" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="F23" s="40" t="s">
-        <v>342</v>
+      <c r="D23" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="E24" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>341</v>
+        <v>345</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="C25" s="40" t="s">
+        <v>346</v>
+      </c>
+      <c r="B25" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="D25" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="F25" s="40" t="s">
-        <v>342</v>
+      <c r="C25" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="C26" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="B26" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="D26" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>342</v>
+      <c r="C26" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="F26" s="41" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -5157,16 +5161,16 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>348</v>
-      </c>
-      <c r="E3" s="41" t="s">
+      <c r="D3" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>100</v>
       </c>
     </row>
@@ -5174,65 +5178,65 @@
       <c r="A4" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="25">
         <v>350000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="E4" s="24">
+        <v>350</v>
+      </c>
+      <c r="E4" s="25">
         <v>250000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B5" s="24">
+        <v>351</v>
+      </c>
+      <c r="B5" s="25">
         <v>150000</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>60000</v>
       </c>
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E6" s="24">
+        <v>352</v>
+      </c>
+      <c r="E6" s="25">
         <v>50000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="E7" s="24">
+        <v>353</v>
+      </c>
+      <c r="E7" s="25">
         <v>140000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B9" s="25">
+        <v>354</v>
+      </c>
+      <c r="B9" s="26">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E9" s="25">
+        <v>355</v>
+      </c>
+      <c r="E9" s="26">
         <v>500000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B10" s="35">
+        <v>356</v>
+      </c>
+      <c r="B10" s="36">
         <v>0</v>
       </c>
     </row>
@@ -5398,7 +5402,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5408,7 +5412,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5417,8 +5421,8 @@
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>358</v>
+      <c r="A4" s="43" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5443,127 +5447,127 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B6" s="24">
+        <v>360</v>
+      </c>
+      <c r="B6" s="25">
         <v>1178333</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>2261600</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>3367965</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>4502532</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>5696361</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="24">
+        <v>276</v>
+      </c>
+      <c r="B7" s="25">
         <v>1330497</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>1785930</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>2034375</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>2296162</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>2571867</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B8" s="25">
+        <v>278</v>
+      </c>
+      <c r="B8" s="26">
         <v>-152164</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>475670</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>1333590</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>2206369</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>3124494</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B9" s="23">
+        <v>279</v>
+      </c>
+      <c r="B9" s="24">
         <v>-0.12913460606689678</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="24">
         <v>0.21032460611271073</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="24">
         <v>0.3959630196229791</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <v>0.49002859951113986</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <v>0.5485069777397931</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B10" s="43">
+        <v>331</v>
+      </c>
+      <c r="B10" s="44">
         <v>-2.26</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="44">
         <v>11.2</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <v>29.6</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <v>48.32</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="44">
         <v>68.01</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B11" s="21">
+        <v>339</v>
+      </c>
+      <c r="B11" s="22">
         <v>148</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <v>137</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="22">
         <v>132</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="22">
         <v>131</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>131</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5572,8 +5576,8 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
-        <v>361</v>
+      <c r="A14" s="43" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5598,127 +5602,127 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B16" s="24">
+        <v>360</v>
+      </c>
+      <c r="B16" s="25">
         <v>1178333</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>2261600</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>3367965</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>4502532</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>5696361</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B17" s="24">
+        <v>276</v>
+      </c>
+      <c r="B17" s="25">
         <v>1330497</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>1785930</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>2034375</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>2296162</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>2571867</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B18" s="25">
+        <v>278</v>
+      </c>
+      <c r="B18" s="26">
         <v>-152164</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <v>475670</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <v>1333590</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <v>2206369</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <v>3124494</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="23">
+        <v>279</v>
+      </c>
+      <c r="B19" s="24">
         <v>-0.12913460606689678</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <v>0.21032460611271073</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <v>0.3959630196229791</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <v>0.49002859951113986</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <v>0.5485069777397931</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="43">
+        <v>331</v>
+      </c>
+      <c r="B20" s="44">
         <v>-2.26</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="44">
         <v>11.2</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="44">
         <v>29.6</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="44">
         <v>48.32</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="44">
         <v>68.01</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B21" s="21">
+        <v>339</v>
+      </c>
+      <c r="B21" s="22">
         <v>125</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="22">
         <v>116</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <v>112</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="22">
         <v>112</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="22">
         <v>111</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5727,8 +5731,8 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
-        <v>363</v>
+      <c r="A24" s="43" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,121 +5757,121 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B26" s="24">
+        <v>360</v>
+      </c>
+      <c r="B26" s="25">
         <v>1084067</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <v>2080672</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="25">
         <v>3098528</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <v>4142329</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="25">
         <v>5240653</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B27" s="24">
+        <v>276</v>
+      </c>
+      <c r="B27" s="25">
         <v>1330497</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <v>1785930</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="25">
         <v>2034375</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <v>2296162</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="25">
         <v>2571867</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B28" s="25">
+        <v>278</v>
+      </c>
+      <c r="B28" s="26">
         <v>-246430</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <v>294742</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="26">
         <v>1064152</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="26">
         <v>1846167</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="26">
         <v>2668785</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B29" s="23">
+        <v>279</v>
+      </c>
+      <c r="B29" s="24">
         <v>-0.22732022398575744</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="24">
         <v>0.1416571805572943</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="24">
         <v>0.34343806480758604</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="24">
         <v>0.4456832603381955</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="24">
         <v>0.5092467149345576</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B30" s="43">
+        <v>331</v>
+      </c>
+      <c r="B30" s="44">
         <v>-4.28</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="44">
         <v>7.32</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="44">
         <v>23.82</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="44">
         <v>40.59</v>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="44">
         <v>58.23</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B31" s="21">
+        <v>339</v>
+      </c>
+      <c r="B31" s="22">
         <v>171</v>
       </c>
-      <c r="C31" s="21">
+      <c r="C31" s="22">
         <v>155</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="22">
         <v>149</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <v>147</v>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="22">
         <v>147</v>
       </c>
     </row>
@@ -5899,7 +5903,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5933,7 +5937,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5957,7 +5961,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5965,7 +5969,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5985,125 +5989,125 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="45" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="D13" s="24">
+        <v>360</v>
+      </c>
+      <c r="D13" s="25">
         <v>1178333</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>2261600</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>3367965</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="25">
         <v>4502532</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="25">
         <v>5696361</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D14" s="24">
+        <v>276</v>
+      </c>
+      <c r="D14" s="25">
         <v>1330497</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>1785930</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>2034375</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="25">
         <v>2296162</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="25">
         <v>2571867</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D15" s="24">
+        <v>278</v>
+      </c>
+      <c r="D15" s="25">
         <v>-212164</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>455670</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>1308590</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="25">
         <v>2196369</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="25">
         <v>3114494</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="D16" s="24">
+        <v>369</v>
+      </c>
+      <c r="D16" s="25">
         <v>74498</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>530168</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>1838758</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="25">
         <v>4035127</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="25">
         <v>7149621</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="D17" s="24">
+        <v>370</v>
+      </c>
+      <c r="D17" s="25">
         <v>323655</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>295685</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>265989</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="25">
         <v>234462</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="25">
         <v>200991</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6123,105 +6127,105 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="45" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="D21" s="23">
+        <v>372</v>
+      </c>
+      <c r="D21" s="24">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0.20148130933167066</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="24">
         <v>0.38854013963461814</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <v>0.48780762672183775</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="24">
         <v>0.54675147116204</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="D22" s="43">
+        <v>331</v>
+      </c>
+      <c r="D22" s="44">
         <v>-2.26</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="44">
         <v>11.2</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="44">
         <v>29.6</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <v>48.32</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="44">
         <v>68.01</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D23" s="23">
+        <v>196</v>
+      </c>
+      <c r="D23" s="24">
         <v>0.2</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="24">
         <v>0.5</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="24">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D24" s="21">
+        <v>373</v>
+      </c>
+      <c r="D24" s="22">
         <v>120</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="22">
         <v>200</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="22">
         <v>300</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="22">
         <v>400</v>
       </c>
-      <c r="H24" s="21">
+      <c r="H24" s="22">
         <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6249,7 +6253,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -7069,72 +7073,60 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B67" s="20">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="B69" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="C69" s="15" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
+      <c r="D69" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="B69" s="17">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="17">
         <v>8200</v>
       </c>
-      <c r="C69" s="17">
+      <c r="C70" s="17">
         <v>9100</v>
       </c>
-      <c r="D69" s="17">
+      <c r="D70" s="17">
         <v>10500</v>
       </c>
     </row>
-    <row r="71" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="B71" s="15" t="s">
+    <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C72" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D71" s="15" t="s">
+      <c r="D72" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E71" s="15" t="s">
+      <c r="E72" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="F71" s="15" t="s">
+      <c r="F72" s="15" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="B72" s="16">
-        <v>80</v>
-      </c>
-      <c r="C72" s="16">
-        <v>130</v>
-      </c>
-      <c r="D72" s="16">
-        <v>180</v>
-      </c>
-      <c r="E72" s="16">
-        <v>230</v>
-      </c>
-      <c r="F72" s="16">
-        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -7142,19 +7134,19 @@
         <v>175</v>
       </c>
       <c r="B73" s="16">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="C73" s="16">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="D73" s="16">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E73" s="16">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="F73" s="16">
-        <v>140</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -7162,18 +7154,38 @@
         <v>176</v>
       </c>
       <c r="B74" s="16">
+        <v>40</v>
+      </c>
+      <c r="C74" s="16">
+        <v>70</v>
+      </c>
+      <c r="D74" s="16">
+        <v>100</v>
+      </c>
+      <c r="E74" s="16">
+        <v>120</v>
+      </c>
+      <c r="F74" s="16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B75" s="16">
         <v>0</v>
       </c>
-      <c r="C74" s="16">
+      <c r="C75" s="16">
         <v>0</v>
       </c>
-      <c r="D74" s="16">
+      <c r="D75" s="16">
         <v>20</v>
       </c>
-      <c r="E74" s="16">
+      <c r="E75" s="16">
         <v>50</v>
       </c>
-      <c r="F74" s="16">
+      <c r="F75" s="16">
         <v>100</v>
       </c>
     </row>
@@ -7209,10 +7221,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7233,10 +7245,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7249,7 +7261,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7260,23 +7272,23 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -7292,31 +7304,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -7376,7 +7388,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7388,19 +7400,19 @@
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <v>120</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>200</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <v>300</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <v>400</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <v>500</v>
       </c>
     </row>
@@ -7408,47 +7420,47 @@
       <c r="A7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="22">
         <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B8" s="22">
+        <v>196</v>
+      </c>
+      <c r="B8" s="23">
         <v>0.2</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="23">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <v>0.5</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="23">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C10" s="23">
+        <v>198</v>
+      </c>
+      <c r="C10" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <v>0.5</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <v>0.25</v>
       </c>
     </row>
@@ -7478,7 +7490,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7508,7 +7520,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7518,141 +7530,141 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="24">
+        <v>201</v>
+      </c>
+      <c r="B5" s="25">
         <v>969000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>1617850</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>2466200</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>3327850</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>4233200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="24">
+        <v>202</v>
+      </c>
+      <c r="B6" s="25">
         <v>90000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <v>154500</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>238703</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>327818</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>422066</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="24">
+        <v>203</v>
+      </c>
+      <c r="B7" s="25">
         <v>132000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <v>226600</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>350097</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>480800</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>619030</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="24">
+        <v>204</v>
+      </c>
+      <c r="B8" s="25">
         <v>150000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>154500</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>159135</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>163909</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>168826</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="24">
+        <v>205</v>
+      </c>
+      <c r="B9" s="25">
         <v>25000</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>25750</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>26523</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>27318</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>28138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B10" s="24">
+        <v>206</v>
+      </c>
+      <c r="B10" s="25">
         <v>48000</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="25">
         <v>82400</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>127308</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>174836</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>225102</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="25">
+        <v>207</v>
+      </c>
+      <c r="B11" s="26">
         <v>1414000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>2261600</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>3367965</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>4502532</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>5696361</v>
       </c>
     </row>
@@ -7706,7 +7718,7 @@
         <v>116</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>118</v>
@@ -7715,7 +7727,7 @@
         <v>119</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7725,19 +7737,19 @@
       <c r="B4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>1</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="25">
         <v>105000</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="24">
         <v>0.26</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="28">
         <v>140333</v>
       </c>
     </row>
@@ -7748,19 +7760,19 @@
       <c r="B5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <v>1</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>82000</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <v>0.26</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="28">
         <v>109593</v>
       </c>
     </row>
@@ -7771,19 +7783,19 @@
       <c r="B6" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>5</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <v>50000</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="24">
         <v>0.26</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="28">
         <v>334125</v>
       </c>
     </row>
@@ -7794,19 +7806,19 @@
       <c r="B7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <v>1</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="25">
         <v>53000</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <v>0.26</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="28">
         <v>70835</v>
       </c>
     </row>
@@ -7817,19 +7829,19 @@
       <c r="B8" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>3</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>28000</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <v>0.18</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="28">
         <v>105546</v>
       </c>
     </row>
@@ -7840,19 +7852,19 @@
       <c r="B9" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <v>1</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>62000</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <v>0.26</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="28">
         <v>82863</v>
       </c>
     </row>
@@ -7863,25 +7875,25 @@
       <c r="B10" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>2</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>36000</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="24">
         <v>0.22</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="28">
         <v>93348</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -7912,61 +7924,61 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="25">
+        <v>211</v>
+      </c>
+      <c r="B14" s="26">
         <v>780535</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <v>964741</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <v>993683</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>1023494</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>1054199</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="23">
+        <v>212</v>
+      </c>
+      <c r="B15" s="24">
         <v>0.5520049504950495</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="24">
         <v>0.4265746639547223</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <v>0.29503973402336425</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <v>0.22731523300861284</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <v>0.18506529677129674</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B16" s="28">
+        <v>213</v>
+      </c>
+      <c r="B16" s="29">
         <v>8.6</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <v>14.3</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <v>21.4</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <v>28.6</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <v>35.7</v>
       </c>
     </row>
@@ -7996,7 +8008,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8036,41 +8048,41 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" s="24">
+        <v>215</v>
+      </c>
+      <c r="B5" s="25">
         <v>78000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <v>133900</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>206875</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>284109</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>365790</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="29">
+        <v>216</v>
+      </c>
+      <c r="B6" s="30">
         <v>78000</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>133900</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>206875</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>284109</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>365790</v>
       </c>
     </row>
@@ -8086,41 +8098,41 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B8" s="24">
+        <v>217</v>
+      </c>
+      <c r="B8" s="25">
         <v>54000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <v>92700</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <v>143222</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>196691</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>253239</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B9" s="29">
+        <v>218</v>
+      </c>
+      <c r="B9" s="30">
         <v>54000</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>92700</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>143222</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>196691</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>253239</v>
       </c>
     </row>
@@ -8136,81 +8148,81 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="24">
+        <v>219</v>
+      </c>
+      <c r="B11" s="25">
         <v>264000</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="25">
         <v>271920</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="25">
         <v>280078</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <v>288480</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="25">
         <v>297134</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B12" s="24">
+        <v>220</v>
+      </c>
+      <c r="B12" s="25">
         <v>36000</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <v>37080</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <v>38192</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <v>39338</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <v>40518</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B13" s="24">
+        <v>221</v>
+      </c>
+      <c r="B13" s="25">
         <v>22000</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="25">
         <v>22660</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="25">
         <v>23340</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <v>24040</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <v>24761</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B14" s="29">
+        <v>222</v>
+      </c>
+      <c r="B14" s="30">
         <v>322000</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>331660</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>341610</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>351858</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>362414</v>
       </c>
     </row>
@@ -8226,121 +8238,121 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B16" s="24">
+        <v>223</v>
+      </c>
+      <c r="B16" s="25">
         <v>30000</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>30900</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>31827</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>32782</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>33765</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B17" s="24">
+        <v>224</v>
+      </c>
+      <c r="B17" s="25">
         <v>12000</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <v>12360</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <v>12731</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <v>13113</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="25">
         <v>13506</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B18" s="24">
+        <v>225</v>
+      </c>
+      <c r="B18" s="25">
         <v>18000</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <v>18540</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <v>19096</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <v>19669</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <v>20259</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B19" s="24">
+        <v>226</v>
+      </c>
+      <c r="B19" s="25">
         <v>90000</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>154500</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <v>238703</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <v>327818</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="25">
         <v>422066</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B20" s="29">
+        <v>227</v>
+      </c>
+      <c r="B20" s="30">
         <v>150000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>216300</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>302357</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <v>393382</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <v>489596</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="B22" s="25">
+        <v>228</v>
+      </c>
+      <c r="B22" s="26">
         <v>604000</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="26">
         <v>774560</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="26">
         <v>994063</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="26">
         <v>1226040</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="26">
         <v>1471040</v>
       </c>
     </row>
@@ -8371,7 +8383,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8396,7 +8408,7 @@
         <v>150</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8409,13 +8421,13 @@
       <c r="C4" s="17">
         <v>350000</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="24">
         <v>0.06</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="22">
         <v>10</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <v>46629</v>
       </c>
     </row>
@@ -8424,34 +8436,34 @@
         <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C5" s="17">
         <v>60000</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="24">
         <v>0</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="22">
         <v>0</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <v>60000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F7" s="25">
+        <v>232</v>
+      </c>
+      <c r="F7" s="26">
         <v>46629</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F8" s="29">
+        <v>233</v>
+      </c>
+      <c r="F8" s="30">
         <v>350000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -357,7 +357,7 @@
     <t>CSP Startup Grant</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Annual Fixed</t>
@@ -645,10 +645,10 @@
     <t>IDEA Special Ed (Public Funding)</t>
   </si>
   <si>
-    <t>CSP Startup Grant (Grants &amp; Contributions)</t>
-  </si>
-  <si>
-    <t>Annual Fundraising (Grants &amp; Contributions)</t>
+    <t>CSP Startup Grant (Philanthropy)</t>
+  </si>
+  <si>
+    <t>Annual Fundraising (Philanthropy)</t>
   </si>
   <si>
     <t>Before/After Care (Other Revenue)</t>
@@ -1169,7 +1169,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1213,7 +1213,7 @@
     <font>
       <i/>
       <color rgb="FF999999"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1231,7 +1231,7 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1249,12 +1249,6 @@
     <font>
       <b/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1329,7 +1323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1385,7 +1379,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5421,7 +5414,7 @@
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="12" t="s">
         <v>359</v>
       </c>
     </row>
@@ -5529,19 +5522,19 @@
       <c r="A10" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="43">
         <v>-2.26</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="43">
         <v>11.2</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="43">
         <v>29.6</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="43">
         <v>48.32</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="43">
         <v>68.01</v>
       </c>
     </row>
@@ -5576,7 +5569,7 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="12" t="s">
         <v>362</v>
       </c>
     </row>
@@ -5684,19 +5677,19 @@
       <c r="A20" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="43">
         <v>-2.26</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="43">
         <v>11.2</v>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="43">
         <v>29.6</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="43">
         <v>48.32</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="43">
         <v>68.01</v>
       </c>
     </row>
@@ -5731,7 +5724,7 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="12" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5839,19 +5832,19 @@
       <c r="A30" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B30" s="44">
+      <c r="B30" s="43">
         <v>-4.28</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="43">
         <v>7.32</v>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="43">
         <v>23.82</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="43">
         <v>40.59</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="43">
         <v>58.23</v>
       </c>
     </row>
@@ -5989,19 +5982,19 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="45" t="s">
+      <c r="E12" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6127,19 +6120,19 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="45" t="s">
+      <c r="F20" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="45" t="s">
+      <c r="G20" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6167,19 +6160,19 @@
       <c r="A22" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="43">
         <v>-2.26</v>
       </c>
-      <c r="E22" s="44">
+      <c r="E22" s="43">
         <v>11.2</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="43">
         <v>29.6</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="43">
         <v>48.32</v>
       </c>
-      <c r="H22" s="44">
+      <c r="H22" s="43">
         <v>68.01</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="377">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -828,6 +828,9 @@
     <t xml:space="preserve">    Property Insurance</t>
   </si>
   <si>
+    <t xml:space="preserve">  Total Occupancy / Facility</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Marketing</t>
   </si>
   <si>
@@ -840,6 +843,9 @@
     <t xml:space="preserve">    Food Service</t>
   </si>
   <si>
+    <t xml:space="preserve">  Total Administrative / General</t>
+  </si>
+  <si>
     <t>Total Operating Expenses</t>
   </si>
   <si>
@@ -1023,6 +1029,9 @@
     <t>CASH FLOW &amp; DEBT</t>
   </si>
   <si>
+    <t>Revenue</t>
+  </si>
+  <si>
     <t>CFADS (Rev - Pers - OpEx)</t>
   </si>
   <si>
@@ -1111,9 +1120,6 @@
   </si>
   <si>
     <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
-  </si>
-  <si>
-    <t>Revenue</t>
   </si>
   <si>
     <t>LOW ADA</t>
@@ -2224,18 +2230,23 @@
         <v>207</v>
       </c>
       <c r="B13" s="26">
+        <f>SUM(B7:B12)</f>
         <v>1414000</v>
       </c>
       <c r="C13" s="26">
+        <f>SUM(C7:C12)</f>
         <v>2261600</v>
       </c>
       <c r="D13" s="26">
+        <f>SUM(D7:D12)</f>
         <v>3367965</v>
       </c>
       <c r="E13" s="26">
+        <f>SUM(E7:E12)</f>
         <v>4502532</v>
       </c>
       <c r="F13" s="26">
+        <f>SUM(F7:F12)</f>
         <v>5696361</v>
       </c>
     </row>
@@ -2388,18 +2399,23 @@
         <v>241</v>
       </c>
       <c r="B8" s="30">
+        <f>SUM(B5:B7)</f>
         <v>425421</v>
       </c>
       <c r="C8" s="30">
+        <f>SUM(C5:C7)</f>
         <v>525821</v>
       </c>
       <c r="D8" s="30">
+        <f>SUM(D5:D7)</f>
         <v>541595</v>
       </c>
       <c r="E8" s="30">
+        <f>SUM(E5:E7)</f>
         <v>557843</v>
       </c>
       <c r="F8" s="30">
+        <f>SUM(F5:F7)</f>
         <v>574578</v>
       </c>
     </row>
@@ -2458,18 +2474,23 @@
         <v>244</v>
       </c>
       <c r="B12" s="30">
+        <f>SUM(B10:B11)</f>
         <v>208271</v>
       </c>
       <c r="C12" s="30">
+        <f>SUM(C10:C11)</f>
         <v>257423</v>
       </c>
       <c r="D12" s="30">
+        <f>SUM(D10:D11)</f>
         <v>265146</v>
       </c>
       <c r="E12" s="30">
+        <f>SUM(E10:E11)</f>
         <v>273100</v>
       </c>
       <c r="F12" s="30">
+        <f>SUM(F10:F11)</f>
         <v>281293</v>
       </c>
     </row>
@@ -2508,18 +2529,23 @@
         <v>246</v>
       </c>
       <c r="B15" s="30">
+        <f>SUM(B14:B14)</f>
         <v>69053</v>
       </c>
       <c r="C15" s="30">
+        <f>SUM(C14:C14)</f>
         <v>85349</v>
       </c>
       <c r="D15" s="30">
+        <f>SUM(D14:D14)</f>
         <v>87909</v>
       </c>
       <c r="E15" s="30">
+        <f>SUM(E14:E14)</f>
         <v>90547</v>
       </c>
       <c r="F15" s="30">
+        <f>SUM(F14:F14)</f>
         <v>93263</v>
       </c>
     </row>
@@ -2558,18 +2584,23 @@
         <v>248</v>
       </c>
       <c r="B18" s="30">
+        <f>SUM(B17:B17)</f>
         <v>77790</v>
       </c>
       <c r="C18" s="30">
+        <f>SUM(C17:C17)</f>
         <v>96148</v>
       </c>
       <c r="D18" s="30">
+        <f>SUM(D17:D17)</f>
         <v>99033</v>
       </c>
       <c r="E18" s="30">
+        <f>SUM(E17:E17)</f>
         <v>102004</v>
       </c>
       <c r="F18" s="30">
+        <f>SUM(F17:F17)</f>
         <v>105064</v>
       </c>
     </row>
@@ -2578,18 +2609,23 @@
         <v>249</v>
       </c>
       <c r="B20" s="26">
+        <f>B8+B12+B15+B18</f>
         <v>780535</v>
       </c>
       <c r="C20" s="26">
+        <f>C8+C12+C15+C18</f>
         <v>964741</v>
       </c>
       <c r="D20" s="26">
+        <f>D8+D12+D15+D18</f>
         <v>993683</v>
       </c>
       <c r="E20" s="26">
+        <f>E8+E12+E15+E18</f>
         <v>1023494</v>
       </c>
       <c r="F20" s="26">
+        <f>F8+F12+F15+F18</f>
         <v>1054199</v>
       </c>
     </row>
@@ -2610,7 +2646,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -2782,18 +2818,23 @@
         <v>258</v>
       </c>
       <c r="B11" s="30">
+        <f>SUM(B5:B10)</f>
         <v>1178333</v>
       </c>
       <c r="C11" s="30">
+        <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
       <c r="D11" s="30">
+        <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
       <c r="E11" s="30">
+        <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
       <c r="F11" s="30">
+        <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
     </row>
@@ -2952,18 +2993,23 @@
         <v>211</v>
       </c>
       <c r="B21" s="30">
+        <f>SUM(B14:B20)</f>
         <v>780535</v>
       </c>
       <c r="C21" s="30">
+        <f>SUM(C14:C20)</f>
         <v>964741</v>
       </c>
       <c r="D21" s="30">
+        <f>SUM(D14:D20)</f>
         <v>993683</v>
       </c>
       <c r="E21" s="30">
+        <f>SUM(E14:E20)</f>
         <v>1023494</v>
       </c>
       <c r="F21" s="30">
+        <f>SUM(F14:F20)</f>
         <v>1054199</v>
       </c>
     </row>
@@ -3092,29 +3138,34 @@
         <v>24761</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="32" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B32" s="30">
+        <f>SUM(B29:B31)</f>
+        <v>268333</v>
+      </c>
+      <c r="C32" s="30">
+        <f>SUM(C29:C31)</f>
+        <v>331660</v>
+      </c>
+      <c r="D32" s="30">
+        <f>SUM(D29:D31)</f>
+        <v>341610</v>
+      </c>
+      <c r="E32" s="30">
+        <f>SUM(E29:E31)</f>
+        <v>351858</v>
+      </c>
+      <c r="F32" s="30">
+        <f>SUM(F29:F31)</f>
+        <v>362414</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="32" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B33" s="25">
-        <v>25000</v>
-      </c>
-      <c r="C33" s="25">
-        <v>30900</v>
-      </c>
-      <c r="D33" s="25">
-        <v>31827</v>
-      </c>
-      <c r="E33" s="25">
-        <v>32782</v>
-      </c>
-      <c r="F33" s="25">
-        <v>33765</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3122,19 +3173,19 @@
         <v>266</v>
       </c>
       <c r="B34" s="25">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="C34" s="25">
-        <v>12360</v>
+        <v>30900</v>
       </c>
       <c r="D34" s="25">
-        <v>12731</v>
+        <v>31827</v>
       </c>
       <c r="E34" s="25">
-        <v>13113</v>
+        <v>32782</v>
       </c>
       <c r="F34" s="25">
-        <v>13506</v>
+        <v>33765</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3142,19 +3193,19 @@
         <v>267</v>
       </c>
       <c r="B35" s="25">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="C35" s="25">
-        <v>18540</v>
+        <v>12360</v>
       </c>
       <c r="D35" s="25">
-        <v>19096</v>
+        <v>12731</v>
       </c>
       <c r="E35" s="25">
-        <v>19669</v>
+        <v>13113</v>
       </c>
       <c r="F35" s="25">
-        <v>20259</v>
+        <v>13506</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3162,108 +3213,163 @@
         <v>268</v>
       </c>
       <c r="B36" s="25">
+        <v>15000</v>
+      </c>
+      <c r="C36" s="25">
+        <v>18540</v>
+      </c>
+      <c r="D36" s="25">
+        <v>19096</v>
+      </c>
+      <c r="E36" s="25">
+        <v>19669</v>
+      </c>
+      <c r="F36" s="25">
+        <v>20259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B37" s="25">
         <v>75000</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C37" s="25">
         <v>154500</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D37" s="25">
         <v>238703</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E37" s="25">
         <v>327818</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F37" s="25">
         <v>422066</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B37" s="30">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B38" s="30">
+        <f>SUM(B34:B37)</f>
+        <v>125000</v>
+      </c>
+      <c r="C38" s="30">
+        <f>SUM(C34:C37)</f>
+        <v>216300</v>
+      </c>
+      <c r="D38" s="30">
+        <f>SUM(D34:D37)</f>
+        <v>302357</v>
+      </c>
+      <c r="E38" s="30">
+        <f>SUM(E34:E37)</f>
+        <v>393382</v>
+      </c>
+      <c r="F38" s="30">
+        <f>SUM(F34:F37)</f>
+        <v>489596</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B39" s="30">
+        <f>B25+B27+B32+B38</f>
         <v>503333</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C39" s="30">
+        <f>C25+C27+C32+C38</f>
         <v>774560</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D39" s="30">
+        <f>D25+D27+D32+D38</f>
         <v>994063</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E39" s="30">
+        <f>E25+E27+E32+E38</f>
         <v>1226040</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F39" s="30">
+        <f>F25+F27+F32+F38</f>
         <v>1471040</v>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B40" s="25">
+    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B42" s="25">
         <v>46629</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C42" s="25">
         <v>46629</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D42" s="25">
         <v>46629</v>
       </c>
-      <c r="E40" s="25">
+      <c r="E42" s="25">
         <v>46629</v>
       </c>
-      <c r="F40" s="25">
+      <c r="F42" s="25">
         <v>46629</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B41" s="25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B43" s="25">
         <v>60000</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C43" s="25">
         <v>20000</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D43" s="25">
         <v>25000</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E43" s="25">
         <v>10000</v>
       </c>
-      <c r="F41" s="25">
+      <c r="F43" s="25">
         <v>10000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B42" s="30">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B44" s="30">
+        <f>SUM(B42:B43)</f>
         <v>106629</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C44" s="30">
+        <f>SUM(C42:C43)</f>
         <v>66629</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D44" s="30">
+        <f>SUM(D42:D43)</f>
         <v>71629</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E44" s="30">
+        <f>SUM(E42:E43)</f>
         <v>56629</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F44" s="30">
+        <f>SUM(F42:F43)</f>
         <v>56629</v>
       </c>
     </row>
@@ -3293,7 +3399,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3326,18 +3432,23 @@
         <v>258</v>
       </c>
       <c r="B4" s="28">
+        <f>'Budget Detail'!B11</f>
         <v>1178333</v>
       </c>
       <c r="C4" s="28">
+        <f>'Budget Detail'!C11</f>
         <v>2261600</v>
       </c>
       <c r="D4" s="28">
+        <f>'Budget Detail'!D11</f>
         <v>3367965</v>
       </c>
       <c r="E4" s="28">
+        <f>'Budget Detail'!E11</f>
         <v>4502532</v>
       </c>
       <c r="F4" s="28">
+        <f>'Budget Detail'!F11</f>
         <v>5696361</v>
       </c>
     </row>
@@ -3346,84 +3457,104 @@
         <v>211</v>
       </c>
       <c r="B5" s="28">
+        <f>'Budget Detail'!B21</f>
         <v>780535</v>
       </c>
       <c r="C5" s="28">
+        <f>'Budget Detail'!C21</f>
         <v>964741</v>
       </c>
       <c r="D5" s="28">
+        <f>'Budget Detail'!D21</f>
         <v>993683</v>
       </c>
       <c r="E5" s="28">
+        <f>'Budget Detail'!E21</f>
         <v>1023494</v>
       </c>
       <c r="F5" s="28">
+        <f>'Budget Detail'!F21</f>
         <v>1054199</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B6" s="28">
+        <f>'Budget Detail'!B39</f>
         <v>503333</v>
       </c>
       <c r="C6" s="28">
+        <f>'Budget Detail'!C39</f>
         <v>774560</v>
       </c>
       <c r="D6" s="28">
+        <f>'Budget Detail'!D39</f>
         <v>994063</v>
       </c>
       <c r="E6" s="28">
+        <f>'Budget Detail'!E39</f>
         <v>1226040</v>
       </c>
       <c r="F6" s="28">
+        <f>'Budget Detail'!F39</f>
         <v>1471040</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B7" s="28">
+        <f>'Budget Detail'!B44</f>
         <v>106629</v>
       </c>
       <c r="C7" s="28">
+        <f>'Budget Detail'!C44</f>
         <v>66629</v>
       </c>
       <c r="D7" s="28">
+        <f>'Budget Detail'!D44</f>
         <v>71629</v>
       </c>
       <c r="E7" s="28">
+        <f>'Budget Detail'!E44</f>
         <v>56629</v>
       </c>
       <c r="F7" s="28">
+        <f>'Budget Detail'!F44</f>
         <v>56629</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B8" s="30">
+        <f>SUM(B5:B7)</f>
         <v>1390497</v>
       </c>
       <c r="C8" s="30">
+        <f>SUM(C5:C7)</f>
         <v>1805930</v>
       </c>
       <c r="D8" s="30">
+        <f>SUM(D5:D7)</f>
         <v>2059375</v>
       </c>
       <c r="E8" s="30">
+        <f>SUM(E5:E7)</f>
         <v>2306162</v>
       </c>
       <c r="F8" s="30">
+        <f>SUM(F5:F7)</f>
         <v>2581867</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3433,47 +3564,57 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B11" s="26">
+        <f>B4-B8</f>
         <v>-212164</v>
       </c>
       <c r="C11" s="26">
+        <f>C4-C8</f>
         <v>455670</v>
       </c>
       <c r="D11" s="26">
+        <f>D4-D8</f>
         <v>1308590</v>
       </c>
       <c r="E11" s="26">
+        <f>E4-E8</f>
         <v>2196369</v>
       </c>
       <c r="F11" s="26">
+        <f>F4-F8</f>
         <v>3114494</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B12" s="24">
-        <v>-0.18005398371894768</v>
+        <f>IF(B4=0,0,B11/B4)</f>
+        <v>-0.18005398</v>
       </c>
       <c r="C12" s="24">
-        <v>0.20148130933167066</v>
+        <f>IF(C4=0,0,C11/C4)</f>
+        <v>0.20148131</v>
       </c>
       <c r="D12" s="24">
-        <v>0.38854013963461814</v>
+        <f>IF(D4=0,0,D11/D4)</f>
+        <v>0.38854014</v>
       </c>
       <c r="E12" s="24">
-        <v>0.48780762672183775</v>
+        <f>IF(E4=0,0,E11/E4)</f>
+        <v>0.48780763</v>
       </c>
       <c r="F12" s="24">
-        <v>0.54675147116204</v>
+        <f>IF(F4=0,0,F11/F4)</f>
+        <v>0.54675147</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B13" s="25">
         <v>-212164</v>
@@ -3513,7 +3654,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B15" s="25">
         <v>11587</v>
@@ -3558,7 +3699,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3579,43 +3720,43 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3682,7 +3823,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3700,7 +3841,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B7" s="25">
         <v>78054</v>
@@ -3744,7 +3885,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B8" s="25">
         <v>50333</v>
@@ -3788,7 +3929,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B9" s="25">
         <v>8886</v>
@@ -3832,7 +3973,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3850,7 +3991,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B12" s="28">
         <v>137273</v>
@@ -3894,7 +4035,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B13" s="28">
         <v>9227</v>
@@ -3938,7 +4079,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B14" s="33">
         <v>9227</v>
@@ -3982,7 +4123,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -3997,7 +4138,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B18" s="33">
         <v>74498</v>
@@ -4005,7 +4146,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B19" s="25">
         <v>9227</v>
@@ -4037,7 +4178,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4095,19 +4236,9 @@
         <v>5696361</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4117,7 +4248,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B8" s="28">
         <v>780535</v>
@@ -4137,7 +4268,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B9" s="28">
         <v>503333</v>
@@ -4157,7 +4288,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B10" s="28">
         <v>106629</v>
@@ -4177,37 +4308,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B11" s="30">
+        <f>SUM(B8:B10)</f>
         <v>1390497</v>
       </c>
       <c r="C11" s="30">
+        <f>SUM(C8:C10)</f>
         <v>1805930</v>
       </c>
       <c r="D11" s="30">
+        <f>SUM(D8:D10)</f>
         <v>2059375</v>
       </c>
       <c r="E11" s="30">
+        <f>SUM(E8:E10)</f>
         <v>2306162</v>
       </c>
       <c r="F11" s="30">
+        <f>SUM(F8:F10)</f>
         <v>2581867</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4217,42 +4343,52 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B14" s="26">
+        <f>B5-B11</f>
         <v>-212164</v>
       </c>
       <c r="C14" s="26">
+        <f>C5-C11</f>
         <v>455670</v>
       </c>
       <c r="D14" s="26">
+        <f>D5-D11</f>
         <v>1308590</v>
       </c>
       <c r="E14" s="26">
+        <f>E5-E11</f>
         <v>2196369</v>
       </c>
       <c r="F14" s="26">
+        <f>F5-F11</f>
         <v>3114494</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B15" s="24">
-        <v>-0.18005398371894768</v>
+        <f>IF(B5=0,0,B14/B5)</f>
+        <v>-0.18005398</v>
       </c>
       <c r="C15" s="24">
-        <v>0.20148130933167066</v>
+        <f>IF(C5=0,0,C14/C5)</f>
+        <v>0.20148131</v>
       </c>
       <c r="D15" s="24">
-        <v>0.38854013963461814</v>
+        <f>IF(D5=0,0,D14/D5)</f>
+        <v>0.38854014</v>
       </c>
       <c r="E15" s="24">
-        <v>0.48780762672183775</v>
+        <f>IF(E5=0,0,E14/E5)</f>
+        <v>0.48780763</v>
       </c>
       <c r="F15" s="24">
-        <v>0.54675147116204</v>
+        <f>IF(F5=0,0,F14/F5)</f>
+        <v>0.54675147</v>
       </c>
     </row>
   </sheetData>
@@ -4321,7 +4457,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B5" s="25">
         <v>350000</v>
@@ -4341,7 +4477,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B6" s="25">
         <v>20283</v>
@@ -4361,7 +4497,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B7" s="25">
         <v>26345</v>
@@ -4381,7 +4517,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B8" s="28">
         <v>46629</v>
@@ -4401,7 +4537,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B9" s="33">
         <v>323655</v>
@@ -4445,7 +4581,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4475,7 +4611,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4485,7 +4621,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B5" s="35">
         <v>74498</v>
@@ -4505,7 +4641,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B6" s="25">
         <v>0</v>
@@ -4525,7 +4661,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B7" s="25">
         <v>0</v>
@@ -4545,7 +4681,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B8" s="25">
         <v>0</v>
@@ -4565,7 +4701,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B9" s="30">
         <v>74498</v>
@@ -4585,7 +4721,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4595,7 +4731,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B12" s="25">
         <v>0</v>
@@ -4615,7 +4751,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B13" s="25">
         <v>323655</v>
@@ -4635,7 +4771,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B14" s="30">
         <v>323655</v>
@@ -4655,7 +4791,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4665,7 +4801,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B17" s="26">
         <v>-249157</v>
@@ -4685,7 +4821,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B19" s="36">
         <v>0</v>
@@ -4720,7 +4856,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4729,7 +4865,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4759,7 +4895,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4769,22 +4905,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B5" s="25">
-        <v>-105535</v>
+        <v>1178333</v>
       </c>
       <c r="C5" s="25">
-        <v>522299</v>
+        <v>2261600</v>
       </c>
       <c r="D5" s="25">
-        <v>1380218</v>
+        <v>3367965</v>
       </c>
       <c r="E5" s="25">
-        <v>2252998</v>
+        <v>4502532</v>
       </c>
       <c r="F5" s="25">
-        <v>3171123</v>
+        <v>5696361</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4792,309 +4928,329 @@
         <v>299</v>
       </c>
       <c r="B6" s="25">
+        <v>780535</v>
+      </c>
+      <c r="C6" s="25">
+        <v>964741</v>
+      </c>
+      <c r="D6" s="25">
+        <v>993683</v>
+      </c>
+      <c r="E6" s="25">
+        <v>1023494</v>
+      </c>
+      <c r="F6" s="25">
+        <v>1054199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B7" s="25">
+        <v>503333</v>
+      </c>
+      <c r="C7" s="25">
+        <v>774560</v>
+      </c>
+      <c r="D7" s="25">
+        <v>994063</v>
+      </c>
+      <c r="E7" s="25">
+        <v>1226040</v>
+      </c>
+      <c r="F7" s="25">
+        <v>1471040</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B8" s="28">
+        <f>B5-B6-B7</f>
+        <v>-105535</v>
+      </c>
+      <c r="C8" s="28">
+        <f>C5-C6-C7</f>
+        <v>522299</v>
+      </c>
+      <c r="D8" s="28">
+        <f>D5-D6-D7</f>
+        <v>1380218</v>
+      </c>
+      <c r="E8" s="28">
+        <f>E5-E6-E7</f>
+        <v>2252998</v>
+      </c>
+      <c r="F8" s="28">
+        <f>F5-F6-F7</f>
+        <v>3171123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" s="25">
         <v>46629</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C9" s="25">
         <v>46629</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D9" s="25">
         <v>46629</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E9" s="25">
         <v>46629</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F9" s="25">
         <v>46629</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B7" s="38">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B10" s="38">
+        <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-2.26</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C10" s="38">
+        <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>11.2</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D10" s="38">
+        <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>29.6</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E10" s="38">
+        <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>48.32</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F10" s="38">
+        <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>68.01</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B10" s="25">
-        <v>74498</v>
-      </c>
-      <c r="C10" s="25">
-        <v>530168</v>
-      </c>
-      <c r="D10" s="25">
-        <v>1838758</v>
-      </c>
-      <c r="E10" s="25">
-        <v>4035127</v>
-      </c>
-      <c r="F10" s="25">
-        <v>7149621</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B11" s="22">
-        <v>20</v>
-      </c>
-      <c r="C11" s="22">
-        <v>108</v>
-      </c>
-      <c r="D11" s="22">
-        <v>330</v>
-      </c>
-      <c r="E11" s="22">
-        <v>641</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="B12" s="29">
-        <v>0.7</v>
-      </c>
-      <c r="C12" s="29">
-        <v>3.6</v>
-      </c>
-      <c r="D12" s="29">
-        <v>10.8</v>
-      </c>
-      <c r="E12" s="29">
-        <v>21.1</v>
-      </c>
-      <c r="F12" s="29">
-        <v>33.4</v>
-      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B13" s="24">
-        <v>0.2</v>
-      </c>
-      <c r="C13" s="24">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D13" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="24">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="F13" s="24">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="B13" s="25">
+        <v>74498</v>
+      </c>
+      <c r="C13" s="25">
+        <v>530168</v>
+      </c>
+      <c r="D13" s="25">
+        <v>1838758</v>
+      </c>
+      <c r="E13" s="25">
+        <v>4035127</v>
+      </c>
+      <c r="F13" s="25">
+        <v>7149621</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B14" s="22">
+        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
+        <v>20</v>
+      </c>
+      <c r="C14" s="22">
+        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
+        <v>108</v>
+      </c>
+      <c r="D14" s="22">
+        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
+        <v>330</v>
+      </c>
+      <c r="E14" s="22">
+        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
+        <v>641</v>
+      </c>
+      <c r="F14" s="22">
+        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="29">
+        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
+        <v>0.7</v>
+      </c>
+      <c r="C15" s="29">
+        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
+        <v>3.6</v>
+      </c>
+      <c r="D15" s="29">
+        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
+        <v>10.8</v>
+      </c>
+      <c r="E15" s="29">
+        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
+        <v>21.1</v>
+      </c>
+      <c r="F15" s="29">
+        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
+        <v>33.4</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="C16" s="24">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D16" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="24">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F16" s="24">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B19" s="25">
         <v>9819</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C19" s="25">
         <v>11308</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D19" s="25">
         <v>11227</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E19" s="25">
         <v>11256</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F19" s="25">
         <v>11393</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B17" s="25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B20" s="25">
         <v>827164</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C20" s="25">
         <v>1011370</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D20" s="25">
         <v>1040312</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E20" s="25">
         <v>1070123</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F20" s="25">
         <v>1100827</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B18" s="25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B21" s="25">
         <v>4194</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C21" s="25">
         <v>3873</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D21" s="25">
         <v>3314</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E21" s="25">
         <v>3065</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F21" s="25">
         <v>2942</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B19" s="39">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B22" s="39">
         <v>148</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C22" s="39">
         <v>137</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D22" s="39">
         <v>132</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E22" s="39">
         <v>131</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F22" s="39">
         <v>131</v>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B22" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="C22" s="41" t="s">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="D22" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B23" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="F24" s="40" t="s">
-        <v>342</v>
-      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="C25" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="B25" s="40" t="s">
-        <v>342</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>343</v>
-      </c>
       <c r="D25" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -5102,19 +5258,79 @@
         <v>347</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>343</v>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="E28" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="F28" s="41" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="D29" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5155,13 +5371,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>100</v>
@@ -5175,7 +5391,7 @@
         <v>350000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E4" s="25">
         <v>250000</v>
@@ -5183,7 +5399,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B5" s="25">
         <v>150000</v>
@@ -5197,7 +5413,7 @@
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E6" s="25">
         <v>50000</v>
@@ -5205,7 +5421,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E7" s="25">
         <v>140000</v>
@@ -5213,13 +5429,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B9" s="26">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E9" s="26">
         <v>500000</v>
@@ -5227,7 +5443,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B10" s="36">
         <v>0</v>
@@ -5395,7 +5611,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5405,7 +5621,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5415,7 +5631,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5440,7 +5656,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="B6" s="25">
         <v>1178333</v>
@@ -5460,7 +5676,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B7" s="25">
         <v>1330497</v>
@@ -5480,7 +5696,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B8" s="26">
         <v>-152164</v>
@@ -5500,7 +5716,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B9" s="24">
         <v>-0.12913460606689678</v>
@@ -5520,7 +5736,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B10" s="43">
         <v>-2.26</v>
@@ -5540,7 +5756,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B11" s="22">
         <v>148</v>
@@ -5560,7 +5776,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5570,7 +5786,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5595,7 +5811,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="B16" s="25">
         <v>1178333</v>
@@ -5615,7 +5831,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B17" s="25">
         <v>1330497</v>
@@ -5635,7 +5851,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B18" s="26">
         <v>-152164</v>
@@ -5655,7 +5871,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B19" s="24">
         <v>-0.12913460606689678</v>
@@ -5675,7 +5891,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B20" s="43">
         <v>-2.26</v>
@@ -5695,7 +5911,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B21" s="22">
         <v>125</v>
@@ -5715,7 +5931,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5725,7 +5941,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5750,7 +5966,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="B26" s="25">
         <v>1084067</v>
@@ -5770,7 +5986,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B27" s="25">
         <v>1330497</v>
@@ -5790,7 +6006,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B28" s="26">
         <v>-246430</v>
@@ -5810,7 +6026,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B29" s="24">
         <v>-0.22732022398575744</v>
@@ -5830,7 +6046,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B30" s="43">
         <v>-4.28</v>
@@ -5850,7 +6066,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B31" s="22">
         <v>171</v>
@@ -5896,7 +6112,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5930,7 +6146,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5954,7 +6170,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5962,7 +6178,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6000,7 +6216,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="D13" s="25">
         <v>1178333</v>
@@ -6020,7 +6236,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D14" s="25">
         <v>1330497</v>
@@ -6040,7 +6256,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D15" s="25">
         <v>-212164</v>
@@ -6060,7 +6276,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D16" s="25">
         <v>74498</v>
@@ -6080,7 +6296,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D17" s="25">
         <v>323655</v>
@@ -6100,7 +6316,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6138,7 +6354,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D21" s="24">
         <v>-0.18005398371894768</v>
@@ -6158,7 +6374,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D22" s="43">
         <v>-2.26</v>
@@ -6198,7 +6414,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D24" s="22">
         <v>120</v>
@@ -6218,7 +6434,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7646,18 +7862,23 @@
         <v>207</v>
       </c>
       <c r="B11" s="26">
+        <f>SUM(B5:B10)</f>
         <v>1414000</v>
       </c>
       <c r="C11" s="26">
+        <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
       <c r="D11" s="26">
+        <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
       <c r="E11" s="26">
+        <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
       <c r="F11" s="26">
+        <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
     </row>
@@ -8064,18 +8285,23 @@
         <v>216</v>
       </c>
       <c r="B6" s="30">
+        <f>SUM(B5:B5)</f>
         <v>78000</v>
       </c>
       <c r="C6" s="30">
+        <f>SUM(C5:C5)</f>
         <v>133900</v>
       </c>
       <c r="D6" s="30">
+        <f>SUM(D5:D5)</f>
         <v>206875</v>
       </c>
       <c r="E6" s="30">
+        <f>SUM(E5:E5)</f>
         <v>284109</v>
       </c>
       <c r="F6" s="30">
+        <f>SUM(F5:F5)</f>
         <v>365790</v>
       </c>
     </row>
@@ -8114,18 +8340,23 @@
         <v>218</v>
       </c>
       <c r="B9" s="30">
+        <f>SUM(B8:B8)</f>
         <v>54000</v>
       </c>
       <c r="C9" s="30">
+        <f>SUM(C8:C8)</f>
         <v>92700</v>
       </c>
       <c r="D9" s="30">
+        <f>SUM(D8:D8)</f>
         <v>143222</v>
       </c>
       <c r="E9" s="30">
+        <f>SUM(E8:E8)</f>
         <v>196691</v>
       </c>
       <c r="F9" s="30">
+        <f>SUM(F8:F8)</f>
         <v>253239</v>
       </c>
     </row>
@@ -8204,18 +8435,23 @@
         <v>222</v>
       </c>
       <c r="B14" s="30">
+        <f>SUM(B11:B13)</f>
         <v>322000</v>
       </c>
       <c r="C14" s="30">
+        <f>SUM(C11:C13)</f>
         <v>331660</v>
       </c>
       <c r="D14" s="30">
+        <f>SUM(D11:D13)</f>
         <v>341610</v>
       </c>
       <c r="E14" s="30">
+        <f>SUM(E11:E13)</f>
         <v>351858</v>
       </c>
       <c r="F14" s="30">
+        <f>SUM(F11:F13)</f>
         <v>362414</v>
       </c>
     </row>
@@ -8314,18 +8550,23 @@
         <v>227</v>
       </c>
       <c r="B20" s="30">
+        <f>SUM(B16:B19)</f>
         <v>150000</v>
       </c>
       <c r="C20" s="30">
+        <f>SUM(C16:C19)</f>
         <v>216300</v>
       </c>
       <c r="D20" s="30">
+        <f>SUM(D16:D19)</f>
         <v>302357</v>
       </c>
       <c r="E20" s="30">
+        <f>SUM(E16:E19)</f>
         <v>393382</v>
       </c>
       <c r="F20" s="30">
+        <f>SUM(F16:F19)</f>
         <v>489596</v>
       </c>
     </row>
@@ -8334,18 +8575,23 @@
         <v>228</v>
       </c>
       <c r="B22" s="26">
+        <f>B6+B9+B14+B20</f>
         <v>604000</v>
       </c>
       <c r="C22" s="26">
+        <f>C6+C9+C14+C20</f>
         <v>774560</v>
       </c>
       <c r="D22" s="26">
+        <f>D6+D9+D14+D20</f>
         <v>994063</v>
       </c>
       <c r="E22" s="26">
+        <f>E6+E9+E14+E20</f>
         <v>1226040</v>
       </c>
       <c r="F22" s="26">
+        <f>F6+F9+F14+F20</f>
         <v>1471040</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -216,7 +216,7 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
-    <t>CONFIDENTIAL — Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
+    <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
     <t>How to Use This Workbook</t>
@@ -225,10 +225,10 @@
     <t>Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas — do not edit.</t>
+    <t>Yellow cells are editable inputs - change these to update your model.</t>
+  </si>
+  <si>
+    <t>Gray cells contain formulas - do not edit.</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -279,7 +279,7 @@
     <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — Assumptions</t>
+    <t>Heritage Academy Charter - Assumptions</t>
   </si>
   <si>
     <t>Yellow cells are editable inputs. All other cells are formulas.</t>
@@ -627,7 +627,7 @@
     <t>Enrollment Growth Rate</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>Tuition &amp; Funding Drivers</t>
@@ -783,7 +783,7 @@
     <t>TOTAL PERSONNEL</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — Budget Detail</t>
+    <t>Heritage Academy Charter - Budget Detail</t>
   </si>
   <si>
     <t>REVENUE</t>
@@ -861,7 +861,7 @@
     <t>Total Capital &amp; Debt</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — Budget Summary</t>
+    <t>Heritage Academy Charter - Budget Summary</t>
   </si>
   <si>
     <t>Total Capital &amp; Debt Service</t>
@@ -885,7 +885,7 @@
     <t>Cost per Student</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — Year 1 Monthly Cash Flow</t>
+    <t>Heritage Academy Charter - Year 1 Monthly Cash Flow</t>
   </si>
   <si>
     <t>July</t>
@@ -957,7 +957,7 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — 5-Year Operating Statement</t>
+    <t>Heritage Academy Charter - 5-Year Operating Statement</t>
   </si>
   <si>
     <t>Capital &amp; Debt Service</t>
@@ -981,7 +981,7 @@
     <t>Ending Balance</t>
   </si>
   <si>
-    <t>Heritage Academy Charter — Balance Sheet</t>
+    <t>Heritage Academy Charter - Balance Sheet</t>
   </si>
   <si>
     <t>ASSETS</t>
@@ -1134,7 +1134,7 @@
     <t>Enrollment: +0%  |  Revenue: -8%  |  Expenses: +0%</t>
   </si>
   <si>
-    <t>Underwriting Snapshot — Loan Committee Summary</t>
+    <t>Underwriting Snapshot - Loan Committee Summary</t>
   </si>
   <si>
     <t>Entity</t>
@@ -1161,7 +1161,7 @@
     <t>Enrollment</t>
   </si>
   <si>
-    <t>Prepared by SchoolStack Budget — budget.schoolstack.ai</t>
+    <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -1119,19 +1119,19 @@
     <t>BASE CASE</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: +0%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>LOW ADA</t>
   </si>
   <si>
-    <t>Enrollment: -15%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: -15%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>FUNDING CUT</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: -8%  |  Expenses: +0%</t>
+    <t>Enrollment: +0%  |  Revenue: -8%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>Underwriting Snapshot - Loan Committee Summary</t>
@@ -5814,19 +5814,19 @@
         <v>332</v>
       </c>
       <c r="B16" s="25">
-        <v>1178333</v>
+        <v>1001583</v>
       </c>
       <c r="C16" s="25">
-        <v>2261600</v>
+        <v>1922360</v>
       </c>
       <c r="D16" s="25">
-        <v>3367965</v>
+        <v>2862770</v>
       </c>
       <c r="E16" s="25">
-        <v>4502532</v>
+        <v>3827152</v>
       </c>
       <c r="F16" s="25">
-        <v>5696361</v>
+        <v>4841907</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5854,19 +5854,19 @@
         <v>280</v>
       </c>
       <c r="B18" s="26">
-        <v>-152164</v>
+        <v>-328914</v>
       </c>
       <c r="C18" s="26">
-        <v>475670</v>
+        <v>136430</v>
       </c>
       <c r="D18" s="26">
-        <v>1333590</v>
+        <v>828395</v>
       </c>
       <c r="E18" s="26">
-        <v>2206369</v>
+        <v>1530989</v>
       </c>
       <c r="F18" s="26">
-        <v>3124494</v>
+        <v>2270040</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5874,19 +5874,19 @@
         <v>281</v>
       </c>
       <c r="B19" s="24">
-        <v>-0.12913460606689678</v>
+        <v>-0.32839365419634914</v>
       </c>
       <c r="C19" s="24">
-        <v>0.21032460611271073</v>
+        <v>0.07097012483848322</v>
       </c>
       <c r="D19" s="24">
-        <v>0.3959630196229791</v>
+        <v>0.28936825837997543</v>
       </c>
       <c r="E19" s="24">
-        <v>0.49002859951113986</v>
+        <v>0.40003364648369394</v>
       </c>
       <c r="F19" s="24">
-        <v>0.5485069777397931</v>
+        <v>0.46883173851740356</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5894,19 +5894,19 @@
         <v>334</v>
       </c>
       <c r="B20" s="43">
-        <v>-2.26</v>
+        <v>-6.05</v>
       </c>
       <c r="C20" s="43">
-        <v>11.2</v>
+        <v>3.93</v>
       </c>
       <c r="D20" s="43">
-        <v>29.6</v>
+        <v>18.77</v>
       </c>
       <c r="E20" s="43">
-        <v>48.32</v>
+        <v>33.83</v>
       </c>
       <c r="F20" s="43">
-        <v>68.01</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -5914,19 +5914,19 @@
         <v>342</v>
       </c>
       <c r="B21" s="22">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="C21" s="22">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="D21" s="22">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="E21" s="22">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="F21" s="22">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -5682,16 +5682,16 @@
         <v>1330497</v>
       </c>
       <c r="C7" s="25">
-        <v>1785930</v>
+        <v>1786230</v>
       </c>
       <c r="D7" s="25">
-        <v>2034375</v>
+        <v>2034780</v>
       </c>
       <c r="E7" s="25">
-        <v>2296162</v>
+        <v>2296343</v>
       </c>
       <c r="F7" s="25">
-        <v>2571867</v>
+        <v>2572777</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5702,16 +5702,16 @@
         <v>-152164</v>
       </c>
       <c r="C8" s="26">
-        <v>475670</v>
+        <v>475370</v>
       </c>
       <c r="D8" s="26">
-        <v>1333590</v>
+        <v>1333185</v>
       </c>
       <c r="E8" s="26">
-        <v>2206369</v>
+        <v>2206189</v>
       </c>
       <c r="F8" s="26">
-        <v>3124494</v>
+        <v>3123585</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5719,19 +5719,19 @@
         <v>281</v>
       </c>
       <c r="B9" s="24">
-        <v>-0.12913460606689678</v>
+        <v>-0.12913460606689658</v>
       </c>
       <c r="C9" s="24">
-        <v>0.21032460611271073</v>
+        <v>0.21019195666099513</v>
       </c>
       <c r="D9" s="24">
-        <v>0.3959630196229791</v>
+        <v>0.3958429768078072</v>
       </c>
       <c r="E9" s="24">
-        <v>0.49002859951113986</v>
+        <v>0.4899885700301692</v>
       </c>
       <c r="F9" s="24">
-        <v>0.5485069777397931</v>
+        <v>0.5483473475657772</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5742,16 +5742,16 @@
         <v>-2.26</v>
       </c>
       <c r="C10" s="43">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
       <c r="D10" s="43">
-        <v>29.6</v>
+        <v>29.59</v>
       </c>
       <c r="E10" s="43">
-        <v>48.32</v>
+        <v>48.31</v>
       </c>
       <c r="F10" s="43">
-        <v>68.01</v>
+        <v>67.99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5837,16 +5837,16 @@
         <v>1330497</v>
       </c>
       <c r="C17" s="25">
-        <v>1785930</v>
+        <v>1786230</v>
       </c>
       <c r="D17" s="25">
-        <v>2034375</v>
+        <v>2034780</v>
       </c>
       <c r="E17" s="25">
-        <v>2296162</v>
+        <v>2296343</v>
       </c>
       <c r="F17" s="25">
-        <v>2571867</v>
+        <v>2572777</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5857,16 +5857,16 @@
         <v>-328914</v>
       </c>
       <c r="C18" s="26">
-        <v>136430</v>
+        <v>136130</v>
       </c>
       <c r="D18" s="26">
-        <v>828395</v>
+        <v>827991</v>
       </c>
       <c r="E18" s="26">
-        <v>1530989</v>
+        <v>1530809</v>
       </c>
       <c r="F18" s="26">
-        <v>2270040</v>
+        <v>2269130</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5874,19 +5874,19 @@
         <v>281</v>
       </c>
       <c r="B19" s="24">
-        <v>-0.32839365419634914</v>
+        <v>-0.32839365419634886</v>
       </c>
       <c r="C19" s="24">
-        <v>0.07097012483848322</v>
+        <v>0.07081406665999428</v>
       </c>
       <c r="D19" s="24">
-        <v>0.28936825837997543</v>
+        <v>0.28922703153859675</v>
       </c>
       <c r="E19" s="24">
-        <v>0.40003364648369394</v>
+        <v>0.39998655297666963</v>
       </c>
       <c r="F19" s="24">
-        <v>0.46883173851740356</v>
+        <v>0.468643938312679</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5897,16 +5897,16 @@
         <v>-6.05</v>
       </c>
       <c r="C20" s="43">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="D20" s="43">
-        <v>18.77</v>
+        <v>18.76</v>
       </c>
       <c r="E20" s="43">
         <v>33.83</v>
       </c>
       <c r="F20" s="43">
-        <v>49.68</v>
+        <v>49.66</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -5992,16 +5992,16 @@
         <v>1330497</v>
       </c>
       <c r="C27" s="25">
-        <v>1785930</v>
+        <v>1786230</v>
       </c>
       <c r="D27" s="25">
-        <v>2034375</v>
+        <v>2034780</v>
       </c>
       <c r="E27" s="25">
-        <v>2296162</v>
+        <v>2296343</v>
       </c>
       <c r="F27" s="25">
-        <v>2571867</v>
+        <v>2572777</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -6012,16 +6012,16 @@
         <v>-246430</v>
       </c>
       <c r="C28" s="26">
-        <v>294742</v>
+        <v>294442</v>
       </c>
       <c r="D28" s="26">
-        <v>1064152</v>
+        <v>1063748</v>
       </c>
       <c r="E28" s="26">
-        <v>1846167</v>
+        <v>1845986</v>
       </c>
       <c r="F28" s="26">
-        <v>2668785</v>
+        <v>2667876</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -6029,19 +6029,19 @@
         <v>281</v>
       </c>
       <c r="B29" s="24">
-        <v>-0.22732022398575744</v>
+        <v>-0.2273202239857572</v>
       </c>
       <c r="C29" s="24">
-        <v>0.1416571805572943</v>
+        <v>0.14151299637064688</v>
       </c>
       <c r="D29" s="24">
-        <v>0.34343806480758604</v>
+        <v>0.34330758348674706</v>
       </c>
       <c r="E29" s="24">
-        <v>0.4456832603381955</v>
+        <v>0.44563975003279266</v>
       </c>
       <c r="F29" s="24">
-        <v>0.5092467149345576</v>
+        <v>0.5090732038758448</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -6052,16 +6052,16 @@
         <v>-4.28</v>
       </c>
       <c r="C30" s="43">
-        <v>7.32</v>
+        <v>7.31</v>
       </c>
       <c r="D30" s="43">
-        <v>23.82</v>
+        <v>23.81</v>
       </c>
       <c r="E30" s="43">
         <v>40.59</v>
       </c>
       <c r="F30" s="43">
-        <v>58.23</v>
+        <v>58.22</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="378">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -502,6 +502,9 @@
   </si>
   <si>
     <t>Salary Escalation Rate</t>
+  </si>
+  <si>
+    <t>Derived from tuition escalation rate</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
@@ -1175,7 +1178,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1243,6 +1246,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1329,7 +1338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1358,6 +1367,7 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1374,14 +1384,14 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2047,7 +2057,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2079,25 +2089,25 @@
       <c r="A4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="32">
         <v>120</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <v>200</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="32">
         <v>300</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>400</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="32">
         <v>500</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2109,19 +2119,19 @@
       <c r="A7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>969000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>1617850</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>2466200</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>3327850</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>4233200</v>
       </c>
     </row>
@@ -2129,19 +2139,19 @@
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <v>90000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>154500</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>238703</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>327818</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>422066</v>
       </c>
     </row>
@@ -2149,19 +2159,19 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <v>132000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>226600</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>350097</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>480800</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>619030</v>
       </c>
     </row>
@@ -2169,19 +2179,19 @@
       <c r="A10" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <v>150000</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>154500</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>159135</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>163909</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>168826</v>
       </c>
     </row>
@@ -2189,19 +2199,19 @@
       <c r="A11" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <v>25000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>25750</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>26523</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>27318</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>28138</v>
       </c>
     </row>
@@ -2209,64 +2219,64 @@
       <c r="A12" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <v>48000</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <v>82400</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <v>127308</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>174836</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <v>225102</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="26">
+        <v>208</v>
+      </c>
+      <c r="B13" s="27">
         <f>SUM(B7:B12)</f>
         <v>1414000</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>SUM(C7:C12)</f>
         <v>2261600</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>SUM(D7:D12)</f>
         <v>3367965</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>SUM(E7:E12)</f>
         <v>4502532</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>SUM(F7:F12)</f>
         <v>5696361</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B15" s="25">
+        <v>237</v>
+      </c>
+      <c r="B15" s="26">
         <v>11783</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <v>11308</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <v>11227</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <v>11256</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <v>11393</v>
       </c>
     </row>
@@ -2296,7 +2306,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2336,85 +2346,85 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B5" s="25">
+        <v>239</v>
+      </c>
+      <c r="B5" s="26">
         <v>278438</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>344149</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>354473</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>365107</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>376061</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B6" s="25">
+        <v>240</v>
+      </c>
+      <c r="B6" s="26">
         <v>59029</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>72960</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>75148</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>77403</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>79725</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="25">
+        <v>241</v>
+      </c>
+      <c r="B7" s="26">
         <v>87955</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>108712</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>111974</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>115333</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>118793</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" s="30">
+        <v>242</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>425421</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>525821</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>541595</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>557843</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>574578</v>
       </c>
@@ -2431,65 +2441,65 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B10" s="25">
+        <v>243</v>
+      </c>
+      <c r="B10" s="26">
         <v>116944</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>144542</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>148879</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>153345</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>157945</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B11" s="25">
+        <v>244</v>
+      </c>
+      <c r="B11" s="26">
         <v>91328</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>112881</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>116267</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>119755</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>123348</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B12" s="30">
+        <v>245</v>
+      </c>
+      <c r="B12" s="31">
         <f>SUM(B10:B11)</f>
         <v>208271</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>SUM(C10:C11)</f>
         <v>257423</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>SUM(D10:D11)</f>
         <v>265146</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>SUM(E10:E11)</f>
         <v>273100</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>SUM(F10:F11)</f>
         <v>281293</v>
       </c>
@@ -2506,45 +2516,45 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" s="25">
+        <v>246</v>
+      </c>
+      <c r="B14" s="26">
         <v>69053</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <v>85349</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <v>87909</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>90547</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>93263</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B15" s="30">
+        <v>247</v>
+      </c>
+      <c r="B15" s="31">
         <f>SUM(B14:B14)</f>
         <v>69053</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>SUM(C14:C14)</f>
         <v>85349</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>SUM(D14:D14)</f>
         <v>87909</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>SUM(E14:E14)</f>
         <v>90547</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>SUM(F14:F14)</f>
         <v>93263</v>
       </c>
@@ -2561,70 +2571,70 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="25">
+        <v>248</v>
+      </c>
+      <c r="B17" s="26">
         <v>77790</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>96148</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>99033</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>102004</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>105064</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="B18" s="30">
+        <v>249</v>
+      </c>
+      <c r="B18" s="31">
         <f>SUM(B17:B17)</f>
         <v>77790</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <f>SUM(C17:C17)</f>
         <v>96148</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <f>SUM(D17:D17)</f>
         <v>99033</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <f>SUM(E17:E17)</f>
         <v>102004</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <f>SUM(F17:F17)</f>
         <v>105064</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B20" s="26">
+        <v>250</v>
+      </c>
+      <c r="B20" s="27">
         <f>B8+B12+B15+B18</f>
         <v>780535</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <f>C8+C12+C15+C18</f>
         <v>964741</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f>D8+D12+D15+D18</f>
         <v>993683</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f>E8+E12+E15+E18</f>
         <v>1023494</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>F8+F12+F15+F18</f>
         <v>1054199</v>
       </c>
@@ -2655,7 +2665,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2685,7 +2695,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2695,152 +2705,152 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="25">
+        <v>253</v>
+      </c>
+      <c r="B5" s="26">
         <v>807500</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>1617850</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>2466200</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>3327850</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>4233200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="25">
+        <v>254</v>
+      </c>
+      <c r="B6" s="26">
         <v>75000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>154500</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>238703</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>327818</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>422066</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="25">
+        <v>255</v>
+      </c>
+      <c r="B7" s="26">
         <v>110000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>226600</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>350097</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>480800</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>619030</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B8" s="25">
+        <v>256</v>
+      </c>
+      <c r="B8" s="26">
         <v>125000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>154500</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>159135</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>163909</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>168826</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B9" s="25">
+        <v>257</v>
+      </c>
+      <c r="B9" s="26">
         <v>20833</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>25750</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>26523</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>27318</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>28138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="25">
+        <v>258</v>
+      </c>
+      <c r="B10" s="26">
         <v>40000</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>82400</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>127308</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>174836</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>225102</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B11" s="30">
+        <v>259</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
         <v>1178333</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2850,165 +2860,165 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B14" s="25">
+        <v>243</v>
+      </c>
+      <c r="B14" s="26">
         <v>116944</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <v>144542</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <v>148879</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>153345</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>157945</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" s="25">
+        <v>244</v>
+      </c>
+      <c r="B15" s="26">
         <v>91328</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <v>112881</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <v>116267</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <v>119755</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <v>123348</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B16" s="25">
+        <v>239</v>
+      </c>
+      <c r="B16" s="26">
         <v>278438</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>344149</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>354473</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>365107</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>376061</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="25">
+        <v>240</v>
+      </c>
+      <c r="B17" s="26">
         <v>59029</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>72960</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>75148</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>77403</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>79725</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" s="25">
+        <v>241</v>
+      </c>
+      <c r="B18" s="26">
         <v>87955</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <v>108712</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <v>111974</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <v>115333</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <v>118793</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B19" s="25">
+        <v>246</v>
+      </c>
+      <c r="B19" s="26">
         <v>69053</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <v>85349</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <v>87909</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <v>90547</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <v>93263</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B20" s="25">
+        <v>248</v>
+      </c>
+      <c r="B20" s="26">
         <v>77790</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <v>96148</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <v>99033</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <v>102004</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <v>105064</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B21" s="30">
+        <v>212</v>
+      </c>
+      <c r="B21" s="31">
         <f>SUM(B14:B20)</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>SUM(C14:C20)</f>
         <v>964741</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>SUM(D14:D20)</f>
         <v>993683</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <f>SUM(E14:E20)</f>
         <v>1023494</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <f>SUM(F14:F20)</f>
         <v>1054199</v>
       </c>
@@ -3024,283 +3034,283 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="33" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" s="25">
+        <v>261</v>
+      </c>
+      <c r="B25" s="26">
         <v>65000</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="26">
         <v>133900</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="26">
         <v>206875</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="26">
         <v>284109</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="26">
         <v>365790</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="33" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B27" s="25">
+        <v>262</v>
+      </c>
+      <c r="B27" s="26">
         <v>45000</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="26">
         <v>92700</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="26">
         <v>143222</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="26">
         <v>196691</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="26">
         <v>253239</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="33" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B29" s="25">
+        <v>263</v>
+      </c>
+      <c r="B29" s="26">
         <v>220000</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <v>271920</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="26">
         <v>280078</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="26">
         <v>288480</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="26">
         <v>297134</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B30" s="25">
+        <v>264</v>
+      </c>
+      <c r="B30" s="26">
         <v>30000</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="26">
         <v>37080</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="26">
         <v>38192</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="26">
         <v>39338</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="26">
         <v>40518</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B31" s="25">
+        <v>265</v>
+      </c>
+      <c r="B31" s="26">
         <v>18333</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="26">
         <v>22660</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="26">
         <v>23340</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="26">
         <v>24040</v>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="26">
         <v>24761</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B32" s="30">
+        <v>266</v>
+      </c>
+      <c r="B32" s="31">
         <f>SUM(B29:B31)</f>
         <v>268333</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <f>SUM(C29:C31)</f>
         <v>331660</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="31">
         <f>SUM(D29:D31)</f>
         <v>341610</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="31">
         <f>SUM(E29:E31)</f>
         <v>351858</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="31">
         <f>SUM(F29:F31)</f>
         <v>362414</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="33" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B34" s="25">
+        <v>267</v>
+      </c>
+      <c r="B34" s="26">
         <v>25000</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="26">
         <v>30900</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="26">
         <v>31827</v>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="26">
         <v>32782</v>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="26">
         <v>33765</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B35" s="25">
+        <v>268</v>
+      </c>
+      <c r="B35" s="26">
         <v>10000</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <v>12360</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="26">
         <v>12731</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="26">
         <v>13113</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="26">
         <v>13506</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B36" s="25">
+        <v>269</v>
+      </c>
+      <c r="B36" s="26">
         <v>15000</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <v>18540</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="26">
         <v>19096</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="26">
         <v>19669</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="26">
         <v>20259</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B37" s="25">
+        <v>270</v>
+      </c>
+      <c r="B37" s="26">
         <v>75000</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="26">
         <v>154500</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="26">
         <v>238703</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="26">
         <v>327818</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="26">
         <v>422066</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B38" s="30">
+        <v>271</v>
+      </c>
+      <c r="B38" s="31">
         <f>SUM(B34:B37)</f>
         <v>125000</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <f>SUM(C34:C37)</f>
         <v>216300</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <f>SUM(D34:D37)</f>
         <v>302357</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <f>SUM(E34:E37)</f>
         <v>393382</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <f>SUM(F34:F37)</f>
         <v>489596</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B39" s="30">
+        <v>272</v>
+      </c>
+      <c r="B39" s="31">
         <f>B25+B27+B32+B38</f>
         <v>503333</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <f>C25+C27+C32+C38</f>
         <v>774560</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="31">
         <f>D25+D27+D32+D38</f>
         <v>994063</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="31">
         <f>E25+E27+E32+E38</f>
         <v>1226040</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="31">
         <f>F25+F27+F32+F38</f>
         <v>1471040</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3310,65 +3320,65 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="B42" s="25">
+        <v>274</v>
+      </c>
+      <c r="B42" s="26">
         <v>46629</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="26">
         <v>46629</v>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="26">
         <v>46629</v>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="26">
         <v>46629</v>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="26">
         <v>46629</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B43" s="25">
+        <v>275</v>
+      </c>
+      <c r="B43" s="26">
         <v>60000</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="26">
         <v>20000</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="26">
         <v>25000</v>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="26">
         <v>10000</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B44" s="30">
+        <v>276</v>
+      </c>
+      <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
         <v>106629</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <f>SUM(C42:C43)</f>
         <v>66629</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="31">
         <f>SUM(D42:D43)</f>
         <v>71629</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="31">
         <f>SUM(E42:E43)</f>
         <v>56629</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="31">
         <f>SUM(F42:F43)</f>
         <v>56629</v>
       </c>
@@ -3399,7 +3409,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3429,132 +3439,132 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="28">
+        <v>259</v>
+      </c>
+      <c r="B4" s="29">
         <f>'Budget Detail'!B11</f>
         <v>1178333</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="29">
         <f>'Budget Detail'!C11</f>
         <v>2261600</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <f>'Budget Detail'!D11</f>
         <v>3367965</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <f>'Budget Detail'!E11</f>
         <v>4502532</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <f>'Budget Detail'!F11</f>
         <v>5696361</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" s="28">
+        <v>212</v>
+      </c>
+      <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
         <v>780535</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="29">
         <f>'Budget Detail'!C21</f>
         <v>964741</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <f>'Budget Detail'!D21</f>
         <v>993683</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>'Budget Detail'!E21</f>
         <v>1023494</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>'Budget Detail'!F21</f>
         <v>1054199</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B6" s="28">
+        <v>272</v>
+      </c>
+      <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
         <v>503333</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="29">
         <f>'Budget Detail'!C39</f>
         <v>774560</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <f>'Budget Detail'!D39</f>
         <v>994063</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="29">
         <f>'Budget Detail'!E39</f>
         <v>1226040</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="29">
         <f>'Budget Detail'!F39</f>
         <v>1471040</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B7" s="28">
+        <v>278</v>
+      </c>
+      <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
         <v>106629</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>'Budget Detail'!C44</f>
         <v>66629</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>'Budget Detail'!D44</f>
         <v>71629</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <f>'Budget Detail'!E44</f>
         <v>56629</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="29">
         <f>'Budget Detail'!F44</f>
         <v>56629</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B8" s="30">
+        <v>279</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>1390497</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>1805930</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>2059375</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>2306162</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>2581867</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3564,111 +3574,111 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B11" s="26">
+        <v>281</v>
+      </c>
+      <c r="B11" s="27">
         <f>B4-B8</f>
         <v>-212164</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>C4-C8</f>
         <v>455670</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>D4-D8</f>
         <v>1308590</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>E4-E8</f>
         <v>2196369</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>F4-F8</f>
         <v>3114494</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B12" s="24">
+        <v>282</v>
+      </c>
+      <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.54675147</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="B13" s="25">
+        <v>283</v>
+      </c>
+      <c r="B13" s="26">
         <v>-212164</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>243507</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>1552096</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>3748465</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>6862959</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="25">
+        <v>237</v>
+      </c>
+      <c r="B14" s="26">
         <v>9819</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <v>11308</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <v>11227</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>11256</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>11393</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B15" s="25">
+        <v>284</v>
+      </c>
+      <c r="B15" s="26">
         <v>11587</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <v>9030</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <v>6865</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <v>5765</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <v>5164</v>
       </c>
     </row>
@@ -3699,7 +3709,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3720,48 +3730,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3779,51 +3789,51 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="30">
+        <v>259</v>
+      </c>
+      <c r="B4" s="31">
         <v>146500</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <v>146500</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>146500</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>146500</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>146500</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>146500</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="31">
         <v>146500</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <v>146500</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="31">
         <v>146500</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="31">
         <v>146500</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="31">
         <v>0</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="31">
         <v>0</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="31">
         <v>1465000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3841,139 +3851,139 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7" s="25">
+        <v>300</v>
+      </c>
+      <c r="B7" s="26">
         <v>78054</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>78054</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>78054</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>78054</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>78054</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="26">
         <v>78054</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="26">
         <v>78054</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="26">
         <v>78054</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="26">
         <v>78054</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="26">
         <v>78054</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="26">
         <v>0</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="26">
         <v>0</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="26">
         <v>780535</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8" s="25">
+        <v>301</v>
+      </c>
+      <c r="B8" s="26">
         <v>50333</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>50333</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>50333</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>50333</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>50333</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <v>50333</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <v>50333</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <v>50333</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="26">
         <v>50333</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <v>50333</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="26">
         <v>0</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="26">
         <v>0</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="26">
         <v>503333</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" s="25">
+        <v>302</v>
+      </c>
+      <c r="B9" s="26">
         <v>8886</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>8886</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>8886</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>8886</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>8886</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <v>8886</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <v>8886</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="26">
         <v>8886</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="26">
         <v>8886</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="26">
         <v>8886</v>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="26">
         <v>8886</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="26">
         <v>8886</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="26">
         <v>106629</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3991,164 +4001,164 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B12" s="28">
+        <v>279</v>
+      </c>
+      <c r="B12" s="29">
         <v>137273</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <v>137273</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <v>137273</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <v>137273</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <v>137273</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="29">
         <v>137273</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="29">
         <v>137273</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="29">
         <v>137273</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="29">
         <v>137273</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="29">
         <v>137273</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="29">
         <v>8886</v>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="29">
         <v>8886</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="29">
         <v>1390502</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B13" s="28">
+        <v>304</v>
+      </c>
+      <c r="B13" s="29">
         <v>9227</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <v>9227</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <v>9227</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <v>9227</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <v>9227</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <v>9227</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <v>9227</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <v>9227</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="29">
         <v>9227</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="29">
         <v>9227</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="29">
         <v>-8886</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="29">
         <v>-8886</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="29">
         <v>74498</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B14" s="33">
+        <v>305</v>
+      </c>
+      <c r="B14" s="34">
         <v>9227</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <v>18454</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <v>27681</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <v>36908</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="34">
         <v>46135</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="34">
         <v>55362</v>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="34">
         <v>64589</v>
       </c>
-      <c r="I14" s="33">
+      <c r="I14" s="34">
         <v>73816</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="34">
         <v>83043</v>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="34">
         <v>92270</v>
       </c>
-      <c r="L14" s="33">
+      <c r="L14" s="34">
         <v>83384</v>
       </c>
-      <c r="M14" s="33">
+      <c r="M14" s="34">
         <v>74498</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="27">
         <v>74498</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B17" s="25">
+        <v>160</v>
+      </c>
+      <c r="B17" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B18" s="33">
+        <v>307</v>
+      </c>
+      <c r="B18" s="34">
         <v>74498</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B19" s="25">
+        <v>308</v>
+      </c>
+      <c r="B19" s="26">
         <v>9227</v>
       </c>
     </row>
@@ -4178,7 +4188,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4208,7 +4218,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4217,28 +4227,28 @@
       <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="30">
+      <c r="A5" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="B5" s="31">
         <v>1178333</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2261600</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>3367965</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>4502532</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>5696361</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4248,92 +4258,92 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B8" s="28">
+        <v>300</v>
+      </c>
+      <c r="B8" s="29">
         <v>780535</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <v>964741</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>993683</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>1023494</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <v>1054199</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B9" s="28">
+        <v>301</v>
+      </c>
+      <c r="B9" s="29">
         <v>503333</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <v>774560</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>994063</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>1226040</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>1471040</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B10" s="28">
+        <v>310</v>
+      </c>
+      <c r="B10" s="29">
         <v>106629</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <v>66629</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <v>71629</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <v>56629</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <v>56629</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>278</v>
-      </c>
-      <c r="B11" s="30">
+      <c r="A11" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
         <v>1390497</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C8:C10)</f>
         <v>1805930</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D8:D10)</f>
         <v>2059375</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E8:E10)</f>
         <v>2306162</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F8:F10)</f>
         <v>2581867</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4342,51 +4352,51 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="B14" s="26">
+      <c r="A14" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="B14" s="27">
         <f>B5-B11</f>
         <v>-212164</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>C5-C11</f>
         <v>455670</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>D5-D11</f>
         <v>1308590</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>E5-E11</f>
         <v>2196369</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>F5-F11</f>
         <v>3114494</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B15" s="24">
+        <v>282</v>
+      </c>
+      <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.54675147</v>
       </c>
@@ -4457,101 +4467,101 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" s="25">
+        <v>312</v>
+      </c>
+      <c r="B5" s="26">
         <v>350000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>323655</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>295685</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>265989</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>234462</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B6" s="25">
+        <v>313</v>
+      </c>
+      <c r="B6" s="26">
         <v>20283</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>18658</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>16933</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>15102</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>13157</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B7" s="25">
+        <v>314</v>
+      </c>
+      <c r="B7" s="26">
         <v>26345</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>27970</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>29695</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>31527</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>33471</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B8" s="28">
+        <v>315</v>
+      </c>
+      <c r="B8" s="29">
         <v>46629</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <v>46629</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>46629</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>46629</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <v>46629</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B9" s="33">
+        <v>316</v>
+      </c>
+      <c r="B9" s="34">
         <v>323655</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>295685</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <v>265989</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <v>234462</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <v>200991</v>
       </c>
     </row>
@@ -4581,7 +4591,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4611,7 +4621,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4621,107 +4631,107 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B5" s="35">
+        <v>319</v>
+      </c>
+      <c r="B5" s="36">
         <v>74498</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="36">
         <v>530168</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="36">
         <v>1838758</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="36">
         <v>4035127</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="36">
         <v>7149621</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B6" s="25">
+        <v>320</v>
+      </c>
+      <c r="B6" s="26">
         <v>0</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>0</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>0</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>0</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B7" s="25">
+        <v>321</v>
+      </c>
+      <c r="B7" s="26">
         <v>0</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>0</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>0</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>0</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B8" s="25">
+        <v>322</v>
+      </c>
+      <c r="B8" s="26">
         <v>0</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>0</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>0</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B9" s="30">
+        <v>323</v>
+      </c>
+      <c r="B9" s="31">
         <v>74498</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>530168</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>1838758</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>4035127</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>7149621</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4731,67 +4741,67 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B12" s="25">
+        <v>325</v>
+      </c>
+      <c r="B12" s="26">
         <v>0</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <v>0</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <v>0</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>0</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B13" s="25">
+        <v>326</v>
+      </c>
+      <c r="B13" s="26">
         <v>323655</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>295685</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>265989</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>234462</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>200991</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B14" s="30">
+        <v>327</v>
+      </c>
+      <c r="B14" s="31">
         <v>323655</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>295685</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>265989</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>234462</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>200991</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4801,41 +4811,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B17" s="26">
+        <v>329</v>
+      </c>
+      <c r="B17" s="27">
         <v>-249157</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <v>234484</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <v>1572769</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>3800665</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <v>6948630</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B19" s="36">
+        <v>330</v>
+      </c>
+      <c r="B19" s="37">
         <v>0</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="38">
         <v>-1</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="37">
         <v>0</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="37">
         <v>0</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="37">
         <v>0</v>
       </c>
     </row>
@@ -4865,7 +4875,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4895,7 +4905,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4905,137 +4915,137 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B5" s="25">
+        <v>333</v>
+      </c>
+      <c r="B5" s="26">
         <v>1178333</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>2261600</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>3367965</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>4502532</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>5696361</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B6" s="25">
+        <v>300</v>
+      </c>
+      <c r="B6" s="26">
         <v>780535</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>964741</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>993683</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>1023494</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>1054199</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B7" s="25">
+        <v>301</v>
+      </c>
+      <c r="B7" s="26">
         <v>503333</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>774560</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>994063</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>1226040</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>1471040</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B8" s="28">
+        <v>334</v>
+      </c>
+      <c r="B8" s="29">
         <f>B5-B6-B7</f>
         <v>-105535</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>C5-C6-C7</f>
         <v>522299</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D5-D6-D7</f>
         <v>1380218</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E5-E6-E7</f>
         <v>2252998</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>F5-F6-F7</f>
         <v>3171123</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9" s="25">
+        <v>302</v>
+      </c>
+      <c r="B9" s="26">
         <v>46629</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>46629</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>46629</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>46629</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>46629</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B10" s="38">
+        <v>335</v>
+      </c>
+      <c r="B10" s="39">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-2.26</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="39">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>11.2</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="39">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>29.6</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="39">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>48.32</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="39">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>68.01</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5045,97 +5055,97 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B13" s="25">
+        <v>337</v>
+      </c>
+      <c r="B13" s="26">
         <v>74498</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>530168</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>1838758</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>4035127</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>7149621</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B14" s="22">
+        <v>338</v>
+      </c>
+      <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>20</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="23">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>108</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="23">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>330</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>641</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="23">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1015</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B15" s="29">
+        <v>339</v>
+      </c>
+      <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>0.7</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>3.6</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>10.8</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>21.1</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>33.4</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="24">
+        <v>197</v>
+      </c>
+      <c r="B16" s="25">
         <v>0.2</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>0.5</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5145,87 +5155,87 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B19" s="25">
+        <v>237</v>
+      </c>
+      <c r="B19" s="26">
         <v>9819</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <v>11308</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <v>11227</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <v>11256</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <v>11393</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B20" s="25">
+        <v>341</v>
+      </c>
+      <c r="B20" s="26">
         <v>827164</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <v>1011370</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <v>1040312</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <v>1070123</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <v>1100827</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B21" s="25">
+        <v>342</v>
+      </c>
+      <c r="B21" s="26">
         <v>4194</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <v>3873</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="26">
         <v>3314</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <v>3065</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="26">
         <v>2942</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B22" s="39">
+        <v>343</v>
+      </c>
+      <c r="B22" s="40">
         <v>148</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="40">
         <v>137</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="40">
         <v>132</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="40">
         <v>131</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="40">
         <v>131</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5235,102 +5245,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B25" s="40" t="s">
         <v>345</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="B25" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="D25" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="E25" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>346</v>
+      <c r="C25" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="C26" s="42" t="s">
         <v>347</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="D26" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="E26" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>346</v>
+      <c r="D26" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="B27" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>345</v>
+        <v>349</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="C28" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="B28" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="D28" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="E28" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="F28" s="41" t="s">
-        <v>346</v>
+      <c r="C28" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>345</v>
-      </c>
-      <c r="C29" s="41" t="s">
+        <v>351</v>
+      </c>
+      <c r="B29" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="D29" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="E29" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="F29" s="41" t="s">
-        <v>346</v>
+      <c r="C29" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="D29" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5370,16 +5380,16 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>351</v>
-      </c>
-      <c r="B3" s="42" t="s">
+      <c r="A3" s="43" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="42" t="s">
-        <v>352</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>353</v>
+      </c>
+      <c r="E3" s="43" t="s">
         <v>100</v>
       </c>
     </row>
@@ -5387,65 +5397,65 @@
       <c r="A4" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <v>350000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="E4" s="25">
+        <v>354</v>
+      </c>
+      <c r="E4" s="26">
         <v>250000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B5" s="25">
+        <v>355</v>
+      </c>
+      <c r="B5" s="26">
         <v>150000</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>60000</v>
       </c>
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="E6" s="25">
+        <v>356</v>
+      </c>
+      <c r="E6" s="26">
         <v>50000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="E7" s="25">
+        <v>357</v>
+      </c>
+      <c r="E7" s="26">
         <v>140000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B9" s="26">
+        <v>358</v>
+      </c>
+      <c r="B9" s="27">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="E9" s="26">
+        <v>359</v>
+      </c>
+      <c r="E9" s="27">
         <v>500000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B10" s="36">
+        <v>360</v>
+      </c>
+      <c r="B10" s="37">
         <v>0</v>
       </c>
     </row>
@@ -5611,7 +5621,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5621,7 +5631,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5631,7 +5641,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5656,127 +5666,127 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B6" s="25">
+        <v>333</v>
+      </c>
+      <c r="B6" s="26">
         <v>1178333</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>2261600</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>3367965</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>4502532</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>5696361</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B7" s="25">
+        <v>279</v>
+      </c>
+      <c r="B7" s="26">
         <v>1330497</v>
       </c>
-      <c r="C7" s="25">
-        <v>1786230</v>
-      </c>
-      <c r="D7" s="25">
-        <v>2034780</v>
-      </c>
-      <c r="E7" s="25">
-        <v>2296343</v>
-      </c>
-      <c r="F7" s="25">
-        <v>2572777</v>
+      <c r="C7" s="26">
+        <v>1785930</v>
+      </c>
+      <c r="D7" s="26">
+        <v>2034375</v>
+      </c>
+      <c r="E7" s="26">
+        <v>2296162</v>
+      </c>
+      <c r="F7" s="26">
+        <v>2571867</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B8" s="26">
+        <v>281</v>
+      </c>
+      <c r="B8" s="27">
         <v>-152164</v>
       </c>
-      <c r="C8" s="26">
-        <v>475370</v>
-      </c>
-      <c r="D8" s="26">
-        <v>1333185</v>
-      </c>
-      <c r="E8" s="26">
-        <v>2206189</v>
-      </c>
-      <c r="F8" s="26">
-        <v>3123585</v>
+      <c r="C8" s="27">
+        <v>475670</v>
+      </c>
+      <c r="D8" s="27">
+        <v>1333590</v>
+      </c>
+      <c r="E8" s="27">
+        <v>2206369</v>
+      </c>
+      <c r="F8" s="27">
+        <v>3124494</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B9" s="24">
+        <v>282</v>
+      </c>
+      <c r="B9" s="25">
         <v>-0.12913460606689658</v>
       </c>
-      <c r="C9" s="24">
-        <v>0.21019195666099513</v>
-      </c>
-      <c r="D9" s="24">
-        <v>0.3958429768078072</v>
-      </c>
-      <c r="E9" s="24">
-        <v>0.4899885700301692</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.5483473475657772</v>
+      <c r="C9" s="25">
+        <v>0.21032460611271073</v>
+      </c>
+      <c r="D9" s="25">
+        <v>0.39596301962297903</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0.49002859951113986</v>
+      </c>
+      <c r="F9" s="25">
+        <v>0.5485069777397931</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B10" s="43">
+        <v>335</v>
+      </c>
+      <c r="B10" s="44">
         <v>-2.26</v>
       </c>
-      <c r="C10" s="43">
-        <v>11.19</v>
-      </c>
-      <c r="D10" s="43">
-        <v>29.59</v>
-      </c>
-      <c r="E10" s="43">
-        <v>48.31</v>
-      </c>
-      <c r="F10" s="43">
-        <v>67.99</v>
+      <c r="C10" s="44">
+        <v>11.2</v>
+      </c>
+      <c r="D10" s="44">
+        <v>29.6</v>
+      </c>
+      <c r="E10" s="44">
+        <v>48.32</v>
+      </c>
+      <c r="F10" s="44">
+        <v>68.01</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B11" s="22">
+        <v>343</v>
+      </c>
+      <c r="B11" s="23">
         <v>148</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <v>137</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <v>132</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <v>131</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <v>131</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5786,7 +5796,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5811,127 +5821,127 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B16" s="25">
+        <v>333</v>
+      </c>
+      <c r="B16" s="26">
         <v>1001583</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>1922360</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>2862770</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>3827152</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>4841907</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B17" s="25">
+        <v>279</v>
+      </c>
+      <c r="B17" s="26">
         <v>1330497</v>
       </c>
-      <c r="C17" s="25">
-        <v>1786230</v>
-      </c>
-      <c r="D17" s="25">
-        <v>2034780</v>
-      </c>
-      <c r="E17" s="25">
-        <v>2296343</v>
-      </c>
-      <c r="F17" s="25">
-        <v>2572777</v>
+      <c r="C17" s="26">
+        <v>1785930</v>
+      </c>
+      <c r="D17" s="26">
+        <v>2034375</v>
+      </c>
+      <c r="E17" s="26">
+        <v>2296162</v>
+      </c>
+      <c r="F17" s="26">
+        <v>2571867</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B18" s="26">
+        <v>281</v>
+      </c>
+      <c r="B18" s="27">
         <v>-328914</v>
       </c>
-      <c r="C18" s="26">
-        <v>136130</v>
-      </c>
-      <c r="D18" s="26">
-        <v>827991</v>
-      </c>
-      <c r="E18" s="26">
-        <v>1530809</v>
-      </c>
-      <c r="F18" s="26">
-        <v>2269130</v>
+      <c r="C18" s="27">
+        <v>136430</v>
+      </c>
+      <c r="D18" s="27">
+        <v>828395</v>
+      </c>
+      <c r="E18" s="27">
+        <v>1530989</v>
+      </c>
+      <c r="F18" s="27">
+        <v>2270040</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B19" s="24">
+        <v>282</v>
+      </c>
+      <c r="B19" s="25">
         <v>-0.32839365419634886</v>
       </c>
-      <c r="C19" s="24">
-        <v>0.07081406665999428</v>
-      </c>
-      <c r="D19" s="24">
-        <v>0.28922703153859675</v>
-      </c>
-      <c r="E19" s="24">
-        <v>0.39998655297666963</v>
-      </c>
-      <c r="F19" s="24">
-        <v>0.468643938312679</v>
+      <c r="C19" s="25">
+        <v>0.07097012483848322</v>
+      </c>
+      <c r="D19" s="25">
+        <v>0.2893682583799753</v>
+      </c>
+      <c r="E19" s="25">
+        <v>0.40003364648369394</v>
+      </c>
+      <c r="F19" s="25">
+        <v>0.46883173851740356</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B20" s="43">
+        <v>335</v>
+      </c>
+      <c r="B20" s="44">
         <v>-6.05</v>
       </c>
-      <c r="C20" s="43">
-        <v>3.92</v>
-      </c>
-      <c r="D20" s="43">
-        <v>18.76</v>
-      </c>
-      <c r="E20" s="43">
+      <c r="C20" s="44">
+        <v>3.93</v>
+      </c>
+      <c r="D20" s="44">
+        <v>18.77</v>
+      </c>
+      <c r="E20" s="44">
         <v>33.83</v>
       </c>
-      <c r="F20" s="43">
-        <v>49.66</v>
+      <c r="F20" s="44">
+        <v>49.68</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B21" s="22">
+        <v>343</v>
+      </c>
+      <c r="B21" s="23">
         <v>170</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <v>150</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <v>142</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <v>140</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="23">
         <v>139</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5941,7 +5951,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5966,121 +5976,121 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B26" s="25">
+        <v>333</v>
+      </c>
+      <c r="B26" s="26">
         <v>1084067</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <v>2080672</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="26">
         <v>3098528</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="26">
         <v>4142329</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="26">
         <v>5240653</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B27" s="25">
+        <v>279</v>
+      </c>
+      <c r="B27" s="26">
         <v>1330497</v>
       </c>
-      <c r="C27" s="25">
-        <v>1786230</v>
-      </c>
-      <c r="D27" s="25">
-        <v>2034780</v>
-      </c>
-      <c r="E27" s="25">
-        <v>2296343</v>
-      </c>
-      <c r="F27" s="25">
-        <v>2572777</v>
+      <c r="C27" s="26">
+        <v>1785930</v>
+      </c>
+      <c r="D27" s="26">
+        <v>2034375</v>
+      </c>
+      <c r="E27" s="26">
+        <v>2296162</v>
+      </c>
+      <c r="F27" s="26">
+        <v>2571867</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B28" s="26">
+        <v>281</v>
+      </c>
+      <c r="B28" s="27">
         <v>-246430</v>
       </c>
-      <c r="C28" s="26">
-        <v>294442</v>
-      </c>
-      <c r="D28" s="26">
-        <v>1063748</v>
-      </c>
-      <c r="E28" s="26">
-        <v>1845986</v>
-      </c>
-      <c r="F28" s="26">
-        <v>2667876</v>
+      <c r="C28" s="27">
+        <v>294742</v>
+      </c>
+      <c r="D28" s="27">
+        <v>1064152</v>
+      </c>
+      <c r="E28" s="27">
+        <v>1846167</v>
+      </c>
+      <c r="F28" s="27">
+        <v>2668785</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B29" s="24">
+        <v>282</v>
+      </c>
+      <c r="B29" s="25">
         <v>-0.2273202239857572</v>
       </c>
-      <c r="C29" s="24">
-        <v>0.14151299637064688</v>
-      </c>
-      <c r="D29" s="24">
-        <v>0.34330758348674706</v>
-      </c>
-      <c r="E29" s="24">
-        <v>0.44563975003279266</v>
-      </c>
-      <c r="F29" s="24">
-        <v>0.5090732038758448</v>
+      <c r="C29" s="25">
+        <v>0.1416571805572943</v>
+      </c>
+      <c r="D29" s="25">
+        <v>0.34343806480758593</v>
+      </c>
+      <c r="E29" s="25">
+        <v>0.4456832603381955</v>
+      </c>
+      <c r="F29" s="25">
+        <v>0.5092467149345576</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B30" s="43">
+        <v>335</v>
+      </c>
+      <c r="B30" s="44">
         <v>-4.28</v>
       </c>
-      <c r="C30" s="43">
-        <v>7.31</v>
-      </c>
-      <c r="D30" s="43">
-        <v>23.81</v>
-      </c>
-      <c r="E30" s="43">
+      <c r="C30" s="44">
+        <v>7.32</v>
+      </c>
+      <c r="D30" s="44">
+        <v>23.82</v>
+      </c>
+      <c r="E30" s="44">
         <v>40.59</v>
       </c>
-      <c r="F30" s="43">
-        <v>58.22</v>
+      <c r="F30" s="44">
+        <v>58.23</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B31" s="22">
+        <v>343</v>
+      </c>
+      <c r="B31" s="23">
         <v>171</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <v>155</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <v>149</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>147</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <v>147</v>
       </c>
     </row>
@@ -6112,7 +6122,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6146,7 +6156,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6170,7 +6180,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6178,7 +6188,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6198,125 +6208,125 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="45" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="D13" s="25">
+        <v>333</v>
+      </c>
+      <c r="D13" s="26">
         <v>1178333</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>2261600</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>3367965</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <v>4502532</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="26">
         <v>5696361</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" s="25">
+        <v>279</v>
+      </c>
+      <c r="D14" s="26">
         <v>1330497</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>1785930</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>2034375</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="26">
         <v>2296162</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="26">
         <v>2571867</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D15" s="25">
+        <v>281</v>
+      </c>
+      <c r="D15" s="26">
         <v>-212164</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <v>455670</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <v>1308590</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="26">
         <v>2196369</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="26">
         <v>3114494</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="D16" s="25">
+        <v>372</v>
+      </c>
+      <c r="D16" s="26">
         <v>74498</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>530168</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>1838758</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="26">
         <v>4035127</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="26">
         <v>7149621</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="D17" s="25">
+        <v>373</v>
+      </c>
+      <c r="D17" s="26">
         <v>323655</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>295685</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>265989</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <v>234462</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>200991</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6336,105 +6346,105 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="45" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D21" s="24">
+        <v>375</v>
+      </c>
+      <c r="D21" s="25">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>0.20148130933167066</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>0.38854013963461814</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="25">
         <v>0.48780762672183775</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="25">
         <v>0.54675147116204</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="D22" s="43">
+        <v>335</v>
+      </c>
+      <c r="D22" s="44">
         <v>-2.26</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="44">
         <v>11.2</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="44">
         <v>29.6</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <v>48.32</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="44">
         <v>68.01</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D23" s="24">
+        <v>197</v>
+      </c>
+      <c r="D23" s="25">
         <v>0.2</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="25">
         <v>0.5</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D24" s="22">
+        <v>376</v>
+      </c>
+      <c r="D24" s="23">
         <v>120</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <v>200</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="23">
         <v>300</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="23">
         <v>400</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="23">
         <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7199,25 +7209,31 @@
       <c r="F55" s="13"/>
       <c r="G55" s="13"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>156</v>
       </c>
       <c r="B56" s="18">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56" s="20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B57" s="18">
         <v>0.03</v>
       </c>
+      <c r="C57" s="20" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B58" s="19">
         <v>0.8333333333333334</v>
@@ -7225,7 +7241,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B59" s="17">
         <v>0</v>
@@ -7233,15 +7249,15 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -7252,15 +7268,15 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>135</v>
@@ -7268,7 +7284,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B65" s="16">
         <v>0</v>
@@ -7276,7 +7292,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B66" s="16">
         <v>0</v>
@@ -7284,29 +7300,29 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B67" s="20">
+        <v>169</v>
+      </c>
+      <c r="B67" s="21">
         <v>0.95</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B70" s="17">
         <v>8200</v>
@@ -7320,7 +7336,7 @@
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>90</v>
@@ -7340,7 +7356,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B73" s="16">
         <v>80</v>
@@ -7360,7 +7376,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B74" s="16">
         <v>40</v>
@@ -7380,7 +7396,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B75" s="16">
         <v>0</v>
@@ -7430,10 +7446,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7454,10 +7470,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7470,7 +7486,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7481,31 +7497,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7513,31 +7529,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -7597,7 +7613,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7609,19 +7625,19 @@
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="22">
         <v>120</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <v>200</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="22">
         <v>300</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="22">
         <v>400</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <v>500</v>
       </c>
     </row>
@@ -7629,47 +7645,47 @@
       <c r="A7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="23">
         <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="B8" s="23">
+        <v>197</v>
+      </c>
+      <c r="B8" s="24">
         <v>0.2</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
         <v>0.5</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="24">
+        <v>199</v>
+      </c>
+      <c r="C10" s="25">
         <v>0.6666666666666666</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="25">
         <v>0.5</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>0.25</v>
       </c>
     </row>
@@ -7699,7 +7715,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7729,7 +7745,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7739,145 +7755,145 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B5" s="25">
+        <v>202</v>
+      </c>
+      <c r="B5" s="26">
         <v>969000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>1617850</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>2466200</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>3327850</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>4233200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B6" s="25">
+        <v>203</v>
+      </c>
+      <c r="B6" s="26">
         <v>90000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>154500</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>238703</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>327818</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>422066</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="25">
+        <v>204</v>
+      </c>
+      <c r="B7" s="26">
         <v>132000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>226600</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>350097</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>480800</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>619030</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B8" s="25">
+        <v>205</v>
+      </c>
+      <c r="B8" s="26">
         <v>150000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>154500</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>159135</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>163909</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>168826</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="25">
+        <v>206</v>
+      </c>
+      <c r="B9" s="26">
         <v>25000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>25750</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>26523</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>27318</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>28138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B10" s="25">
+        <v>207</v>
+      </c>
+      <c r="B10" s="26">
         <v>48000</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>82400</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>127308</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>174836</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>225102</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="26">
+        <v>208</v>
+      </c>
+      <c r="B11" s="27">
         <f>SUM(B5:B10)</f>
         <v>1414000</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
@@ -7932,7 +7948,7 @@
         <v>116</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>118</v>
@@ -7941,7 +7957,7 @@
         <v>119</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7951,19 +7967,19 @@
       <c r="B4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="28">
         <v>1</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <v>105000</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="25">
         <v>0.26</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="29">
         <v>140333</v>
       </c>
     </row>
@@ -7974,19 +7990,19 @@
       <c r="B5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <v>1</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>82000</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>0.26</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <v>109593</v>
       </c>
     </row>
@@ -7997,19 +8013,19 @@
       <c r="B6" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <v>5</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>50000</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>0.26</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="29">
         <v>334125</v>
       </c>
     </row>
@@ -8020,19 +8036,19 @@
       <c r="B7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <v>1</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>53000</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>0.26</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="29">
         <v>70835</v>
       </c>
     </row>
@@ -8043,19 +8059,19 @@
       <c r="B8" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>3</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>28000</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>0.18</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <v>105546</v>
       </c>
     </row>
@@ -8066,19 +8082,19 @@
       <c r="B9" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <v>1</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>62000</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>0.26</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <v>82863</v>
       </c>
     </row>
@@ -8089,25 +8105,25 @@
       <c r="B10" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <v>2</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>36000</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <v>0.22</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <v>93348</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -8138,61 +8154,61 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="26">
+        <v>212</v>
+      </c>
+      <c r="B14" s="27">
         <v>780535</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <v>964741</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <v>993683</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <v>1023494</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <v>1054199</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B15" s="24">
+        <v>213</v>
+      </c>
+      <c r="B15" s="25">
         <v>0.5520049504950495</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <v>0.4265746639547223</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <v>0.29503973402336425</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <v>0.22731523300861284</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <v>0.18506529677129674</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B16" s="29">
+        <v>214</v>
+      </c>
+      <c r="B16" s="30">
         <v>8.6</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>14.3</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>21.4</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>28.6</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>35.7</v>
       </c>
     </row>
@@ -8222,7 +8238,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8262,45 +8278,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="25">
+        <v>216</v>
+      </c>
+      <c r="B5" s="26">
         <v>78000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>133900</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>206875</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>284109</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>365790</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B6" s="30">
+        <v>217</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
         <v>78000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>SUM(C5:C5)</f>
         <v>133900</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>SUM(D5:D5)</f>
         <v>206875</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>SUM(E5:E5)</f>
         <v>284109</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>SUM(F5:F5)</f>
         <v>365790</v>
       </c>
@@ -8317,45 +8333,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B8" s="25">
+        <v>218</v>
+      </c>
+      <c r="B8" s="26">
         <v>54000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>92700</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>143222</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>196691</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>253239</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="30">
+        <v>219</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>54000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>92700</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>143222</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>196691</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>253239</v>
       </c>
@@ -8372,85 +8388,85 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B11" s="25">
+        <v>220</v>
+      </c>
+      <c r="B11" s="26">
         <v>264000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>271920</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>280078</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>288480</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>297134</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="25">
+        <v>221</v>
+      </c>
+      <c r="B12" s="26">
         <v>36000</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <v>37080</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <v>38192</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>39338</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <v>40518</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="25">
+        <v>222</v>
+      </c>
+      <c r="B13" s="26">
         <v>22000</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>22660</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>23340</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>24040</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>24761</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="30">
+        <v>223</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B11:B13)</f>
         <v>322000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C11:C13)</f>
         <v>331660</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D11:D13)</f>
         <v>341610</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E11:E13)</f>
         <v>351858</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F11:F13)</f>
         <v>362414</v>
       </c>
@@ -8467,130 +8483,130 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B16" s="25">
+        <v>224</v>
+      </c>
+      <c r="B16" s="26">
         <v>30000</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>30900</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>31827</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>32782</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>33765</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B17" s="25">
+        <v>225</v>
+      </c>
+      <c r="B17" s="26">
         <v>12000</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>12360</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>12731</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>13113</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>13506</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B18" s="25">
+        <v>226</v>
+      </c>
+      <c r="B18" s="26">
         <v>18000</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <v>18540</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <v>19096</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <v>19669</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <v>20259</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B19" s="25">
+        <v>227</v>
+      </c>
+      <c r="B19" s="26">
         <v>90000</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <v>154500</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <v>238703</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <v>327818</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <v>422066</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B20" s="30">
+        <v>228</v>
+      </c>
+      <c r="B20" s="31">
         <f>SUM(B16:B19)</f>
         <v>150000</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <f>SUM(C16:C19)</f>
         <v>216300</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <f>SUM(D16:D19)</f>
         <v>302357</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <f>SUM(E16:E19)</f>
         <v>393382</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <f>SUM(F16:F19)</f>
         <v>489596</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="B22" s="26">
+        <v>229</v>
+      </c>
+      <c r="B22" s="27">
         <f>B6+B9+B14+B20</f>
         <v>604000</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>C6+C9+C14+C20</f>
         <v>774560</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>D6+D9+D14+D20</f>
         <v>994063</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>E6+E9+E14+E20</f>
         <v>1226040</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>F6+F9+F14+F20</f>
         <v>1471040</v>
       </c>
@@ -8622,7 +8638,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8647,7 +8663,7 @@
         <v>150</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8660,13 +8676,13 @@
       <c r="C4" s="17">
         <v>350000</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="25">
         <v>0.06</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="23">
         <v>10</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <v>46629</v>
       </c>
     </row>
@@ -8675,34 +8691,34 @@
         <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C5" s="17">
         <v>60000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>0</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="23">
         <v>0</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <v>60000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="26">
+        <v>233</v>
+      </c>
+      <c r="F7" s="27">
         <v>46629</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F8" s="30">
+        <v>234</v>
+      </c>
+      <c r="F8" s="31">
         <v>350000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="379">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -504,10 +504,13 @@
     <t>Salary Escalation Rate</t>
   </si>
   <si>
-    <t>Derived from tuition escalation rate</t>
+    <t>Salary input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
+  </si>
+  <si>
+    <t>Cost inflation input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Year 1 Proration Factor</t>
@@ -2057,7 +2060,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2107,7 +2110,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2237,7 +2240,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B13" s="27">
         <f>SUM(B7:B12)</f>
@@ -2262,7 +2265,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B15" s="26">
         <v>11783</v>
@@ -2306,7 +2309,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2346,7 +2349,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B5" s="26">
         <v>278438</v>
@@ -2366,7 +2369,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B6" s="26">
         <v>59029</v>
@@ -2386,7 +2389,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B7" s="26">
         <v>87955</v>
@@ -2406,7 +2409,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -2441,7 +2444,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B10" s="26">
         <v>116944</v>
@@ -2461,7 +2464,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B11" s="26">
         <v>91328</v>
@@ -2481,7 +2484,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B10:B11)</f>
@@ -2516,7 +2519,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B14" s="26">
         <v>69053</v>
@@ -2536,7 +2539,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B14:B14)</f>
@@ -2571,7 +2574,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B17" s="26">
         <v>77790</v>
@@ -2591,7 +2594,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B18" s="31">
         <f>SUM(B17:B17)</f>
@@ -2616,7 +2619,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B20" s="27">
         <f>B8+B12+B15+B18</f>
@@ -2665,7 +2668,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2695,7 +2698,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2705,7 +2708,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B5" s="26">
         <v>807500</v>
@@ -2725,7 +2728,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B6" s="26">
         <v>75000</v>
@@ -2745,7 +2748,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B7" s="26">
         <v>110000</v>
@@ -2765,7 +2768,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B8" s="26">
         <v>125000</v>
@@ -2785,7 +2788,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B9" s="26">
         <v>20833</v>
@@ -2805,7 +2808,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B10" s="26">
         <v>40000</v>
@@ -2825,7 +2828,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
@@ -2850,7 +2853,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2860,7 +2863,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B14" s="26">
         <v>116944</v>
@@ -2880,7 +2883,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B15" s="26">
         <v>91328</v>
@@ -2900,7 +2903,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="26">
         <v>278438</v>
@@ -2920,7 +2923,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="26">
         <v>59029</v>
@@ -2940,7 +2943,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="26">
         <v>87955</v>
@@ -2960,7 +2963,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B19" s="26">
         <v>69053</v>
@@ -2980,7 +2983,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B20" s="26">
         <v>77790</v>
@@ -3000,7 +3003,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B14:B20)</f>
@@ -3040,7 +3043,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B25" s="26">
         <v>65000</v>
@@ -3065,7 +3068,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" s="26">
         <v>45000</v>
@@ -3090,7 +3093,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B29" s="26">
         <v>220000</v>
@@ -3110,7 +3113,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B30" s="26">
         <v>30000</v>
@@ -3130,7 +3133,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" s="26">
         <v>18333</v>
@@ -3150,7 +3153,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" s="31">
         <f>SUM(B29:B31)</f>
@@ -3180,7 +3183,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" s="26">
         <v>25000</v>
@@ -3200,7 +3203,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B35" s="26">
         <v>10000</v>
@@ -3220,7 +3223,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B36" s="26">
         <v>15000</v>
@@ -3240,7 +3243,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B37" s="26">
         <v>75000</v>
@@ -3260,7 +3263,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B38" s="31">
         <f>SUM(B34:B37)</f>
@@ -3285,7 +3288,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B39" s="31">
         <f>B25+B27+B32+B38</f>
@@ -3310,7 +3313,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3320,7 +3323,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B42" s="26">
         <v>46629</v>
@@ -3340,7 +3343,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B43" s="26">
         <v>60000</v>
@@ -3360,7 +3363,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
@@ -3409,7 +3412,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3439,7 +3442,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B4" s="29">
         <f>'Budget Detail'!B11</f>
@@ -3464,7 +3467,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
@@ -3489,7 +3492,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
@@ -3514,7 +3517,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
@@ -3539,7 +3542,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3564,7 +3567,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3574,7 +3577,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B11" s="27">
         <f>B4-B8</f>
@@ -3599,7 +3602,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3624,7 +3627,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B13" s="26">
         <v>-212164</v>
@@ -3644,7 +3647,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="26">
         <v>9819</v>
@@ -3664,7 +3667,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B15" s="26">
         <v>11587</v>
@@ -3709,7 +3712,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3730,48 +3733,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3789,7 +3792,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B4" s="31">
         <v>146500</v>
@@ -3833,7 +3836,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3851,7 +3854,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B7" s="26">
         <v>78054</v>
@@ -3895,7 +3898,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B8" s="26">
         <v>50333</v>
@@ -3939,7 +3942,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B9" s="26">
         <v>8886</v>
@@ -3983,7 +3986,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4001,7 +4004,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B12" s="29">
         <v>137273</v>
@@ -4045,7 +4048,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B13" s="29">
         <v>9227</v>
@@ -4089,7 +4092,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B14" s="34">
         <v>9227</v>
@@ -4133,14 +4136,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" s="26">
         <v>0</v>
@@ -4148,7 +4151,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B18" s="34">
         <v>74498</v>
@@ -4156,7 +4159,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B19" s="26">
         <v>9227</v>
@@ -4188,7 +4191,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4218,7 +4221,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4228,7 +4231,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B5" s="31">
         <v>1178333</v>
@@ -4248,7 +4251,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4258,7 +4261,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B8" s="29">
         <v>780535</v>
@@ -4278,7 +4281,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B9" s="29">
         <v>503333</v>
@@ -4298,7 +4301,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B10" s="29">
         <v>106629</v>
@@ -4318,7 +4321,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
@@ -4343,7 +4346,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4353,7 +4356,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B14" s="27">
         <f>B5-B11</f>
@@ -4378,7 +4381,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4467,7 +4470,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B5" s="26">
         <v>350000</v>
@@ -4487,7 +4490,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="26">
         <v>20283</v>
@@ -4507,7 +4510,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B7" s="26">
         <v>26345</v>
@@ -4527,7 +4530,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B8" s="29">
         <v>46629</v>
@@ -4547,7 +4550,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B9" s="34">
         <v>323655</v>
@@ -4591,7 +4594,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4621,7 +4624,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4631,7 +4634,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B5" s="36">
         <v>74498</v>
@@ -4651,7 +4654,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B6" s="26">
         <v>0</v>
@@ -4671,7 +4674,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B7" s="26">
         <v>0</v>
@@ -4691,7 +4694,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B8" s="26">
         <v>0</v>
@@ -4711,7 +4714,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B9" s="31">
         <v>74498</v>
@@ -4731,7 +4734,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4741,7 +4744,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B12" s="26">
         <v>0</v>
@@ -4761,7 +4764,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B13" s="26">
         <v>323655</v>
@@ -4781,7 +4784,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B14" s="31">
         <v>323655</v>
@@ -4801,7 +4804,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4811,7 +4814,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B17" s="27">
         <v>-249157</v>
@@ -4831,7 +4834,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B19" s="37">
         <v>0</v>
@@ -4875,7 +4878,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4905,7 +4908,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4915,7 +4918,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B5" s="26">
         <v>1178333</v>
@@ -4935,7 +4938,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B6" s="26">
         <v>780535</v>
@@ -4955,7 +4958,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B7" s="26">
         <v>503333</v>
@@ -4975,7 +4978,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B8" s="29">
         <f>B5-B6-B7</f>
@@ -5000,7 +5003,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B9" s="26">
         <v>46629</v>
@@ -5020,7 +5023,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B10" s="39">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5045,7 +5048,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5055,7 +5058,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B13" s="26">
         <v>74498</v>
@@ -5075,7 +5078,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5100,7 +5103,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5125,7 +5128,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" s="25">
         <v>0.2</v>
@@ -5145,7 +5148,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5155,7 +5158,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B19" s="26">
         <v>9819</v>
@@ -5175,7 +5178,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B20" s="26">
         <v>827164</v>
@@ -5195,7 +5198,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B21" s="26">
         <v>4194</v>
@@ -5215,7 +5218,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B22" s="40">
         <v>148</v>
@@ -5235,7 +5238,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5245,102 +5248,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B25" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="42" t="s">
         <v>348</v>
       </c>
-      <c r="B26" s="41" t="s">
-        <v>346</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>347</v>
-      </c>
       <c r="D26" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -5381,13 +5384,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>100</v>
@@ -5401,7 +5404,7 @@
         <v>350000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E4" s="26">
         <v>250000</v>
@@ -5409,7 +5412,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B5" s="26">
         <v>150000</v>
@@ -5423,7 +5426,7 @@
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E6" s="26">
         <v>50000</v>
@@ -5431,7 +5434,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E7" s="26">
         <v>140000</v>
@@ -5439,13 +5442,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B9" s="27">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E9" s="27">
         <v>500000</v>
@@ -5453,7 +5456,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B10" s="37">
         <v>0</v>
@@ -5621,7 +5624,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5631,7 +5634,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5641,7 +5644,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5666,7 +5669,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B6" s="26">
         <v>1178333</v>
@@ -5686,7 +5689,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B7" s="26">
         <v>1330497</v>
@@ -5706,7 +5709,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B8" s="27">
         <v>-152164</v>
@@ -5726,7 +5729,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B9" s="25">
         <v>-0.12913460606689658</v>
@@ -5746,7 +5749,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B10" s="44">
         <v>-2.26</v>
@@ -5766,7 +5769,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B11" s="23">
         <v>148</v>
@@ -5786,7 +5789,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5796,7 +5799,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5821,7 +5824,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B16" s="26">
         <v>1001583</v>
@@ -5841,7 +5844,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B17" s="26">
         <v>1330497</v>
@@ -5861,7 +5864,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B18" s="27">
         <v>-328914</v>
@@ -5881,7 +5884,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B19" s="25">
         <v>-0.32839365419634886</v>
@@ -5901,7 +5904,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B20" s="44">
         <v>-6.05</v>
@@ -5921,7 +5924,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B21" s="23">
         <v>170</v>
@@ -5941,7 +5944,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5951,7 +5954,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5976,7 +5979,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B26" s="26">
         <v>1084067</v>
@@ -5996,7 +5999,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B27" s="26">
         <v>1330497</v>
@@ -6016,7 +6019,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" s="27">
         <v>-246430</v>
@@ -6036,7 +6039,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B29" s="25">
         <v>-0.2273202239857572</v>
@@ -6056,7 +6059,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B30" s="44">
         <v>-4.28</v>
@@ -6076,7 +6079,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B31" s="23">
         <v>171</v>
@@ -6122,7 +6125,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6156,7 +6159,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6180,7 +6183,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6188,7 +6191,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6226,7 +6229,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D13" s="26">
         <v>1178333</v>
@@ -6246,7 +6249,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D14" s="26">
         <v>1330497</v>
@@ -6266,7 +6269,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D15" s="26">
         <v>-212164</v>
@@ -6286,7 +6289,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D16" s="26">
         <v>74498</v>
@@ -6306,7 +6309,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D17" s="26">
         <v>323655</v>
@@ -6326,7 +6329,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6364,7 +6367,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D21" s="25">
         <v>-0.18005398371894768</v>
@@ -6384,7 +6387,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D22" s="44">
         <v>-2.26</v>
@@ -6404,7 +6407,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D23" s="25">
         <v>0.2</v>
@@ -6424,7 +6427,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D24" s="23">
         <v>120</v>
@@ -6444,7 +6447,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7228,12 +7231,12 @@
         <v>0.03</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B58" s="19">
         <v>0.8333333333333334</v>
@@ -7241,7 +7244,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B59" s="17">
         <v>0</v>
@@ -7249,15 +7252,15 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -7268,15 +7271,15 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>135</v>
@@ -7284,7 +7287,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B65" s="16">
         <v>0</v>
@@ -7292,7 +7295,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B66" s="16">
         <v>0</v>
@@ -7300,7 +7303,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B67" s="21">
         <v>0.95</v>
@@ -7308,21 +7311,21 @@
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B70" s="17">
         <v>8200</v>
@@ -7336,7 +7339,7 @@
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B72" s="15" t="s">
         <v>90</v>
@@ -7356,7 +7359,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B73" s="16">
         <v>80</v>
@@ -7376,7 +7379,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B74" s="16">
         <v>40</v>
@@ -7396,7 +7399,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B75" s="16">
         <v>0</v>
@@ -7446,10 +7449,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7470,10 +7473,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7486,7 +7489,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7497,31 +7500,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7529,31 +7532,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -7613,7 +7616,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7651,7 +7654,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B8" s="24">
         <v>0.2</v>
@@ -7671,10 +7674,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C10" s="25">
         <v>0.6666666666666666</v>
@@ -7715,7 +7718,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7745,7 +7748,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7755,7 +7758,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B5" s="26">
         <v>969000</v>
@@ -7775,7 +7778,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B6" s="26">
         <v>90000</v>
@@ -7795,7 +7798,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B7" s="26">
         <v>132000</v>
@@ -7815,7 +7818,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B8" s="26">
         <v>150000</v>
@@ -7835,7 +7838,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B9" s="26">
         <v>25000</v>
@@ -7855,7 +7858,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B10" s="26">
         <v>48000</v>
@@ -7875,7 +7878,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B11" s="27">
         <f>SUM(B5:B10)</f>
@@ -7948,7 +7951,7 @@
         <v>116</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>118</v>
@@ -7957,7 +7960,7 @@
         <v>119</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -8123,7 +8126,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -8154,7 +8157,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B14" s="27">
         <v>780535</v>
@@ -8174,7 +8177,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B15" s="25">
         <v>0.5520049504950495</v>
@@ -8194,7 +8197,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B16" s="30">
         <v>8.6</v>
@@ -8238,7 +8241,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8278,7 +8281,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B5" s="26">
         <v>78000</v>
@@ -8298,7 +8301,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -8333,7 +8336,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B8" s="26">
         <v>54000</v>
@@ -8353,7 +8356,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -8388,7 +8391,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B11" s="26">
         <v>264000</v>
@@ -8408,7 +8411,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B12" s="26">
         <v>36000</v>
@@ -8428,7 +8431,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B13" s="26">
         <v>22000</v>
@@ -8448,7 +8451,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B11:B13)</f>
@@ -8483,7 +8486,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B16" s="26">
         <v>30000</v>
@@ -8503,7 +8506,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B17" s="26">
         <v>12000</v>
@@ -8523,7 +8526,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B18" s="26">
         <v>18000</v>
@@ -8543,7 +8546,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B19" s="26">
         <v>90000</v>
@@ -8563,7 +8566,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" s="31">
         <f>SUM(B16:B19)</f>
@@ -8588,7 +8591,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B22" s="27">
         <f>B6+B9+B14+B20</f>
@@ -8638,7 +8641,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8663,7 +8666,7 @@
         <v>150</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8691,7 +8694,7 @@
         <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C5" s="17">
         <v>60000</v>
@@ -8708,7 +8711,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F7" s="27">
         <v>46629</v>
@@ -8716,7 +8719,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F8" s="31">
         <v>350000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -26,7 +26,7 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>Stage</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="390">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -222,13 +222,13 @@
     <t>How to Use This Workbook</t>
   </si>
   <si>
-    <t>Color Legend</t>
-  </si>
-  <si>
-    <t>Yellow cells are editable inputs - change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas - do not edit.</t>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Yellow cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -258,6 +258,24 @@
     <t>Tabs 18-21: Analysis &amp; underwriting</t>
   </si>
   <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
+  </si>
+  <si>
+    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
+  </si>
+  <si>
+    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+  </si>
+  <si>
     <t>Tips</t>
   </si>
   <si>
@@ -970,6 +988,21 @@
   </si>
   <si>
     <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>LOAN TERMS</t>
+  </si>
+  <si>
+    <t>Loan Name</t>
+  </si>
+  <si>
+    <t>Annual Rate</t>
+  </si>
+  <si>
+    <t>Term (Years)</t>
+  </si>
+  <si>
+    <t>AMORTIZATION: Startup Loan</t>
   </si>
   <si>
     <t>Beginning Balance</t>
@@ -1341,7 +1374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1386,6 +1419,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2060,7 +2096,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2073,24 +2109,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B4" s="32">
         <v>120</v>
@@ -2110,7 +2146,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2120,7 +2156,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B7" s="26">
         <v>969000</v>
@@ -2140,7 +2176,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B8" s="26">
         <v>90000</v>
@@ -2160,7 +2196,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" s="26">
         <v>132000</v>
@@ -2180,7 +2216,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B10" s="26">
         <v>150000</v>
@@ -2200,7 +2236,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B11" s="26">
         <v>25000</v>
@@ -2220,7 +2256,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B12" s="26">
         <v>48000</v>
@@ -2240,7 +2276,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B13" s="27">
         <f>SUM(B7:B12)</f>
@@ -2265,7 +2301,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B15" s="26">
         <v>11783</v>
@@ -2309,7 +2345,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2322,24 +2358,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2349,7 +2385,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B5" s="26">
         <v>278438</v>
@@ -2369,7 +2405,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B6" s="26">
         <v>59029</v>
@@ -2389,7 +2425,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B7" s="26">
         <v>87955</v>
@@ -2409,7 +2445,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -2434,7 +2470,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2444,7 +2480,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B10" s="26">
         <v>116944</v>
@@ -2464,7 +2500,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B11" s="26">
         <v>91328</v>
@@ -2484,7 +2520,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B10:B11)</f>
@@ -2509,7 +2545,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2519,7 +2555,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B14" s="26">
         <v>69053</v>
@@ -2539,7 +2575,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B14:B14)</f>
@@ -2564,7 +2600,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2574,7 +2610,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B17" s="26">
         <v>77790</v>
@@ -2594,7 +2630,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B18" s="31">
         <f>SUM(B17:B17)</f>
@@ -2619,7 +2655,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B20" s="27">
         <f>B8+B12+B15+B18</f>
@@ -2668,7 +2704,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2681,24 +2717,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2708,7 +2744,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B5" s="26">
         <v>807500</v>
@@ -2728,7 +2764,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B6" s="26">
         <v>75000</v>
@@ -2748,7 +2784,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B7" s="26">
         <v>110000</v>
@@ -2768,7 +2804,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B8" s="26">
         <v>125000</v>
@@ -2788,7 +2824,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B9" s="26">
         <v>20833</v>
@@ -2808,7 +2844,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B10" s="26">
         <v>40000</v>
@@ -2828,7 +2864,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
@@ -2853,7 +2889,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2863,7 +2899,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B14" s="26">
         <v>116944</v>
@@ -2883,7 +2919,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B15" s="26">
         <v>91328</v>
@@ -2903,7 +2939,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B16" s="26">
         <v>278438</v>
@@ -2923,7 +2959,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B17" s="26">
         <v>59029</v>
@@ -2943,7 +2979,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B18" s="26">
         <v>87955</v>
@@ -2963,7 +2999,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B19" s="26">
         <v>69053</v>
@@ -2983,7 +3019,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B20" s="26">
         <v>77790</v>
@@ -3003,7 +3039,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B14:B20)</f>
@@ -3028,7 +3064,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3038,12 +3074,12 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B25" s="26">
         <v>65000</v>
@@ -3063,12 +3099,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="33" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B27" s="26">
         <v>45000</v>
@@ -3088,12 +3124,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B29" s="26">
         <v>220000</v>
@@ -3113,7 +3149,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B30" s="26">
         <v>30000</v>
@@ -3133,7 +3169,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B31" s="26">
         <v>18333</v>
@@ -3153,7 +3189,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B32" s="31">
         <f>SUM(B29:B31)</f>
@@ -3178,12 +3214,12 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B34" s="26">
         <v>25000</v>
@@ -3203,7 +3239,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B35" s="26">
         <v>10000</v>
@@ -3223,7 +3259,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B36" s="26">
         <v>15000</v>
@@ -3243,7 +3279,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B37" s="26">
         <v>75000</v>
@@ -3263,7 +3299,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B38" s="31">
         <f>SUM(B34:B37)</f>
@@ -3288,7 +3324,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B39" s="31">
         <f>B25+B27+B32+B38</f>
@@ -3313,7 +3349,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3323,7 +3359,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B42" s="26">
         <v>46629</v>
@@ -3343,7 +3379,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B43" s="26">
         <v>60000</v>
@@ -3363,7 +3399,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
@@ -3412,7 +3448,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3425,24 +3461,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B4" s="29">
         <f>'Budget Detail'!B11</f>
@@ -3467,7 +3503,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
@@ -3492,7 +3528,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
@@ -3517,7 +3553,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
@@ -3542,7 +3578,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3567,7 +3603,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3577,7 +3613,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B11" s="27">
         <f>B4-B8</f>
@@ -3602,7 +3638,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3627,7 +3663,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B13" s="26">
         <v>-212164</v>
@@ -3647,7 +3683,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B14" s="26">
         <v>9819</v>
@@ -3667,7 +3703,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B15" s="26">
         <v>11587</v>
@@ -3712,7 +3748,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3733,48 +3769,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3792,7 +3828,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B4" s="31">
         <v>146500</v>
@@ -3836,7 +3872,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3854,7 +3890,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B7" s="26">
         <v>78054</v>
@@ -3898,7 +3934,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B8" s="26">
         <v>50333</v>
@@ -3942,7 +3978,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B9" s="26">
         <v>8886</v>
@@ -3986,7 +4022,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4004,7 +4040,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B12" s="29">
         <v>137273</v>
@@ -4048,7 +4084,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B13" s="29">
         <v>9227</v>
@@ -4092,7 +4128,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B14" s="34">
         <v>9227</v>
@@ -4136,14 +4172,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B17" s="26">
         <v>0</v>
@@ -4151,7 +4187,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B18" s="34">
         <v>74498</v>
@@ -4159,7 +4195,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B19" s="26">
         <v>9227</v>
@@ -4191,7 +4227,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4204,24 +4240,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4231,7 +4267,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B5" s="31">
         <v>1178333</v>
@@ -4251,7 +4287,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4261,7 +4297,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B8" s="29">
         <v>780535</v>
@@ -4281,7 +4317,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B9" s="29">
         <v>503333</v>
@@ -4301,7 +4337,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B10" s="29">
         <v>106629</v>
@@ -4321,7 +4357,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
@@ -4346,7 +4382,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4356,7 +4392,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B14" s="27">
         <f>B5-B11</f>
@@ -4381,7 +4417,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4421,7 +4457,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4443,24 +4479,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>151</v>
+        <v>319</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4468,103 +4504,173 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B5" s="26">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>322</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="17">
         <v>350000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C6" s="18">
+        <v>0.06</v>
+      </c>
+      <c r="D6" s="14">
+        <v>10</v>
+      </c>
+      <c r="E6" s="26">
+        <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
+        <v>46629</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B9" s="26">
+        <f>B6</f>
+        <v>350000</v>
+      </c>
+      <c r="C9" s="26">
+        <f>B13</f>
         <v>323655</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D9" s="26">
+        <f>C13</f>
         <v>295685</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E9" s="26">
+        <f>D13</f>
         <v>265989</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F9" s="26">
+        <f>E13</f>
         <v>234462</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B6" s="26">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B10" s="26">
+        <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>20283</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C10" s="26">
+        <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>18658</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D10" s="26">
+        <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>16933</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E10" s="26">
+        <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>15102</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F10" s="26">
+        <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>13157</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B7" s="26">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B11" s="26">
+        <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>26345</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C11" s="26">
+        <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>27970</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D11" s="26">
+        <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>29695</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E11" s="26">
+        <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>31527</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F11" s="26">
+        <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>33471</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B8" s="29">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="29">
+        <f>B10+B11</f>
         <v>46629</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C12" s="29">
+        <f>C10+C11</f>
         <v>46629</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D12" s="29">
+        <f>D10+D11</f>
         <v>46629</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E12" s="29">
+        <f>E10+E11</f>
         <v>46629</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F12" s="29">
+        <f>F10+F11</f>
         <v>46629</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B9" s="34">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B13" s="34">
+        <f>MAX(0,B9-B11)</f>
         <v>323655</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C13" s="34">
+        <f>MAX(0,C9-C11)</f>
         <v>295685</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D13" s="34">
+        <f>MAX(0,D9-D11)</f>
         <v>265989</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E13" s="34">
+        <f>MAX(0,E9-E11)</f>
         <v>234462</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F13" s="34">
+        <f>MAX(0,F9-F11)</f>
         <v>200991</v>
       </c>
     </row>
@@ -4594,7 +4700,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4607,24 +4713,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4634,27 +4740,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="36">
+        <v>331</v>
+      </c>
+      <c r="B5" s="39">
         <v>74498</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="39">
         <v>530168</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="39">
         <v>1838758</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="39">
         <v>4035127</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="39">
         <v>7149621</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B6" s="26">
         <v>0</v>
@@ -4674,7 +4780,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B7" s="26">
         <v>0</v>
@@ -4694,7 +4800,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B8" s="26">
         <v>0</v>
@@ -4714,7 +4820,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B9" s="31">
         <v>74498</v>
@@ -4734,7 +4840,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4744,7 +4850,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B12" s="26">
         <v>0</v>
@@ -4764,7 +4870,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B13" s="26">
         <v>323655</v>
@@ -4784,7 +4890,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B14" s="31">
         <v>323655</v>
@@ -4804,7 +4910,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4814,7 +4920,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B17" s="27">
         <v>-249157</v>
@@ -4834,21 +4940,21 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B19" s="37">
+        <v>342</v>
+      </c>
+      <c r="B19" s="40">
         <v>0</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="41">
         <v>-1</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="40">
         <v>0</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="40">
         <v>0</v>
       </c>
-      <c r="F19" s="37">
+      <c r="F19" s="40">
         <v>0</v>
       </c>
     </row>
@@ -4878,7 +4984,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4891,24 +4997,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4918,7 +5024,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B5" s="26">
         <v>1178333</v>
@@ -4938,7 +5044,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B6" s="26">
         <v>780535</v>
@@ -4958,7 +5064,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B7" s="26">
         <v>503333</v>
@@ -4978,7 +5084,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="B8" s="29">
         <f>B5-B6-B7</f>
@@ -5003,7 +5109,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B9" s="26">
         <v>46629</v>
@@ -5023,32 +5129,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B10" s="39">
+        <v>347</v>
+      </c>
+      <c r="B10" s="42">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-2.26</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="42">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>11.2</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="42">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>29.6</v>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="42">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>48.32</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="42">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>68.01</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5058,7 +5164,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B13" s="26">
         <v>74498</v>
@@ -5078,7 +5184,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5103,7 +5209,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5128,7 +5234,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B16" s="25">
         <v>0.2</v>
@@ -5148,7 +5254,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5158,7 +5264,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B19" s="26">
         <v>9819</v>
@@ -5178,7 +5284,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B20" s="26">
         <v>827164</v>
@@ -5198,7 +5304,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B21" s="26">
         <v>4194</v>
@@ -5218,27 +5324,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B22" s="40">
+        <v>355</v>
+      </c>
+      <c r="B22" s="43">
         <v>148</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="43">
         <v>137</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="43">
         <v>132</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="43">
         <v>131</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="43">
         <v>131</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5248,102 +5354,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>348</v>
+        <v>357</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="F25" s="45" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>348</v>
+        <v>360</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="F26" s="45" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B27" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="E27" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>347</v>
+        <v>361</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="F27" s="44" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="F28" s="42" t="s">
-        <v>348</v>
+        <v>362</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="D28" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E28" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="F28" s="45" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B29" s="41" t="s">
-        <v>347</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="D29" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="E29" s="42" t="s">
-        <v>348</v>
-      </c>
-      <c r="F29" s="42" t="s">
-        <v>348</v>
+        <v>363</v>
+      </c>
+      <c r="B29" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="D29" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="E29" s="45" t="s">
+        <v>359</v>
+      </c>
+      <c r="F29" s="45" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5383,28 +5489,28 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
-        <v>353</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>354</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>100</v>
+      <c r="A3" s="46" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>365</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B4" s="26">
         <v>350000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="E4" s="26">
         <v>250000</v>
@@ -5412,13 +5518,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B5" s="26">
         <v>150000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E5" s="26">
         <v>60000</v>
@@ -5426,7 +5532,7 @@
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E6" s="26">
         <v>50000</v>
@@ -5434,7 +5540,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="E7" s="26">
         <v>140000</v>
@@ -5442,13 +5548,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B9" s="27">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E9" s="27">
         <v>500000</v>
@@ -5456,9 +5562,9 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B10" s="37">
+        <v>372</v>
+      </c>
+      <c r="B10" s="40">
         <v>0</v>
       </c>
     </row>
@@ -5479,7 +5585,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="B2:B32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5583,22 +5689,57 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>79</v>
+      <c r="B23" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -5624,7 +5765,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5634,7 +5775,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5644,7 +5785,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5652,24 +5793,24 @@
         <v>67</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B6" s="26">
         <v>1178333</v>
@@ -5689,7 +5830,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B7" s="26">
         <v>1330497</v>
@@ -5709,7 +5850,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B8" s="27">
         <v>-152164</v>
@@ -5729,7 +5870,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B9" s="25">
         <v>-0.12913460606689658</v>
@@ -5749,27 +5890,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B10" s="44">
+        <v>347</v>
+      </c>
+      <c r="B10" s="47">
         <v>-2.26</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="47">
         <v>11.2</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="47">
         <v>29.6</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="47">
         <v>48.32</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="47">
         <v>68.01</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B11" s="23">
         <v>148</v>
@@ -5789,7 +5930,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5799,7 +5940,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5807,24 +5948,24 @@
         <v>67</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B16" s="26">
         <v>1001583</v>
@@ -5844,7 +5985,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B17" s="26">
         <v>1330497</v>
@@ -5864,7 +6005,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B18" s="27">
         <v>-328914</v>
@@ -5884,7 +6025,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B19" s="25">
         <v>-0.32839365419634886</v>
@@ -5904,27 +6045,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20" s="44">
+        <v>347</v>
+      </c>
+      <c r="B20" s="47">
         <v>-6.05</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="47">
         <v>3.93</v>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="47">
         <v>18.77</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="47">
         <v>33.83</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F20" s="47">
         <v>49.68</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B21" s="23">
         <v>170</v>
@@ -5944,7 +6085,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5954,7 +6095,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5962,24 +6103,24 @@
         <v>67</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B26" s="26">
         <v>1084067</v>
@@ -5999,7 +6140,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B27" s="26">
         <v>1330497</v>
@@ -6019,7 +6160,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B28" s="27">
         <v>-246430</v>
@@ -6039,7 +6180,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B29" s="25">
         <v>-0.2273202239857572</v>
@@ -6059,27 +6200,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B30" s="44">
+        <v>347</v>
+      </c>
+      <c r="B30" s="47">
         <v>-4.28</v>
       </c>
-      <c r="C30" s="44">
+      <c r="C30" s="47">
         <v>7.32</v>
       </c>
-      <c r="D30" s="44">
+      <c r="D30" s="47">
         <v>23.82</v>
       </c>
-      <c r="E30" s="44">
+      <c r="E30" s="47">
         <v>40.59</v>
       </c>
-      <c r="F30" s="44">
+      <c r="F30" s="47">
         <v>58.23</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B31" s="23">
         <v>171</v>
@@ -6125,7 +6266,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6137,7 +6278,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -6151,7 +6292,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -6159,7 +6300,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6183,7 +6324,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6191,7 +6332,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6211,25 +6352,25 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="45" t="s">
-        <v>94</v>
+      <c r="D12" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D13" s="26">
         <v>1178333</v>
@@ -6249,7 +6390,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D14" s="26">
         <v>1330497</v>
@@ -6269,7 +6410,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D15" s="26">
         <v>-212164</v>
@@ -6289,7 +6430,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="D16" s="26">
         <v>74498</v>
@@ -6309,7 +6450,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="D17" s="26">
         <v>323655</v>
@@ -6329,7 +6470,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6349,25 +6490,25 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="H20" s="45" t="s">
-        <v>94</v>
+      <c r="D20" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="48" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="D21" s="25">
         <v>-0.18005398371894768</v>
@@ -6387,27 +6528,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="D22" s="44">
+        <v>347</v>
+      </c>
+      <c r="D22" s="47">
         <v>-2.26</v>
       </c>
-      <c r="E22" s="44">
+      <c r="E22" s="47">
         <v>11.2</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F22" s="47">
         <v>29.6</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="47">
         <v>48.32</v>
       </c>
-      <c r="H22" s="44">
+      <c r="H22" s="47">
         <v>68.01</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D23" s="25">
         <v>0.2</v>
@@ -6427,7 +6568,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D24" s="23">
         <v>120</v>
@@ -6447,7 +6588,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6485,7 +6626,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6496,12 +6637,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6544,10 +6685,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6568,7 +6709,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -6576,7 +6717,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="14">
         <v>600</v>
@@ -6584,7 +6725,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6598,24 +6739,24 @@
         <v>67</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B17" s="16">
         <v>120</v>
@@ -6635,7 +6776,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6646,30 +6787,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>8500</v>
@@ -6680,13 +6821,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>750</v>
@@ -6697,13 +6838,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D23" s="17">
         <v>1100</v>
@@ -6714,13 +6855,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D24" s="17">
         <v>150000</v>
@@ -6731,13 +6872,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D25" s="17">
         <v>25000</v>
@@ -6748,13 +6889,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D26" s="17">
         <v>400</v>
@@ -6765,7 +6906,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -6776,36 +6917,36 @@
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D30" s="19">
         <v>1</v>
@@ -6822,13 +6963,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D31" s="19">
         <v>1</v>
@@ -6845,13 +6986,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D32" s="19">
         <v>5</v>
@@ -6868,13 +7009,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D33" s="19">
         <v>1</v>
@@ -6891,13 +7032,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D34" s="19">
         <v>3</v>
@@ -6914,13 +7055,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="D35" s="19">
         <v>1</v>
@@ -6937,13 +7078,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D36" s="19">
         <v>2</v>
@@ -6960,7 +7101,7 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -6971,30 +7112,30 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D40" s="17">
         <v>22000</v>
@@ -7005,13 +7146,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D41" s="17">
         <v>3000</v>
@@ -7022,13 +7163,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D42" s="17">
         <v>22000</v>
@@ -7039,13 +7180,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D43" s="17">
         <v>650</v>
@@ -7056,13 +7197,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D44" s="17">
         <v>450</v>
@@ -7073,13 +7214,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D45" s="17">
         <v>30000</v>
@@ -7090,13 +7231,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D46" s="17">
         <v>12000</v>
@@ -7107,13 +7248,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D47" s="17">
         <v>18000</v>
@@ -7124,13 +7265,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D48" s="17">
         <v>750</v>
@@ -7141,7 +7282,7 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -7152,27 +7293,27 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C52" s="17">
         <v>350000</v>
@@ -7186,10 +7327,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C53" s="17">
         <v>60000</v>
@@ -7203,7 +7344,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -7214,29 +7355,29 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B56" s="18">
         <v>0.03</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B57" s="18">
         <v>0.03</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B58" s="19">
         <v>0.8333333333333334</v>
@@ -7244,7 +7385,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B59" s="17">
         <v>0</v>
@@ -7252,15 +7393,15 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -7271,23 +7412,23 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B65" s="16">
         <v>0</v>
@@ -7295,7 +7436,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B66" s="16">
         <v>0</v>
@@ -7303,7 +7444,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B67" s="21">
         <v>0.95</v>
@@ -7311,21 +7452,21 @@
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B70" s="17">
         <v>8200</v>
@@ -7339,27 +7480,27 @@
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B73" s="16">
         <v>80</v>
@@ -7379,7 +7520,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B74" s="16">
         <v>40</v>
@@ -7399,7 +7540,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B75" s="16">
         <v>0</v>
@@ -7449,10 +7590,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7473,10 +7614,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7489,7 +7630,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7497,66 +7638,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -7599,24 +7740,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7626,7 +7767,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B6" s="22">
         <v>120</v>
@@ -7646,7 +7787,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B7" s="23">
         <v>600</v>
@@ -7654,7 +7795,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B8" s="24">
         <v>0.2</v>
@@ -7674,10 +7815,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C10" s="25">
         <v>0.6666666666666666</v>
@@ -7718,7 +7859,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7731,24 +7872,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7758,7 +7899,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B5" s="26">
         <v>969000</v>
@@ -7778,7 +7919,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B6" s="26">
         <v>90000</v>
@@ -7798,7 +7939,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B7" s="26">
         <v>132000</v>
@@ -7818,7 +7959,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B8" s="26">
         <v>150000</v>
@@ -7838,7 +7979,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B9" s="26">
         <v>25000</v>
@@ -7858,7 +7999,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B10" s="26">
         <v>48000</v>
@@ -7878,7 +8019,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B11" s="27">
         <f>SUM(B5:B10)</f>
@@ -7942,33 +8083,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C4" s="28">
         <v>1</v>
@@ -7988,10 +8129,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C5" s="28">
         <v>1</v>
@@ -8011,10 +8152,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C6" s="28">
         <v>5</v>
@@ -8034,10 +8175,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C7" s="28">
         <v>1</v>
@@ -8057,10 +8198,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C8" s="28">
         <v>3</v>
@@ -8080,10 +8221,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C9" s="28">
         <v>1</v>
@@ -8103,10 +8244,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C10" s="28">
         <v>2</v>
@@ -8126,7 +8267,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -8140,24 +8281,24 @@
         <v>67</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B14" s="27">
         <v>780535</v>
@@ -8177,7 +8318,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B15" s="25">
         <v>0.5520049504950495</v>
@@ -8197,7 +8338,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B16" s="30">
         <v>8.6</v>
@@ -8241,7 +8382,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8254,24 +8395,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8281,7 +8422,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B5" s="26">
         <v>78000</v>
@@ -8301,7 +8442,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -8326,7 +8467,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -8336,7 +8477,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B8" s="26">
         <v>54000</v>
@@ -8356,7 +8497,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -8381,7 +8522,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -8391,7 +8532,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B11" s="26">
         <v>264000</v>
@@ -8411,7 +8552,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B12" s="26">
         <v>36000</v>
@@ -8431,7 +8572,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B13" s="26">
         <v>22000</v>
@@ -8451,7 +8592,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B11:B13)</f>
@@ -8476,7 +8617,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8486,7 +8627,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B16" s="26">
         <v>30000</v>
@@ -8506,7 +8647,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B17" s="26">
         <v>12000</v>
@@ -8526,7 +8667,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B18" s="26">
         <v>18000</v>
@@ -8546,7 +8687,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B19" s="26">
         <v>90000</v>
@@ -8566,7 +8707,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B20" s="31">
         <f>SUM(B16:B19)</f>
@@ -8591,7 +8732,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B22" s="27">
         <f>B6+B9+B14+B20</f>
@@ -8641,7 +8782,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8651,30 +8792,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C4" s="17">
         <v>350000</v>
@@ -8691,10 +8832,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C5" s="17">
         <v>60000</v>
@@ -8711,7 +8852,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="F7" s="27">
         <v>46629</v>
@@ -8719,7 +8860,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F8" s="31">
         <v>350000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -3867,6 +3867,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="31">
+        <f>SUM(B4:M4)</f>
         <v>1465000</v>
       </c>
     </row>
@@ -3929,6 +3930,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="26">
+        <f>SUM(B7:M7)</f>
         <v>780535</v>
       </c>
     </row>
@@ -3973,6 +3975,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="26">
+        <f>SUM(B8:M8)</f>
         <v>503333</v>
       </c>
     </row>
@@ -4017,6 +4020,7 @@
         <v>8886</v>
       </c>
       <c r="N9" s="26">
+        <f>SUM(B9:M9)</f>
         <v>106629</v>
       </c>
     </row>
@@ -4043,42 +4047,55 @@
         <v>286</v>
       </c>
       <c r="B12" s="29">
+        <f>B7+B8+B9</f>
         <v>137273</v>
       </c>
       <c r="C12" s="29">
+        <f>C7+C8+C9</f>
         <v>137273</v>
       </c>
       <c r="D12" s="29">
+        <f>D7+D8+D9</f>
         <v>137273</v>
       </c>
       <c r="E12" s="29">
+        <f>E7+E8+E9</f>
         <v>137273</v>
       </c>
       <c r="F12" s="29">
+        <f>F7+F8+F9</f>
         <v>137273</v>
       </c>
       <c r="G12" s="29">
+        <f>G7+G8+G9</f>
         <v>137273</v>
       </c>
       <c r="H12" s="29">
+        <f>H7+H8+H9</f>
         <v>137273</v>
       </c>
       <c r="I12" s="29">
+        <f>I7+I8+I9</f>
         <v>137273</v>
       </c>
       <c r="J12" s="29">
+        <f>J7+J8+J9</f>
         <v>137273</v>
       </c>
       <c r="K12" s="29">
+        <f>K7+K8+K9</f>
         <v>137273</v>
       </c>
       <c r="L12" s="29">
+        <f>L7+L8+L9</f>
         <v>8886</v>
       </c>
       <c r="M12" s="29">
+        <f>M7+M8+M9</f>
         <v>8886</v>
       </c>
       <c r="N12" s="29">
+        <f>SUM(B12:M12)</f>
         <v>1390502</v>
       </c>
     </row>
@@ -4087,42 +4104,55 @@
         <v>311</v>
       </c>
       <c r="B13" s="29">
+        <f>B4-B12</f>
         <v>9227</v>
       </c>
       <c r="C13" s="29">
+        <f>C4-C12</f>
         <v>9227</v>
       </c>
       <c r="D13" s="29">
+        <f>D4-D12</f>
         <v>9227</v>
       </c>
       <c r="E13" s="29">
+        <f>E4-E12</f>
         <v>9227</v>
       </c>
       <c r="F13" s="29">
+        <f>F4-F12</f>
         <v>9227</v>
       </c>
       <c r="G13" s="29">
+        <f>G4-G12</f>
         <v>9227</v>
       </c>
       <c r="H13" s="29">
+        <f>H4-H12</f>
         <v>9227</v>
       </c>
       <c r="I13" s="29">
+        <f>I4-I12</f>
         <v>9227</v>
       </c>
       <c r="J13" s="29">
+        <f>J4-J12</f>
         <v>9227</v>
       </c>
       <c r="K13" s="29">
+        <f>K4-K12</f>
         <v>9227</v>
       </c>
       <c r="L13" s="29">
+        <f>L4-L12</f>
         <v>-8886</v>
       </c>
       <c r="M13" s="29">
+        <f>M4-M12</f>
         <v>-8886</v>
       </c>
       <c r="N13" s="29">
+        <f>SUM(B13:M13)</f>
         <v>74498</v>
       </c>
     </row>
@@ -4131,42 +4161,55 @@
         <v>312</v>
       </c>
       <c r="B14" s="34">
+        <f>B17+B13</f>
         <v>9227</v>
       </c>
       <c r="C14" s="34">
+        <f>B14+C13</f>
         <v>18454</v>
       </c>
       <c r="D14" s="34">
+        <f>C14+D13</f>
         <v>27681</v>
       </c>
       <c r="E14" s="34">
+        <f>D14+E13</f>
         <v>36908</v>
       </c>
       <c r="F14" s="34">
+        <f>E14+F13</f>
         <v>46135</v>
       </c>
       <c r="G14" s="34">
+        <f>F14+G13</f>
         <v>55362</v>
       </c>
       <c r="H14" s="34">
+        <f>G14+H13</f>
         <v>64589</v>
       </c>
       <c r="I14" s="34">
+        <f>H14+I13</f>
         <v>73816</v>
       </c>
       <c r="J14" s="34">
+        <f>I14+J13</f>
         <v>83043</v>
       </c>
       <c r="K14" s="34">
+        <f>J14+K13</f>
         <v>92270</v>
       </c>
       <c r="L14" s="34">
+        <f>K14+L13</f>
         <v>83384</v>
       </c>
       <c r="M14" s="34">
+        <f>L14+M13</f>
         <v>74498</v>
       </c>
       <c r="N14" s="27">
+        <f>M14</f>
         <v>74498</v>
       </c>
     </row>
@@ -4181,7 +4224,7 @@
       <c r="A17" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="17">
         <v>0</v>
       </c>
     </row>
@@ -4190,6 +4233,7 @@
         <v>314</v>
       </c>
       <c r="B18" s="34">
+        <f>M14</f>
         <v>74498</v>
       </c>
     </row>
@@ -4198,6 +4242,7 @@
         <v>315</v>
       </c>
       <c r="B19" s="26">
+        <f>MIN(B14:M14)</f>
         <v>9227</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -4788,18 +4788,23 @@
         <v>331</v>
       </c>
       <c r="B5" s="39">
+        <f>'Monthly Cash Flow Y1'!M14</f>
         <v>74498</v>
       </c>
       <c r="C5" s="39">
+        <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>530168</v>
       </c>
       <c r="D5" s="39">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>1838758</v>
       </c>
       <c r="E5" s="39">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>4035127</v>
       </c>
       <c r="F5" s="39">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>7149621</v>
       </c>
     </row>
@@ -4868,18 +4873,23 @@
         <v>335</v>
       </c>
       <c r="B9" s="31">
+        <f>SUM(B5:B8)</f>
         <v>74498</v>
       </c>
       <c r="C9" s="31">
+        <f>SUM(C5:C8)</f>
         <v>530168</v>
       </c>
       <c r="D9" s="31">
+        <f>SUM(D5:D8)</f>
         <v>1838758</v>
       </c>
       <c r="E9" s="31">
+        <f>SUM(E5:E8)</f>
         <v>4035127</v>
       </c>
       <c r="F9" s="31">
+        <f>SUM(F5:F8)</f>
         <v>7149621</v>
       </c>
     </row>
@@ -4918,18 +4928,23 @@
         <v>338</v>
       </c>
       <c r="B13" s="26">
+        <f>'Debt Schedule'!B13</f>
         <v>323655</v>
       </c>
       <c r="C13" s="26">
+        <f>'Debt Schedule'!C13</f>
         <v>295685</v>
       </c>
       <c r="D13" s="26">
+        <f>'Debt Schedule'!D13</f>
         <v>265989</v>
       </c>
       <c r="E13" s="26">
+        <f>'Debt Schedule'!E13</f>
         <v>234462</v>
       </c>
       <c r="F13" s="26">
+        <f>'Debt Schedule'!F13</f>
         <v>200991</v>
       </c>
     </row>
@@ -4938,18 +4953,23 @@
         <v>339</v>
       </c>
       <c r="B14" s="31">
+        <f>SUM(B12:B13)</f>
         <v>323655</v>
       </c>
       <c r="C14" s="31">
+        <f>SUM(C12:C13)</f>
         <v>295685</v>
       </c>
       <c r="D14" s="31">
+        <f>SUM(D12:D13)</f>
         <v>265989</v>
       </c>
       <c r="E14" s="31">
+        <f>SUM(E12:E13)</f>
         <v>234462</v>
       </c>
       <c r="F14" s="31">
+        <f>SUM(F12:F13)</f>
         <v>200991</v>
       </c>
     </row>
@@ -4968,18 +4988,23 @@
         <v>341</v>
       </c>
       <c r="B17" s="27">
+        <f>B9-B14</f>
         <v>-249157</v>
       </c>
       <c r="C17" s="27">
+        <f>C9-C14</f>
         <v>234484</v>
       </c>
       <c r="D17" s="27">
+        <f>D9-D14</f>
         <v>1572769</v>
       </c>
       <c r="E17" s="27">
+        <f>E9-E14</f>
         <v>3800665</v>
       </c>
       <c r="F17" s="27">
+        <f>F9-F14</f>
         <v>6948630</v>
       </c>
     </row>
@@ -4987,19 +5012,24 @@
       <c r="A19" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="40" t="str">
+        <f>B9-B14-B17</f>
         <v>0</v>
       </c>
       <c r="C19" s="41">
+        <f>C9-C14-C17</f>
         <v>-1</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="40" t="str">
+        <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="40" t="str">
+        <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="40" t="str">
+        <f>F9-F14-F17</f>
         <v>0</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -25,13 +25,14 @@
     <sheet sheetId="19" name="Sources &amp; Uses" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="428">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -72,7 +73,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -216,6 +217,12 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
+    <t>22.</t>
+  </si>
+  <si>
+    <t>Financial Health</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -225,7 +232,7 @@
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
   </si>
   <si>
     <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
@@ -255,37 +262,28 @@
     <t>Tabs 14-17: Financial statements</t>
   </si>
   <si>
-    <t>Tabs 18-21: Analysis &amp; underwriting</t>
+    <t>Tabs 18-22: Analysis, underwriting &amp; dashboard</t>
   </si>
   <si>
     <t>Debt Service Convention</t>
   </si>
   <si>
-    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+    <t>operating expense on the Operating Statement. This is a standard</t>
   </si>
   <si>
     <t>simplification used in school financial underwriting that ensures internal</t>
   </si>
   <si>
-    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
-  </si>
-  <si>
-    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
-  </si>
-  <si>
-    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+    <t>consistency across all tabs.</t>
   </si>
   <si>
     <t>Tips</t>
   </si>
   <si>
-    <t>Review the Budget Summary for a high-level view.</t>
-  </si>
-  <si>
-    <t>Check DSCR &amp; Covenants for lender readiness.</t>
-  </si>
-  <si>
-    <t>The Underwriting Snapshot provides a one-page summary.</t>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -300,7 +298,7 @@
     <t>Heritage Academy Charter - Assumptions</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs. All other cells are formulas.</t>
+    <t>Blue cells are editable inputs. All other cells are formulas.</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1201,6 +1199,123 @@
   </si>
   <si>
     <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Heritage Academy Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 19% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 68.01x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>33.4 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>6 Healthy  |  0 Watch  |  1 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1329,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1280,6 +1395,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -1303,8 +1423,32 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1318,7 +1462,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1329,6 +1473,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1374,7 +1523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1395,15 +1544,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1423,19 +1572,56 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1780,7 +1966,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C42"/>
+  <dimension ref="B3:C43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2038,18 +2224,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="8"/>
+      <c r="C40" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Cover'!A1"/>
@@ -2073,6 +2267,7 @@
     <hyperlink ref="C37" r:id="rId19" location="#'Sources &amp; Uses'!A1"/>
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
+    <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2096,7 +2291,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2106,27 +2301,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="32">
         <v>120</v>
@@ -2146,7 +2341,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2156,7 +2351,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="26">
         <v>969000</v>
@@ -2176,7 +2371,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="26">
         <v>90000</v>
@@ -2196,7 +2391,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="26">
         <v>132000</v>
@@ -2216,7 +2411,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="26">
         <v>150000</v>
@@ -2236,7 +2431,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="26">
         <v>25000</v>
@@ -2256,7 +2451,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B12" s="26">
         <v>48000</v>
@@ -2276,7 +2471,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B13" s="27">
         <f>SUM(B7:B12)</f>
@@ -2301,7 +2496,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B15" s="26">
         <v>11783</v>
@@ -2345,7 +2540,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2355,27 +2550,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2385,7 +2580,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B5" s="26">
         <v>278438</v>
@@ -2405,7 +2600,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B6" s="26">
         <v>59029</v>
@@ -2425,7 +2620,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B7" s="26">
         <v>87955</v>
@@ -2445,7 +2640,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -2470,7 +2665,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2480,7 +2675,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B10" s="26">
         <v>116944</v>
@@ -2500,7 +2695,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B11" s="26">
         <v>91328</v>
@@ -2520,7 +2715,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B10:B11)</f>
@@ -2545,7 +2740,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2555,7 +2750,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B14" s="26">
         <v>69053</v>
@@ -2575,7 +2770,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B14:B14)</f>
@@ -2600,7 +2795,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -2610,7 +2805,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B17" s="26">
         <v>77790</v>
@@ -2630,7 +2825,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B18" s="31">
         <f>SUM(B17:B17)</f>
@@ -2655,7 +2850,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B20" s="27">
         <f>B8+B12+B15+B18</f>
@@ -2704,7 +2899,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2714,27 +2909,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2744,7 +2939,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B5" s="26">
         <v>807500</v>
@@ -2764,7 +2959,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B6" s="26">
         <v>75000</v>
@@ -2784,7 +2979,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B7" s="26">
         <v>110000</v>
@@ -2804,7 +2999,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B8" s="26">
         <v>125000</v>
@@ -2824,7 +3019,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" s="26">
         <v>20833</v>
@@ -2844,7 +3039,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B10" s="26">
         <v>40000</v>
@@ -2864,7 +3059,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
@@ -2889,7 +3084,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -2899,7 +3094,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B14" s="26">
         <v>116944</v>
@@ -2919,7 +3114,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B15" s="26">
         <v>91328</v>
@@ -2939,7 +3134,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B16" s="26">
         <v>278438</v>
@@ -2959,7 +3154,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B17" s="26">
         <v>59029</v>
@@ -2979,7 +3174,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B18" s="26">
         <v>87955</v>
@@ -2999,7 +3194,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B19" s="26">
         <v>69053</v>
@@ -3019,7 +3214,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B20" s="26">
         <v>77790</v>
@@ -3039,7 +3234,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B14:B20)</f>
@@ -3064,7 +3259,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3074,12 +3269,12 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B25" s="26">
         <v>65000</v>
@@ -3099,12 +3294,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="33" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B27" s="26">
         <v>45000</v>
@@ -3124,12 +3319,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B29" s="26">
         <v>220000</v>
@@ -3149,7 +3344,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B30" s="26">
         <v>30000</v>
@@ -3169,7 +3364,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B31" s="26">
         <v>18333</v>
@@ -3189,7 +3384,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B32" s="31">
         <f>SUM(B29:B31)</f>
@@ -3214,12 +3409,12 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B34" s="26">
         <v>25000</v>
@@ -3239,7 +3434,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B35" s="26">
         <v>10000</v>
@@ -3259,7 +3454,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B36" s="26">
         <v>15000</v>
@@ -3279,7 +3474,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B37" s="26">
         <v>75000</v>
@@ -3299,7 +3494,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B38" s="31">
         <f>SUM(B34:B37)</f>
@@ -3324,7 +3519,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B39" s="31">
         <f>B25+B27+B32+B38</f>
@@ -3349,7 +3544,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3359,7 +3554,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B42" s="26">
         <v>46629</v>
@@ -3379,7 +3574,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B43" s="26">
         <v>60000</v>
@@ -3399,7 +3594,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
@@ -3448,7 +3643,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3458,27 +3653,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B4" s="29">
         <f>'Budget Detail'!B11</f>
@@ -3503,7 +3698,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
@@ -3528,7 +3723,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
@@ -3553,7 +3748,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
@@ -3578,7 +3773,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3603,7 +3798,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3613,7 +3808,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B11" s="27">
         <f>B4-B8</f>
@@ -3638,7 +3833,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3663,7 +3858,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B13" s="26">
         <v>-212164</v>
@@ -3683,7 +3878,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B14" s="26">
         <v>9819</v>
@@ -3703,7 +3898,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B15" s="26">
         <v>11587</v>
@@ -3748,7 +3943,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3766,51 +3961,51 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>304</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3828,7 +4023,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B4" s="31">
         <v>146500</v>
@@ -3873,7 +4068,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3891,7 +4086,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B7" s="26">
         <v>78054</v>
@@ -3936,7 +4131,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B8" s="26">
         <v>50333</v>
@@ -3981,7 +4176,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B9" s="26">
         <v>8886</v>
@@ -4026,7 +4221,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4044,7 +4239,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B12" s="29">
         <f>B7+B8+B9</f>
@@ -4101,7 +4296,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B13" s="29">
         <f>B4-B12</f>
@@ -4158,7 +4353,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B14" s="34">
         <f>B17+B13</f>
@@ -4215,14 +4410,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B17" s="17">
         <v>0</v>
@@ -4230,7 +4425,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B18" s="34">
         <f>M14</f>
@@ -4239,7 +4434,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B19" s="26">
         <f>MIN(B14:M14)</f>
@@ -4272,7 +4467,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4282,27 +4477,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4312,7 +4507,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B5" s="31">
         <v>1178333</v>
@@ -4332,7 +4527,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4342,7 +4537,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B8" s="29">
         <v>780535</v>
@@ -4362,7 +4557,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B9" s="29">
         <v>503333</v>
@@ -4382,7 +4577,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B10" s="29">
         <v>106629</v>
@@ -4402,7 +4597,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
@@ -4427,7 +4622,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4437,7 +4632,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B14" s="27">
         <f>B5-B11</f>
@@ -4462,7 +4657,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4521,27 +4716,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4551,24 +4746,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="B5" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="C5" s="38" t="s">
+      <c r="D5" s="36" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>322</v>
-      </c>
       <c r="E5" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B6" s="17">
         <v>350000</v>
@@ -4586,7 +4781,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -4596,7 +4791,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B9" s="26">
         <f>B6</f>
@@ -4621,7 +4816,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B10" s="26">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4646,7 +4841,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B11" s="26">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4671,7 +4866,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B12" s="29">
         <f>B10+B11</f>
@@ -4696,7 +4891,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B13" s="34">
         <f>MAX(0,B9-B11)</f>
@@ -4745,7 +4940,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4755,27 +4950,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4785,7 +4980,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B5" s="39">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -4810,7 +5005,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B6" s="26">
         <v>0</v>
@@ -4830,7 +5025,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B7" s="26">
         <v>0</v>
@@ -4850,7 +5045,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B8" s="26">
         <v>0</v>
@@ -4870,7 +5065,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
@@ -4895,7 +5090,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4905,7 +5100,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B12" s="26">
         <v>0</v>
@@ -4925,7 +5120,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B13" s="26">
         <f>'Debt Schedule'!B13</f>
@@ -4950,7 +5145,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
@@ -4975,7 +5170,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4985,7 +5180,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B17" s="27">
         <f>B9-B14</f>
@@ -5010,7 +5205,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B19" s="40" t="str">
         <f>B9-B14-B17</f>
@@ -5059,7 +5254,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5069,27 +5264,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5099,7 +5294,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B5" s="26">
         <v>1178333</v>
@@ -5119,7 +5314,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B6" s="26">
         <v>780535</v>
@@ -5139,7 +5334,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B7" s="26">
         <v>503333</v>
@@ -5159,7 +5354,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B8" s="29">
         <f>B5-B6-B7</f>
@@ -5184,7 +5379,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B9" s="26">
         <v>46629</v>
@@ -5204,7 +5399,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B10" s="42">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5229,7 +5424,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5239,7 +5434,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B13" s="26">
         <v>74498</v>
@@ -5259,7 +5454,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5284,7 +5479,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5309,7 +5504,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" s="25">
         <v>0.2</v>
@@ -5329,7 +5524,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5339,7 +5534,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B19" s="26">
         <v>9819</v>
@@ -5359,7 +5554,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B20" s="26">
         <v>827164</v>
@@ -5379,7 +5574,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B21" s="26">
         <v>4194</v>
@@ -5399,7 +5594,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B22" s="43">
         <v>148</v>
@@ -5419,7 +5614,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5429,102 +5624,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B25" s="44" t="s">
         <v>357</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="C25" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="C25" s="45" t="s">
-        <v>359</v>
-      </c>
       <c r="D25" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E25" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F25" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B26" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="C26" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="C26" s="45" t="s">
-        <v>359</v>
-      </c>
       <c r="D26" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B28" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="C28" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="C28" s="45" t="s">
-        <v>359</v>
-      </c>
       <c r="D28" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E28" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F28" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B29" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="C29" s="45" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="45" t="s">
-        <v>359</v>
-      </c>
       <c r="D29" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E29" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F29" s="45" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -5565,27 +5760,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="46" t="s">
         <v>364</v>
       </c>
-      <c r="B3" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>365</v>
-      </c>
       <c r="E3" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B4" s="26">
         <v>350000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E4" s="26">
         <v>250000</v>
@@ -5593,13 +5788,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B5" s="26">
         <v>150000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E5" s="26">
         <v>60000</v>
@@ -5607,7 +5802,7 @@
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E6" s="26">
         <v>50000</v>
@@ -5615,7 +5810,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E7" s="26">
         <v>140000</v>
@@ -5623,13 +5818,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B9" s="27">
         <v>500000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E9" s="27">
         <v>500000</v>
@@ -5637,7 +5832,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B10" s="40">
         <v>0</v>
@@ -5660,7 +5855,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B32"/>
+  <dimension ref="B2:B29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5669,152 +5864,137 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>80</v>
+      <c r="B23" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>81</v>
+      <c r="B25" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>83</v>
+      <c r="B27" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -5840,7 +6020,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5850,7 +6030,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5860,32 +6040,32 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B6" s="26">
         <v>1178333</v>
@@ -5905,7 +6085,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B7" s="26">
         <v>1330497</v>
@@ -5925,7 +6105,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B8" s="27">
         <v>-152164</v>
@@ -5945,7 +6125,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B9" s="25">
         <v>-0.12913460606689658</v>
@@ -5965,7 +6145,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B10" s="47">
         <v>-2.26</v>
@@ -5985,7 +6165,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B11" s="23">
         <v>148</v>
@@ -6005,7 +6185,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -6015,32 +6195,32 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B16" s="26">
         <v>1001583</v>
@@ -6060,7 +6240,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B17" s="26">
         <v>1330497</v>
@@ -6080,7 +6260,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B18" s="27">
         <v>-328914</v>
@@ -6100,7 +6280,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B19" s="25">
         <v>-0.32839365419634886</v>
@@ -6120,7 +6300,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B20" s="47">
         <v>-6.05</v>
@@ -6140,7 +6320,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B21" s="23">
         <v>170</v>
@@ -6160,7 +6340,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6170,32 +6350,32 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B26" s="26">
         <v>1084067</v>
@@ -6215,7 +6395,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B27" s="26">
         <v>1330497</v>
@@ -6235,7 +6415,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B28" s="27">
         <v>-246430</v>
@@ -6255,7 +6435,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B29" s="25">
         <v>-0.2273202239857572</v>
@@ -6275,7 +6455,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B30" s="47">
         <v>-4.28</v>
@@ -6295,7 +6475,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B31" s="23">
         <v>171</v>
@@ -6341,7 +6521,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6353,7 +6533,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -6367,7 +6547,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -6375,7 +6555,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6399,7 +6579,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6407,7 +6587,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6419,33 +6599,33 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D12" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="F12" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="G12" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="H12" s="48" t="s">
         <v>99</v>
-      </c>
-      <c r="H12" s="48" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D13" s="26">
         <v>1178333</v>
@@ -6465,7 +6645,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D14" s="26">
         <v>1330497</v>
@@ -6485,7 +6665,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D15" s="26">
         <v>-212164</v>
@@ -6505,7 +6685,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D16" s="26">
         <v>74498</v>
@@ -6525,7 +6705,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D17" s="26">
         <v>323655</v>
@@ -6545,7 +6725,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6557,33 +6737,33 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="48" t="s">
+      <c r="F20" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="48" t="s">
+      <c r="G20" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="48" t="s">
+      <c r="H20" s="48" t="s">
         <v>99</v>
-      </c>
-      <c r="H20" s="48" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D21" s="25">
         <v>-0.18005398371894768</v>
@@ -6603,7 +6783,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D22" s="47">
         <v>-2.26</v>
@@ -6623,7 +6803,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D23" s="25">
         <v>0.2</v>
@@ -6643,7 +6823,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D24" s="23">
         <v>120</v>
@@ -6663,7 +6843,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6677,6 +6857,399 @@
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A26:H26"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="49" t="s">
+        <v>390</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>393</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>394</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>395</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C6" s="51">
+        <v>120</v>
+      </c>
+      <c r="D6" s="51">
+        <v>200</v>
+      </c>
+      <c r="E6" s="51">
+        <v>300</v>
+      </c>
+      <c r="F6" s="51">
+        <v>400</v>
+      </c>
+      <c r="G6" s="51">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C7" s="52">
+        <v>1178333.3333333335</v>
+      </c>
+      <c r="D7" s="52">
+        <v>2261600</v>
+      </c>
+      <c r="E7" s="52">
+        <v>3367965</v>
+      </c>
+      <c r="F7" s="52">
+        <v>4502531.525</v>
+      </c>
+      <c r="G7" s="52">
+        <v>5696361.453</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="52">
+        <v>780535</v>
+      </c>
+      <c r="D8" s="52">
+        <v>964741.26</v>
+      </c>
+      <c r="E8" s="52">
+        <v>993683.4978</v>
+      </c>
+      <c r="F8" s="52">
+        <v>1023494.002734</v>
+      </c>
+      <c r="G8" s="52">
+        <v>1054198.82281602</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" s="52">
+        <v>503333.3333333334</v>
+      </c>
+      <c r="D9" s="52">
+        <v>774560</v>
+      </c>
+      <c r="E9" s="52">
+        <v>994063.2999999999</v>
+      </c>
+      <c r="F9" s="52">
+        <v>1226039.6940000001</v>
+      </c>
+      <c r="G9" s="52">
+        <v>1471040.01467</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C10" s="52">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="D10" s="52">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="E10" s="52">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="F10" s="52">
+        <v>46628.6108154935</v>
+      </c>
+      <c r="G10" s="52">
+        <v>46628.6108154935</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C11" s="53">
+        <v>-212163.6108154934</v>
+      </c>
+      <c r="D11" s="54">
+        <v>455670.12918450637</v>
+      </c>
+      <c r="E11" s="54">
+        <v>1308589.5913845068</v>
+      </c>
+      <c r="F11" s="54">
+        <v>2196369.217450507</v>
+      </c>
+      <c r="G11" s="54">
+        <v>3114494.004698486</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" s="54">
+        <v>74498</v>
+      </c>
+      <c r="D12" s="54">
+        <v>530168.1291845064</v>
+      </c>
+      <c r="E12" s="54">
+        <v>1838757.7205690132</v>
+      </c>
+      <c r="F12" s="54">
+        <v>4035126.93801952</v>
+      </c>
+      <c r="G12" s="54">
+        <v>7149620.942718007</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C13" s="55">
+        <v>-0.18005398371894768</v>
+      </c>
+      <c r="D13" s="56">
+        <v>0.20148130933167066</v>
+      </c>
+      <c r="E13" s="56">
+        <v>0.38854013963461814</v>
+      </c>
+      <c r="F13" s="56">
+        <v>0.48780762672183775</v>
+      </c>
+      <c r="G13" s="56">
+        <v>0.54675147116204</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="36" t="s">
+        <v>402</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="E16" s="58"/>
+      <c r="F16" s="59" t="s">
+        <v>405</v>
+      </c>
+      <c r="G16" s="59"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="36" t="s">
+        <v>406</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>407</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="E17" s="58"/>
+      <c r="F17" s="59" t="s">
+        <v>409</v>
+      </c>
+      <c r="G17" s="59"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="E18" s="58"/>
+      <c r="F18" s="59" t="s">
+        <v>412</v>
+      </c>
+      <c r="G18" s="59"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59" t="s">
+        <v>415</v>
+      </c>
+      <c r="G19" s="59"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>417</v>
+      </c>
+      <c r="E20" s="58"/>
+      <c r="F20" s="59" t="s">
+        <v>418</v>
+      </c>
+      <c r="G20" s="59"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="E21" s="58"/>
+      <c r="F21" s="59" t="s">
+        <v>421</v>
+      </c>
+      <c r="G21" s="59"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="36" t="s">
+        <v>422</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>403</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>423</v>
+      </c>
+      <c r="E22" s="58"/>
+      <c r="F22" s="59" t="s">
+        <v>424</v>
+      </c>
+      <c r="G22" s="59"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="36" t="s">
+        <v>425</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6701,7 +7274,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6712,12 +7285,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6760,10 +7333,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6784,7 +7357,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -6792,7 +7365,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="14">
         <v>600</v>
@@ -6800,7 +7373,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6811,27 +7384,27 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="16">
         <v>120</v>
@@ -6851,7 +7424,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6862,30 +7435,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>8500</v>
@@ -6896,13 +7469,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>750</v>
@@ -6913,13 +7486,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D23" s="17">
         <v>1100</v>
@@ -6930,13 +7503,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="D24" s="17">
         <v>150000</v>
@@ -6947,13 +7520,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="D25" s="17">
         <v>25000</v>
@@ -6964,13 +7537,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="C26" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D26" s="17">
         <v>400</v>
@@ -6981,7 +7554,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -6992,36 +7565,36 @@
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="15" t="s">
+      <c r="D29" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="E29" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="F29" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="G29" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="D30" s="19">
         <v>1</v>
@@ -7038,13 +7611,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="D31" s="19">
         <v>1</v>
@@ -7061,13 +7634,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="C32" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D32" s="19">
         <v>5</v>
@@ -7084,13 +7657,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" s="19">
         <v>1</v>
@@ -7107,13 +7680,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="19">
         <v>3</v>
@@ -7130,13 +7703,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="C35" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D35" s="19">
         <v>1</v>
@@ -7153,13 +7726,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="C36" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D36" s="19">
         <v>2</v>
@@ -7176,7 +7749,7 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -7187,30 +7760,30 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="C39" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="D39" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="E39" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="C40" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="D40" s="17">
         <v>22000</v>
@@ -7221,13 +7794,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="D41" s="17">
         <v>3000</v>
@@ -7238,13 +7811,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D42" s="17">
         <v>22000</v>
@@ -7255,13 +7828,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="C43" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D43" s="17">
         <v>650</v>
@@ -7272,13 +7845,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="C44" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D44" s="17">
         <v>450</v>
@@ -7289,13 +7862,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="C45" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D45" s="17">
         <v>30000</v>
@@ -7306,13 +7879,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D46" s="17">
         <v>12000</v>
@@ -7323,13 +7896,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D47" s="17">
         <v>18000</v>
@@ -7340,13 +7913,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D48" s="17">
         <v>750</v>
@@ -7357,7 +7930,7 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -7368,27 +7941,27 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B51" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51" s="15" t="s">
+      <c r="D51" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>155</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="C52" s="17">
         <v>350000</v>
@@ -7402,10 +7975,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="C53" s="17">
         <v>60000</v>
@@ -7419,7 +7992,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -7430,29 +8003,29 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B56" s="18">
         <v>0.03</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B57" s="18">
         <v>0.03</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B58" s="19">
         <v>0.8333333333333334</v>
@@ -7460,7 +8033,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B59" s="17">
         <v>0</v>
@@ -7468,15 +8041,15 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B60" s="14" t="s">
         <v>168</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -7487,23 +8060,23 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B63" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B65" s="16">
         <v>0</v>
@@ -7511,7 +8084,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B66" s="16">
         <v>0</v>
@@ -7519,7 +8092,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B67" s="21">
         <v>0.95</v>
@@ -7527,21 +8100,21 @@
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="B69" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="C69" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="D69" s="15" t="s">
         <v>179</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B70" s="17">
         <v>8200</v>
@@ -7555,27 +8128,27 @@
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B72" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C72" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="D72" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D72" s="15" t="s">
+      <c r="E72" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="F72" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B73" s="16">
         <v>80</v>
@@ -7595,7 +8168,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B74" s="16">
         <v>40</v>
@@ -7615,7 +8188,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B75" s="16">
         <v>0</v>
@@ -7665,10 +8238,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7689,10 +8262,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7705,7 +8278,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7713,66 +8286,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -7812,27 +8385,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7842,7 +8415,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="22">
         <v>120</v>
@@ -7862,7 +8435,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" s="23">
         <v>600</v>
@@ -7870,7 +8443,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B8" s="24">
         <v>0.2</v>
@@ -7890,10 +8463,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>205</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>206</v>
       </c>
       <c r="C10" s="25">
         <v>0.6666666666666666</v>
@@ -7934,7 +8507,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7944,27 +8517,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7974,7 +8547,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B5" s="26">
         <v>969000</v>
@@ -7994,7 +8567,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B6" s="26">
         <v>90000</v>
@@ -8014,7 +8587,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B7" s="26">
         <v>132000</v>
@@ -8034,7 +8607,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B8" s="26">
         <v>150000</v>
@@ -8054,7 +8627,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B9" s="26">
         <v>25000</v>
@@ -8074,7 +8647,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10" s="26">
         <v>48000</v>
@@ -8094,7 +8667,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B11" s="27">
         <f>SUM(B5:B10)</f>
@@ -8158,33 +8731,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>216</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="C4" s="28">
         <v>1</v>
@@ -8204,10 +8777,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="28">
         <v>1</v>
@@ -8227,10 +8800,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="C6" s="28">
         <v>5</v>
@@ -8250,10 +8823,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="28">
         <v>1</v>
@@ -8273,10 +8846,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="28">
         <v>3</v>
@@ -8296,10 +8869,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="C9" s="28">
         <v>1</v>
@@ -8319,10 +8892,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="C10" s="28">
         <v>2</v>
@@ -8342,7 +8915,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -8353,27 +8926,27 @@
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B13" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="D13" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="F13" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="27">
         <v>780535</v>
@@ -8393,7 +8966,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B15" s="25">
         <v>0.5520049504950495</v>
@@ -8413,7 +8986,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B16" s="30">
         <v>8.6</v>
@@ -8457,7 +9030,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8467,27 +9040,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8497,7 +9070,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="26">
         <v>78000</v>
@@ -8517,7 +9090,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -8542,7 +9115,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -8552,7 +9125,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B8" s="26">
         <v>54000</v>
@@ -8572,7 +9145,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -8597,7 +9170,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -8607,7 +9180,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B11" s="26">
         <v>264000</v>
@@ -8627,7 +9200,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B12" s="26">
         <v>36000</v>
@@ -8647,7 +9220,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B13" s="26">
         <v>22000</v>
@@ -8667,7 +9240,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B11:B13)</f>
@@ -8692,7 +9265,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -8702,7 +9275,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B16" s="26">
         <v>30000</v>
@@ -8722,7 +9295,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B17" s="26">
         <v>12000</v>
@@ -8742,7 +9315,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B18" s="26">
         <v>18000</v>
@@ -8762,7 +9335,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B19" s="26">
         <v>90000</v>
@@ -8782,7 +9355,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" s="31">
         <f>SUM(B16:B19)</f>
@@ -8807,7 +9380,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B22" s="27">
         <f>B6+B9+B14+B20</f>
@@ -8857,7 +9430,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8867,30 +9440,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="F3" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>157</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="C4" s="17">
         <v>350000</v>
@@ -8907,10 +9480,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C5" s="17">
         <v>60000</v>
@@ -8927,7 +9500,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F7" s="27">
         <v>46629</v>
@@ -8935,7 +9508,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F8" s="31">
         <v>350000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="434">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -1226,6 +1226,24 @@
   </si>
   <si>
     <t>Net Income</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1523,7 +1541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1609,6 +1627,14 @@
     <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="168" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6871,7 +6897,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7080,176 +7106,302 @@
         <v>0.54675147116204</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="52">
+        <v>9819.444444444445</v>
+      </c>
+      <c r="D14" s="52">
+        <v>11308</v>
+      </c>
+      <c r="E14" s="52">
+        <v>11226.55</v>
+      </c>
+      <c r="F14" s="52">
+        <v>11256.328812500002</v>
+      </c>
+      <c r="G14" s="52">
+        <v>11392.722905999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="55">
+        <v>0.6624059405940593</v>
+      </c>
+      <c r="D15" s="56">
+        <v>0.4265746639547223</v>
+      </c>
+      <c r="E15" s="56">
+        <v>0.29503973402336425</v>
+      </c>
+      <c r="F15" s="56">
+        <v>0.22731523300861284</v>
+      </c>
+      <c r="G15" s="56">
+        <v>0.18506529677129674</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="C16" s="56">
+        <v>0.12814710042432814</v>
+      </c>
+      <c r="D16" s="56">
+        <v>0.10274495932083481</v>
+      </c>
+      <c r="E16" s="56">
+        <v>0.08854575092080826</v>
+      </c>
+      <c r="F16" s="56">
+        <v>0.0816900239693491</v>
+      </c>
+      <c r="G16" s="56">
+        <v>0.07747261265673058</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
+      <c r="C17" s="55">
+        <v>-0.08956294200848645</v>
+      </c>
+      <c r="D17" s="56">
+        <v>0.23094213830916166</v>
+      </c>
+      <c r="E17" s="56">
+        <v>0.40980776290727494</v>
+      </c>
+      <c r="F17" s="56">
+        <v>0.5003846870935568</v>
+      </c>
+      <c r="G17" s="56">
+        <v>0.5566926610396014</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" s="57">
+        <v>-2.2633099754482346</v>
+      </c>
+      <c r="D18" s="58">
+        <v>11.201250281006729</v>
+      </c>
+      <c r="E18" s="58">
+        <v>29.600242813611526</v>
+      </c>
+      <c r="F18" s="58">
+        <v>48.31792731679209</v>
+      </c>
+      <c r="G18" s="58">
+        <v>68.00808688171976</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="36" t="s">
+      <c r="C19" s="59" t="s">
+        <v>393</v>
+      </c>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C20" s="60" t="s">
         <v>403</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>404</v>
       </c>
-      <c r="E16" s="58"/>
-      <c r="F16" s="59" t="s">
+      <c r="C22" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="G16" s="59"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="36" t="s">
+      <c r="D22" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="C17" s="60" t="s">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="36" t="s">
         <v>408</v>
       </c>
-      <c r="E17" s="58"/>
-      <c r="F17" s="59" t="s">
+      <c r="C23" s="61" t="s">
         <v>409</v>
       </c>
-      <c r="G17" s="59"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="36" t="s">
+      <c r="D23" s="62" t="s">
         <v>410</v>
       </c>
-      <c r="C18" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="D18" s="58" t="s">
+      <c r="E23" s="62"/>
+      <c r="F23" s="63" t="s">
         <v>411</v>
       </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="59" t="s">
+      <c r="G23" s="63"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="36" t="s">
         <v>412</v>
       </c>
-      <c r="G18" s="59"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="36" t="s">
+      <c r="C24" s="64" t="s">
         <v>413</v>
       </c>
-      <c r="C19" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="D19" s="58" t="s">
+      <c r="D24" s="62" t="s">
         <v>414</v>
       </c>
-      <c r="E19" s="58"/>
-      <c r="F19" s="59" t="s">
+      <c r="E24" s="62"/>
+      <c r="F24" s="63" t="s">
         <v>415</v>
       </c>
-      <c r="G19" s="59"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="36" t="s">
+      <c r="G24" s="63"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="36" t="s">
         <v>416</v>
       </c>
-      <c r="C20" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="D20" s="58" t="s">
+      <c r="C25" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="D25" s="62" t="s">
         <v>417</v>
       </c>
-      <c r="E20" s="58"/>
-      <c r="F20" s="59" t="s">
+      <c r="E25" s="62"/>
+      <c r="F25" s="63" t="s">
         <v>418</v>
       </c>
-      <c r="G20" s="59"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="36" t="s">
+      <c r="G25" s="63"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="36" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="D21" s="58" t="s">
+      <c r="C26" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="D26" s="62" t="s">
         <v>420</v>
       </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="59" t="s">
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
         <v>421</v>
       </c>
-      <c r="G21" s="59"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="36" t="s">
+      <c r="G26" s="63"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="36" t="s">
         <v>422</v>
       </c>
-      <c r="C22" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="D22" s="58" t="s">
+      <c r="C27" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="D27" s="62" t="s">
         <v>423</v>
       </c>
-      <c r="E22" s="58"/>
-      <c r="F22" s="59" t="s">
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
         <v>424</v>
       </c>
-      <c r="G22" s="59"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="36" t="s">
+      <c r="G27" s="63"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="36" t="s">
         <v>425</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C28" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="D28" s="62" t="s">
         <v>426</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="61" t="s">
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
         <v>427</v>
       </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
+      <c r="G28" s="63"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="36" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="D29" s="62" t="s">
+        <v>429</v>
+      </c>
+      <c r="E29" s="62"/>
+      <c r="F29" s="63" t="s">
+        <v>430</v>
+      </c>
+      <c r="G29" s="63"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="36" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="65" t="s">
+        <v>433</v>
+      </c>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="440">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1570,7 +1570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1593,6 +1593,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2388,22 +2389,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2411,49 +2412,49 @@
       <c r="A4" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="37">
         <v>120</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="37">
         <v>200</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="37">
         <v>300</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="37">
         <v>400</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="37">
         <v>500</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>969000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1617850</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>2466200</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>3327850</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>4233200</v>
       </c>
     </row>
@@ -2461,19 +2462,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>90000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>154500</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>238703</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>327818</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>422066</v>
       </c>
     </row>
@@ -2481,19 +2482,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>132000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>226600</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>350097</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>480800</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>619030</v>
       </c>
     </row>
@@ -2501,19 +2502,19 @@
       <c r="A10" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>150000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>154500</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>159135</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>163909</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>168826</v>
       </c>
     </row>
@@ -2521,19 +2522,19 @@
       <c r="A11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>25000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>25750</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>26523</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>27318</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>28138</v>
       </c>
     </row>
@@ -2541,43 +2542,43 @@
       <c r="A12" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>48000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>82400</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>127308</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>174836</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>225102</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>SUM(B7:B12)</f>
         <v>1414000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>SUM(C7:C12)</f>
         <v>2261600</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>SUM(D7:D12)</f>
         <v>3367965</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>SUM(E7:E12)</f>
         <v>4502532</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>SUM(F7:F12)</f>
         <v>5696361</v>
       </c>
@@ -2586,19 +2587,19 @@
       <c r="A15" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <v>11783</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>11308</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>11227</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>11256</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>11393</v>
       </c>
     </row>
@@ -2637,52 +2638,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>278438</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>344149</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>354473</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>365107</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>376061</v>
       </c>
     </row>
@@ -2690,19 +2691,19 @@
       <c r="A6" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>59029</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>72960</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>75148</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>77403</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>79725</v>
       </c>
     </row>
@@ -2710,19 +2711,19 @@
       <c r="A7" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>87955</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>108712</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>111974</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>115333</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>118793</v>
       </c>
     </row>
@@ -2730,54 +2731,54 @@
       <c r="A8" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="36">
         <f>SUM(B5:B7)</f>
         <v>425421</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>SUM(C5:C7)</f>
         <v>525821</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="36">
         <f>SUM(D5:D7)</f>
         <v>541595</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="36">
         <f>SUM(E5:E7)</f>
         <v>557843</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="36">
         <f>SUM(F5:F7)</f>
         <v>574578</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>116944</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>144542</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>148879</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>153345</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>157945</v>
       </c>
     </row>
@@ -2785,19 +2786,19 @@
       <c r="A11" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>91328</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>112881</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>116267</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>119755</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>123348</v>
       </c>
     </row>
@@ -2805,54 +2806,54 @@
       <c r="A12" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <f>SUM(B10:B11)</f>
         <v>208271</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="36">
         <f>SUM(C10:C11)</f>
         <v>257423</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="36">
         <f>SUM(D10:D11)</f>
         <v>265146</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="36">
         <f>SUM(E10:E11)</f>
         <v>273100</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="36">
         <f>SUM(F10:F11)</f>
         <v>281293</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <v>69053</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>85349</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>87909</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>90547</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>93263</v>
       </c>
     </row>
@@ -2860,54 +2861,54 @@
       <c r="A15" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <f>SUM(B14:B14)</f>
         <v>69053</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>SUM(C14:C14)</f>
         <v>85349</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>SUM(D14:D14)</f>
         <v>87909</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>SUM(E14:E14)</f>
         <v>90547</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="36">
         <f>SUM(F14:F14)</f>
         <v>93263</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>77790</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>96148</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>99033</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>102004</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>105064</v>
       </c>
     </row>
@@ -2915,48 +2916,48 @@
       <c r="A18" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="36">
         <f>SUM(B17:B17)</f>
         <v>77790</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="36">
         <f>SUM(C17:C17)</f>
         <v>96148</v>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="36">
         <f>SUM(D17:D17)</f>
         <v>99033</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="36">
         <f>SUM(E17:E17)</f>
         <v>102004</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="36">
         <f>SUM(F17:F17)</f>
         <v>105064</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="32">
         <f>B8+B12+B15+B18</f>
         <v>780535</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>C8+C12+C15+C18</f>
         <v>964741</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="32">
         <f>D8+D12+D15+D18</f>
         <v>993683</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="32">
         <f>E8+E12+E15+E18</f>
         <v>1023494</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>F8+F12+F15+F18</f>
         <v>1054199</v>
       </c>
@@ -2996,52 +2997,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>807500</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1617850</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>2466200</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>3327850</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>4233200</v>
       </c>
     </row>
@@ -3049,19 +3050,19 @@
       <c r="A6" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>75000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>154500</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>238703</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>327818</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>422066</v>
       </c>
     </row>
@@ -3069,19 +3070,19 @@
       <c r="A7" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>110000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>226600</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>350097</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>480800</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>619030</v>
       </c>
     </row>
@@ -3089,19 +3090,19 @@
       <c r="A8" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>125000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>154500</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>159135</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>163909</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>168826</v>
       </c>
     </row>
@@ -3109,19 +3110,19 @@
       <c r="A9" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>20833</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>25750</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>26523</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>27318</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>28138</v>
       </c>
     </row>
@@ -3129,19 +3130,19 @@
       <c r="A10" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>40000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>82400</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>127308</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>174836</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>225102</v>
       </c>
     </row>
@@ -3149,54 +3150,54 @@
       <c r="A11" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>1178333</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <v>116944</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>144542</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>148879</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>153345</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>157945</v>
       </c>
     </row>
@@ -3204,19 +3205,19 @@
       <c r="A15" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <v>91328</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>112881</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>116267</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>119755</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>123348</v>
       </c>
     </row>
@@ -3224,19 +3225,19 @@
       <c r="A16" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>278438</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>344149</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>354473</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>365107</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>376061</v>
       </c>
     </row>
@@ -3244,19 +3245,19 @@
       <c r="A17" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>59029</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>72960</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>75148</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>77403</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>79725</v>
       </c>
     </row>
@@ -3264,19 +3265,19 @@
       <c r="A18" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <v>87955</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>108712</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>111974</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>115333</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>118793</v>
       </c>
     </row>
@@ -3284,19 +3285,19 @@
       <c r="A19" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <v>69053</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>85349</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>87909</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>90547</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>93263</v>
       </c>
     </row>
@@ -3304,19 +3305,19 @@
       <c r="A20" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <v>77790</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>96148</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>99033</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>102004</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>105064</v>
       </c>
     </row>
@@ -3324,39 +3325,39 @@
       <c r="A21" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="36">
         <f>SUM(B14:B20)</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="36">
         <f>SUM(C14:C20)</f>
         <v>964741</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <f>SUM(D14:D20)</f>
         <v>993683</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="36">
         <f>SUM(E14:E20)</f>
         <v>1023494</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="36">
         <f>SUM(F14:F20)</f>
         <v>1054199</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="38" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3364,24 +3365,24 @@
       <c r="A25" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <v>65000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>133900</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>206875</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>284109</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>365790</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="38" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3389,24 +3390,24 @@
       <c r="A27" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <v>45000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>92700</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>143222</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>196691</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>253239</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="38" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3414,19 +3415,19 @@
       <c r="A29" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="31">
         <v>220000</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <v>271920</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="31">
         <v>280078</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="31">
         <v>288480</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="31">
         <v>297134</v>
       </c>
     </row>
@@ -3434,19 +3435,19 @@
       <c r="A30" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="31">
         <v>30000</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <v>37080</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="31">
         <v>38192</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="31">
         <v>39338</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <v>40518</v>
       </c>
     </row>
@@ -3454,19 +3455,19 @@
       <c r="A31" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="31">
         <v>18333</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <v>22660</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="31">
         <v>23340</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="31">
         <v>24040</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="31">
         <v>24761</v>
       </c>
     </row>
@@ -3474,29 +3475,29 @@
       <c r="A32" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="36">
         <f>SUM(B29:B31)</f>
         <v>268333</v>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="36">
         <f>SUM(C29:C31)</f>
         <v>331660</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="36">
         <f>SUM(D29:D31)</f>
         <v>341610</v>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="36">
         <f>SUM(E29:E31)</f>
         <v>351858</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="36">
         <f>SUM(F29:F31)</f>
         <v>362414</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="37" t="s">
+      <c r="A33" s="38" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3504,19 +3505,19 @@
       <c r="A34" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <v>25000</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <v>30900</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="31">
         <v>31827</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="31">
         <v>32782</v>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="31">
         <v>33765</v>
       </c>
     </row>
@@ -3524,19 +3525,19 @@
       <c r="A35" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="31">
         <v>10000</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <v>12360</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <v>12731</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <v>13113</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <v>13506</v>
       </c>
     </row>
@@ -3544,19 +3545,19 @@
       <c r="A36" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <v>15000</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <v>18540</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <v>19096</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <v>19669</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <v>20259</v>
       </c>
     </row>
@@ -3564,19 +3565,19 @@
       <c r="A37" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="31">
         <v>75000</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <v>154500</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="31">
         <v>238703</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="31">
         <v>327818</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="31">
         <v>422066</v>
       </c>
     </row>
@@ -3584,23 +3585,23 @@
       <c r="A38" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B38" s="35">
+      <c r="B38" s="36">
         <f>SUM(B34:B37)</f>
         <v>125000</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="36">
         <f>SUM(C34:C37)</f>
         <v>216300</v>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="36">
         <f>SUM(D34:D37)</f>
         <v>302357</v>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="36">
         <f>SUM(E34:E37)</f>
         <v>393382</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="36">
         <f>SUM(F34:F37)</f>
         <v>489596</v>
       </c>
@@ -3609,54 +3610,54 @@
       <c r="A39" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B39" s="35">
+      <c r="B39" s="36">
         <f>B25+B27+B32+B38</f>
         <v>503333</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="36">
         <f>C25+C27+C32+C38</f>
         <v>774560</v>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="36">
         <f>D25+D27+D32+D38</f>
         <v>994063</v>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="36">
         <f>E25+E27+E32+E38</f>
         <v>1226040</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="36">
         <f>F25+F27+F32+F38</f>
         <v>1471040</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <v>46629</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <v>46629</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <v>46629</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="31">
         <v>46629</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <v>46629</v>
       </c>
     </row>
@@ -3664,19 +3665,19 @@
       <c r="A43" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="31">
         <v>60000</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <v>20000</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <v>25000</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <v>10000</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <v>10000</v>
       </c>
     </row>
@@ -3684,23 +3685,23 @@
       <c r="A44" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="35">
+      <c r="B44" s="36">
         <f>SUM(B42:B43)</f>
         <v>106629</v>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <f>SUM(C42:C43)</f>
         <v>66629</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="36">
         <f>SUM(D42:D43)</f>
         <v>71629</v>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="36">
         <f>SUM(E42:E43)</f>
         <v>56629</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="36">
         <f>SUM(F42:F43)</f>
         <v>56629</v>
       </c>
@@ -3740,22 +3741,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3763,23 +3764,23 @@
       <c r="A4" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="34">
         <f>'Budget Detail'!B11</f>
         <v>1178333</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="34">
         <f>'Budget Detail'!C11</f>
         <v>2261600</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="34">
         <f>'Budget Detail'!D11</f>
         <v>3367965</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="34">
         <f>'Budget Detail'!E11</f>
         <v>4502532</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <f>'Budget Detail'!F11</f>
         <v>5696361</v>
       </c>
@@ -3788,23 +3789,23 @@
       <c r="A5" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
         <v>780535</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>'Budget Detail'!C21</f>
         <v>964741</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="34">
         <f>'Budget Detail'!D21</f>
         <v>993683</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="34">
         <f>'Budget Detail'!E21</f>
         <v>1023494</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <f>'Budget Detail'!F21</f>
         <v>1054199</v>
       </c>
@@ -3813,23 +3814,23 @@
       <c r="A6" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
         <v>503333</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>'Budget Detail'!C39</f>
         <v>774560</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <f>'Budget Detail'!D39</f>
         <v>994063</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>'Budget Detail'!E39</f>
         <v>1226040</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="34">
         <f>'Budget Detail'!F39</f>
         <v>1471040</v>
       </c>
@@ -3838,23 +3839,23 @@
       <c r="A7" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
         <v>106629</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="34">
         <f>'Budget Detail'!C44</f>
         <v>66629</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="34">
         <f>'Budget Detail'!D44</f>
         <v>71629</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="34">
         <f>'Budget Detail'!E44</f>
         <v>56629</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="34">
         <f>'Budget Detail'!F44</f>
         <v>56629</v>
       </c>
@@ -3863,58 +3864,58 @@
       <c r="A8" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="36">
         <f>SUM(B5:B7)</f>
         <v>1390497</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>SUM(C5:C7)</f>
         <v>1805930</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="36">
         <f>SUM(D5:D7)</f>
         <v>2059375</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="36">
         <f>SUM(E5:E7)</f>
         <v>2306162</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="36">
         <f>SUM(F5:F7)</f>
         <v>2581867</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>B4-B8</f>
         <v>-212164</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>C4-C8</f>
         <v>455670</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>D4-D8</f>
         <v>1308590</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>E4-E8</f>
         <v>2196369</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>F4-F8</f>
         <v>3114494</v>
       </c>
@@ -3923,23 +3924,23 @@
       <c r="A12" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.54675147</v>
       </c>
@@ -3948,19 +3949,19 @@
       <c r="A13" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>-212164</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>243507</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>1552096</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>3748465</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>6862959</v>
       </c>
     </row>
@@ -3968,19 +3969,19 @@
       <c r="A14" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <v>9819</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>11308</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>11227</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>11256</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>11393</v>
       </c>
     </row>
@@ -3988,19 +3989,19 @@
       <c r="A15" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <v>11587</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>9030</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>6865</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>5765</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>5164</v>
       </c>
     </row>
@@ -4048,171 +4049,171 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="20" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="36">
         <v>146500</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>146500</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <v>146500</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <v>146500</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="36">
         <v>146500</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="36">
         <v>146500</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="36">
         <v>146500</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="36">
         <v>146500</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="36">
         <v>146500</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="36">
         <v>146500</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="36">
         <v>0</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="36">
         <v>0</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="36">
         <f>SUM(B4:M4)</f>
         <v>1465000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>78054</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>78054</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>78054</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>78054</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>78054</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>78054</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <v>78054</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <v>78054</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <v>78054</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="31">
         <v>78054</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="31">
         <v>0</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="31">
         <v>0</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="31">
         <f>SUM(B7:M7)</f>
         <v>780535</v>
       </c>
@@ -4221,43 +4222,43 @@
       <c r="A8" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>50333</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>50333</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>50333</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>50333</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>50333</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>50333</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <v>50333</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <v>50333</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="31">
         <v>50333</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="31">
         <v>50333</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="31">
         <v>0</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="31">
         <v>0</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="31">
         <f>SUM(B8:M8)</f>
         <v>503333</v>
       </c>
@@ -4266,118 +4267,118 @@
       <c r="A9" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>8886</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>8886</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>8886</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>8886</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>8886</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>8886</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <v>8886</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <v>8886</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="31">
         <v>8886</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="31">
         <v>8886</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="31">
         <v>8886</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="31">
         <v>8886</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="31">
         <f>SUM(B9:M9)</f>
         <v>106629</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>B7+B8+B9</f>
         <v>137273</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>C7+C8+C9</f>
         <v>137273</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>D7+D8+D9</f>
         <v>137273</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E7+E8+E9</f>
         <v>137273</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>F7+F8+F9</f>
         <v>137273</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="34">
         <f>G7+G8+G9</f>
         <v>137273</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>H7+H8+H9</f>
         <v>137273</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="34">
         <f>I7+I8+I9</f>
         <v>137273</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="34">
         <f>J7+J8+J9</f>
         <v>137273</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="34">
         <f>K7+K8+K9</f>
         <v>137273</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12" s="34">
         <f>L7+L8+L9</f>
         <v>8886</v>
       </c>
-      <c r="M12" s="33">
+      <c r="M12" s="34">
         <f>M7+M8+M9</f>
         <v>8886</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
         <v>1390502</v>
       </c>
@@ -4386,55 +4387,55 @@
       <c r="A13" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>B4-B12</f>
         <v>9227</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="34">
         <f>C4-C12</f>
         <v>9227</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <f>D4-D12</f>
         <v>9227</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>E4-E12</f>
         <v>9227</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="34">
         <f>F4-F12</f>
         <v>9227</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="34">
         <f>G4-G12</f>
         <v>9227</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="34">
         <f>H4-H12</f>
         <v>9227</v>
       </c>
-      <c r="I13" s="33">
+      <c r="I13" s="34">
         <f>I4-I12</f>
         <v>9227</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="34">
         <f>J4-J12</f>
         <v>9227</v>
       </c>
-      <c r="K13" s="33">
+      <c r="K13" s="34">
         <f>K4-K12</f>
         <v>9227</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="34">
         <f>L4-L12</f>
         <v>-8886</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="34">
         <f>M4-M12</f>
         <v>-8886</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
         <v>74498</v>
       </c>
@@ -4443,71 +4444,71 @@
       <c r="A14" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="39">
         <f>B17+B13</f>
         <v>9227</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="39">
         <f>B14+C13</f>
         <v>18454</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="39">
         <f>C14+D13</f>
         <v>27681</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="39">
         <f>D14+E13</f>
         <v>36908</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="39">
         <f>E14+F13</f>
         <v>46135</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="39">
         <f>F14+G13</f>
         <v>55362</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="39">
         <f>G14+H13</f>
         <v>64589</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="39">
         <f>H14+I13</f>
         <v>73816</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14" s="39">
         <f>I14+J13</f>
         <v>83043</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="39">
         <f>J14+K13</f>
         <v>92270</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="39">
         <f>K14+L13</f>
         <v>83384</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="39">
         <f>L14+M13</f>
         <v>74498</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="32">
         <f>M14</f>
         <v>74498</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="22">
         <v>0</v>
       </c>
     </row>
@@ -4515,7 +4516,7 @@
       <c r="A18" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="39">
         <f>M14</f>
         <v>74498</v>
       </c>
@@ -4524,7 +4525,7 @@
       <c r="A19" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
         <v>9227</v>
       </c>
@@ -4564,82 +4565,82 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="36">
         <v>1178333</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="36">
         <v>2261600</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="36">
         <v>3367965</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="36">
         <v>4502532</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="36">
         <v>5696361</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <v>780535</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>964741</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>993683</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>1023494</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>1054199</v>
       </c>
     </row>
@@ -4647,19 +4648,19 @@
       <c r="A9" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="34">
         <v>503333</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>774560</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <v>994063</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <v>1226040</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <v>1471040</v>
       </c>
     </row>
@@ -4667,78 +4668,78 @@
       <c r="A10" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="34">
         <v>106629</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="34">
         <v>66629</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>71629</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>56629</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>56629</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B8:B10)</f>
         <v>1390497</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <f>SUM(C8:C10)</f>
         <v>1805930</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <f>SUM(D8:D10)</f>
         <v>2059375</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <f>SUM(E8:E10)</f>
         <v>2306162</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <f>SUM(F8:F10)</f>
         <v>2581867</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>B5-B11</f>
         <v>-212164</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>C5-C11</f>
         <v>455670</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>D5-D11</f>
         <v>1308590</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E5-E11</f>
         <v>2196369</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F5-F11</f>
         <v>3114494</v>
       </c>
@@ -4747,23 +4748,23 @@
       <c r="A15" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.54675147</v>
       </c>
@@ -4803,101 +4804,101 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="41" t="s">
         <v>325</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="41" t="s">
         <v>327</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="42" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="22">
         <v>350000</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <v>0.06</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <v>10</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>46629</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>328</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>B6</f>
         <v>350000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>B13</f>
         <v>323655</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>C13</f>
         <v>295685</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>D13</f>
         <v>265989</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>E13</f>
         <v>234462</v>
       </c>
@@ -4906,23 +4907,23 @@
       <c r="A10" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>20283</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>18658</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>16933</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>15102</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>13157</v>
       </c>
@@ -4931,23 +4932,23 @@
       <c r="A11" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>26345</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>27970</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>29695</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>31527</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>33471</v>
       </c>
@@ -4956,23 +4957,23 @@
       <c r="A12" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>B10+B11</f>
         <v>46629</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>C10+C11</f>
         <v>46629</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>D10+D11</f>
         <v>46629</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E10+E11</f>
         <v>46629</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>F10+F11</f>
         <v>46629</v>
       </c>
@@ -4981,23 +4982,23 @@
       <c r="A13" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="39">
         <f>MAX(0,B9-B11)</f>
         <v>323655</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="39">
         <f>MAX(0,C9-C11)</f>
         <v>295685</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="39">
         <f>MAX(0,D9-D11)</f>
         <v>265989</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="39">
         <f>MAX(0,E9-E11)</f>
         <v>234462</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="39">
         <f>MAX(0,F9-F11)</f>
         <v>200991</v>
       </c>
@@ -5037,56 +5038,56 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="44">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>74498</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>530168</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>1838758</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>4035127</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="44">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>7149621</v>
       </c>
@@ -5095,19 +5096,19 @@
       <c r="A6" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>0</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>0</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>0</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>0</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>0</v>
       </c>
     </row>
@@ -5115,19 +5116,19 @@
       <c r="A7" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>0</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>0</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>0</v>
       </c>
     </row>
@@ -5135,19 +5136,19 @@
       <c r="A8" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>0</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>0</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>0</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>0</v>
       </c>
     </row>
@@ -5155,54 +5156,54 @@
       <c r="A9" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>74498</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>SUM(C5:C8)</f>
         <v>530168</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <f>SUM(D5:D8)</f>
         <v>1838758</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="36">
         <f>SUM(E5:E8)</f>
         <v>4035127</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="36">
         <f>SUM(F5:F8)</f>
         <v>7149621</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>0</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>0</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>0</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>0</v>
       </c>
     </row>
@@ -5210,23 +5211,23 @@
       <c r="A13" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
         <v>323655</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>'Debt Schedule'!C13</f>
         <v>295685</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>'Debt Schedule'!D13</f>
         <v>265989</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>'Debt Schedule'!E13</f>
         <v>234462</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>'Debt Schedule'!F13</f>
         <v>200991</v>
       </c>
@@ -5235,58 +5236,58 @@
       <c r="A14" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="36">
         <f>SUM(B12:B13)</f>
         <v>323655</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>SUM(C12:C13)</f>
         <v>295685</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="36">
         <f>SUM(D12:D13)</f>
         <v>265989</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>SUM(E12:E13)</f>
         <v>234462</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="36">
         <f>SUM(F12:F13)</f>
         <v>200991</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>B9-B14</f>
         <v>-249157</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>C9-C14</f>
         <v>234484</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>D9-D14</f>
         <v>1572769</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E9-E14</f>
         <v>3800665</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F9-F14</f>
         <v>6948630</v>
       </c>
@@ -5295,23 +5296,23 @@
       <c r="A19" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="B19" s="44" t="str">
+      <c r="B19" s="45" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="45">
+      <c r="C19" s="46">
         <f>C9-C14-C17</f>
         <v>-1</v>
       </c>
-      <c r="D19" s="44" t="str">
+      <c r="D19" s="45" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="44" t="str">
+      <c r="E19" s="45" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="44" t="str">
+      <c r="F19" s="45" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -5351,52 +5352,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>349</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>1178333</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2261600</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>3367965</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>4502532</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>5696361</v>
       </c>
     </row>
@@ -5404,19 +5405,19 @@
       <c r="A6" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>780535</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>964741</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>993683</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>1023494</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>1054199</v>
       </c>
     </row>
@@ -5424,19 +5425,19 @@
       <c r="A7" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>503333</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>774560</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>994063</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>1226040</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>1471040</v>
       </c>
     </row>
@@ -5444,23 +5445,23 @@
       <c r="A8" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <f>B5-B6-B7</f>
         <v>-105535</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <f>C5-C6-C7</f>
         <v>522299</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <f>D5-D6-D7</f>
         <v>1380218</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <f>E5-E6-E7</f>
         <v>2252998</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <f>F5-F6-F7</f>
         <v>3171123</v>
       </c>
@@ -5469,19 +5470,19 @@
       <c r="A9" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>46629</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>46629</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>46629</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>46629</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>46629</v>
       </c>
     </row>
@@ -5489,54 +5490,54 @@
       <c r="A10" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="47">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-2.26</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="47">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>11.2</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="47">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>29.6</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="47">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>48.32</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="47">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>68.01</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>74498</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>530168</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>1838758</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>4035127</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>7149621</v>
       </c>
     </row>
@@ -5544,23 +5545,23 @@
       <c r="A14" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>20</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>108</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>330</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>641</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1015</v>
       </c>
@@ -5569,23 +5570,23 @@
       <c r="A15" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>0.7</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>3.6</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>10.8</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>21.1</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>33.4</v>
       </c>
@@ -5594,49 +5595,49 @@
       <c r="A16" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>0.2</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>0.5</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <v>9819</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>11308</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>11227</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>11256</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>11393</v>
       </c>
     </row>
@@ -5644,19 +5645,19 @@
       <c r="A20" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <v>827164</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>1011370</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>1040312</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>1070123</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>1100827</v>
       </c>
     </row>
@@ -5664,19 +5665,19 @@
       <c r="A21" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <v>4194</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>3873</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>3314</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>3065</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>2942</v>
       </c>
     </row>
@@ -5684,49 +5685,49 @@
       <c r="A22" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B22" s="47">
+      <c r="B22" s="48">
         <v>148</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="48">
         <v>137</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="48">
         <v>132</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="48">
         <v>131</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="48">
         <v>131</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="E25" s="49" t="s">
+      <c r="E25" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="F25" s="49" t="s">
+      <c r="F25" s="50" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5734,19 +5735,19 @@
       <c r="A26" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="E26" s="49" t="s">
+      <c r="E26" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="F26" s="49" t="s">
+      <c r="F26" s="50" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5754,19 +5755,19 @@
       <c r="A27" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="49" t="s">
         <v>363</v>
       </c>
     </row>
@@ -5774,19 +5775,19 @@
       <c r="A28" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="B28" s="48" t="s">
+      <c r="B28" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="E28" s="49" t="s">
+      <c r="E28" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="F28" s="49" t="s">
+      <c r="F28" s="50" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5794,19 +5795,19 @@
       <c r="A29" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="49" t="s">
         <v>363</v>
       </c>
-      <c r="C29" s="49" t="s">
+      <c r="C29" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="E29" s="49" t="s">
+      <c r="E29" s="50" t="s">
         <v>364</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="50" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5847,16 +5848,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
         <v>369</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="51" t="s">
         <v>370</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="51" t="s">
         <v>111</v>
       </c>
     </row>
@@ -5864,13 +5865,13 @@
       <c r="A4" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <v>350000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>250000</v>
       </c>
     </row>
@@ -5878,13 +5879,13 @@
       <c r="A5" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>150000</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>60000</v>
       </c>
     </row>
@@ -5892,7 +5893,7 @@
       <c r="D6" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>50000</v>
       </c>
     </row>
@@ -5900,7 +5901,7 @@
       <c r="D7" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>140000</v>
       </c>
     </row>
@@ -5908,13 +5909,13 @@
       <c r="A9" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <v>500000</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <v>500000</v>
       </c>
     </row>
@@ -5922,7 +5923,7 @@
       <c r="A10" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="45">
         <v>0</v>
       </c>
     </row>
@@ -6277,37 +6278,37 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6315,19 +6316,19 @@
       <c r="A6" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>1178333</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>2261600</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>3367965</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>4502532</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>5696361</v>
       </c>
     </row>
@@ -6335,19 +6336,19 @@
       <c r="A7" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>1330497</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1785930</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>2034375</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>2296162</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>2571867</v>
       </c>
     </row>
@@ -6355,19 +6356,19 @@
       <c r="A8" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <v>-152164</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <v>475670</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <v>1333590</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <v>2206369</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <v>3124494</v>
       </c>
     </row>
@@ -6375,19 +6376,19 @@
       <c r="A9" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>-0.12913460606689658</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>0.21032460611271073</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>0.39596301962297903</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0.49002859951113986</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0.5485069777397931</v>
       </c>
     </row>
@@ -6395,19 +6396,19 @@
       <c r="A10" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B10" s="51">
+      <c r="B10" s="52">
         <v>-2.26</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="52">
         <v>11.2</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="52">
         <v>29.6</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="52">
         <v>48.32</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="52">
         <v>68.01</v>
       </c>
     </row>
@@ -6415,54 +6416,54 @@
       <c r="A11" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="28">
         <v>148</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <v>137</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <v>132</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="28">
         <v>131</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="28">
         <v>131</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>381</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6470,19 +6471,19 @@
       <c r="A16" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>1001583</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>1922360</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>2862770</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>3827152</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>4841907</v>
       </c>
     </row>
@@ -6490,19 +6491,19 @@
       <c r="A17" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>1330497</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>1785930</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>2034375</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>2296162</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>2571867</v>
       </c>
     </row>
@@ -6510,19 +6511,19 @@
       <c r="A18" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <v>-328914</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <v>136430</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <v>828395</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <v>1530989</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <v>2270040</v>
       </c>
     </row>
@@ -6530,19 +6531,19 @@
       <c r="A19" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>-0.32839365419634886</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>0.07097012483848322</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>0.2893682583799753</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>0.40003364648369394</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>0.46883173851740356</v>
       </c>
     </row>
@@ -6550,19 +6551,19 @@
       <c r="A20" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B20" s="51">
+      <c r="B20" s="52">
         <v>-6.05</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="52">
         <v>3.93</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="52">
         <v>18.77</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="52">
         <v>33.83</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="52">
         <v>49.68</v>
       </c>
     </row>
@@ -6570,54 +6571,54 @@
       <c r="A21" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <v>170</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <v>150</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <v>142</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <v>140</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <v>139</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6625,19 +6626,19 @@
       <c r="A26" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <v>1084067</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <v>2080672</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <v>3098528</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <v>4142329</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <v>5240653</v>
       </c>
     </row>
@@ -6645,19 +6646,19 @@
       <c r="A27" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <v>1330497</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>1785930</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>2034375</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>2296162</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>2571867</v>
       </c>
     </row>
@@ -6665,19 +6666,19 @@
       <c r="A28" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <v>-246430</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>294742</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>1064152</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>1846167</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>2668785</v>
       </c>
     </row>
@@ -6685,19 +6686,19 @@
       <c r="A29" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="30">
         <v>-0.2273202239857572</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>0.1416571805572943</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>0.34343806480758593</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>0.4456832603381955</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>0.5092467149345576</v>
       </c>
     </row>
@@ -6705,19 +6706,19 @@
       <c r="A30" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B30" s="51">
+      <c r="B30" s="52">
         <v>-4.28</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="52">
         <v>7.32</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="52">
         <v>23.82</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="52">
         <v>40.59</v>
       </c>
-      <c r="F30" s="51">
+      <c r="F30" s="52">
         <v>58.23</v>
       </c>
     </row>
@@ -6725,19 +6726,19 @@
       <c r="A31" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>171</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <v>155</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <v>149</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <v>147</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="28">
         <v>147</v>
       </c>
     </row>
@@ -6780,10 +6781,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -6834,16 +6835,16 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -6855,19 +6856,19 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6875,19 +6876,19 @@
       <c r="A13" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>1178333</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>2261600</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>3367965</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <v>4502532</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <v>5696361</v>
       </c>
     </row>
@@ -6895,19 +6896,19 @@
       <c r="A14" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>1330497</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>1785930</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>2034375</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <v>2296162</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <v>2571867</v>
       </c>
     </row>
@@ -6915,19 +6916,19 @@
       <c r="A15" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>-212164</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>455670</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>1308590</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <v>2196369</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <v>3114494</v>
       </c>
     </row>
@@ -6935,19 +6936,19 @@
       <c r="A16" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>74498</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>530168</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>1838758</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <v>4035127</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <v>7149621</v>
       </c>
     </row>
@@ -6955,33 +6956,33 @@
       <c r="A17" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>323655</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>295685</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>265989</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <v>234462</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <v>200991</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>391</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -6993,19 +6994,19 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="52" t="s">
+      <c r="G20" s="53" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="53" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7013,19 +7014,19 @@
       <c r="A21" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>0.20148130933167066</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>0.38854013963461814</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>0.48780762672183775</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>0.54675147116204</v>
       </c>
     </row>
@@ -7033,19 +7034,19 @@
       <c r="A22" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="52">
         <v>-2.26</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="52">
         <v>11.2</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="52">
         <v>29.6</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="52">
         <v>48.32</v>
       </c>
-      <c r="H22" s="51">
+      <c r="H22" s="52">
         <v>68.01</v>
       </c>
     </row>
@@ -7053,19 +7054,19 @@
       <c r="A23" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>0.2</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>0.5</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -7073,19 +7074,19 @@
       <c r="A24" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <v>120</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <v>200</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="28">
         <v>300</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="28">
         <v>400</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="28">
         <v>500</v>
       </c>
     </row>
@@ -7140,32 +7141,32 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="54" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="55" t="s">
         <v>398</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="55" t="s">
         <v>399</v>
       </c>
-      <c r="E5" s="54" t="s">
+      <c r="E5" s="55" t="s">
         <v>400</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="55" t="s">
         <v>401</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="G5" s="55" t="s">
         <v>402</v>
       </c>
     </row>
@@ -7173,19 +7174,19 @@
       <c r="B6" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="56">
         <v>120</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="56">
         <v>200</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="56">
         <v>300</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="56">
         <v>400</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="56">
         <v>500</v>
       </c>
     </row>
@@ -7193,19 +7194,19 @@
       <c r="B7" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="57">
         <v>1178333.3333333335</v>
       </c>
-      <c r="D7" s="56">
+      <c r="D7" s="57">
         <v>2261600</v>
       </c>
-      <c r="E7" s="56">
+      <c r="E7" s="57">
         <v>3367965</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="57">
         <v>4502531.525</v>
       </c>
-      <c r="G7" s="56">
+      <c r="G7" s="57">
         <v>5696361.453</v>
       </c>
     </row>
@@ -7213,19 +7214,19 @@
       <c r="B8" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="57">
         <v>780535</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="57">
         <v>964741.26</v>
       </c>
-      <c r="E8" s="56">
+      <c r="E8" s="57">
         <v>993683.4978</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="57">
         <v>1023494.002734</v>
       </c>
-      <c r="G8" s="56">
+      <c r="G8" s="57">
         <v>1054198.82281602</v>
       </c>
     </row>
@@ -7233,19 +7234,19 @@
       <c r="B9" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="57">
         <v>503333.3333333334</v>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="57">
         <v>774560</v>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="57">
         <v>994063.2999999999</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="57">
         <v>1226039.6940000001</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="57">
         <v>1471040.01467</v>
       </c>
     </row>
@@ -7253,19 +7254,19 @@
       <c r="B10" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="57">
         <v>46628.6108154935</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="57">
         <v>46628.6108154935</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="57">
         <v>46628.6108154935</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="57">
         <v>46628.6108154935</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="57">
         <v>46628.6108154935</v>
       </c>
     </row>
@@ -7273,19 +7274,19 @@
       <c r="B11" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="58">
         <v>-212163.6108154934</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="59">
         <v>455670.12918450637</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="59">
         <v>1308589.5913845068</v>
       </c>
-      <c r="F11" s="58">
+      <c r="F11" s="59">
         <v>2196369.217450507</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="59">
         <v>3114494.004698486</v>
       </c>
     </row>
@@ -7293,19 +7294,19 @@
       <c r="B12" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="58">
+      <c r="C12" s="59">
         <v>74498</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="59">
         <v>530168.1291845064</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="59">
         <v>1838757.7205690132</v>
       </c>
-      <c r="F12" s="58">
+      <c r="F12" s="59">
         <v>4035126.93801952</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G12" s="59">
         <v>7149620.942718007</v>
       </c>
     </row>
@@ -7313,19 +7314,19 @@
       <c r="B13" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="60">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="61">
         <v>0.20148130933167066</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="61">
         <v>0.38854013963461814</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="61">
         <v>0.48780762672183775</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G13" s="61">
         <v>0.54675147116204</v>
       </c>
     </row>
@@ -7333,19 +7334,19 @@
       <c r="B14" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="56">
+      <c r="C14" s="57">
         <v>9819.444444444445</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D14" s="57">
         <v>11308</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E14" s="57">
         <v>11226.55</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="57">
         <v>11256.328812500002</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="57">
         <v>11392.722905999999</v>
       </c>
     </row>
@@ -7353,19 +7354,19 @@
       <c r="B15" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="C15" s="59">
+      <c r="C15" s="60">
         <v>0.6624059405940593</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="61">
         <v>0.4265746639547223</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="61">
         <v>0.29503973402336425</v>
       </c>
-      <c r="F15" s="60">
+      <c r="F15" s="61">
         <v>0.22731523300861284</v>
       </c>
-      <c r="G15" s="60">
+      <c r="G15" s="61">
         <v>0.18506529677129674</v>
       </c>
     </row>
@@ -7373,19 +7374,19 @@
       <c r="B16" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="C16" s="60">
+      <c r="C16" s="61">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="61">
         <v>0.10274495932083481</v>
       </c>
-      <c r="E16" s="60">
+      <c r="E16" s="61">
         <v>0.08854575092080826</v>
       </c>
-      <c r="F16" s="60">
+      <c r="F16" s="61">
         <v>0.0816900239693491</v>
       </c>
-      <c r="G16" s="60">
+      <c r="G16" s="61">
         <v>0.07747261265673058</v>
       </c>
     </row>
@@ -7393,19 +7394,19 @@
       <c r="B17" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="60">
         <v>-0.08956294200848645</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="61">
         <v>0.23094213830916166</v>
       </c>
-      <c r="E17" s="60">
+      <c r="E17" s="61">
         <v>0.40980776290727494</v>
       </c>
-      <c r="F17" s="60">
+      <c r="F17" s="61">
         <v>0.5003846870935568</v>
       </c>
-      <c r="G17" s="60">
+      <c r="G17" s="61">
         <v>0.5566926610396014</v>
       </c>
     </row>
@@ -7413,19 +7414,19 @@
       <c r="B18" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="C18" s="61">
+      <c r="C18" s="62">
         <v>-2.2633099754482346</v>
       </c>
-      <c r="D18" s="62">
+      <c r="D18" s="63">
         <v>11.201250281006729</v>
       </c>
-      <c r="E18" s="62">
+      <c r="E18" s="63">
         <v>29.600242813611526</v>
       </c>
-      <c r="F18" s="62">
+      <c r="F18" s="63">
         <v>48.31792731679209</v>
       </c>
-      <c r="G18" s="62">
+      <c r="G18" s="63">
         <v>68.00808688171976</v>
       </c>
     </row>
@@ -7433,156 +7434,156 @@
       <c r="B19" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="64" t="s">
         <v>399</v>
       </c>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="C20" s="64" t="s">
+      <c r="C20" s="65" t="s">
         <v>409</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>412</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17" t="s">
+      <c r="E22" s="18"/>
+      <c r="F22" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="18"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="41" t="s">
         <v>414</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="C23" s="66" t="s">
         <v>415</v>
       </c>
-      <c r="D23" s="66" t="s">
+      <c r="D23" s="67" t="s">
         <v>416</v>
       </c>
-      <c r="E23" s="66"/>
-      <c r="F23" s="67" t="s">
+      <c r="E23" s="67"/>
+      <c r="F23" s="68" t="s">
         <v>417</v>
       </c>
-      <c r="G23" s="67"/>
+      <c r="G23" s="68"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="41" t="s">
         <v>418</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="69" t="s">
         <v>419</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="D24" s="67" t="s">
         <v>420</v>
       </c>
-      <c r="E24" s="66"/>
-      <c r="F24" s="67" t="s">
+      <c r="E24" s="67"/>
+      <c r="F24" s="68" t="s">
         <v>421</v>
       </c>
-      <c r="G24" s="67"/>
+      <c r="G24" s="68"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="41" t="s">
         <v>422</v>
       </c>
-      <c r="C25" s="65" t="s">
+      <c r="C25" s="66" t="s">
         <v>415</v>
       </c>
-      <c r="D25" s="66" t="s">
+      <c r="D25" s="67" t="s">
         <v>423</v>
       </c>
-      <c r="E25" s="66"/>
-      <c r="F25" s="67" t="s">
+      <c r="E25" s="67"/>
+      <c r="F25" s="68" t="s">
         <v>424</v>
       </c>
-      <c r="G25" s="67"/>
+      <c r="G25" s="68"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="41" t="s">
         <v>425</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="66" t="s">
         <v>415</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="D26" s="67" t="s">
         <v>426</v>
       </c>
-      <c r="E26" s="66"/>
-      <c r="F26" s="67" t="s">
+      <c r="E26" s="67"/>
+      <c r="F26" s="68" t="s">
         <v>427</v>
       </c>
-      <c r="G26" s="67"/>
+      <c r="G26" s="68"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="41" t="s">
         <v>428</v>
       </c>
-      <c r="C27" s="65" t="s">
+      <c r="C27" s="66" t="s">
         <v>415</v>
       </c>
-      <c r="D27" s="66" t="s">
+      <c r="D27" s="67" t="s">
         <v>429</v>
       </c>
-      <c r="E27" s="66"/>
-      <c r="F27" s="67" t="s">
+      <c r="E27" s="67"/>
+      <c r="F27" s="68" t="s">
         <v>430</v>
       </c>
-      <c r="G27" s="67"/>
+      <c r="G27" s="68"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="41" t="s">
         <v>431</v>
       </c>
-      <c r="C28" s="65" t="s">
+      <c r="C28" s="66" t="s">
         <v>415</v>
       </c>
-      <c r="D28" s="66" t="s">
+      <c r="D28" s="67" t="s">
         <v>432</v>
       </c>
-      <c r="E28" s="66"/>
-      <c r="F28" s="67" t="s">
+      <c r="E28" s="67"/>
+      <c r="F28" s="68" t="s">
         <v>433</v>
       </c>
-      <c r="G28" s="67"/>
+      <c r="G28" s="68"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="41" t="s">
         <v>434</v>
       </c>
-      <c r="C29" s="65" t="s">
+      <c r="C29" s="66" t="s">
         <v>415</v>
       </c>
-      <c r="D29" s="66" t="s">
+      <c r="D29" s="67" t="s">
         <v>435</v>
       </c>
-      <c r="E29" s="66"/>
-      <c r="F29" s="67" t="s">
+      <c r="E29" s="67"/>
+      <c r="F29" s="68" t="s">
         <v>436</v>
       </c>
-      <c r="G29" s="67"/>
+      <c r="G29" s="68"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="41" t="s">
         <v>437</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -7592,14 +7593,14 @@
       <c r="E31" s="10"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="69" t="s">
+      <c r="B33" s="70" t="s">
         <v>439</v>
       </c>
-      <c r="C33" s="69"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
-      <c r="F33" s="69"/>
-      <c r="G33" s="69"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -7735,27 +7736,30 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7763,7 +7767,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7771,7 +7775,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7779,7 +7783,7 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>38</v>
       </c>
     </row>
@@ -7787,7 +7791,7 @@
       <c r="A9" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7795,7 +7799,7 @@
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -7803,7 +7807,7 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7811,7 +7815,7 @@
       <c r="A12" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>7</v>
       </c>
     </row>
@@ -7819,38 +7823,38 @@
       <c r="A13" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>600</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7858,47 +7862,47 @@
       <c r="A17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="21">
         <v>120</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>200</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>300</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>400</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>500</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -7912,10 +7916,10 @@
       <c r="C21" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <v>8500</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7929,10 +7933,10 @@
       <c r="C22" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <v>750</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7946,10 +7950,10 @@
       <c r="C23" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="22">
         <v>1100</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7963,10 +7967,10 @@
       <c r="C24" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="22">
         <v>150000</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7980,10 +7984,10 @@
       <c r="C25" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="22">
         <v>25000</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7997,44 +8001,44 @@
       <c r="C26" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="22">
         <v>400</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="20" t="s">
         <v>130</v>
       </c>
     </row>
@@ -8048,16 +8052,16 @@
       <c r="C30" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="24">
         <v>1</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="22">
         <v>105000</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="23">
         <v>0.26</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8071,16 +8075,16 @@
       <c r="C31" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="24">
         <v>1</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <v>82000</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <v>0.26</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8094,16 +8098,16 @@
       <c r="C32" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="24">
         <v>5</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="22">
         <v>50000</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="23">
         <v>0.26</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8117,16 +8121,16 @@
       <c r="C33" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="24">
         <v>1</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="22">
         <v>53000</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="23">
         <v>0.26</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8140,16 +8144,16 @@
       <c r="C34" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="24">
         <v>3</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="22">
         <v>28000</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="23">
         <v>0.18</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8163,16 +8167,16 @@
       <c r="C35" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="24">
         <v>1</v>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="22">
         <v>62000</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="23">
         <v>0.26</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8186,44 +8190,44 @@
       <c r="C36" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="24">
         <v>2</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="22">
         <v>36000</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="23">
         <v>0.22</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="23">
         <v>0.0765</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -8237,10 +8241,10 @@
       <c r="C40" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="22">
         <v>22000</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="23">
         <v>0.03</v>
       </c>
     </row>
@@ -8254,10 +8258,10 @@
       <c r="C41" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="22">
         <v>3000</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8271,10 +8275,10 @@
       <c r="C42" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="22">
         <v>22000</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8288,10 +8292,10 @@
       <c r="C43" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="22">
         <v>650</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8305,10 +8309,10 @@
       <c r="C44" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="21">
+      <c r="D44" s="22">
         <v>450</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8322,10 +8326,10 @@
       <c r="C45" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="22">
         <v>30000</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8339,10 +8343,10 @@
       <c r="C46" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D46" s="21">
+      <c r="D46" s="22">
         <v>12000</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8356,10 +8360,10 @@
       <c r="C47" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="22">
         <v>18000</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8373,38 +8377,38 @@
       <c r="C48" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D48" s="21">
+      <c r="D48" s="22">
         <v>750</v>
       </c>
-      <c r="E48" s="22">
+      <c r="E48" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D51" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="20" t="s">
         <v>161</v>
       </c>
     </row>
@@ -8415,13 +8419,13 @@
       <c r="B52" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="22">
         <v>350000</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="23">
         <v>0.06</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="21">
         <v>10</v>
       </c>
     </row>
@@ -8432,35 +8436,35 @@
       <c r="B53" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C53" s="21">
+      <c r="C53" s="22">
         <v>60000</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="23">
         <v>0</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B56" s="22">
+      <c r="B56" s="23">
         <v>0.03</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="C56" s="25" t="s">
         <v>168</v>
       </c>
     </row>
@@ -8468,10 +8472,10 @@
       <c r="A57" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B57" s="22">
+      <c r="B57" s="23">
         <v>0.03</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="25" t="s">
         <v>170</v>
       </c>
     </row>
@@ -8479,7 +8483,7 @@
       <c r="A58" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B58" s="24">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -8487,7 +8491,7 @@
       <c r="A59" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B59" s="21">
+      <c r="B59" s="22">
         <v>0</v>
       </c>
     </row>
@@ -8495,26 +8499,26 @@
       <c r="A60" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="19" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="19" t="s">
         <v>177</v>
       </c>
     </row>
@@ -8522,7 +8526,7 @@
       <c r="A64" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="19" t="s">
         <v>146</v>
       </c>
     </row>
@@ -8530,7 +8534,7 @@
       <c r="A65" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="21">
         <v>0</v>
       </c>
     </row>
@@ -8538,7 +8542,7 @@
       <c r="A66" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="21">
         <v>0</v>
       </c>
     </row>
@@ -8546,21 +8550,21 @@
       <c r="A67" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B67" s="25">
+      <c r="B67" s="26">
         <v>0.95</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="19" t="s">
+      <c r="A69" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="C69" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="20" t="s">
         <v>185</v>
       </c>
     </row>
@@ -8568,33 +8572,33 @@
       <c r="A70" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="B70" s="21">
+      <c r="B70" s="22">
         <v>8200</v>
       </c>
-      <c r="C70" s="21">
+      <c r="C70" s="22">
         <v>9100</v>
       </c>
-      <c r="D70" s="21">
+      <c r="D70" s="22">
         <v>10500</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="19" t="s">
+      <c r="A72" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B72" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D72" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="19" t="s">
+      <c r="E72" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F72" s="19" t="s">
+      <c r="F72" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -8602,19 +8606,19 @@
       <c r="A73" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B73" s="20">
+      <c r="B73" s="21">
         <v>80</v>
       </c>
-      <c r="C73" s="20">
+      <c r="C73" s="21">
         <v>130</v>
       </c>
-      <c r="D73" s="20">
+      <c r="D73" s="21">
         <v>180</v>
       </c>
-      <c r="E73" s="20">
+      <c r="E73" s="21">
         <v>230</v>
       </c>
-      <c r="F73" s="20">
+      <c r="F73" s="21">
         <v>260</v>
       </c>
     </row>
@@ -8622,19 +8626,19 @@
       <c r="A74" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="B74" s="20">
+      <c r="B74" s="21">
         <v>40</v>
       </c>
-      <c r="C74" s="20">
+      <c r="C74" s="21">
         <v>70</v>
       </c>
-      <c r="D74" s="20">
+      <c r="D74" s="21">
         <v>100</v>
       </c>
-      <c r="E74" s="20">
+      <c r="E74" s="21">
         <v>120</v>
       </c>
-      <c r="F74" s="20">
+      <c r="F74" s="21">
         <v>140</v>
       </c>
     </row>
@@ -8642,19 +8646,19 @@
       <c r="A75" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B75" s="20">
+      <c r="B75" s="21">
         <v>0</v>
       </c>
-      <c r="C75" s="20">
+      <c r="C75" s="21">
         <v>0</v>
       </c>
-      <c r="D75" s="20">
+      <c r="D75" s="21">
         <v>20</v>
       </c>
-      <c r="E75" s="20">
+      <c r="E75" s="21">
         <v>50</v>
       </c>
-      <c r="F75" s="20">
+      <c r="F75" s="21">
         <v>100</v>
       </c>
     </row>
@@ -8836,52 +8840,52 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>120</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>200</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <v>300</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>400</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <v>500</v>
       </c>
     </row>
@@ -8889,7 +8893,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>600</v>
       </c>
     </row>
@@ -8897,19 +8901,19 @@
       <c r="A8" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="29">
         <v>0.2</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>0.5</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -8920,16 +8924,16 @@
       <c r="B10" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>0.6666666666666666</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>0.5</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>0.25</v>
       </c>
     </row>
@@ -8968,52 +8972,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>969000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1617850</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>2466200</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>3327850</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>4233200</v>
       </c>
     </row>
@@ -9021,19 +9025,19 @@
       <c r="A6" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>90000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>154500</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>238703</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>327818</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>422066</v>
       </c>
     </row>
@@ -9041,19 +9045,19 @@
       <c r="A7" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>132000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>226600</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>350097</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>480800</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>619030</v>
       </c>
     </row>
@@ -9061,19 +9065,19 @@
       <c r="A8" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>150000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>154500</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>159135</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>163909</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>168826</v>
       </c>
     </row>
@@ -9081,19 +9085,19 @@
       <c r="A9" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>25000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>25750</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>26523</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>27318</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>28138</v>
       </c>
     </row>
@@ -9101,43 +9105,43 @@
       <c r="A10" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>48000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>82400</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>127308</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>174836</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>225102</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>SUM(B5:B10)</f>
         <v>1414000</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
@@ -9182,25 +9186,25 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="20" t="s">
         <v>222</v>
       </c>
     </row>
@@ -9211,19 +9215,19 @@
       <c r="B4" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <v>1</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>105000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>0.26</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="34">
         <v>140333</v>
       </c>
     </row>
@@ -9234,19 +9238,19 @@
       <c r="B5" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="33">
         <v>1</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>82000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>0.26</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <v>109593</v>
       </c>
     </row>
@@ -9257,19 +9261,19 @@
       <c r="B6" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <v>5</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>50000</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>0.26</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="34">
         <v>334125</v>
       </c>
     </row>
@@ -9280,19 +9284,19 @@
       <c r="B7" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <v>1</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>53000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>0.26</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="34">
         <v>70835</v>
       </c>
     </row>
@@ -9303,19 +9307,19 @@
       <c r="B8" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>3</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>28000</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>0.18</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="34">
         <v>105546</v>
       </c>
     </row>
@@ -9326,19 +9330,19 @@
       <c r="B9" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>1</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>62000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0.26</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="34">
         <v>82863</v>
       </c>
     </row>
@@ -9349,50 +9353,50 @@
       <c r="B10" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <v>2</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>36000</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>0.22</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="34">
         <v>93348</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -9400,19 +9404,19 @@
       <c r="A14" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <v>780535</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <v>964741</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <v>993683</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <v>1023494</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <v>1054199</v>
       </c>
     </row>
@@ -9420,19 +9424,19 @@
       <c r="A15" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>0.5520049504950495</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>0.4265746639547223</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>0.29503973402336425</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>0.22731523300861284</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>0.18506529677129674</v>
       </c>
     </row>
@@ -9440,19 +9444,19 @@
       <c r="A16" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <v>8.6</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="35">
         <v>14.3</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="35">
         <v>21.4</v>
       </c>
-      <c r="E16" s="34">
+      <c r="E16" s="35">
         <v>28.6</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="35">
         <v>35.7</v>
       </c>
     </row>
@@ -9491,52 +9495,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>78000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>133900</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>206875</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>284109</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>365790</v>
       </c>
     </row>
@@ -9544,54 +9548,54 @@
       <c r="A6" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <f>SUM(B5:B5)</f>
         <v>78000</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="36">
         <f>SUM(C5:C5)</f>
         <v>133900</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="36">
         <f>SUM(D5:D5)</f>
         <v>206875</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="36">
         <f>SUM(E5:E5)</f>
         <v>284109</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="36">
         <f>SUM(F5:F5)</f>
         <v>365790</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>54000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>92700</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>143222</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>196691</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>253239</v>
       </c>
     </row>
@@ -9599,54 +9603,54 @@
       <c r="A9" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B8:B8)</f>
         <v>54000</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>SUM(C8:C8)</f>
         <v>92700</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <f>SUM(D8:D8)</f>
         <v>143222</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="36">
         <f>SUM(E8:E8)</f>
         <v>196691</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="36">
         <f>SUM(F8:F8)</f>
         <v>253239</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>264000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>271920</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>280078</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>288480</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>297134</v>
       </c>
     </row>
@@ -9654,19 +9658,19 @@
       <c r="A12" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>36000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>37080</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>38192</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>39338</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>40518</v>
       </c>
     </row>
@@ -9674,19 +9678,19 @@
       <c r="A13" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>22000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>22660</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>23340</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>24040</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>24761</v>
       </c>
     </row>
@@ -9694,54 +9698,54 @@
       <c r="A14" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="36">
         <f>SUM(B11:B13)</f>
         <v>322000</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>SUM(C11:C13)</f>
         <v>331660</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="36">
         <f>SUM(D11:D13)</f>
         <v>341610</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>SUM(E11:E13)</f>
         <v>351858</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="36">
         <f>SUM(F11:F13)</f>
         <v>362414</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>30000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>30900</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>31827</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>32782</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>33765</v>
       </c>
     </row>
@@ -9749,19 +9753,19 @@
       <c r="A17" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>12000</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>12360</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>12731</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>13113</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>13506</v>
       </c>
     </row>
@@ -9769,19 +9773,19 @@
       <c r="A18" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <v>18000</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>18540</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>19096</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>19669</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>20259</v>
       </c>
     </row>
@@ -9789,19 +9793,19 @@
       <c r="A19" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <v>90000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>154500</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>238703</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>327818</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>422066</v>
       </c>
     </row>
@@ -9809,48 +9813,48 @@
       <c r="A20" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="36">
         <f>SUM(B16:B19)</f>
         <v>150000</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="36">
         <f>SUM(C16:C19)</f>
         <v>216300</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="36">
         <f>SUM(D16:D19)</f>
         <v>302357</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="36">
         <f>SUM(E16:E19)</f>
         <v>393382</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="36">
         <f>SUM(F16:F19)</f>
         <v>489596</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>B6+B9+B14+B20</f>
         <v>604000</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>C6+C9+C14+C20</f>
         <v>774560</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <f>D6+D9+D14+D20</f>
         <v>994063</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <f>E6+E9+E14+E20</f>
         <v>1226040</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>F6+F9+F14+F20</f>
         <v>1471040</v>
       </c>
@@ -9891,22 +9895,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>243</v>
       </c>
     </row>
@@ -9917,16 +9921,16 @@
       <c r="B4" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="22">
         <v>350000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>0.06</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="28">
         <v>10</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <v>46629</v>
       </c>
     </row>
@@ -9937,16 +9941,16 @@
       <c r="B5" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="22">
         <v>60000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <v>0</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <v>60000</v>
       </c>
     </row>
@@ -9954,7 +9958,7 @@
       <c r="A7" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <v>46629</v>
       </c>
     </row>
@@ -9962,7 +9966,7 @@
       <c r="A8" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="36">
         <v>350000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="440">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -673,112 +673,112 @@
     <t>Tuition &amp; Funding Drivers</t>
   </si>
   <si>
-    <t>REVENUE BY LINE ITEM</t>
-  </si>
-  <si>
-    <t>State Per-Pupil Funding (Public Funding)</t>
-  </si>
-  <si>
-    <t>Federal Title I (Public Funding)</t>
-  </si>
-  <si>
-    <t>IDEA Special Ed (Public Funding)</t>
-  </si>
-  <si>
-    <t>CSP Startup Grant (Philanthropy)</t>
-  </si>
-  <si>
-    <t>Annual Fundraising (Philanthropy)</t>
-  </si>
-  <si>
-    <t>Before/After Care (Other Revenue)</t>
+    <t>PUBLIC FUNDING</t>
+  </si>
+  <si>
+    <t>Total Public Funding</t>
+  </si>
+  <si>
+    <t>PHILANTHROPY</t>
+  </si>
+  <si>
+    <t>Total Philanthropy</t>
+  </si>
+  <si>
+    <t>OTHER REVENUE</t>
+  </si>
+  <si>
+    <t>Total Other Revenue</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL REVENUE</t>
+  </si>
+  <si>
+    <t>Base Rate</t>
+  </si>
+  <si>
+    <t>Loaded Cost</t>
+  </si>
+  <si>
+    <t>5-YEAR TOTAL PERSONNEL COST</t>
+  </si>
+  <si>
+    <t>Total Personnel</t>
+  </si>
+  <si>
+    <t>Personnel as % of Revenue</t>
+  </si>
+  <si>
+    <t>Students per FTE</t>
+  </si>
+  <si>
+    <t>Operating Expense Drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Curriculum</t>
+  </si>
+  <si>
+    <t>Total Instructional / Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Devices &amp; Software</t>
+  </si>
+  <si>
+    <t>Total Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility Lease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Property Insurance</t>
+  </si>
+  <si>
+    <t>Total Occupancy / Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Professional Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Legal &amp; Audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Food Service</t>
+  </si>
+  <si>
+    <t>Total Administrative / General</t>
+  </si>
+  <si>
+    <t>TOTAL OPERATING EXPENSES</t>
+  </si>
+  <si>
+    <t>Capital Stack &amp; Loan Terms</t>
+  </si>
+  <si>
+    <t>Annual Payment</t>
+  </si>
+  <si>
+    <t>Capital Expense</t>
+  </si>
+  <si>
+    <t>Total Annual Debt Service</t>
+  </si>
+  <si>
+    <t>Total Loan Principal</t>
+  </si>
+  <si>
+    <t>Enrollment &amp; Tuition Forecast</t>
+  </si>
+  <si>
+    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>TOTAL REVENUE</t>
-  </si>
-  <si>
-    <t>Base Rate</t>
-  </si>
-  <si>
-    <t>Loaded Cost</t>
-  </si>
-  <si>
-    <t>5-YEAR TOTAL PERSONNEL COST</t>
-  </si>
-  <si>
-    <t>Total Personnel</t>
-  </si>
-  <si>
-    <t>Personnel as % of Revenue</t>
-  </si>
-  <si>
-    <t>Students per FTE</t>
-  </si>
-  <si>
-    <t>Operating Expense Drivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Curriculum</t>
-  </si>
-  <si>
-    <t>Total Instructional / Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Devices &amp; Software</t>
-  </si>
-  <si>
-    <t>Total Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility Lease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Property Insurance</t>
-  </si>
-  <si>
-    <t>Total Occupancy / Facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Professional Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Legal &amp; Audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Food Service</t>
-  </si>
-  <si>
-    <t>Total Administrative / General</t>
-  </si>
-  <si>
-    <t>TOTAL OPERATING EXPENSES</t>
-  </si>
-  <si>
-    <t>Capital Stack &amp; Loan Terms</t>
-  </si>
-  <si>
-    <t>Annual Payment</t>
-  </si>
-  <si>
-    <t>Capital Expense</t>
-  </si>
-  <si>
-    <t>Total Annual Debt Service</t>
-  </si>
-  <si>
-    <t>Total Loan Principal</t>
-  </si>
-  <si>
-    <t>Enrollment &amp; Tuition Forecast</t>
-  </si>
-  <si>
-    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>Revenue per Student</t>
@@ -1607,15 +1607,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2380,7 +2380,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2442,19 +2442,19 @@
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>969000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>1617850</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>2466200</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>3327850</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>4233200</v>
       </c>
     </row>
@@ -2462,19 +2462,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>90000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>154500</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>238703</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>327818</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>422066</v>
       </c>
     </row>
@@ -2482,19 +2482,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <v>132000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>226600</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>350097</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>480800</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>619030</v>
       </c>
     </row>
@@ -2502,19 +2502,19 @@
       <c r="A10" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>150000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>154500</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <v>159135</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>163909</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <v>168826</v>
       </c>
     </row>
@@ -2522,19 +2522,19 @@
       <c r="A11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>25000</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>25750</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>26523</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <v>27318</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>28138</v>
       </c>
     </row>
@@ -2542,25 +2542,25 @@
       <c r="A12" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>48000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>82400</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="30">
         <v>127308</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>174836</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>225102</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="B13" s="32">
         <f>SUM(B7:B12)</f>
@@ -2587,19 +2587,19 @@
       <c r="A15" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>11783</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="30">
         <v>11308</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <v>11227</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>11256</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>11393</v>
       </c>
     </row>
@@ -2671,19 +2671,19 @@
       <c r="A5" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <v>278438</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>344149</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>354473</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>365107</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>376061</v>
       </c>
     </row>
@@ -2691,19 +2691,19 @@
       <c r="A6" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>59029</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>72960</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>75148</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>77403</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>79725</v>
       </c>
     </row>
@@ -2711,19 +2711,19 @@
       <c r="A7" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>87955</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>108712</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>111974</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>115333</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>118793</v>
       </c>
     </row>
@@ -2731,23 +2731,23 @@
       <c r="A8" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>425421</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>525821</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>541595</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>557843</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>574578</v>
       </c>
@@ -2766,19 +2766,19 @@
       <c r="A10" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>116944</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>144542</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <v>148879</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>153345</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <v>157945</v>
       </c>
     </row>
@@ -2786,19 +2786,19 @@
       <c r="A11" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>91328</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>112881</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>116267</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <v>119755</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>123348</v>
       </c>
     </row>
@@ -2806,23 +2806,23 @@
       <c r="A12" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="31">
         <f>SUM(B10:B11)</f>
         <v>208271</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="31">
         <f>SUM(C10:C11)</f>
         <v>257423</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="31">
         <f>SUM(D10:D11)</f>
         <v>265146</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="31">
         <f>SUM(E10:E11)</f>
         <v>273100</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="31">
         <f>SUM(F10:F11)</f>
         <v>281293</v>
       </c>
@@ -2841,19 +2841,19 @@
       <c r="A14" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>69053</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="30">
         <v>85349</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>87909</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <v>90547</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>93263</v>
       </c>
     </row>
@@ -2861,23 +2861,23 @@
       <c r="A15" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="31">
         <f>SUM(B14:B14)</f>
         <v>69053</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="31">
         <f>SUM(C14:C14)</f>
         <v>85349</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="31">
         <f>SUM(D14:D14)</f>
         <v>87909</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="31">
         <f>SUM(E14:E14)</f>
         <v>90547</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="31">
         <f>SUM(F14:F14)</f>
         <v>93263</v>
       </c>
@@ -2896,19 +2896,19 @@
       <c r="A17" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="30">
         <v>77790</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>96148</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>99033</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>102004</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>105064</v>
       </c>
     </row>
@@ -2916,23 +2916,23 @@
       <c r="A18" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="31">
         <f>SUM(B17:B17)</f>
         <v>77790</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="31">
         <f>SUM(C17:C17)</f>
         <v>96148</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="31">
         <f>SUM(D17:D17)</f>
         <v>99033</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="31">
         <f>SUM(E17:E17)</f>
         <v>102004</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="31">
         <f>SUM(F17:F17)</f>
         <v>105064</v>
       </c>
@@ -3030,19 +3030,19 @@
       <c r="A5" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <v>807500</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>1617850</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>2466200</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>3327850</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>4233200</v>
       </c>
     </row>
@@ -3050,19 +3050,19 @@
       <c r="A6" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>75000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>154500</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>238703</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>327818</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>422066</v>
       </c>
     </row>
@@ -3070,19 +3070,19 @@
       <c r="A7" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>110000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>226600</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>350097</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>480800</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>619030</v>
       </c>
     </row>
@@ -3090,19 +3090,19 @@
       <c r="A8" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>125000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>154500</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>159135</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>163909</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>168826</v>
       </c>
     </row>
@@ -3110,19 +3110,19 @@
       <c r="A9" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <v>20833</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>25750</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>26523</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>27318</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>28138</v>
       </c>
     </row>
@@ -3130,19 +3130,19 @@
       <c r="A10" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>40000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>82400</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <v>127308</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>174836</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <v>225102</v>
       </c>
     </row>
@@ -3150,23 +3150,23 @@
       <c r="A11" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="31">
         <f>SUM(B5:B10)</f>
         <v>1178333</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="31">
         <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="31">
         <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="31">
         <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="31">
         <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
@@ -3185,19 +3185,19 @@
       <c r="A14" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>116944</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="30">
         <v>144542</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>148879</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <v>153345</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>157945</v>
       </c>
     </row>
@@ -3205,19 +3205,19 @@
       <c r="A15" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>91328</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="30">
         <v>112881</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <v>116267</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>119755</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>123348</v>
       </c>
     </row>
@@ -3225,19 +3225,19 @@
       <c r="A16" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>278438</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>344149</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>354473</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>365107</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>376061</v>
       </c>
     </row>
@@ -3245,19 +3245,19 @@
       <c r="A17" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="30">
         <v>59029</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>72960</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>75148</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>77403</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>79725</v>
       </c>
     </row>
@@ -3265,19 +3265,19 @@
       <c r="A18" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="30">
         <v>87955</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>108712</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="30">
         <v>111974</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <v>115333</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <v>118793</v>
       </c>
     </row>
@@ -3285,19 +3285,19 @@
       <c r="A19" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>69053</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>85349</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="30">
         <v>87909</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="30">
         <v>90547</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <v>93263</v>
       </c>
     </row>
@@ -3305,43 +3305,43 @@
       <c r="A20" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>77790</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="30">
         <v>96148</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="30">
         <v>99033</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="30">
         <v>102004</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <v>105064</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B21" s="36">
+        <v>223</v>
+      </c>
+      <c r="B21" s="31">
         <f>SUM(B14:B20)</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="31">
         <f>SUM(C14:C20)</f>
         <v>964741</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="31">
         <f>SUM(D14:D20)</f>
         <v>993683</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="31">
         <f>SUM(E14:E20)</f>
         <v>1023494</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="31">
         <f>SUM(F14:F20)</f>
         <v>1054199</v>
       </c>
@@ -3365,19 +3365,19 @@
       <c r="A25" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="30">
         <v>65000</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="30">
         <v>133900</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="30">
         <v>206875</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="30">
         <v>284109</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="30">
         <v>365790</v>
       </c>
     </row>
@@ -3390,19 +3390,19 @@
       <c r="A27" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>45000</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="30">
         <v>92700</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="30">
         <v>143222</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="30">
         <v>196691</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="30">
         <v>253239</v>
       </c>
     </row>
@@ -3415,19 +3415,19 @@
       <c r="A29" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B29" s="31">
+      <c r="B29" s="30">
         <v>220000</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="30">
         <v>271920</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="30">
         <v>280078</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="30">
         <v>288480</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="30">
         <v>297134</v>
       </c>
     </row>
@@ -3435,19 +3435,19 @@
       <c r="A30" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="30">
         <v>30000</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="30">
         <v>37080</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="30">
         <v>38192</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="30">
         <v>39338</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="30">
         <v>40518</v>
       </c>
     </row>
@@ -3455,19 +3455,19 @@
       <c r="A31" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="30">
         <v>18333</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="30">
         <v>22660</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="30">
         <v>23340</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="30">
         <v>24040</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="30">
         <v>24761</v>
       </c>
     </row>
@@ -3475,23 +3475,23 @@
       <c r="A32" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B32" s="36">
+      <c r="B32" s="31">
         <f>SUM(B29:B31)</f>
         <v>268333</v>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="31">
         <f>SUM(C29:C31)</f>
         <v>331660</v>
       </c>
-      <c r="D32" s="36">
+      <c r="D32" s="31">
         <f>SUM(D29:D31)</f>
         <v>341610</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="31">
         <f>SUM(E29:E31)</f>
         <v>351858</v>
       </c>
-      <c r="F32" s="36">
+      <c r="F32" s="31">
         <f>SUM(F29:F31)</f>
         <v>362414</v>
       </c>
@@ -3505,19 +3505,19 @@
       <c r="A34" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="30">
         <v>25000</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="30">
         <v>30900</v>
       </c>
-      <c r="D34" s="31">
+      <c r="D34" s="30">
         <v>31827</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="30">
         <v>32782</v>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="30">
         <v>33765</v>
       </c>
     </row>
@@ -3525,19 +3525,19 @@
       <c r="A35" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="30">
         <v>10000</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="30">
         <v>12360</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D35" s="30">
         <v>12731</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="30">
         <v>13113</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="30">
         <v>13506</v>
       </c>
     </row>
@@ -3545,19 +3545,19 @@
       <c r="A36" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="30">
         <v>15000</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="30">
         <v>18540</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="30">
         <v>19096</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="30">
         <v>19669</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="30">
         <v>20259</v>
       </c>
     </row>
@@ -3565,19 +3565,19 @@
       <c r="A37" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B37" s="31">
+      <c r="B37" s="30">
         <v>75000</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="30">
         <v>154500</v>
       </c>
-      <c r="D37" s="31">
+      <c r="D37" s="30">
         <v>238703</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="30">
         <v>327818</v>
       </c>
-      <c r="F37" s="31">
+      <c r="F37" s="30">
         <v>422066</v>
       </c>
     </row>
@@ -3585,23 +3585,23 @@
       <c r="A38" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B38" s="36">
+      <c r="B38" s="31">
         <f>SUM(B34:B37)</f>
         <v>125000</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="31">
         <f>SUM(C34:C37)</f>
         <v>216300</v>
       </c>
-      <c r="D38" s="36">
+      <c r="D38" s="31">
         <f>SUM(D34:D37)</f>
         <v>302357</v>
       </c>
-      <c r="E38" s="36">
+      <c r="E38" s="31">
         <f>SUM(E34:E37)</f>
         <v>393382</v>
       </c>
-      <c r="F38" s="36">
+      <c r="F38" s="31">
         <f>SUM(F34:F37)</f>
         <v>489596</v>
       </c>
@@ -3610,23 +3610,23 @@
       <c r="A39" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B39" s="36">
+      <c r="B39" s="31">
         <f>B25+B27+B32+B38</f>
         <v>503333</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="31">
         <f>C25+C27+C32+C38</f>
         <v>774560</v>
       </c>
-      <c r="D39" s="36">
+      <c r="D39" s="31">
         <f>D25+D27+D32+D38</f>
         <v>994063</v>
       </c>
-      <c r="E39" s="36">
+      <c r="E39" s="31">
         <f>E25+E27+E32+E38</f>
         <v>1226040</v>
       </c>
-      <c r="F39" s="36">
+      <c r="F39" s="31">
         <f>F25+F27+F32+F38</f>
         <v>1471040</v>
       </c>
@@ -3645,19 +3645,19 @@
       <c r="A42" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="30">
         <v>46629</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="30">
         <v>46629</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="30">
         <v>46629</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="30">
         <v>46629</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="30">
         <v>46629</v>
       </c>
     </row>
@@ -3665,19 +3665,19 @@
       <c r="A43" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="30">
         <v>60000</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="30">
         <v>20000</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="30">
         <v>25000</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="30">
         <v>10000</v>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="30">
         <v>10000</v>
       </c>
     </row>
@@ -3685,23 +3685,23 @@
       <c r="A44" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="36">
+      <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
         <v>106629</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="31">
         <f>SUM(C42:C43)</f>
         <v>66629</v>
       </c>
-      <c r="D44" s="36">
+      <c r="D44" s="31">
         <f>SUM(D42:D43)</f>
         <v>71629</v>
       </c>
-      <c r="E44" s="36">
+      <c r="E44" s="31">
         <f>SUM(E42:E43)</f>
         <v>56629</v>
       </c>
-      <c r="F44" s="36">
+      <c r="F44" s="31">
         <f>SUM(F42:F43)</f>
         <v>56629</v>
       </c>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
@@ -3864,23 +3864,23 @@
       <c r="A8" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>1390497</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>1805930</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>2059375</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>2306162</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>2581867</v>
       </c>
@@ -3924,23 +3924,23 @@
       <c r="A12" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.54675147</v>
       </c>
@@ -3949,19 +3949,19 @@
       <c r="A13" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>-212164</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>243507</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>1552096</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>3748465</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>6862959</v>
       </c>
     </row>
@@ -3969,19 +3969,19 @@
       <c r="A14" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="30">
         <v>9819</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="30">
         <v>11308</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>11227</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <v>11256</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>11393</v>
       </c>
     </row>
@@ -3989,19 +3989,19 @@
       <c r="A15" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="30">
         <v>11587</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="30">
         <v>9030</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <v>6865</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>5765</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>5164</v>
       </c>
     </row>
@@ -4114,43 +4114,43 @@
       <c r="A4" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B4" s="36">
+      <c r="B4" s="31">
         <v>146500</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="31">
         <v>146500</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="31">
         <v>146500</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="31">
         <v>146500</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="31">
         <v>146500</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="31">
         <v>146500</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="31">
         <v>146500</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="31">
         <v>146500</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="31">
         <v>146500</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="31">
         <v>146500</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="31">
         <v>0</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="31">
         <v>0</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="31">
         <f>SUM(B4:M4)</f>
         <v>1465000</v>
       </c>
@@ -4177,43 +4177,43 @@
       <c r="A7" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>78054</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>78054</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>78054</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>78054</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>78054</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="30">
         <v>78054</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="30">
         <v>78054</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="30">
         <v>78054</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="30">
         <v>78054</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="30">
         <v>78054</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="30">
         <v>0</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="30">
         <v>0</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N7" s="30">
         <f>SUM(B7:M7)</f>
         <v>780535</v>
       </c>
@@ -4222,43 +4222,43 @@
       <c r="A8" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>50333</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>50333</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>50333</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>50333</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>50333</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="30">
         <v>50333</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="30">
         <v>50333</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="30">
         <v>50333</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="30">
         <v>50333</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="30">
         <v>50333</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="30">
         <v>0</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="30">
         <v>0</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="30">
         <f>SUM(B8:M8)</f>
         <v>503333</v>
       </c>
@@ -4267,43 +4267,43 @@
       <c r="A9" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <v>8886</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>8886</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>8886</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>8886</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>8886</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="30">
         <v>8886</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="30">
         <v>8886</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="30">
         <v>8886</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="30">
         <v>8886</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="30">
         <v>8886</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="30">
         <v>8886</v>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="30">
         <v>8886</v>
       </c>
-      <c r="N9" s="31">
+      <c r="N9" s="30">
         <f>SUM(B9:M9)</f>
         <v>106629</v>
       </c>
@@ -4525,7 +4525,7 @@
       <c r="A19" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
         <v>9227</v>
       </c>
@@ -4598,19 +4598,19 @@
       <c r="A5" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="31">
         <v>1178333</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="31">
         <v>2261600</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="31">
         <v>3367965</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="31">
         <v>4502532</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="31">
         <v>5696361</v>
       </c>
     </row>
@@ -4688,23 +4688,23 @@
       <c r="A11" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
         <v>1390497</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="31">
         <f>SUM(C8:C10)</f>
         <v>1805930</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="31">
         <f>SUM(D8:D10)</f>
         <v>2059375</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="31">
         <f>SUM(E8:E10)</f>
         <v>2306162</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="31">
         <f>SUM(F8:F10)</f>
         <v>2581867</v>
       </c>
@@ -4748,23 +4748,23 @@
       <c r="A15" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.54675147</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>327</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4863,7 +4863,7 @@
       <c r="D6" s="19">
         <v>10</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>46629</v>
       </c>
@@ -4882,23 +4882,23 @@
       <c r="A9" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <f>B6</f>
         <v>350000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <f>B13</f>
         <v>323655</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <f>C13</f>
         <v>295685</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <f>D13</f>
         <v>265989</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <f>E13</f>
         <v>234462</v>
       </c>
@@ -4907,23 +4907,23 @@
       <c r="A10" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>20283</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>18658</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>16933</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>15102</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>13157</v>
       </c>
@@ -4932,23 +4932,23 @@
       <c r="A11" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>26345</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>27970</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>29695</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>31527</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>33471</v>
       </c>
@@ -5096,19 +5096,19 @@
       <c r="A6" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>0</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>0</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>0</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>0</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5116,19 +5116,19 @@
       <c r="A7" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>0</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>0</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>0</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>0</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5136,19 +5136,19 @@
       <c r="A8" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>0</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>0</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>0</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>0</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5156,23 +5156,23 @@
       <c r="A9" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
         <v>74498</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
         <v>530168</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
         <v>1838758</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
         <v>4035127</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
         <v>7149621</v>
       </c>
@@ -5191,19 +5191,19 @@
       <c r="A12" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>0</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>0</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="30">
         <v>0</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>0</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>0</v>
       </c>
     </row>
@@ -5211,23 +5211,23 @@
       <c r="A13" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <f>'Debt Schedule'!B13</f>
         <v>323655</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <f>'Debt Schedule'!C13</f>
         <v>295685</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <f>'Debt Schedule'!D13</f>
         <v>265989</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <f>'Debt Schedule'!E13</f>
         <v>234462</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <f>'Debt Schedule'!F13</f>
         <v>200991</v>
       </c>
@@ -5236,23 +5236,23 @@
       <c r="A14" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
         <v>323655</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="31">
         <f>SUM(C12:C13)</f>
         <v>295685</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="31">
         <f>SUM(D12:D13)</f>
         <v>265989</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="31">
         <f>SUM(E12:E13)</f>
         <v>234462</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="31">
         <f>SUM(F12:F13)</f>
         <v>200991</v>
       </c>
@@ -5385,19 +5385,19 @@
       <c r="A5" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <v>1178333</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>2261600</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>3367965</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>4502532</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>5696361</v>
       </c>
     </row>
@@ -5405,19 +5405,19 @@
       <c r="A6" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>780535</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>964741</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>993683</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>1023494</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>1054199</v>
       </c>
     </row>
@@ -5425,19 +5425,19 @@
       <c r="A7" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>503333</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>774560</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>994063</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>1226040</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>1471040</v>
       </c>
     </row>
@@ -5470,19 +5470,19 @@
       <c r="A9" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <v>46629</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>46629</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>46629</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>46629</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>46629</v>
       </c>
     </row>
@@ -5525,19 +5525,19 @@
       <c r="A13" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>74498</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>530168</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>1838758</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>4035127</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>7149621</v>
       </c>
     </row>
@@ -5545,23 +5545,23 @@
       <c r="A14" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>20</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="36">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>108</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="36">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>330</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="36">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>641</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="36">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>1015</v>
       </c>
@@ -5595,19 +5595,19 @@
       <c r="A16" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>0.2</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>0.5</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -5625,19 +5625,19 @@
       <c r="A19" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="30">
         <v>9819</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>11308</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="30">
         <v>11227</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="30">
         <v>11256</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <v>11393</v>
       </c>
     </row>
@@ -5645,19 +5645,19 @@
       <c r="A20" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="30">
         <v>827164</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="30">
         <v>1011370</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="30">
         <v>1040312</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="30">
         <v>1070123</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <v>1100827</v>
       </c>
     </row>
@@ -5665,19 +5665,19 @@
       <c r="A21" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="30">
         <v>4194</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="30">
         <v>3873</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="30">
         <v>3314</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="30">
         <v>3065</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="30">
         <v>2942</v>
       </c>
     </row>
@@ -5865,13 +5865,13 @@
       <c r="A4" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>350000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="30">
         <v>250000</v>
       </c>
     </row>
@@ -5879,13 +5879,13 @@
       <c r="A5" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <v>150000</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>60000</v>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       <c r="D6" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>50000</v>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       <c r="D7" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>140000</v>
       </c>
     </row>
@@ -6316,19 +6316,19 @@
       <c r="A6" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="30">
         <v>1178333</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>2261600</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>3367965</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>4502532</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>5696361</v>
       </c>
     </row>
@@ -6336,19 +6336,19 @@
       <c r="A7" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>1330497</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>1785930</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>2034375</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>2296162</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>2571867</v>
       </c>
     </row>
@@ -6376,19 +6376,19 @@
       <c r="A9" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>-0.12913460606689658</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>0.21032460611271073</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>0.39596301962297903</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>0.49002859951113986</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>0.5485069777397931</v>
       </c>
     </row>
@@ -6416,19 +6416,19 @@
       <c r="A11" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="36">
         <v>148</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="36">
         <v>137</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="36">
         <v>132</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="36">
         <v>131</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="36">
         <v>131</v>
       </c>
     </row>
@@ -6471,19 +6471,19 @@
       <c r="A16" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="30">
         <v>1001583</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>1922360</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>2862770</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>3827152</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>4841907</v>
       </c>
     </row>
@@ -6491,19 +6491,19 @@
       <c r="A17" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="30">
         <v>1330497</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>1785930</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>2034375</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>2296162</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>2571867</v>
       </c>
     </row>
@@ -6531,19 +6531,19 @@
       <c r="A19" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>-0.32839365419634886</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <v>0.07097012483848322</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>0.2893682583799753</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>0.40003364648369394</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>0.46883173851740356</v>
       </c>
     </row>
@@ -6571,19 +6571,19 @@
       <c r="A21" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="36">
         <v>170</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="36">
         <v>150</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="36">
         <v>142</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="36">
         <v>140</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="36">
         <v>139</v>
       </c>
     </row>
@@ -6626,19 +6626,19 @@
       <c r="A26" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="30">
         <v>1084067</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="30">
         <v>2080672</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="30">
         <v>3098528</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="30">
         <v>4142329</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="30">
         <v>5240653</v>
       </c>
     </row>
@@ -6646,19 +6646,19 @@
       <c r="A27" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="30">
         <v>1330497</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="30">
         <v>1785930</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="30">
         <v>2034375</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="30">
         <v>2296162</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="30">
         <v>2571867</v>
       </c>
     </row>
@@ -6686,19 +6686,19 @@
       <c r="A29" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>-0.2273202239857572</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="29">
         <v>0.1416571805572943</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>0.34343806480758593</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="29">
         <v>0.4456832603381955</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="29">
         <v>0.5092467149345576</v>
       </c>
     </row>
@@ -6726,19 +6726,19 @@
       <c r="A31" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="36">
         <v>171</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="36">
         <v>155</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="36">
         <v>149</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="36">
         <v>147</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="36">
         <v>147</v>
       </c>
     </row>
@@ -6876,19 +6876,19 @@
       <c r="A13" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>1178333</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>2261600</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>3367965</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="30">
         <v>4502532</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="30">
         <v>5696361</v>
       </c>
     </row>
@@ -6896,19 +6896,19 @@
       <c r="A14" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>1330497</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <v>1785930</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>2034375</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="30">
         <v>2296162</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="30">
         <v>2571867</v>
       </c>
     </row>
@@ -6916,19 +6916,19 @@
       <c r="A15" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <v>-212164</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>455670</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>1308590</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="30">
         <v>2196369</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="30">
         <v>3114494</v>
       </c>
     </row>
@@ -6936,19 +6936,19 @@
       <c r="A16" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>74498</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>530168</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>1838758</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="30">
         <v>4035127</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="30">
         <v>7149621</v>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
       <c r="A17" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>323655</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>295685</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>265989</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <v>234462</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="30">
         <v>200991</v>
       </c>
     </row>
@@ -7014,19 +7014,19 @@
       <c r="A21" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="29">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>0.20148130933167066</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>0.38854013963461814</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="29">
         <v>0.48780762672183775</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="29">
         <v>0.54675147116204</v>
       </c>
     </row>
@@ -7054,19 +7054,19 @@
       <c r="A23" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="29">
         <v>0.2</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="29">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="29">
         <v>0.5</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="29">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="29">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -7074,19 +7074,19 @@
       <c r="A24" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="36">
         <v>120</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="36">
         <v>200</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="36">
         <v>300</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="36">
         <v>400</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="36">
         <v>500</v>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="21">
         <v>600</v>
       </c>
     </row>
@@ -8901,20 +8901,25 @@
       <c r="A8" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="28">
+        <f>B6/$B$7</f>
         <v>0.2</v>
       </c>
-      <c r="C8" s="29">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D8" s="29">
+      <c r="C8" s="28">
+        <f>C6/$B$7</f>
+        <v>0.33333333</v>
+      </c>
+      <c r="D8" s="28">
+        <f>D6/$B$7</f>
         <v>0.5</v>
       </c>
-      <c r="E8" s="29">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="F8" s="29">
-        <v>0.8333333333333334</v>
+      <c r="E8" s="28">
+        <f>E6/$B$7</f>
+        <v>0.66666667</v>
+      </c>
+      <c r="F8" s="28">
+        <f>F6/$B$7</f>
+        <v>0.83333333</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -8924,16 +8929,20 @@
       <c r="B10" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C10" s="30">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="D10" s="30">
+      <c r="C10" s="29">
+        <f>IF(B6=0,0,(C6-B6)/B6)</f>
+        <v>0.66666667</v>
+      </c>
+      <c r="D10" s="29">
+        <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.5</v>
       </c>
-      <c r="E10" s="30">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="F10" s="30">
+      <c r="E10" s="29">
+        <f>IF(D6=0,0,(E6-D6)/D6)</f>
+        <v>0.33333333</v>
+      </c>
+      <c r="F10" s="29">
+        <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0.25</v>
       </c>
     </row>
@@ -8954,10 +8963,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9003,146 +9012,241 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" s="31">
+        <v>113</v>
+      </c>
+      <c r="B5" s="30">
         <v>969000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>1617850</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>2466200</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>3327850</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>4233200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="31">
+        <v>116</v>
+      </c>
+      <c r="B6" s="30">
         <v>90000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>154500</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>238703</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>327818</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>422066</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" s="31">
+        <v>117</v>
+      </c>
+      <c r="B7" s="30">
         <v>132000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>226600</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>350097</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>480800</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>619030</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>217</v>
+      <c r="A8" s="10" t="s">
+        <v>214</v>
       </c>
       <c r="B8" s="31">
-        <v>150000</v>
+        <f>SUBTOTAL(9,B5:B7)</f>
+        <v>1191000</v>
       </c>
       <c r="C8" s="31">
-        <v>154500</v>
+        <f>SUBTOTAL(9,C5:C7)</f>
+        <v>1998950</v>
       </c>
       <c r="D8" s="31">
-        <v>159135</v>
+        <f>SUBTOTAL(9,D5:D7)</f>
+        <v>3055000</v>
       </c>
       <c r="E8" s="31">
-        <v>163909</v>
+        <f>SUBTOTAL(9,E5:E7)</f>
+        <v>4136468</v>
       </c>
       <c r="F8" s="31">
-        <v>168826</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B9" s="31">
-        <v>25000</v>
-      </c>
-      <c r="C9" s="31">
-        <v>25750</v>
-      </c>
-      <c r="D9" s="31">
-        <v>26523</v>
-      </c>
-      <c r="E9" s="31">
-        <v>27318</v>
-      </c>
-      <c r="F9" s="31">
-        <v>28138</v>
-      </c>
+        <f>SUBTOTAL(9,F5:F7)</f>
+        <v>5274296</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="22">
+        <v>150000</v>
+      </c>
+      <c r="C10" s="30">
+        <v>154500</v>
+      </c>
+      <c r="D10" s="30">
+        <v>159135</v>
+      </c>
+      <c r="E10" s="30">
+        <v>163909</v>
+      </c>
+      <c r="F10" s="30">
+        <v>168826</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="22">
+        <v>25000</v>
+      </c>
+      <c r="C11" s="30">
+        <v>25750</v>
+      </c>
+      <c r="D11" s="30">
+        <v>26523</v>
+      </c>
+      <c r="E11" s="30">
+        <v>27318</v>
+      </c>
+      <c r="F11" s="30">
+        <v>28138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="31">
+        <f>SUBTOTAL(9,B10:B11)</f>
+        <v>175000</v>
+      </c>
+      <c r="C12" s="31">
+        <f>SUBTOTAL(9,C10:C11)</f>
+        <v>180250</v>
+      </c>
+      <c r="D12" s="31">
+        <f>SUBTOTAL(9,D10:D11)</f>
+        <v>185658</v>
+      </c>
+      <c r="E12" s="31">
+        <f>SUBTOTAL(9,E10:E11)</f>
+        <v>191227</v>
+      </c>
+      <c r="F12" s="31">
+        <f>SUBTOTAL(9,F10:F11)</f>
+        <v>196964</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="30">
+        <v>48000</v>
+      </c>
+      <c r="C14" s="30">
+        <v>82400</v>
+      </c>
+      <c r="D14" s="30">
+        <v>127308</v>
+      </c>
+      <c r="E14" s="30">
+        <v>174836</v>
+      </c>
+      <c r="F14" s="30">
+        <v>225102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="31">
+        <f>SUBTOTAL(9,B14:B14)</f>
+        <v>48000</v>
+      </c>
+      <c r="C15" s="31">
+        <f>SUBTOTAL(9,C14:C14)</f>
+        <v>82400</v>
+      </c>
+      <c r="D15" s="31">
+        <f>SUBTOTAL(9,D14:D14)</f>
+        <v>127308</v>
+      </c>
+      <c r="E15" s="31">
+        <f>SUBTOTAL(9,E14:E14)</f>
+        <v>174836</v>
+      </c>
+      <c r="F15" s="31">
+        <f>SUBTOTAL(9,F14:F14)</f>
+        <v>225102</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="31">
-        <v>48000</v>
-      </c>
-      <c r="C10" s="31">
-        <v>82400</v>
-      </c>
-      <c r="D10" s="31">
-        <v>127308</v>
-      </c>
-      <c r="E10" s="31">
-        <v>174836</v>
-      </c>
-      <c r="F10" s="31">
-        <v>225102</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="32">
-        <f>SUM(B5:B10)</f>
+      <c r="B17" s="32">
+        <f>SUM(B8,B12,B15)</f>
         <v>1414000</v>
       </c>
-      <c r="C11" s="32">
-        <f>SUM(C5:C10)</f>
+      <c r="C17" s="32">
+        <f>SUM(C8,C12,C15)</f>
         <v>2261600</v>
       </c>
-      <c r="D11" s="32">
-        <f>SUM(D5:D10)</f>
+      <c r="D17" s="32">
+        <f>SUM(D8,D12,D15)</f>
         <v>3367965</v>
       </c>
-      <c r="E11" s="32">
-        <f>SUM(E5:E10)</f>
+      <c r="E17" s="32">
+        <f>SUM(E8,E12,E15)</f>
         <v>4502532</v>
       </c>
-      <c r="F11" s="32">
-        <f>SUM(F5:F10)</f>
+      <c r="F17" s="32">
+        <f>SUM(F8,F12,F15)</f>
         <v>5696361</v>
       </c>
     </row>
@@ -9196,7 +9300,7 @@
         <v>127</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>129</v>
@@ -9205,7 +9309,7 @@
         <v>130</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9218,13 +9322,13 @@
       <c r="C4" s="33">
         <v>1</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="30">
         <v>105000</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="29">
         <v>0.26</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="29">
         <v>0.0765</v>
       </c>
       <c r="G4" s="34">
@@ -9241,13 +9345,13 @@
       <c r="C5" s="33">
         <v>1</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>82000</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>0.26</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>0.0765</v>
       </c>
       <c r="G5" s="34">
@@ -9264,13 +9368,13 @@
       <c r="C6" s="33">
         <v>5</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>50000</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>0.26</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>0.0765</v>
       </c>
       <c r="G6" s="34">
@@ -9287,13 +9391,13 @@
       <c r="C7" s="33">
         <v>1</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>53000</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>0.26</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>0.0765</v>
       </c>
       <c r="G7" s="34">
@@ -9310,13 +9414,13 @@
       <c r="C8" s="33">
         <v>3</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>28000</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>0.18</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>0.0765</v>
       </c>
       <c r="G8" s="34">
@@ -9333,13 +9437,13 @@
       <c r="C9" s="33">
         <v>1</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>62000</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>0.26</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>0.0765</v>
       </c>
       <c r="G9" s="34">
@@ -9356,13 +9460,13 @@
       <c r="C10" s="33">
         <v>2</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <v>36000</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
         <v>0.22</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <v>0.0765</v>
       </c>
       <c r="G10" s="34">
@@ -9371,7 +9475,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -9402,7 +9506,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B14" s="32">
         <v>780535</v>
@@ -9422,27 +9526,27 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B15" s="30">
+        <v>224</v>
+      </c>
+      <c r="B15" s="29">
         <v>0.5520049504950495</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>0.4265746639547223</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>0.29503973402336425</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <v>0.22731523300861284</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>0.18506529677129674</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B16" s="35">
         <v>8.6</v>
@@ -9486,7 +9590,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9526,45 +9630,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="31">
+        <v>227</v>
+      </c>
+      <c r="B5" s="30">
         <v>78000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>133900</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>206875</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>284109</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>365790</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="36">
+        <v>228</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
         <v>78000</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="31">
         <f>SUM(C5:C5)</f>
         <v>133900</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="31">
         <f>SUM(D5:D5)</f>
         <v>206875</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="31">
         <f>SUM(E5:E5)</f>
         <v>284109</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="31">
         <f>SUM(F5:F5)</f>
         <v>365790</v>
       </c>
@@ -9581,45 +9685,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="31">
+        <v>229</v>
+      </c>
+      <c r="B8" s="30">
         <v>54000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>92700</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>143222</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>196691</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>253239</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" s="36">
+        <v>230</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>54000</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>92700</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>143222</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>196691</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>253239</v>
       </c>
@@ -9636,85 +9740,85 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B11" s="31">
+        <v>231</v>
+      </c>
+      <c r="B11" s="30">
         <v>264000</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>271920</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>280078</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <v>288480</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>297134</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B12" s="31">
+        <v>232</v>
+      </c>
+      <c r="B12" s="30">
         <v>36000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>37080</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="30">
         <v>38192</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>39338</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>40518</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B13" s="31">
+        <v>233</v>
+      </c>
+      <c r="B13" s="30">
         <v>22000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>22660</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>23340</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>24040</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>24761</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" s="36">
+        <v>234</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B11:B13)</f>
         <v>322000</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="31">
         <f>SUM(C11:C13)</f>
         <v>331660</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="31">
         <f>SUM(D11:D13)</f>
         <v>341610</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="31">
         <f>SUM(E11:E13)</f>
         <v>351858</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="31">
         <f>SUM(F11:F13)</f>
         <v>362414</v>
       </c>
@@ -9731,112 +9835,112 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B16" s="31">
+        <v>235</v>
+      </c>
+      <c r="B16" s="30">
         <v>30000</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>30900</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>31827</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>32782</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>33765</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B17" s="31">
+        <v>236</v>
+      </c>
+      <c r="B17" s="30">
         <v>12000</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>12360</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>12731</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>13113</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B18" s="31">
+        <v>237</v>
+      </c>
+      <c r="B18" s="30">
         <v>18000</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>18540</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="30">
         <v>19096</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <v>19669</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <v>20259</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B19" s="31">
+        <v>238</v>
+      </c>
+      <c r="B19" s="30">
         <v>90000</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>154500</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="30">
         <v>238703</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="30">
         <v>327818</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <v>422066</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="B20" s="36">
+        <v>239</v>
+      </c>
+      <c r="B20" s="31">
         <f>SUM(B16:B19)</f>
         <v>150000</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="31">
         <f>SUM(C16:C19)</f>
         <v>216300</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="31">
         <f>SUM(D16:D19)</f>
         <v>302357</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="31">
         <f>SUM(E16:E19)</f>
         <v>393382</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="31">
         <f>SUM(F16:F19)</f>
         <v>489596</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22" s="32">
         <f>B6+B9+B14+B20</f>
@@ -9886,7 +9990,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9911,7 +10015,7 @@
         <v>161</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -9924,10 +10028,10 @@
       <c r="C4" s="22">
         <v>350000</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="29">
         <v>0.06</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="36">
         <v>10</v>
       </c>
       <c r="F4" s="34">
@@ -9939,15 +10043,15 @@
         <v>164</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C5" s="22">
         <v>60000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>0</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="36">
         <v>0</v>
       </c>
       <c r="F5" s="34">
@@ -9956,7 +10060,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F7" s="32">
         <v>46629</v>
@@ -9964,9 +10068,9 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F8" s="36">
+        <v>245</v>
+      </c>
+      <c r="F8" s="31">
         <v>350000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -9075,23 +9075,23 @@
         <v>214</v>
       </c>
       <c r="B8" s="31">
-        <f>SUBTOTAL(9,B5:B7)</f>
+        <f>SUM(B5,B6,B7)</f>
         <v>1191000</v>
       </c>
       <c r="C8" s="31">
-        <f>SUBTOTAL(9,C5:C7)</f>
+        <f>SUM(C5,C6,C7)</f>
         <v>1998950</v>
       </c>
       <c r="D8" s="31">
-        <f>SUBTOTAL(9,D5:D7)</f>
+        <f>SUM(D5,D6,D7)</f>
         <v>3055000</v>
       </c>
       <c r="E8" s="31">
-        <f>SUBTOTAL(9,E5:E7)</f>
+        <f>SUM(E5,E6,E7)</f>
         <v>4136468</v>
       </c>
       <c r="F8" s="31">
-        <f>SUBTOTAL(9,F5:F7)</f>
+        <f>SUM(F5,F6,F7)</f>
         <v>5274296</v>
       </c>
     </row>
@@ -9150,23 +9150,23 @@
         <v>216</v>
       </c>
       <c r="B12" s="31">
-        <f>SUBTOTAL(9,B10:B11)</f>
+        <f>SUM(B10,B11)</f>
         <v>175000</v>
       </c>
       <c r="C12" s="31">
-        <f>SUBTOTAL(9,C10:C11)</f>
+        <f>SUM(C10,C11)</f>
         <v>180250</v>
       </c>
       <c r="D12" s="31">
-        <f>SUBTOTAL(9,D10:D11)</f>
+        <f>SUM(D10,D11)</f>
         <v>185658</v>
       </c>
       <c r="E12" s="31">
-        <f>SUBTOTAL(9,E10:E11)</f>
+        <f>SUM(E10,E11)</f>
         <v>191227</v>
       </c>
       <c r="F12" s="31">
-        <f>SUBTOTAL(9,F10:F11)</f>
+        <f>SUM(F10,F11)</f>
         <v>196964</v>
       </c>
     </row>
@@ -9205,23 +9205,23 @@
         <v>218</v>
       </c>
       <c r="B15" s="31">
-        <f>SUBTOTAL(9,B14:B14)</f>
+        <f>SUM(B14)</f>
         <v>48000</v>
       </c>
       <c r="C15" s="31">
-        <f>SUBTOTAL(9,C14:C14)</f>
+        <f>SUM(C14)</f>
         <v>82400</v>
       </c>
       <c r="D15" s="31">
-        <f>SUBTOTAL(9,D14:D14)</f>
+        <f>SUM(D14)</f>
         <v>127308</v>
       </c>
       <c r="E15" s="31">
-        <f>SUBTOTAL(9,E14:E14)</f>
+        <f>SUM(E14)</f>
         <v>174836</v>
       </c>
       <c r="F15" s="31">
-        <f>SUBTOTAL(9,F14:F14)</f>
+        <f>SUM(F14)</f>
         <v>225102</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="441">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -316,7 +316,10 @@
     <t>Heritage Academy Charter - Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs. All other cells are formulas.</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1495,7 +1498,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1514,6 +1517,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
@@ -1528,7 +1536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1546,6 +1554,15 @@
       <top style="thin">
         <color rgb="FFD0D0D0"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
@@ -1595,9 +1612,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1606,20 +1624,19 @@
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1634,13 +1651,13 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1649,22 +1666,22 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2380,7 +2397,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2389,28 +2406,28 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B4" s="37">
         <v>120</v>
@@ -2429,177 +2446,177 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="30">
+        <v>114</v>
+      </c>
+      <c r="B7" s="31">
         <v>969000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1617850</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>2466200</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>3327850</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>4233200</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="30">
+        <v>117</v>
+      </c>
+      <c r="B8" s="31">
         <v>90000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>154500</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>238703</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>327818</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>422066</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="30">
+        <v>118</v>
+      </c>
+      <c r="B9" s="31">
         <v>132000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>226600</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>350097</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>480800</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>619030</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="30">
+        <v>119</v>
+      </c>
+      <c r="B10" s="31">
         <v>150000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>154500</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>159135</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>163909</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>168826</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="30">
+        <v>122</v>
+      </c>
+      <c r="B11" s="31">
         <v>25000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>25750</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>26523</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>27318</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>28138</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="30">
+        <v>123</v>
+      </c>
+      <c r="B12" s="31">
         <v>48000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>82400</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>127308</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>174836</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>225102</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="32">
+      <c r="A13" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="33">
         <f>SUM(B7:B12)</f>
         <v>1414000</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>SUM(C7:C12)</f>
         <v>2261600</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>SUM(D7:D12)</f>
         <v>3367965</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>SUM(E7:E12)</f>
         <v>4502532</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>SUM(F7:F12)</f>
         <v>5696361</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="30">
+        <v>250</v>
+      </c>
+      <c r="B15" s="31">
         <v>11783</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>11308</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>11227</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>11256</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>11393</v>
       </c>
     </row>
@@ -2629,7 +2646,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2638,326 +2655,326 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B5" s="30">
+        <v>252</v>
+      </c>
+      <c r="B5" s="31">
         <v>278438</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>344149</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>354473</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>365107</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>376061</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B6" s="30">
+        <v>253</v>
+      </c>
+      <c r="B6" s="31">
         <v>59029</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>72960</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>75148</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>77403</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>79725</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="30">
+        <v>254</v>
+      </c>
+      <c r="B7" s="31">
         <v>87955</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>108712</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>111974</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>115333</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>118793</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="B8" s="31">
+        <v>255</v>
+      </c>
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v>425421</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>SUM(C5:C7)</f>
         <v>525821</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
         <v>541595</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v>557843</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v>574578</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B10" s="30">
+        <v>256</v>
+      </c>
+      <c r="B10" s="31">
         <v>116944</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>144542</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>148879</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>153345</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>157945</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="30">
+        <v>257</v>
+      </c>
+      <c r="B11" s="31">
         <v>91328</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>112881</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>116267</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>119755</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>123348</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="B12" s="31">
+        <v>258</v>
+      </c>
+      <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
         <v>208271</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>SUM(C10:C11)</f>
         <v>257423</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>SUM(D10:D11)</f>
         <v>265146</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>SUM(E10:E11)</f>
         <v>273100</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>SUM(F10:F11)</f>
         <v>281293</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B14" s="30">
+        <v>259</v>
+      </c>
+      <c r="B14" s="31">
         <v>69053</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>85349</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>87909</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>90547</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>93263</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B15" s="31">
+        <v>260</v>
+      </c>
+      <c r="B15" s="32">
         <f>SUM(B14:B14)</f>
         <v>69053</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>SUM(C14:C14)</f>
         <v>85349</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>SUM(D14:D14)</f>
         <v>87909</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>SUM(E14:E14)</f>
         <v>90547</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>SUM(F14:F14)</f>
         <v>93263</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B17" s="30">
+        <v>261</v>
+      </c>
+      <c r="B17" s="31">
         <v>77790</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>96148</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>99033</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>102004</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>105064</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="B18" s="31">
+        <v>262</v>
+      </c>
+      <c r="B18" s="32">
         <f>SUM(B17:B17)</f>
         <v>77790</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>SUM(C17:C17)</f>
         <v>96148</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <f>SUM(D17:D17)</f>
         <v>99033</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <f>SUM(E17:E17)</f>
         <v>102004</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <f>SUM(F17:F17)</f>
         <v>105064</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="B20" s="32">
+      <c r="A20" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="33">
         <f>B8+B12+B15+B18</f>
         <v>780535</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="33">
         <f>C8+C12+C15+C18</f>
         <v>964741</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="33">
         <f>D8+D12+D15+D18</f>
         <v>993683</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="33">
         <f>E8+E12+E15+E18</f>
         <v>1023494</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="33">
         <f>F8+F12+F15+F18</f>
         <v>1054199</v>
       </c>
@@ -2988,7 +3005,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2997,711 +3014,711 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="30">
+        <v>266</v>
+      </c>
+      <c r="B5" s="31">
         <v>807500</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1617850</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>2466200</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>3327850</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>4233200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="30">
+        <v>267</v>
+      </c>
+      <c r="B6" s="31">
         <v>75000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>154500</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>238703</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>327818</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>422066</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="30">
+        <v>268</v>
+      </c>
+      <c r="B7" s="31">
         <v>110000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>226600</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>350097</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>480800</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>619030</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="30">
+        <v>269</v>
+      </c>
+      <c r="B8" s="31">
         <v>125000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>154500</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>159135</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>163909</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>168826</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="30">
+        <v>270</v>
+      </c>
+      <c r="B9" s="31">
         <v>20833</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>25750</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>26523</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>27318</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>28138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B10" s="30">
+        <v>271</v>
+      </c>
+      <c r="B10" s="31">
         <v>40000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>82400</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>127308</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>174836</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>225102</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="31">
+        <v>272</v>
+      </c>
+      <c r="B11" s="32">
         <f>SUM(B5:B10)</f>
         <v>1178333</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>SUM(C5:C10)</f>
         <v>2261600</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>SUM(D5:D10)</f>
         <v>3367965</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>SUM(E5:E10)</f>
         <v>4502532</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>SUM(F5:F10)</f>
         <v>5696361</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="30">
+        <v>256</v>
+      </c>
+      <c r="B14" s="31">
         <v>116944</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>144542</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>148879</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>153345</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>157945</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B15" s="30">
+        <v>257</v>
+      </c>
+      <c r="B15" s="31">
         <v>91328</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>112881</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>116267</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>119755</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>123348</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B16" s="30">
+        <v>252</v>
+      </c>
+      <c r="B16" s="31">
         <v>278438</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>344149</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>354473</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>365107</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>376061</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B17" s="30">
+        <v>253</v>
+      </c>
+      <c r="B17" s="31">
         <v>59029</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>72960</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>75148</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>77403</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>79725</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B18" s="30">
+        <v>254</v>
+      </c>
+      <c r="B18" s="31">
         <v>87955</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>108712</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>111974</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>115333</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>118793</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B19" s="30">
+        <v>259</v>
+      </c>
+      <c r="B19" s="31">
         <v>69053</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>85349</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>87909</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>90547</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>93263</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B20" s="30">
+        <v>261</v>
+      </c>
+      <c r="B20" s="31">
         <v>77790</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>96148</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>99033</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>102004</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>105064</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B21" s="31">
+        <v>224</v>
+      </c>
+      <c r="B21" s="32">
         <f>SUM(B14:B20)</f>
         <v>780535</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>SUM(C14:C20)</f>
         <v>964741</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <f>SUM(D14:D20)</f>
         <v>993683</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <f>SUM(E14:E20)</f>
         <v>1023494</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>SUM(F14:F20)</f>
         <v>1054199</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="B25" s="30">
+        <v>274</v>
+      </c>
+      <c r="B25" s="31">
         <v>65000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>133900</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>206875</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>284109</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>365790</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B27" s="30">
+        <v>275</v>
+      </c>
+      <c r="B27" s="31">
         <v>45000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>92700</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>143222</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>196691</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>253239</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="B29" s="30">
+        <v>276</v>
+      </c>
+      <c r="B29" s="31">
         <v>220000</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <v>271920</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="31">
         <v>280078</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="31">
         <v>288480</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="31">
         <v>297134</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="B30" s="30">
+        <v>277</v>
+      </c>
+      <c r="B30" s="31">
         <v>30000</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <v>37080</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="31">
         <v>38192</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="31">
         <v>39338</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <v>40518</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B31" s="30">
+        <v>278</v>
+      </c>
+      <c r="B31" s="31">
         <v>18333</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <v>22660</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="31">
         <v>23340</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="31">
         <v>24040</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="31">
         <v>24761</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="B32" s="31">
+        <v>279</v>
+      </c>
+      <c r="B32" s="32">
         <f>SUM(B29:B31)</f>
         <v>268333</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="32">
         <f>SUM(C29:C31)</f>
         <v>331660</v>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="32">
         <f>SUM(D29:D31)</f>
         <v>341610</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="32">
         <f>SUM(E29:E31)</f>
         <v>351858</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="32">
         <f>SUM(F29:F31)</f>
         <v>362414</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B34" s="30">
+        <v>280</v>
+      </c>
+      <c r="B34" s="31">
         <v>25000</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <v>30900</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="31">
         <v>31827</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="31">
         <v>32782</v>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="31">
         <v>33765</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="B35" s="30">
+        <v>281</v>
+      </c>
+      <c r="B35" s="31">
         <v>10000</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <v>12360</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <v>12731</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <v>13113</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <v>13506</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="B36" s="30">
+        <v>282</v>
+      </c>
+      <c r="B36" s="31">
         <v>15000</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <v>18540</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <v>19096</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <v>19669</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <v>20259</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B37" s="30">
+        <v>283</v>
+      </c>
+      <c r="B37" s="31">
         <v>75000</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <v>154500</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="31">
         <v>238703</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="31">
         <v>327818</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="31">
         <v>422066</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="B38" s="31">
+        <v>284</v>
+      </c>
+      <c r="B38" s="32">
         <f>SUM(B34:B37)</f>
         <v>125000</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <f>SUM(C34:C37)</f>
         <v>216300</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <f>SUM(D34:D37)</f>
         <v>302357</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <f>SUM(E34:E37)</f>
         <v>393382</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <f>SUM(F34:F37)</f>
         <v>489596</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="B39" s="31">
+        <v>285</v>
+      </c>
+      <c r="B39" s="32">
         <f>B25+B27+B32+B38</f>
         <v>503333</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <f>C25+C27+C32+C38</f>
         <v>774560</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <f>D25+D27+D32+D38</f>
         <v>994063</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <f>E25+E27+E32+E38</f>
         <v>1226040</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <f>F25+F27+F32+F38</f>
         <v>1471040</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="A41" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="B42" s="30">
+        <v>287</v>
+      </c>
+      <c r="B42" s="31">
         <v>46629</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <v>46629</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <v>46629</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="31">
         <v>46629</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <v>46629</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="B43" s="30">
+        <v>288</v>
+      </c>
+      <c r="B43" s="31">
         <v>60000</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <v>20000</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <v>25000</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <v>10000</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <v>10000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="B44" s="31">
+        <v>289</v>
+      </c>
+      <c r="B44" s="32">
         <f>SUM(B42:B43)</f>
         <v>106629</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <f>SUM(C42:C43)</f>
         <v>66629</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <f>SUM(D42:D43)</f>
         <v>71629</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <f>SUM(E42:E43)</f>
         <v>56629</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <f>SUM(F42:F43)</f>
         <v>56629</v>
       </c>
@@ -3732,7 +3749,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3741,28 +3758,28 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B4" s="34">
         <f>'Budget Detail'!B11</f>
@@ -3787,7 +3804,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
@@ -3812,7 +3829,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
@@ -3837,7 +3854,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
@@ -3862,146 +3879,146 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="B8" s="31">
+        <v>292</v>
+      </c>
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v>1390497</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>SUM(C5:C7)</f>
         <v>1805930</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
         <v>2059375</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v>2306162</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v>2581867</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="32">
+        <v>294</v>
+      </c>
+      <c r="B11" s="33">
         <f>B4-B8</f>
         <v>-212164</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>C4-C8</f>
         <v>455670</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>D4-D8</f>
         <v>1308590</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>E4-E8</f>
         <v>2196369</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>F4-F8</f>
         <v>3114494</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B12" s="29">
+        <v>295</v>
+      </c>
+      <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.54675147</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="B13" s="30">
+        <v>296</v>
+      </c>
+      <c r="B13" s="31">
         <v>-212164</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>243507</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>1552096</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>3748465</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>6862959</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B14" s="30">
+        <v>250</v>
+      </c>
+      <c r="B14" s="31">
         <v>9819</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>11308</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>11227</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>11256</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>11393</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="B15" s="30">
+        <v>297</v>
+      </c>
+      <c r="B15" s="31">
         <v>11587</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>9030</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>6865</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>5765</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>5164</v>
       </c>
     </row>
@@ -4032,7 +4049,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4049,286 +4066,286 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>307</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>310</v>
       </c>
+      <c r="N2" s="21" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B4" s="31">
+        <v>272</v>
+      </c>
+      <c r="B4" s="32">
         <v>146500</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <v>146500</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="32">
         <v>146500</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>146500</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="32">
         <v>146500</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="32">
         <v>146500</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <v>146500</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="32">
         <v>146500</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="32">
         <v>146500</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="32">
         <v>146500</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="32">
         <v>0</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="32">
         <v>0</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="32">
         <f>SUM(B4:M4)</f>
         <v>1465000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="B7" s="30">
+        <v>313</v>
+      </c>
+      <c r="B7" s="31">
         <v>78054</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>78054</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>78054</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>78054</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>78054</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>78054</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <v>78054</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <v>78054</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <v>78054</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="31">
         <v>78054</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="31">
         <v>0</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="31">
         <v>0</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="31">
         <f>SUM(B7:M7)</f>
         <v>780535</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="30">
+        <v>314</v>
+      </c>
+      <c r="B8" s="31">
         <v>50333</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>50333</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>50333</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>50333</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>50333</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>50333</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <v>50333</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <v>50333</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="31">
         <v>50333</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="31">
         <v>50333</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="31">
         <v>0</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="31">
         <v>0</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="31">
         <f>SUM(B8:M8)</f>
         <v>503333</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B9" s="30">
+        <v>315</v>
+      </c>
+      <c r="B9" s="31">
         <v>8886</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>8886</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>8886</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>8886</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>8886</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>8886</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <v>8886</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <v>8886</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="31">
         <v>8886</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="31">
         <v>8886</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="31">
         <v>8886</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="31">
         <v>8886</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="31">
         <f>SUM(B9:M9)</f>
         <v>106629</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -4385,7 +4402,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -4442,7 +4459,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B14" s="39">
         <f>B17+B13</f>
@@ -4492,29 +4509,29 @@
         <f>L14+M13</f>
         <v>74498</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="33">
         <f>M14</f>
         <v>74498</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B17" s="22">
+        <v>173</v>
+      </c>
+      <c r="B17" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B18" s="39">
         <f>M14</f>
@@ -4523,9 +4540,9 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B19" s="30">
+        <v>321</v>
+      </c>
+      <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
         <v>9227</v>
       </c>
@@ -4556,7 +4573,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4565,68 +4582,68 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>271</v>
-      </c>
-      <c r="B5" s="31">
+        <v>272</v>
+      </c>
+      <c r="B5" s="32">
         <v>1178333</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <v>2261600</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <v>3367965</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>4502532</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <v>5696361</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B8" s="34">
         <v>780535</v>
@@ -4646,7 +4663,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B9" s="34">
         <v>503333</v>
@@ -4666,7 +4683,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B10" s="34">
         <v>106629</v>
@@ -4686,85 +4703,85 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
-        <v>291</v>
-      </c>
-      <c r="B11" s="31">
+        <v>292</v>
+      </c>
+      <c r="B11" s="32">
         <f>SUM(B8:B10)</f>
         <v>1390497</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>SUM(C8:C10)</f>
         <v>1805930</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>SUM(D8:D10)</f>
         <v>2059375</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>SUM(E8:E10)</f>
         <v>2306162</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>SUM(F8:F10)</f>
         <v>2581867</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="32">
+        <v>294</v>
+      </c>
+      <c r="B14" s="33">
         <f>B5-B11</f>
         <v>-212164</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>C5-C11</f>
         <v>455670</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>D5-D11</f>
         <v>1308590</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>E5-E11</f>
         <v>2196369</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>F5-F11</f>
         <v>3114494</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B15" s="29">
+        <v>295</v>
+      </c>
+      <c r="B15" s="30">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.54675147</v>
       </c>
@@ -4804,158 +4821,158 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="23">
         <v>350000</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="24">
         <v>0.06</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>10</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>46629</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="B9" s="30">
+        <v>330</v>
+      </c>
+      <c r="B9" s="31">
         <f>B6</f>
         <v>350000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>B13</f>
         <v>323655</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>C13</f>
         <v>295685</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>D13</f>
         <v>265989</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>E13</f>
         <v>234462</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B10" s="30">
+        <v>331</v>
+      </c>
+      <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>20283</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>18658</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>16933</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>15102</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>13157</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B11" s="30">
+        <v>332</v>
+      </c>
+      <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>26345</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>27970</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>29695</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>31527</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>33471</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -4980,7 +4997,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B13" s="39">
         <f>MAX(0,B9-B11)</f>
@@ -5029,7 +5046,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5038,38 +5055,38 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B5" s="44">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -5094,207 +5111,207 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B6" s="30">
+        <v>338</v>
+      </c>
+      <c r="B6" s="31">
         <v>0</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>0</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>0</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>0</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B7" s="30">
+        <v>339</v>
+      </c>
+      <c r="B7" s="31">
         <v>0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>0</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>0</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="B8" s="30">
+        <v>340</v>
+      </c>
+      <c r="B8" s="31">
         <v>0</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>0</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>0</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="B9" s="31">
+        <v>341</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v>74498</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
         <v>530168</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v>1838758</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v>4035127</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v>7149621</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="B12" s="30">
+        <v>343</v>
+      </c>
+      <c r="B12" s="31">
         <v>0</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>0</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>0</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="B13" s="30">
+        <v>344</v>
+      </c>
+      <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
         <v>323655</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>'Debt Schedule'!C13</f>
         <v>295685</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>'Debt Schedule'!D13</f>
         <v>265989</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>'Debt Schedule'!E13</f>
         <v>234462</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>'Debt Schedule'!F13</f>
         <v>200991</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="B14" s="31">
+        <v>345</v>
+      </c>
+      <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
         <v>323655</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C12:C13)</f>
         <v>295685</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D12:D13)</f>
         <v>265989</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E12:E13)</f>
         <v>234462</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F12:F13)</f>
         <v>200991</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="B17" s="32">
+        <v>347</v>
+      </c>
+      <c r="B17" s="33">
         <f>B9-B14</f>
         <v>-249157</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>C9-C14</f>
         <v>234484</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>D9-D14</f>
         <v>1572769</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E9-E14</f>
         <v>3800665</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>F9-F14</f>
         <v>6948630</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B19" s="45" t="str">
         <f>B9-B14-B17</f>
@@ -5343,7 +5360,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5352,98 +5369,98 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B5" s="30">
+        <v>351</v>
+      </c>
+      <c r="B5" s="31">
         <v>1178333</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2261600</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>3367965</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>4502532</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>5696361</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="B6" s="30">
+        <v>313</v>
+      </c>
+      <c r="B6" s="31">
         <v>780535</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>964741</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>993683</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>1023494</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>1054199</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B7" s="30">
+        <v>314</v>
+      </c>
+      <c r="B7" s="31">
         <v>503333</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>774560</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>994063</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>1226040</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>1471040</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -5468,27 +5485,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B9" s="30">
+        <v>315</v>
+      </c>
+      <c r="B9" s="31">
         <v>46629</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>46629</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>46629</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>46629</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>46629</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B10" s="47">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5512,38 +5529,38 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="B13" s="30">
+        <v>355</v>
+      </c>
+      <c r="B13" s="31">
         <v>74498</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>530168</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>1838758</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>4035127</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>7149621</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5568,7 +5585,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5593,97 +5610,97 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="29">
+        <v>210</v>
+      </c>
+      <c r="B16" s="30">
         <v>0.2</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>0.5</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>357</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B19" s="30">
+        <v>250</v>
+      </c>
+      <c r="B19" s="31">
         <v>9819</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>11308</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>11227</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>11256</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>11393</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="B20" s="30">
+        <v>359</v>
+      </c>
+      <c r="B20" s="31">
         <v>827164</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>1011370</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>1040312</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>1070123</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>1100827</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="B21" s="30">
+        <v>360</v>
+      </c>
+      <c r="B21" s="31">
         <v>4194</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>3873</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>3314</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>3065</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>2942</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B22" s="48">
         <v>148</v>
@@ -5702,113 +5719,113 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="A24" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B26" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="C26" s="50" t="s">
         <v>365</v>
       </c>
-      <c r="B26" s="49" t="s">
-        <v>363</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>364</v>
-      </c>
       <c r="D26" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E27" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -5849,79 +5866,79 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="51" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="30">
+        <v>163</v>
+      </c>
+      <c r="B4" s="31">
         <v>350000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="E4" s="30">
+        <v>372</v>
+      </c>
+      <c r="E4" s="31">
         <v>250000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="B5" s="30">
+        <v>373</v>
+      </c>
+      <c r="B5" s="31">
         <v>150000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="E5" s="30">
+        <v>165</v>
+      </c>
+      <c r="E5" s="31">
         <v>60000</v>
       </c>
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="E6" s="30">
+        <v>374</v>
+      </c>
+      <c r="E6" s="31">
         <v>50000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="E7" s="30">
+        <v>375</v>
+      </c>
+      <c r="E7" s="31">
         <v>140000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="B9" s="32">
+        <v>376</v>
+      </c>
+      <c r="B9" s="33">
         <v>500000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="E9" s="32">
+        <v>377</v>
+      </c>
+      <c r="E9" s="33">
         <v>500000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B10" s="45">
         <v>0</v>
@@ -6269,7 +6286,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6278,123 +6295,123 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B6" s="30">
+        <v>351</v>
+      </c>
+      <c r="B6" s="31">
         <v>1178333</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>2261600</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>3367965</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>4502532</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>5696361</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B7" s="30">
+        <v>292</v>
+      </c>
+      <c r="B7" s="31">
         <v>1330497</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1785930</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>2034375</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>2296162</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>2571867</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B8" s="32">
+        <v>294</v>
+      </c>
+      <c r="B8" s="33">
         <v>-152164</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>475670</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <v>1333590</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <v>2206369</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <v>3124494</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B9" s="29">
+        <v>295</v>
+      </c>
+      <c r="B9" s="30">
         <v>-0.12913460606689658</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>0.21032460611271073</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>0.39596301962297903</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0.49002859951113986</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0.5485069777397931</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B10" s="52">
         <v>-2.26</v>
@@ -6414,7 +6431,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B11" s="36">
         <v>148</v>
@@ -6433,123 +6450,123 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B16" s="30">
+        <v>351</v>
+      </c>
+      <c r="B16" s="31">
         <v>1001583</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>1922360</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>2862770</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>3827152</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>4841907</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B17" s="30">
+        <v>292</v>
+      </c>
+      <c r="B17" s="31">
         <v>1330497</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>1785930</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>2034375</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>2296162</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>2571867</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B18" s="32">
+        <v>294</v>
+      </c>
+      <c r="B18" s="33">
         <v>-328914</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <v>136430</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <v>828395</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <v>1530989</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <v>2270040</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B19" s="29">
+        <v>295</v>
+      </c>
+      <c r="B19" s="30">
         <v>-0.32839365419634886</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>0.07097012483848322</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>0.2893682583799753</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>0.40003364648369394</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>0.46883173851740356</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B20" s="52">
         <v>-6.05</v>
@@ -6569,7 +6586,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B21" s="36">
         <v>170</v>
@@ -6588,123 +6605,123 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="B25" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="C25" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="D25" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="E25" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B26" s="30">
+        <v>351</v>
+      </c>
+      <c r="B26" s="31">
         <v>1084067</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <v>2080672</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <v>3098528</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <v>4142329</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <v>5240653</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="B27" s="30">
+        <v>292</v>
+      </c>
+      <c r="B27" s="31">
         <v>1330497</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>1785930</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>2034375</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>2296162</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>2571867</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B28" s="32">
+        <v>294</v>
+      </c>
+      <c r="B28" s="33">
         <v>-246430</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>294742</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>1064152</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>1846167</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>2668785</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="B29" s="29">
+        <v>295</v>
+      </c>
+      <c r="B29" s="30">
         <v>-0.2273202239857572</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>0.1416571805572943</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>0.34343806480758593</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>0.4456832603381955</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>0.5092467149345576</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B30" s="52">
         <v>-4.28</v>
@@ -6724,7 +6741,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B31" s="36">
         <v>171</v>
@@ -6770,7 +6787,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6781,10 +6798,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -6796,7 +6813,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -6804,7 +6821,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6828,23 +6845,23 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -6857,132 +6874,132 @@
         <v>7</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D13" s="30">
+        <v>351</v>
+      </c>
+      <c r="D13" s="31">
         <v>1178333</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>2261600</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>3367965</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <v>4502532</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <v>5696361</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="D14" s="30">
+        <v>292</v>
+      </c>
+      <c r="D14" s="31">
         <v>1330497</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>1785930</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>2034375</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <v>2296162</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <v>2571867</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="D15" s="30">
+        <v>294</v>
+      </c>
+      <c r="D15" s="31">
         <v>-212164</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>455670</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>1308590</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <v>2196369</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <v>3114494</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="D16" s="30">
+        <v>390</v>
+      </c>
+      <c r="D16" s="31">
         <v>74498</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>530168</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>1838758</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <v>4035127</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <v>7149621</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D17" s="30">
+        <v>391</v>
+      </c>
+      <c r="D17" s="31">
         <v>323655</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>295685</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>265989</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <v>234462</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <v>200991</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>391</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -6995,44 +7012,44 @@
         <v>7</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" s="53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" s="53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="D21" s="29">
+        <v>393</v>
+      </c>
+      <c r="D21" s="30">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>0.20148130933167066</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>0.38854013963461814</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>0.48780762672183775</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>0.54675147116204</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D22" s="52">
         <v>-2.26</v>
@@ -7052,27 +7069,27 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D23" s="29">
+        <v>210</v>
+      </c>
+      <c r="D23" s="30">
         <v>0.2</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>0.3333333333333333</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>0.5</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>0.6666666666666666</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D24" s="36">
         <v>120</v>
@@ -7092,7 +7109,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7132,7 +7149,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7142,7 +7159,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
@@ -7151,28 +7168,28 @@
       <c r="G3" s="54"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>397</v>
+      <c r="B5" s="19" t="s">
+        <v>398</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E5" s="55" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F5" s="55" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G5" s="55" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C6" s="56">
         <v>120</v>
@@ -7192,7 +7209,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C7" s="57">
         <v>1178333.3333333335</v>
@@ -7212,7 +7229,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C8" s="57">
         <v>780535</v>
@@ -7232,7 +7249,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C9" s="57">
         <v>503333.3333333334</v>
@@ -7252,7 +7269,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C10" s="57">
         <v>46628.6108154935</v>
@@ -7272,7 +7289,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C11" s="58">
         <v>-212163.6108154934</v>
@@ -7292,7 +7309,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C12" s="59">
         <v>74498</v>
@@ -7312,7 +7329,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C13" s="60">
         <v>-0.18005398371894768</v>
@@ -7332,7 +7349,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C14" s="57">
         <v>9819.444444444445</v>
@@ -7352,7 +7369,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C15" s="60">
         <v>0.6624059405940593</v>
@@ -7372,7 +7389,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C16" s="61">
         <v>0.12814710042432814</v>
@@ -7392,7 +7409,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C17" s="60">
         <v>-0.08956294200848645</v>
@@ -7412,7 +7429,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C18" s="62">
         <v>-2.2633099754482346</v>
@@ -7432,10 +7449,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D19" s="64"/>
       <c r="E19" s="64"/>
@@ -7444,10 +7461,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65"/>
@@ -7455,146 +7472,146 @@
       <c r="G20" s="65"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="41" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D23" s="67" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E23" s="67"/>
       <c r="F23" s="68" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G23" s="68"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="41" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C24" s="69" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D24" s="67" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E24" s="67"/>
       <c r="F24" s="68" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G24" s="68"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="41" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D25" s="67" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E25" s="67"/>
       <c r="F25" s="68" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G25" s="68"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="41" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D26" s="67" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E26" s="67"/>
       <c r="F26" s="68" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G26" s="68"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="41" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D27" s="67" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E27" s="67"/>
       <c r="F27" s="68" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G27" s="68"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="41" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C28" s="66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D28" s="67" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E28" s="67"/>
       <c r="F28" s="68" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G28" s="68"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D29" s="67" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E29" s="67"/>
       <c r="F29" s="68" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G29" s="68"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="41" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="70" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C33" s="70"/>
       <c r="D33" s="70"/>
@@ -7736,30 +7753,36 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
+      <c r="D2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7767,7 +7790,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7775,7 +7798,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7783,23 +7806,23 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="19" t="s">
         <v>97</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -7807,858 +7830,858 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="19">
+        <v>99</v>
+      </c>
+      <c r="B12" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="19">
+        <v>100</v>
+      </c>
+      <c r="B13" s="20">
         <v>600</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+      <c r="A15" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="D16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="E16" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="21">
+        <v>107</v>
+      </c>
+      <c r="B17" s="22">
         <v>120</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <v>200</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="22">
         <v>300</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="22">
         <v>400</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="22">
         <v>500</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="22">
+        <v>116</v>
+      </c>
+      <c r="D21" s="23">
         <v>8500</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <v>750</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="22">
+        <v>116</v>
+      </c>
+      <c r="D23" s="23">
         <v>1100</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="22">
+        <v>121</v>
+      </c>
+      <c r="D24" s="23">
         <v>150000</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <v>25000</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="22">
+        <v>116</v>
+      </c>
+      <c r="D26" s="23">
         <v>400</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
+      <c r="A28" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="B29" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="D29" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="F29" s="21" t="s">
         <v>130</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="24">
+        <v>134</v>
+      </c>
+      <c r="D30" s="25">
         <v>1</v>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="23">
         <v>105000</v>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="24">
         <v>0.26</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <v>1</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>82000</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="24">
         <v>0.26</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="24">
+        <v>134</v>
+      </c>
+      <c r="D32" s="25">
         <v>5</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="23">
         <v>50000</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="24">
         <v>0.26</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>136</v>
-      </c>
       <c r="C33" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D33" s="24">
+        <v>134</v>
+      </c>
+      <c r="D33" s="25">
         <v>1</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="23">
         <v>53000</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="24">
         <v>0.26</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="24">
+        <v>134</v>
+      </c>
+      <c r="D34" s="25">
         <v>3</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="23">
         <v>28000</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="24">
         <v>0.18</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" s="24">
+        <v>134</v>
+      </c>
+      <c r="D35" s="25">
         <v>1</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="23">
         <v>62000</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="24">
         <v>0.26</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D36" s="24">
+        <v>134</v>
+      </c>
+      <c r="D36" s="25">
         <v>2</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="23">
         <v>36000</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="24">
         <v>0.22</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
+      <c r="A38" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="20" t="s">
+      <c r="A39" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="B39" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="C39" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="D39" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D40" s="22">
+        <v>147</v>
+      </c>
+      <c r="D40" s="23">
         <v>22000</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="24">
         <v>0.03</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D41" s="22">
+      <c r="D41" s="23">
         <v>3000</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="22">
+        <v>121</v>
+      </c>
+      <c r="D42" s="23">
         <v>22000</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" s="22">
+        <v>116</v>
+      </c>
+      <c r="D43" s="23">
         <v>650</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" s="22">
+        <v>116</v>
+      </c>
+      <c r="D44" s="23">
         <v>450</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D45" s="22">
+        <v>121</v>
+      </c>
+      <c r="D45" s="23">
         <v>30000</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>154</v>
-      </c>
       <c r="C46" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D46" s="22">
+        <v>121</v>
+      </c>
+      <c r="D46" s="23">
         <v>12000</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D47" s="22">
+        <v>121</v>
+      </c>
+      <c r="D47" s="23">
         <v>18000</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D48" s="22">
+        <v>116</v>
+      </c>
+      <c r="D48" s="23">
         <v>750</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
+      <c r="A50" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C51" s="20" t="s">
+      <c r="A51" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="D51" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E51" s="20" t="s">
+      <c r="B51" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>161</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="C52" s="22">
+        <v>164</v>
+      </c>
+      <c r="C52" s="23">
         <v>350000</v>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="24">
         <v>0.06</v>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="22">
         <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C53" s="22">
+        <v>166</v>
+      </c>
+      <c r="C53" s="23">
         <v>60000</v>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="24">
         <v>0</v>
       </c>
-      <c r="E53" s="21">
+      <c r="E53" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
+      <c r="A55" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B56" s="23">
+        <v>168</v>
+      </c>
+      <c r="B56" s="24">
         <v>0.03</v>
       </c>
-      <c r="C56" s="25" t="s">
-        <v>168</v>
+      <c r="C56" s="26" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B57" s="23">
+        <v>170</v>
+      </c>
+      <c r="B57" s="24">
         <v>0.03</v>
       </c>
-      <c r="C57" s="25" t="s">
-        <v>170</v>
+      <c r="C57" s="26" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="B58" s="24">
+        <v>172</v>
+      </c>
+      <c r="B58" s="25">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B59" s="22">
+        <v>173</v>
+      </c>
+      <c r="B59" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B60" s="19" t="s">
         <v>174</v>
       </c>
+      <c r="B60" s="20" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="B62" s="18"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
+      <c r="A62" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B63" s="19" t="s">
         <v>177</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>146</v>
+        <v>179</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B65" s="21">
+        <v>180</v>
+      </c>
+      <c r="B65" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B66" s="21">
+        <v>181</v>
+      </c>
+      <c r="B66" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B67" s="26">
+        <v>182</v>
+      </c>
+      <c r="B67" s="27">
         <v>0.95</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="B69" s="20" t="s">
+      <c r="A69" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="C69" s="20" t="s">
+      <c r="B69" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="D69" s="20" t="s">
+      <c r="C69" s="21" t="s">
         <v>185</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B70" s="22">
+        <v>187</v>
+      </c>
+      <c r="B70" s="23">
         <v>8200</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="23">
         <v>9100</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="23">
         <v>10500</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" s="20" t="s">
+      <c r="A72" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D72" s="20" t="s">
+      <c r="C72" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="D72" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F72" s="20" t="s">
+      <c r="E72" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="B73" s="21">
+        <v>189</v>
+      </c>
+      <c r="B73" s="22">
         <v>80</v>
       </c>
-      <c r="C73" s="21">
+      <c r="C73" s="22">
         <v>130</v>
       </c>
-      <c r="D73" s="21">
+      <c r="D73" s="22">
         <v>180</v>
       </c>
-      <c r="E73" s="21">
+      <c r="E73" s="22">
         <v>230</v>
       </c>
-      <c r="F73" s="21">
+      <c r="F73" s="22">
         <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="B74" s="21">
+        <v>190</v>
+      </c>
+      <c r="B74" s="22">
         <v>40</v>
       </c>
-      <c r="C74" s="21">
+      <c r="C74" s="22">
         <v>70</v>
       </c>
-      <c r="D74" s="21">
+      <c r="D74" s="22">
         <v>100</v>
       </c>
-      <c r="E74" s="21">
+      <c r="E74" s="22">
         <v>120</v>
       </c>
-      <c r="F74" s="21">
+      <c r="F74" s="22">
         <v>140</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B75" s="21">
+        <v>191</v>
+      </c>
+      <c r="B75" s="22">
         <v>0</v>
       </c>
-      <c r="C75" s="21">
+      <c r="C75" s="22">
         <v>0</v>
       </c>
-      <c r="D75" s="21">
+      <c r="D75" s="22">
         <v>20</v>
       </c>
-      <c r="E75" s="21">
+      <c r="E75" s="22">
         <v>50</v>
       </c>
-      <c r="F75" s="21">
+      <c r="F75" s="22">
         <v>100</v>
       </c>
     </row>
@@ -8694,10 +8717,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8718,10 +8741,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -8734,7 +8757,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -8742,66 +8765,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -8840,108 +8863,108 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="A5" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="27">
+        <v>107</v>
+      </c>
+      <c r="B6" s="28">
         <v>120</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <v>200</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <v>300</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <v>400</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="21">
+        <v>100</v>
+      </c>
+      <c r="B7" s="22">
         <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="B8" s="28">
+        <v>210</v>
+      </c>
+      <c r="B8" s="29">
         <f>B6/$B$7</f>
         <v>0.2</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>C6/$B$7</f>
         <v>0.33333333</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D6/$B$7</f>
         <v>0.5</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E6/$B$7</f>
         <v>0.66666667</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>F6/$B$7</f>
         <v>0.83333333</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="C10" s="29">
+        <v>212</v>
+      </c>
+      <c r="C10" s="30">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
         <v>0.66666667</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.5</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.33333333</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0.25</v>
       </c>
@@ -8972,7 +8995,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8981,271 +9004,271 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="30">
+        <v>114</v>
+      </c>
+      <c r="B5" s="31">
         <v>969000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1617850</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>2466200</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>3327850</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>4233200</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="30">
+        <v>117</v>
+      </c>
+      <c r="B6" s="31">
         <v>90000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>154500</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>238703</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>327818</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>422066</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="30">
+        <v>118</v>
+      </c>
+      <c r="B7" s="31">
         <v>132000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>226600</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>350097</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>480800</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>619030</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B8" s="31">
+        <v>215</v>
+      </c>
+      <c r="B8" s="32">
         <f>SUM(B5,B6,B7)</f>
         <v>1191000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>SUM(C5,C6,C7)</f>
         <v>1998950</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5,D6,D7)</f>
         <v>3055000</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5,E6,E7)</f>
         <v>4136468</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5,F6,F7)</f>
         <v>5274296</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="22">
+        <v>119</v>
+      </c>
+      <c r="B10" s="23">
         <v>150000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>154500</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>159135</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>163909</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>168826</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="22">
+        <v>122</v>
+      </c>
+      <c r="B11" s="23">
         <v>25000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>25750</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>26523</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>27318</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>28138</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="B12" s="31">
+        <v>217</v>
+      </c>
+      <c r="B12" s="32">
         <f>SUM(B10,B11)</f>
         <v>175000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>SUM(C10,C11)</f>
         <v>180250</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>SUM(D10,D11)</f>
         <v>185658</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>SUM(E10,E11)</f>
         <v>191227</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>SUM(F10,F11)</f>
         <v>196964</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B14" s="30">
+        <v>123</v>
+      </c>
+      <c r="B14" s="31">
         <v>48000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>82400</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>127308</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>174836</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>225102</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="B15" s="31">
+        <v>219</v>
+      </c>
+      <c r="B15" s="32">
         <f>SUM(B14)</f>
         <v>48000</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>SUM(C14)</f>
         <v>82400</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>SUM(D14)</f>
         <v>127308</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>SUM(E14)</f>
         <v>174836</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>SUM(F14)</f>
         <v>225102</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B17" s="32">
+      <c r="A17" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="33">
         <f>SUM(B8,B12,B15)</f>
         <v>1414000</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>SUM(C8,C12,C15)</f>
         <v>2261600</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>SUM(D8,D12,D15)</f>
         <v>3367965</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>SUM(E8,E12,E15)</f>
         <v>4502532</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>SUM(F8,F12,F15)</f>
         <v>5696361</v>
       </c>
@@ -9290,45 +9313,45 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="F3" s="20" t="s">
+      <c r="A3" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>221</v>
+      <c r="F3" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="33">
+        <v>133</v>
+      </c>
+      <c r="C4" s="25">
         <v>1</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="23">
         <v>105000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="24">
         <v>0.26</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="24">
         <v>0.0765</v>
       </c>
       <c r="G4" s="34">
@@ -9337,21 +9360,21 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="33">
+        <v>133</v>
+      </c>
+      <c r="C5" s="25">
         <v>1</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="23">
         <v>82000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="24">
         <v>0.26</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="24">
         <v>0.0765</v>
       </c>
       <c r="G5" s="34">
@@ -9360,21 +9383,21 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="33">
+        <v>137</v>
+      </c>
+      <c r="C6" s="25">
         <v>5</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="23">
         <v>50000</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="24">
         <v>0.26</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="24">
         <v>0.0765</v>
       </c>
       <c r="G6" s="34">
@@ -9383,21 +9406,21 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="33">
+      <c r="C7" s="25">
         <v>1</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="23">
         <v>53000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="24">
         <v>0.26</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="24">
         <v>0.0765</v>
       </c>
       <c r="G7" s="34">
@@ -9406,21 +9429,21 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="33">
+        <v>137</v>
+      </c>
+      <c r="C8" s="25">
         <v>3</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="23">
         <v>28000</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="24">
         <v>0.18</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="24">
         <v>0.0765</v>
       </c>
       <c r="G8" s="34">
@@ -9429,21 +9452,21 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="33">
+        <v>141</v>
+      </c>
+      <c r="C9" s="25">
         <v>1</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="23">
         <v>62000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="24">
         <v>0.26</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="24">
         <v>0.0765</v>
       </c>
       <c r="G9" s="34">
@@ -9452,21 +9475,21 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" s="33">
+        <v>143</v>
+      </c>
+      <c r="C10" s="25">
         <v>2</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="23">
         <v>36000</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="24">
         <v>0.22</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="24">
         <v>0.0765</v>
       </c>
       <c r="G10" s="34">
@@ -9474,79 +9497,79 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="A12" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="20" t="s">
+      <c r="B13" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="C13" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="D13" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="32">
+        <v>224</v>
+      </c>
+      <c r="B14" s="33">
         <v>780535</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <v>964741</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <v>993683</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <v>1023494</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <v>1054199</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="29">
+        <v>225</v>
+      </c>
+      <c r="B15" s="30">
         <v>0.5520049504950495</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>0.4265746639547223</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>0.29503973402336425</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>0.22731523300861284</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>0.18506529677129674</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B16" s="35">
         <v>8.6</v>
@@ -9590,7 +9613,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9599,366 +9622,366 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="30">
+        <v>228</v>
+      </c>
+      <c r="B5" s="31">
         <v>78000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>133900</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>206875</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>284109</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>365790</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6" s="31">
+        <v>229</v>
+      </c>
+      <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
         <v>78000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>SUM(C5:C5)</f>
         <v>133900</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>SUM(D5:D5)</f>
         <v>206875</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>SUM(E5:E5)</f>
         <v>284109</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>SUM(F5:F5)</f>
         <v>365790</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="30">
+        <v>230</v>
+      </c>
+      <c r="B8" s="31">
         <v>54000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>92700</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>143222</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>196691</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>253239</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="31">
+        <v>231</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
         <v>54000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C8:C8)</f>
         <v>92700</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D8:D8)</f>
         <v>143222</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E8:E8)</f>
         <v>196691</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F8:F8)</f>
         <v>253239</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B11" s="30">
+        <v>232</v>
+      </c>
+      <c r="B11" s="31">
         <v>264000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>271920</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>280078</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>288480</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>297134</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B12" s="30">
+        <v>233</v>
+      </c>
+      <c r="B12" s="31">
         <v>36000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>37080</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>38192</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>39338</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>40518</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B13" s="30">
+        <v>234</v>
+      </c>
+      <c r="B13" s="31">
         <v>22000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>22660</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>23340</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>24040</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>24761</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B14" s="31">
+        <v>235</v>
+      </c>
+      <c r="B14" s="32">
         <f>SUM(B11:B13)</f>
         <v>322000</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C11:C13)</f>
         <v>331660</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D11:D13)</f>
         <v>341610</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E11:E13)</f>
         <v>351858</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F11:F13)</f>
         <v>362414</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B16" s="30">
+        <v>236</v>
+      </c>
+      <c r="B16" s="31">
         <v>30000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>30900</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>31827</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>32782</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>33765</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" s="30">
+        <v>237</v>
+      </c>
+      <c r="B17" s="31">
         <v>12000</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>12360</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>12731</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>13113</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>13506</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B18" s="30">
+        <v>238</v>
+      </c>
+      <c r="B18" s="31">
         <v>18000</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>18540</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>19096</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>19669</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>20259</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B19" s="30">
+        <v>239</v>
+      </c>
+      <c r="B19" s="31">
         <v>90000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>154500</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>238703</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>327818</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>422066</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B20" s="31">
+        <v>240</v>
+      </c>
+      <c r="B20" s="32">
         <f>SUM(B16:B19)</f>
         <v>150000</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>SUM(C16:C19)</f>
         <v>216300</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="32">
         <f>SUM(D16:D19)</f>
         <v>302357</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="32">
         <f>SUM(E16:E19)</f>
         <v>393382</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>SUM(F16:F19)</f>
         <v>489596</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="B22" s="33">
         <f>B6+B9+B14+B20</f>
         <v>604000</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <f>C6+C9+C14+C20</f>
         <v>774560</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <f>D6+D9+D14+D20</f>
         <v>994063</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <f>E6+E9+E14+E20</f>
         <v>1226040</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <f>F6+F9+F14+F20</f>
         <v>1471040</v>
       </c>
@@ -9990,7 +10013,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9999,39 +10022,39 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="B3" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>242</v>
+      <c r="D3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="C4" s="22">
+        <v>164</v>
+      </c>
+      <c r="C4" s="23">
         <v>350000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="24">
         <v>0.06</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="22">
         <v>10</v>
       </c>
       <c r="F4" s="34">
@@ -10040,15 +10063,15 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="C5" s="22">
+        <v>244</v>
+      </c>
+      <c r="C5" s="23">
         <v>60000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
       <c r="E5" s="36">
@@ -10060,17 +10083,17 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="F7" s="32">
+        <v>245</v>
+      </c>
+      <c r="F7" s="33">
         <v>46629</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F8" s="31">
+        <v>246</v>
+      </c>
+      <c r="F8" s="32">
         <v>350000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="453">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1228,6 +1228,15 @@
     <t>Generated March 26, 2026</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -1246,18 +1255,42 @@
     <t>Year 5</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Net Income</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
     <t>Break-even Year</t>
   </si>
   <si>
@@ -1265,6 +1298,9 @@
   </si>
   <si>
     <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1368,7 +1404,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1487,6 +1523,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FFDC2626"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1498,7 +1540,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1533,6 +1575,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1587,7 +1634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1657,6 +1704,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1678,6 +1728,14 @@
     <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1685,7 +1743,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1695,17 +1753,38 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7135,19 +7214,20 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>396</v>
       </c>
@@ -7156,8 +7236,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="54" t="s">
         <v>397</v>
       </c>
@@ -7166,559 +7247,632 @@
       <c r="E3" s="54"/>
       <c r="F3" s="54"/>
       <c r="G3" s="54"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="H3" s="54"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="55" t="s">
         <v>398</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="D4" s="56" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="F4" s="57" t="s">
         <v>400</v>
       </c>
-      <c r="E5" s="55" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="F5" s="55" t="s">
+      <c r="C6" s="58" t="s">
         <v>402</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="D6" s="58" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="C6" s="56">
-        <v>120</v>
-      </c>
-      <c r="D6" s="56">
-        <v>200</v>
-      </c>
-      <c r="E6" s="56">
-        <v>300</v>
-      </c>
-      <c r="F6" s="56">
-        <v>400</v>
-      </c>
-      <c r="G6" s="56">
-        <v>500</v>
+      <c r="E6" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="F6" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="G6" s="58" t="s">
+        <v>406</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="C7" s="57">
-        <v>1178333.3333333335</v>
-      </c>
-      <c r="D7" s="57">
-        <v>2261600</v>
-      </c>
-      <c r="E7" s="57">
-        <v>3367965</v>
-      </c>
-      <c r="F7" s="57">
-        <v>4502531.525</v>
-      </c>
-      <c r="G7" s="57">
-        <v>5696361.453</v>
+        <v>394</v>
+      </c>
+      <c r="C7" s="59">
+        <v>120</v>
+      </c>
+      <c r="D7" s="59">
+        <v>200</v>
+      </c>
+      <c r="E7" s="59">
+        <v>300</v>
+      </c>
+      <c r="F7" s="59">
+        <v>400</v>
+      </c>
+      <c r="G7" s="59">
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="C8" s="57">
-        <v>780535</v>
-      </c>
-      <c r="D8" s="57">
-        <v>964741.26</v>
-      </c>
-      <c r="E8" s="57">
-        <v>993683.4978</v>
-      </c>
-      <c r="F8" s="57">
-        <v>1023494.002734</v>
-      </c>
-      <c r="G8" s="57">
-        <v>1054198.82281602</v>
+        <v>351</v>
+      </c>
+      <c r="C8" s="60">
+        <v>1178333.3333333335</v>
+      </c>
+      <c r="D8" s="60">
+        <v>2261600</v>
+      </c>
+      <c r="E8" s="60">
+        <v>3367965</v>
+      </c>
+      <c r="F8" s="60">
+        <v>4502531.525</v>
+      </c>
+      <c r="G8" s="60">
+        <v>5696361.453</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="C9" s="57">
-        <v>503333.3333333334</v>
-      </c>
-      <c r="D9" s="57">
-        <v>774560</v>
-      </c>
-      <c r="E9" s="57">
-        <v>994063.2999999999</v>
-      </c>
-      <c r="F9" s="57">
-        <v>1226039.6940000001</v>
-      </c>
-      <c r="G9" s="57">
-        <v>1471040.01467</v>
+        <v>313</v>
+      </c>
+      <c r="C9" s="60">
+        <v>780535</v>
+      </c>
+      <c r="D9" s="60">
+        <v>964741.26</v>
+      </c>
+      <c r="E9" s="60">
+        <v>993683.4978</v>
+      </c>
+      <c r="F9" s="60">
+        <v>1023494.002734</v>
+      </c>
+      <c r="G9" s="60">
+        <v>1054198.82281602</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="60">
+        <v>503333.3333333334</v>
+      </c>
+      <c r="D10" s="60">
+        <v>774560</v>
+      </c>
+      <c r="E10" s="60">
+        <v>994063.2999999999</v>
+      </c>
+      <c r="F10" s="60">
+        <v>1226039.6940000001</v>
+      </c>
+      <c r="G10" s="60">
+        <v>1471040.01467</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C11" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="D10" s="57">
+      <c r="D11" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="E10" s="57">
+      <c r="E11" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="F10" s="57">
+      <c r="F11" s="60">
         <v>46628.6108154935</v>
       </c>
-      <c r="G10" s="57">
+      <c r="G11" s="60">
         <v>46628.6108154935</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="C11" s="58">
-        <v>-212163.6108154934</v>
-      </c>
-      <c r="D11" s="59">
-        <v>455670.12918450637</v>
-      </c>
-      <c r="E11" s="59">
-        <v>1308589.5913845068</v>
-      </c>
-      <c r="F11" s="59">
-        <v>2196369.217450507</v>
-      </c>
-      <c r="G11" s="59">
-        <v>3114494.004698486</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="C12" s="59">
-        <v>74498</v>
-      </c>
-      <c r="D12" s="59">
-        <v>530168.1291845064</v>
-      </c>
-      <c r="E12" s="59">
-        <v>1838757.7205690132</v>
-      </c>
-      <c r="F12" s="59">
-        <v>4035126.93801952</v>
-      </c>
-      <c r="G12" s="59">
-        <v>7149620.942718007</v>
+        <v>408</v>
+      </c>
+      <c r="C12" s="61">
+        <v>-212163.6108154934</v>
+      </c>
+      <c r="D12" s="62">
+        <v>455670.12918450637</v>
+      </c>
+      <c r="E12" s="62">
+        <v>1308589.5913845068</v>
+      </c>
+      <c r="F12" s="62">
+        <v>2196369.217450507</v>
+      </c>
+      <c r="G12" s="62">
+        <v>3114494.004698486</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="C13" s="60">
-        <v>-0.18005398371894768</v>
-      </c>
-      <c r="D13" s="61">
-        <v>0.20148130933167066</v>
-      </c>
-      <c r="E13" s="61">
-        <v>0.38854013963461814</v>
-      </c>
-      <c r="F13" s="61">
-        <v>0.48780762672183775</v>
-      </c>
-      <c r="G13" s="61">
-        <v>0.54675147116204</v>
+        <v>355</v>
+      </c>
+      <c r="C13" s="62">
+        <v>74498</v>
+      </c>
+      <c r="D13" s="62">
+        <v>530168.1291845064</v>
+      </c>
+      <c r="E13" s="62">
+        <v>1838757.7205690132</v>
+      </c>
+      <c r="F13" s="62">
+        <v>4035126.93801952</v>
+      </c>
+      <c r="G13" s="62">
+        <v>7149620.942718007</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C14" s="63">
+        <v>-0.18005398371894768</v>
+      </c>
+      <c r="D14" s="64">
+        <v>0.20148130933167066</v>
+      </c>
+      <c r="E14" s="64">
+        <v>0.38854013963461814</v>
+      </c>
+      <c r="F14" s="64">
+        <v>0.48780762672183775</v>
+      </c>
+      <c r="G14" s="64">
+        <v>0.54675147116204</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C14" s="57">
+      <c r="C15" s="65">
         <v>9819.444444444445</v>
       </c>
-      <c r="D14" s="57">
+      <c r="D15" s="66">
         <v>11308</v>
       </c>
-      <c r="E14" s="57">
+      <c r="E15" s="66">
         <v>11226.55</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F15" s="66">
         <v>11256.328812500002</v>
       </c>
-      <c r="G14" s="57">
+      <c r="G15" s="66">
         <v>11392.722905999999</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="C15" s="60">
+      <c r="H15" s="67" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="C16" s="63">
         <v>0.6624059405940593</v>
       </c>
-      <c r="D15" s="61">
+      <c r="D16" s="64">
         <v>0.4265746639547223</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E16" s="64">
         <v>0.29503973402336425</v>
       </c>
-      <c r="F15" s="61">
+      <c r="F16" s="64">
         <v>0.22731523300861284</v>
       </c>
-      <c r="G15" s="61">
+      <c r="G16" s="64">
         <v>0.18506529677129674</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="C16" s="61">
+      <c r="H16" s="67" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C17" s="64">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D17" s="64">
         <v>0.10274495932083481</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E17" s="64">
         <v>0.08854575092080826</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F17" s="64">
         <v>0.0816900239693491</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G17" s="64">
         <v>0.07747261265673058</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="C17" s="60">
+      <c r="H17" s="67" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C18" s="63">
         <v>-0.08956294200848645</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D18" s="64">
         <v>0.23094213830916166</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E18" s="64">
         <v>0.40980776290727494</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F18" s="64">
         <v>0.5003846870935568</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G18" s="64">
         <v>0.5566926610396014</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="H18" s="67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C19" s="68">
+        <v>1</v>
+      </c>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="67" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="C18" s="62">
+      <c r="C20" s="69">
         <v>-2.2633099754482346</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D20" s="70">
         <v>11.201250281006729</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E20" s="70">
         <v>29.600242813611526</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F20" s="70">
         <v>48.31792731679209</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G20" s="70">
         <v>68.00808688171976</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="C19" s="64" t="s">
-        <v>400</v>
-      </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>410</v>
-      </c>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="41" t="s">
-        <v>415</v>
-      </c>
-      <c r="C23" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="D23" s="67" t="s">
-        <v>417</v>
-      </c>
-      <c r="E23" s="67"/>
-      <c r="F23" s="68" t="s">
+      <c r="H20" s="67" t="s">
         <v>418</v>
       </c>
-      <c r="G23" s="68"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="41" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="C24" s="69" t="s">
+      <c r="C21" s="71" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="67" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="C22" s="72" t="s">
         <v>421</v>
       </c>
-      <c r="E24" s="67"/>
-      <c r="F24" s="68" t="s">
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="67" t="s">
         <v>422</v>
       </c>
-      <c r="G24" s="68"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="41" t="s">
-        <v>423</v>
-      </c>
-      <c r="C25" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>424</v>
-      </c>
-      <c r="E25" s="67"/>
-      <c r="F25" s="68" t="s">
-        <v>425</v>
-      </c>
-      <c r="G25" s="68"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="D25" s="74" t="s">
+        <v>429</v>
+      </c>
+      <c r="E25" s="74"/>
+      <c r="F25" s="75" t="s">
+        <v>430</v>
+      </c>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="41" t="s">
-        <v>426</v>
-      </c>
-      <c r="C26" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="D26" s="67" t="s">
-        <v>427</v>
-      </c>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68" t="s">
+        <v>431</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>432</v>
+      </c>
+      <c r="D26" s="74" t="s">
+        <v>433</v>
+      </c>
+      <c r="E26" s="74"/>
+      <c r="F26" s="75" t="s">
+        <v>434</v>
+      </c>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="41" t="s">
+        <v>435</v>
+      </c>
+      <c r="C27" s="73" t="s">
         <v>428</v>
       </c>
-      <c r="G26" s="68"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="41" t="s">
-        <v>429</v>
-      </c>
-      <c r="C27" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="D27" s="67" t="s">
-        <v>430</v>
-      </c>
-      <c r="E27" s="67"/>
-      <c r="F27" s="68" t="s">
-        <v>431</v>
-      </c>
-      <c r="G27" s="68"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D27" s="74" t="s">
+        <v>436</v>
+      </c>
+      <c r="E27" s="74"/>
+      <c r="F27" s="75" t="s">
+        <v>437</v>
+      </c>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="41" t="s">
-        <v>432</v>
-      </c>
-      <c r="C28" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="D28" s="67" t="s">
-        <v>433</v>
-      </c>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68" t="s">
-        <v>434</v>
-      </c>
-      <c r="G28" s="68"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+      <c r="C28" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="D28" s="74" t="s">
+        <v>439</v>
+      </c>
+      <c r="E28" s="74"/>
+      <c r="F28" s="75" t="s">
+        <v>440</v>
+      </c>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
-        <v>435</v>
-      </c>
-      <c r="C29" s="66" t="s">
-        <v>416</v>
-      </c>
-      <c r="D29" s="67" t="s">
-        <v>436</v>
-      </c>
-      <c r="E29" s="67"/>
-      <c r="F29" s="68" t="s">
-        <v>437</v>
-      </c>
-      <c r="G29" s="68"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+      <c r="C29" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="D29" s="74" t="s">
+        <v>442</v>
+      </c>
+      <c r="E29" s="74"/>
+      <c r="F29" s="75" t="s">
+        <v>443</v>
+      </c>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="41" t="s">
+        <v>444</v>
+      </c>
+      <c r="C30" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="D30" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="E30" s="74"/>
+      <c r="F30" s="75" t="s">
+        <v>446</v>
+      </c>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="41" t="s">
-        <v>438</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="70" t="s">
-        <v>440</v>
-      </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
+        <v>447</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="D31" s="74" t="s">
+        <v>448</v>
+      </c>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75" t="s">
+        <v>449</v>
+      </c>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="41" t="s">
+        <v>450</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="77" t="s">
+        <v>452</v>
+      </c>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="456">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1007,6 +1007,15 @@
   </si>
   <si>
     <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>Cumulative Profit</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>LOAN TERMS</t>
@@ -1499,6 +1508,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF328555"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1512,12 +1527,6 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1634,7 +1643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1684,18 +1693,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1703,8 +1718,8 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1734,23 +1749,20 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4643,7 +4655,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4863,6 +4875,51 @@
       <c r="F15" s="30">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.54675147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" s="34">
+        <f>B14</f>
+        <v>-212164</v>
+      </c>
+      <c r="C16" s="34">
+        <f>B16+C14</f>
+        <v>243507</v>
+      </c>
+      <c r="D16" s="34">
+        <f>C16+D14</f>
+        <v>1552096</v>
+      </c>
+      <c r="E16" s="34">
+        <f>D16+E14</f>
+        <v>3748465</v>
+      </c>
+      <c r="F16" s="34">
+        <f>E16+F14</f>
+        <v>6862959</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4921,7 +4978,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4930,19 +4987,19 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>326</v>
-      </c>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="43" t="s">
-        <v>327</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="E5" s="42" t="s">
+      <c r="C5" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>331</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>243</v>
       </c>
     </row>
@@ -4966,7 +5023,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -4976,7 +5033,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B9" s="31">
         <f>B6</f>
@@ -5001,7 +5058,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5026,7 +5083,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5051,7 +5108,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -5076,7 +5133,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B13" s="39">
         <f>MAX(0,B9-B11)</f>
@@ -5125,7 +5182,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5155,7 +5212,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5165,32 +5222,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B5" s="44">
+        <v>340</v>
+      </c>
+      <c r="B5" s="46">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>74498</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="46">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>530168</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="46">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>1838758</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="46">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>4035127</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="46">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>7149621</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B6" s="31">
         <v>0</v>
@@ -5210,7 +5267,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B7" s="31">
         <v>0</v>
@@ -5230,7 +5287,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B8" s="31">
         <v>0</v>
@@ -5250,7 +5307,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
@@ -5275,7 +5332,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5285,7 +5342,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B12" s="31">
         <v>0</v>
@@ -5305,7 +5362,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
@@ -5330,7 +5387,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
@@ -5355,7 +5412,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5365,7 +5422,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
@@ -5390,25 +5447,25 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="B19" s="45" t="str">
+        <v>351</v>
+      </c>
+      <c r="B19" s="47" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="48">
         <f>C9-C14-C17</f>
         <v>-1</v>
       </c>
-      <c r="D19" s="45" t="str">
+      <c r="D19" s="47" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="45" t="str">
+      <c r="E19" s="47" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="45" t="str">
+      <c r="F19" s="47" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -5439,7 +5496,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5469,7 +5526,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5479,7 +5536,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B5" s="31">
         <v>1178333</v>
@@ -5539,7 +5596,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -5584,32 +5641,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="B10" s="47">
+        <v>356</v>
+      </c>
+      <c r="B10" s="49">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>-2.26</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="49">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>11.2</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="49">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>29.6</v>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="49">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>48.32</v>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="49">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>68.01</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -5619,7 +5676,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B13" s="31">
         <v>74498</v>
@@ -5639,7 +5696,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5664,7 +5721,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5709,7 +5766,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5739,7 +5796,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B20" s="31">
         <v>827164</v>
@@ -5759,7 +5816,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B21" s="31">
         <v>4194</v>
@@ -5779,27 +5836,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="B22" s="48">
+        <v>364</v>
+      </c>
+      <c r="B22" s="50">
         <v>148</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="50">
         <v>137</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="50">
         <v>132</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="50">
         <v>131</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="50">
         <v>131</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -5809,102 +5866,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B25" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="F25" s="50" t="s">
-        <v>365</v>
+        <v>366</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="F25" s="52" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="B26" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="D26" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="F26" s="50" t="s">
-        <v>365</v>
+        <v>369</v>
+      </c>
+      <c r="B26" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="E26" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="F26" s="52" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="B27" s="51" t="s">
         <v>367</v>
       </c>
-      <c r="B27" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="F27" s="49" t="s">
-        <v>364</v>
+      <c r="C27" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="C28" s="52" t="s">
         <v>368</v>
       </c>
-      <c r="B28" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="D28" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="E28" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="F28" s="50" t="s">
-        <v>365</v>
+      <c r="D28" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="B29" s="49" t="s">
-        <v>364</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="D29" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="E29" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="F29" s="50" t="s">
-        <v>365</v>
+        <v>372</v>
+      </c>
+      <c r="B29" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -5944,16 +6001,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
-        <v>370</v>
-      </c>
-      <c r="B3" s="51" t="s">
+      <c r="A3" s="53" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="51" t="s">
-        <v>371</v>
-      </c>
-      <c r="E3" s="51" t="s">
+      <c r="D3" s="53" t="s">
+        <v>374</v>
+      </c>
+      <c r="E3" s="53" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5965,7 +6022,7 @@
         <v>350000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E4" s="31">
         <v>250000</v>
@@ -5973,7 +6030,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B5" s="31">
         <v>150000</v>
@@ -5987,7 +6044,7 @@
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E6" s="31">
         <v>50000</v>
@@ -5995,7 +6052,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E7" s="31">
         <v>140000</v>
@@ -6003,13 +6060,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B9" s="33">
         <v>500000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E9" s="33">
         <v>500000</v>
@@ -6017,9 +6074,9 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="B10" s="45">
+        <v>381</v>
+      </c>
+      <c r="B10" s="47">
         <v>0</v>
       </c>
     </row>
@@ -6365,7 +6422,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6375,7 +6432,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6385,7 +6442,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6410,7 +6467,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B6" s="31">
         <v>1178333</v>
@@ -6490,27 +6547,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B10" s="52">
+        <v>356</v>
+      </c>
+      <c r="B10" s="54">
         <v>-2.26</v>
       </c>
-      <c r="C10" s="52">
+      <c r="C10" s="54">
         <v>11.2</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="54">
         <v>29.6</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="54">
         <v>48.32</v>
       </c>
-      <c r="F10" s="52">
+      <c r="F10" s="54">
         <v>68.01</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B11" s="36">
         <v>148</v>
@@ -6530,7 +6587,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6540,7 +6597,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6565,7 +6622,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B16" s="31">
         <v>1001583</v>
@@ -6645,27 +6702,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B20" s="52">
+        <v>356</v>
+      </c>
+      <c r="B20" s="54">
         <v>-6.05</v>
       </c>
-      <c r="C20" s="52">
+      <c r="C20" s="54">
         <v>3.93</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="54">
         <v>18.77</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="54">
         <v>33.83</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="54">
         <v>49.68</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B21" s="36">
         <v>170</v>
@@ -6685,7 +6742,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6695,7 +6752,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6720,7 +6777,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B26" s="31">
         <v>1084067</v>
@@ -6800,27 +6857,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B30" s="52">
+        <v>356</v>
+      </c>
+      <c r="B30" s="54">
         <v>-4.28</v>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="54">
         <v>7.32</v>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="54">
         <v>23.82</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="54">
         <v>40.59</v>
       </c>
-      <c r="F30" s="52">
+      <c r="F30" s="54">
         <v>58.23</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B31" s="36">
         <v>171</v>
@@ -6866,7 +6923,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6900,7 +6957,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6924,7 +6981,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6932,7 +6989,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6952,25 +7009,25 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="53" t="s">
+      <c r="G12" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="53" t="s">
+      <c r="H12" s="55" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D13" s="31">
         <v>1178333</v>
@@ -7030,7 +7087,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D16" s="31">
         <v>74498</v>
@@ -7050,7 +7107,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D17" s="31">
         <v>323655</v>
@@ -7070,7 +7127,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7090,25 +7147,25 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="53" t="s">
+      <c r="G20" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="53" t="s">
+      <c r="H20" s="55" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D21" s="30">
         <v>-0.18005398371894768</v>
@@ -7128,21 +7185,21 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="D22" s="52">
+        <v>356</v>
+      </c>
+      <c r="D22" s="54">
         <v>-2.26</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="54">
         <v>11.2</v>
       </c>
-      <c r="F22" s="52">
+      <c r="F22" s="54">
         <v>29.6</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="54">
         <v>48.32</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="54">
         <v>68.01</v>
       </c>
     </row>
@@ -7168,7 +7225,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D24" s="36">
         <v>120</v>
@@ -7188,7 +7245,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7229,7 +7286,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7239,87 +7296,87 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="54" t="s">
-        <v>397</v>
-      </c>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="B3" s="56" t="s">
+        <v>400</v>
+      </c>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="55" t="s">
-        <v>398</v>
-      </c>
-      <c r="D4" s="56" t="s">
-        <v>399</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>400</v>
+      <c r="B4" s="57" t="s">
+        <v>401</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="C6" s="58" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>403</v>
-      </c>
-      <c r="E6" s="58" t="s">
         <v>404</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="C6" s="60" t="s">
         <v>405</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="D6" s="60" t="s">
         <v>406</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="E6" s="60" t="s">
         <v>407</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>408</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>409</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="C7" s="59">
+        <v>397</v>
+      </c>
+      <c r="C7" s="61">
         <v>120</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="61">
         <v>200</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="61">
         <v>300</v>
       </c>
-      <c r="F7" s="59">
+      <c r="F7" s="61">
         <v>400</v>
       </c>
-      <c r="G7" s="59">
+      <c r="G7" s="61">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="C8" s="60">
+        <v>354</v>
+      </c>
+      <c r="C8" s="62">
         <v>1178333.3333333335</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="62">
         <v>2261600</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="62">
         <v>3367965</v>
       </c>
-      <c r="F8" s="60">
+      <c r="F8" s="62">
         <v>4502531.525</v>
       </c>
-      <c r="G8" s="60">
+      <c r="G8" s="62">
         <v>5696361.453</v>
       </c>
     </row>
@@ -7327,19 +7384,19 @@
       <c r="B9" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="C9" s="60">
+      <c r="C9" s="62">
         <v>780535</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="62">
         <v>964741.26</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="62">
         <v>993683.4978</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="62">
         <v>1023494.002734</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="62">
         <v>1054198.82281602</v>
       </c>
     </row>
@@ -7347,19 +7404,19 @@
       <c r="B10" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="C10" s="60">
+      <c r="C10" s="62">
         <v>503333.3333333334</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="62">
         <v>774560</v>
       </c>
-      <c r="E10" s="60">
+      <c r="E10" s="62">
         <v>994063.2999999999</v>
       </c>
-      <c r="F10" s="60">
+      <c r="F10" s="62">
         <v>1226039.6940000001</v>
       </c>
-      <c r="G10" s="60">
+      <c r="G10" s="62">
         <v>1471040.01467</v>
       </c>
     </row>
@@ -7367,79 +7424,79 @@
       <c r="B11" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="62">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="62">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="60">
+      <c r="E11" s="62">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="62">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="60">
+      <c r="G11" s="62">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="C12" s="61">
+        <v>411</v>
+      </c>
+      <c r="C12" s="63">
         <v>-212163.6108154934</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="64">
         <v>455670.12918450637</v>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="64">
         <v>1308589.5913845068</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="64">
         <v>2196369.217450507</v>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="64">
         <v>3114494.004698486</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="C13" s="62">
+        <v>358</v>
+      </c>
+      <c r="C13" s="64">
         <v>74498</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="64">
         <v>530168.1291845064</v>
       </c>
-      <c r="E13" s="62">
+      <c r="E13" s="64">
         <v>1838757.7205690132</v>
       </c>
-      <c r="F13" s="62">
+      <c r="F13" s="64">
         <v>4035126.93801952</v>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="64">
         <v>7149620.942718007</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="C14" s="63">
+        <v>396</v>
+      </c>
+      <c r="C14" s="65">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="66">
         <v>0.20148130933167066</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="66">
         <v>0.38854013963461814</v>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="66">
         <v>0.48780762672183775</v>
       </c>
-      <c r="G14" s="64">
+      <c r="G14" s="66">
         <v>0.54675147116204</v>
       </c>
     </row>
@@ -7447,319 +7504,319 @@
       <c r="B15" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="67">
         <v>9819.444444444445</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="68">
         <v>11308</v>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="68">
         <v>11226.55</v>
       </c>
-      <c r="F15" s="66">
+      <c r="F15" s="68">
         <v>11256.328812500002</v>
       </c>
-      <c r="G15" s="66">
+      <c r="G15" s="68">
         <v>11392.722905999999</v>
       </c>
-      <c r="H15" s="67" t="s">
-        <v>409</v>
+      <c r="H15" s="69" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="C16" s="63">
+        <v>413</v>
+      </c>
+      <c r="C16" s="65">
         <v>0.6624059405940593</v>
       </c>
-      <c r="D16" s="64">
+      <c r="D16" s="66">
         <v>0.4265746639547223</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="66">
         <v>0.29503973402336425</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="66">
         <v>0.22731523300861284</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="66">
         <v>0.18506529677129674</v>
       </c>
-      <c r="H16" s="67" t="s">
-        <v>411</v>
+      <c r="H16" s="69" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="C17" s="64">
+        <v>415</v>
+      </c>
+      <c r="C17" s="66">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="66">
         <v>0.10274495932083481</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="66">
         <v>0.08854575092080826</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="66">
         <v>0.0816900239693491</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="66">
         <v>0.07747261265673058</v>
       </c>
-      <c r="H17" s="67" t="s">
-        <v>413</v>
+      <c r="H17" s="69" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="C18" s="63">
+        <v>417</v>
+      </c>
+      <c r="C18" s="65">
         <v>-0.08956294200848645</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="66">
         <v>0.23094213830916166</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="66">
         <v>0.40980776290727494</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="66">
         <v>0.5003846870935568</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="66">
         <v>0.5566926610396014</v>
       </c>
-      <c r="H18" s="67" t="s">
-        <v>415</v>
+      <c r="H18" s="69" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C19" s="68">
-        <v>1</v>
-      </c>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="67" t="s">
-        <v>417</v>
+        <v>419</v>
+      </c>
+      <c r="C19" s="70">
+        <v>3</v>
+      </c>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="69" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" s="69">
+        <v>356</v>
+      </c>
+      <c r="C20" s="71">
         <v>-2.2633099754482346</v>
       </c>
-      <c r="D20" s="70">
+      <c r="D20" s="72">
         <v>11.201250281006729</v>
       </c>
-      <c r="E20" s="70">
+      <c r="E20" s="72">
         <v>29.600242813611526</v>
       </c>
-      <c r="F20" s="70">
+      <c r="F20" s="72">
         <v>48.31792731679209</v>
       </c>
-      <c r="G20" s="70">
+      <c r="G20" s="72">
         <v>68.00808688171976</v>
       </c>
-      <c r="H20" s="67" t="s">
-        <v>418</v>
+      <c r="H20" s="69" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="C21" s="71" t="s">
-        <v>403</v>
-      </c>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="67" t="s">
-        <v>402</v>
+        <v>422</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="69" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>421</v>
-      </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="67" t="s">
-        <v>422</v>
+        <v>423</v>
+      </c>
+      <c r="C22" s="74" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="69" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="41" t="s">
-        <v>427</v>
-      </c>
-      <c r="C25" s="73" t="s">
-        <v>428</v>
-      </c>
-      <c r="D25" s="74" t="s">
-        <v>429</v>
-      </c>
-      <c r="E25" s="74"/>
-      <c r="F25" s="75" t="s">
+      <c r="B25" s="43" t="s">
         <v>430</v>
       </c>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
+      <c r="C25" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>432</v>
+      </c>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76" t="s">
+        <v>433</v>
+      </c>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="43" t="s">
+        <v>434</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>435</v>
+      </c>
+      <c r="D26" s="75" t="s">
+        <v>436</v>
+      </c>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76" t="s">
+        <v>437</v>
+      </c>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="C27" s="42" t="s">
         <v>431</v>
       </c>
-      <c r="C26" s="76" t="s">
-        <v>432</v>
-      </c>
-      <c r="D26" s="74" t="s">
-        <v>433</v>
-      </c>
-      <c r="E26" s="74"/>
-      <c r="F26" s="75" t="s">
-        <v>434</v>
-      </c>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="41" t="s">
-        <v>435</v>
-      </c>
-      <c r="C27" s="73" t="s">
-        <v>428</v>
-      </c>
-      <c r="D27" s="74" t="s">
-        <v>436</v>
-      </c>
-      <c r="E27" s="74"/>
-      <c r="F27" s="75" t="s">
-        <v>437</v>
-      </c>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="D27" s="75" t="s">
+        <v>439</v>
+      </c>
+      <c r="E27" s="75"/>
+      <c r="F27" s="76" t="s">
+        <v>440</v>
+      </c>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="41" t="s">
-        <v>438</v>
-      </c>
-      <c r="C28" s="73" t="s">
-        <v>428</v>
-      </c>
-      <c r="D28" s="74" t="s">
-        <v>439</v>
-      </c>
-      <c r="E28" s="74"/>
-      <c r="F28" s="75" t="s">
-        <v>440</v>
-      </c>
-      <c r="G28" s="75"/>
-      <c r="H28" s="75"/>
+      <c r="B28" s="43" t="s">
+        <v>441</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>442</v>
+      </c>
+      <c r="E28" s="75"/>
+      <c r="F28" s="76" t="s">
+        <v>443</v>
+      </c>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="41" t="s">
-        <v>441</v>
-      </c>
-      <c r="C29" s="73" t="s">
-        <v>428</v>
-      </c>
-      <c r="D29" s="74" t="s">
-        <v>442</v>
-      </c>
-      <c r="E29" s="74"/>
-      <c r="F29" s="75" t="s">
-        <v>443</v>
-      </c>
-      <c r="G29" s="75"/>
-      <c r="H29" s="75"/>
+      <c r="B29" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>445</v>
+      </c>
+      <c r="E29" s="75"/>
+      <c r="F29" s="76" t="s">
+        <v>446</v>
+      </c>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="41" t="s">
-        <v>444</v>
-      </c>
-      <c r="C30" s="73" t="s">
-        <v>428</v>
-      </c>
-      <c r="D30" s="74" t="s">
-        <v>445</v>
-      </c>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75" t="s">
-        <v>446</v>
-      </c>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
+      <c r="B30" s="43" t="s">
+        <v>447</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>448</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>449</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="41" t="s">
-        <v>447</v>
-      </c>
-      <c r="C31" s="73" t="s">
-        <v>428</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>448</v>
-      </c>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75" t="s">
-        <v>449</v>
-      </c>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
+      <c r="B31" s="43" t="s">
+        <v>450</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>451</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>452</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="41" t="s">
-        <v>450</v>
+      <c r="B33" s="43" t="s">
+        <v>453</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="77" t="s">
-        <v>452</v>
-      </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="B35" s="78" t="s">
+        <v>455</v>
+      </c>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -7926,10 +7926,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="456">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1757,7 +1757,9 @@
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7634,13 +7636,26 @@
       <c r="B21" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="C21" s="73" t="s">
-        <v>406</v>
-      </c>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
+      <c r="C21" s="73" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="42" t="str">
+        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="73" t="str">
+        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="73" t="str">
+        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="73" t="str">
+        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="69" t="s">
         <v>405</v>
       </c>
@@ -7819,11 +7834,10 @@
       <c r="H35" s="78"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -7904,10 +7918,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="455">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1303,13 +1303,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1643,7 +1640,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1750,7 +1747,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="168" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1760,7 +1759,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -7601,10 +7605,18 @@
       <c r="C19" s="70">
         <v>3</v>
       </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
+      <c r="D19" s="70">
+        <v>3</v>
+      </c>
+      <c r="E19" s="70">
+        <v>3</v>
+      </c>
+      <c r="F19" s="70">
+        <v>3</v>
+      </c>
+      <c r="G19" s="70">
+        <v>3</v>
+      </c>
       <c r="H19" s="69" t="s">
         <v>420</v>
       </c>
@@ -7641,19 +7653,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="42" t="str">
-        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="E21" s="73" t="str">
-        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="73" t="str">
-        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="73" t="str">
-        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="69" t="s">
@@ -7664,181 +7676,187 @@
       <c r="B22" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="C22" s="74" t="s">
+      <c r="C22" s="74">
+        <v>1</v>
+      </c>
+      <c r="D22" s="74">
+        <v>4</v>
+      </c>
+      <c r="E22" s="74">
+        <v>11</v>
+      </c>
+      <c r="F22" s="75">
+        <v>21</v>
+      </c>
+      <c r="G22" s="70">
+        <v>33</v>
+      </c>
+      <c r="H22" s="69" t="s">
         <v>424</v>
-      </c>
-      <c r="D22" s="74"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="69" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>426</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" s="19" t="s">
         <v>427</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>428</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="C25" s="42" t="s">
         <v>430</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="D25" s="76" t="s">
         <v>431</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="E25" s="76"/>
+      <c r="F25" s="77" t="s">
         <v>432</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76" t="s">
-        <v>433</v>
-      </c>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="43" t="s">
+        <v>433</v>
+      </c>
+      <c r="C26" s="78" t="s">
         <v>434</v>
       </c>
-      <c r="C26" s="77" t="s">
+      <c r="D26" s="76" t="s">
         <v>435</v>
       </c>
-      <c r="D26" s="75" t="s">
+      <c r="E26" s="76"/>
+      <c r="F26" s="77" t="s">
         <v>436</v>
       </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76" t="s">
-        <v>437</v>
-      </c>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="43" t="s">
+        <v>437</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="D27" s="76" t="s">
         <v>438</v>
       </c>
-      <c r="C27" s="42" t="s">
-        <v>431</v>
-      </c>
-      <c r="D27" s="75" t="s">
+      <c r="E27" s="76"/>
+      <c r="F27" s="77" t="s">
         <v>439</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76" t="s">
-        <v>440</v>
-      </c>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="43" t="s">
+        <v>440</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="D28" s="76" t="s">
         <v>441</v>
       </c>
-      <c r="C28" s="42" t="s">
-        <v>431</v>
-      </c>
-      <c r="D28" s="75" t="s">
+      <c r="E28" s="76"/>
+      <c r="F28" s="77" t="s">
         <v>442</v>
       </c>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76" t="s">
-        <v>443</v>
-      </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="43" t="s">
+        <v>443</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="D29" s="76" t="s">
         <v>444</v>
       </c>
-      <c r="C29" s="42" t="s">
-        <v>431</v>
-      </c>
-      <c r="D29" s="75" t="s">
+      <c r="E29" s="76"/>
+      <c r="F29" s="77" t="s">
         <v>445</v>
       </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76" t="s">
-        <v>446</v>
-      </c>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="D30" s="76" t="s">
         <v>447</v>
       </c>
-      <c r="C30" s="42" t="s">
-        <v>431</v>
-      </c>
-      <c r="D30" s="75" t="s">
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
         <v>448</v>
       </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>449</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="43" t="s">
+        <v>449</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="D31" s="76" t="s">
         <v>450</v>
       </c>
-      <c r="C31" s="42" t="s">
-        <v>431</v>
-      </c>
-      <c r="D31" s="75" t="s">
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
         <v>451</v>
       </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
-        <v>452</v>
-      </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="43" t="s">
+        <v>452</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>453</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>454</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="78" t="s">
-        <v>455</v>
-      </c>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="B35" s="79" t="s">
+        <v>454</v>
+      </c>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -1357,7 +1357,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 8% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -7556,20 +7556,20 @@
       <c r="B17" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.12814710042432814</v>
+      <c r="C17" s="65">
+        <v>0.27326732673267323</v>
       </c>
       <c r="D17" s="66">
-        <v>0.10274495932083481</v>
+        <v>0.14664839051998585</v>
       </c>
       <c r="E17" s="66">
-        <v>0.08854575092080826</v>
+        <v>0.1014291419299191</v>
       </c>
       <c r="F17" s="66">
-        <v>0.0816900239693491</v>
+        <v>0.07814672524697092</v>
       </c>
       <c r="G17" s="66">
-        <v>0.07747261265673058</v>
+        <v>0.06362198744062038</v>
       </c>
       <c r="H17" s="69" t="s">
         <v>416</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -40,7 +40,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +160,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1234,7 +1234,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="462">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -790,6 +790,78 @@
     <t>Staffing Costs Forecast</t>
   </si>
   <si>
+    <t xml:space="preserve">  Lead Teachers [5 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SPED Teacher [1 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional Aides [3 FTE]</t>
+  </si>
+  <si>
+    <t>Total Instructional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Head of School [1 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Assistant Principal [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total School Leadership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Business Manager [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Front Office [2 FTE]</t>
+  </si>
+  <si>
+    <t>Total Administrative</t>
+  </si>
+  <si>
+    <t>TOTAL PERSONNEL</t>
+  </si>
+  <si>
+    <t>Heritage Academy Charter - Budget Detail</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  State Per-Pupil Funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Federal Title I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  IDEA Special Ed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  CSP Startup Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Annual Fundraising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Before/After Care</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>PERSONNEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Head of School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Assistant Principal</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Lead Teachers</t>
   </si>
   <si>
@@ -799,61 +871,10 @@
     <t xml:space="preserve">  Instructional Aides</t>
   </si>
   <si>
-    <t>Total Instructional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Head of School</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Assistant Principal</t>
-  </si>
-  <si>
-    <t>Total School Leadership</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Business Manager</t>
   </si>
   <si>
-    <t>Total Operations</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Front Office</t>
-  </si>
-  <si>
-    <t>Total Administrative</t>
-  </si>
-  <si>
-    <t>TOTAL PERSONNEL</t>
-  </si>
-  <si>
-    <t>Heritage Academy Charter - Budget Detail</t>
-  </si>
-  <si>
-    <t>REVENUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  State Per-Pupil Funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Federal Title I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  IDEA Special Ed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  CSP Startup Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Annual Fundraising</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Before/After Care</t>
-  </si>
-  <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>PERSONNEL</t>
   </si>
   <si>
     <t xml:space="preserve">    Curriculum</t>
@@ -3297,7 +3318,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B14" s="31">
         <v>116944</v>
@@ -3317,7 +3338,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B15" s="31">
         <v>91328</v>
@@ -3337,7 +3358,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="B16" s="31">
         <v>278438</v>
@@ -3357,7 +3378,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="B17" s="31">
         <v>59029</v>
@@ -3377,7 +3398,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="B18" s="31">
         <v>87955</v>
@@ -3397,7 +3418,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B19" s="31">
         <v>69053</v>
@@ -3417,7 +3438,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="B20" s="31">
         <v>77790</v>
@@ -3477,7 +3498,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B25" s="31">
         <v>65000</v>
@@ -3502,7 +3523,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B27" s="31">
         <v>45000</v>
@@ -3527,7 +3548,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B29" s="31">
         <v>220000</v>
@@ -3547,7 +3568,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B30" s="31">
         <v>30000</v>
@@ -3567,7 +3588,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B31" s="31">
         <v>18333</v>
@@ -3587,7 +3608,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B32" s="32">
         <f>SUM(B29:B31)</f>
@@ -3617,7 +3638,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B34" s="31">
         <v>25000</v>
@@ -3637,7 +3658,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B35" s="31">
         <v>10000</v>
@@ -3657,7 +3678,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B36" s="31">
         <v>15000</v>
@@ -3677,7 +3698,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B37" s="31">
         <v>75000</v>
@@ -3697,7 +3718,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B38" s="32">
         <f>SUM(B34:B37)</f>
@@ -3722,7 +3743,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B39" s="32">
         <f>B25+B27+B32+B38</f>
@@ -3747,7 +3768,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -3757,7 +3778,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B42" s="31">
         <v>46629</v>
@@ -3777,7 +3798,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B43" s="31">
         <v>60000</v>
@@ -3797,7 +3818,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B44" s="32">
         <f>SUM(B42:B43)</f>
@@ -3846,7 +3867,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3926,7 +3947,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
@@ -3951,7 +3972,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
@@ -3976,7 +3997,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
@@ -4001,7 +4022,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -4011,7 +4032,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B11" s="33">
         <f>B4-B8</f>
@@ -4036,7 +4057,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -4061,7 +4082,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B13" s="31">
         <v>-212164</v>
@@ -4101,7 +4122,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B15" s="31">
         <v>11587</v>
@@ -4146,7 +4167,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4167,43 +4188,43 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -4271,7 +4292,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4289,7 +4310,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B7" s="31">
         <v>78054</v>
@@ -4334,7 +4355,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B8" s="31">
         <v>50333</v>
@@ -4379,7 +4400,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B9" s="31">
         <v>8886</v>
@@ -4424,7 +4445,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4442,7 +4463,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -4499,7 +4520,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -4556,7 +4577,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B14" s="39">
         <f>B17+B13</f>
@@ -4613,7 +4634,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4628,7 +4649,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B18" s="39">
         <f>M14</f>
@@ -4637,7 +4658,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
@@ -4670,7 +4691,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4730,7 +4751,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4740,7 +4761,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B8" s="34">
         <v>780535</v>
@@ -4760,7 +4781,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B9" s="34">
         <v>503333</v>
@@ -4780,7 +4801,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B10" s="34">
         <v>106629</v>
@@ -4800,7 +4821,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B11" s="32">
         <f>SUM(B8:B10)</f>
@@ -4825,7 +4846,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -4835,7 +4856,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="40" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B14" s="33">
         <f>B5-B11</f>
@@ -4860,7 +4881,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B15" s="30">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4885,7 +4906,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B16" s="34">
         <f>B14</f>
@@ -4910,13 +4931,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B17" s="41" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D17" s="41" t="s">
         <v>7</v>
@@ -4984,7 +5005,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4994,16 +5015,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B5" s="44" t="s">
         <v>161</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E5" s="44" t="s">
         <v>243</v>
@@ -5029,7 +5050,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -5039,7 +5060,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B9" s="31">
         <f>B6</f>
@@ -5064,7 +5085,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5089,7 +5110,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5114,7 +5135,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -5139,7 +5160,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B13" s="39">
         <f>MAX(0,B9-B11)</f>
@@ -5188,7 +5209,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5218,7 +5239,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5228,7 +5249,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B5" s="46">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -5253,7 +5274,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B6" s="31">
         <v>0</v>
@@ -5273,7 +5294,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B7" s="31">
         <v>0</v>
@@ -5293,7 +5314,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B8" s="31">
         <v>0</v>
@@ -5313,7 +5334,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
@@ -5338,7 +5359,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5348,7 +5369,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B12" s="31">
         <v>0</v>
@@ -5368,7 +5389,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
@@ -5393,7 +5414,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
@@ -5418,7 +5439,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5428,7 +5449,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
@@ -5453,7 +5474,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B19" s="47" t="str">
         <f>B9-B14-B17</f>
@@ -5502,7 +5523,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5532,7 +5553,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5542,7 +5563,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B5" s="31">
         <v>1178333</v>
@@ -5562,7 +5583,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B6" s="31">
         <v>780535</v>
@@ -5582,7 +5603,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B7" s="31">
         <v>503333</v>
@@ -5602,7 +5623,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -5627,7 +5648,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B9" s="31">
         <v>46629</v>
@@ -5647,7 +5668,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B10" s="49">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5672,7 +5693,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -5682,7 +5703,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B13" s="31">
         <v>74498</v>
@@ -5702,7 +5723,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5727,7 +5748,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5772,7 +5793,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5802,7 +5823,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B20" s="31">
         <v>827164</v>
@@ -5822,7 +5843,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="B21" s="31">
         <v>4194</v>
@@ -5842,7 +5863,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B22" s="50">
         <v>148</v>
@@ -5862,7 +5883,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -5872,102 +5893,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E25" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F25" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E26" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E28" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F28" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C29" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E29" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -6008,13 +6029,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E3" s="53" t="s">
         <v>112</v>
@@ -6028,7 +6049,7 @@
         <v>350000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E4" s="31">
         <v>250000</v>
@@ -6036,7 +6057,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B5" s="31">
         <v>150000</v>
@@ -6050,7 +6071,7 @@
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E6" s="31">
         <v>50000</v>
@@ -6058,7 +6079,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="E7" s="31">
         <v>140000</v>
@@ -6066,13 +6087,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B9" s="33">
         <v>500000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E9" s="33">
         <v>500000</v>
@@ -6080,7 +6101,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B10" s="47">
         <v>0</v>
@@ -6428,7 +6449,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6438,7 +6459,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6448,7 +6469,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6473,7 +6494,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B6" s="31">
         <v>1178333</v>
@@ -6493,7 +6514,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B7" s="31">
         <v>1330497</v>
@@ -6513,7 +6534,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B8" s="33">
         <v>-152164</v>
@@ -6533,7 +6554,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B9" s="30">
         <v>-0.12913460606689658</v>
@@ -6553,7 +6574,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B10" s="54">
         <v>-2.26</v>
@@ -6573,7 +6594,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B11" s="36">
         <v>148</v>
@@ -6593,7 +6614,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6603,7 +6624,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6628,7 +6649,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B16" s="31">
         <v>1001583</v>
@@ -6648,7 +6669,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B17" s="31">
         <v>1330497</v>
@@ -6668,7 +6689,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B18" s="33">
         <v>-328914</v>
@@ -6688,7 +6709,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B19" s="30">
         <v>-0.32839365419634886</v>
@@ -6708,7 +6729,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B20" s="54">
         <v>-6.05</v>
@@ -6728,7 +6749,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B21" s="36">
         <v>170</v>
@@ -6748,7 +6769,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6758,7 +6779,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,7 +6804,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B26" s="31">
         <v>1084067</v>
@@ -6803,7 +6824,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B27" s="31">
         <v>1330497</v>
@@ -6823,7 +6844,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B28" s="33">
         <v>-246430</v>
@@ -6843,7 +6864,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B29" s="30">
         <v>-0.2273202239857572</v>
@@ -6863,7 +6884,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B30" s="54">
         <v>-4.28</v>
@@ -6883,7 +6904,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B31" s="36">
         <v>171</v>
@@ -6929,7 +6950,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6963,7 +6984,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6987,7 +7008,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6995,7 +7016,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -7033,7 +7054,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="D13" s="31">
         <v>1178333</v>
@@ -7053,7 +7074,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D14" s="31">
         <v>1330497</v>
@@ -7073,7 +7094,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D15" s="31">
         <v>-212164</v>
@@ -7093,7 +7114,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="D16" s="31">
         <v>74498</v>
@@ -7113,7 +7134,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D17" s="31">
         <v>323655</v>
@@ -7133,7 +7154,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7171,7 +7192,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D21" s="30">
         <v>-0.18005398371894768</v>
@@ -7191,7 +7212,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D22" s="54">
         <v>-2.26</v>
@@ -7231,7 +7252,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="D24" s="36">
         <v>120</v>
@@ -7251,7 +7272,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7292,7 +7313,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7303,7 +7324,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="56" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="56"/>
@@ -7314,41 +7335,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="57" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C6" s="60" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="D6" s="60" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="E6" s="60" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="F6" s="60" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="G6" s="60" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="H6" s="60" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C7" s="61">
         <v>120</v>
@@ -7368,7 +7389,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C8" s="62">
         <v>1178333.3333333335</v>
@@ -7388,7 +7409,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C9" s="62">
         <v>780535</v>
@@ -7408,7 +7429,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C10" s="62">
         <v>503333.3333333334</v>
@@ -7428,7 +7449,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C11" s="62">
         <v>46628.6108154935</v>
@@ -7448,7 +7469,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C12" s="63">
         <v>-212163.6108154934</v>
@@ -7468,7 +7489,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C13" s="64">
         <v>74498</v>
@@ -7488,7 +7509,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="C14" s="65">
         <v>-0.18005398371894768</v>
@@ -7526,12 +7547,12 @@
         <v>11392.722905999999</v>
       </c>
       <c r="H15" s="69" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C16" s="65">
         <v>0.6624059405940593</v>
@@ -7549,12 +7570,12 @@
         <v>0.18506529677129674</v>
       </c>
       <c r="H16" s="69" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C17" s="65">
         <v>0.27326732673267323</v>
@@ -7572,12 +7593,12 @@
         <v>0.06362198744062038</v>
       </c>
       <c r="H17" s="69" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C18" s="65">
         <v>-0.08956294200848645</v>
@@ -7595,12 +7616,12 @@
         <v>0.5566926610396014</v>
       </c>
       <c r="H18" s="69" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C19" s="70">
         <v>3</v>
@@ -7618,12 +7639,12 @@
         <v>3</v>
       </c>
       <c r="H19" s="69" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C20" s="71">
         <v>-2.2633099754482346</v>
@@ -7641,12 +7662,12 @@
         <v>68.00808688171976</v>
       </c>
       <c r="H20" s="69" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C21" s="73" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
@@ -7669,12 +7690,12 @@
         <v>0</v>
       </c>
       <c r="H21" s="69" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C22" s="74">
         <v>1</v>
@@ -7692,151 +7713,151 @@
         <v>33</v>
       </c>
       <c r="H22" s="69" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="43" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D25" s="76" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E25" s="76"/>
       <c r="F25" s="77" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G25" s="77"/>
       <c r="H25" s="77"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="43" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C26" s="78" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D26" s="76" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="E26" s="76"/>
       <c r="F26" s="77" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="G26" s="77"/>
       <c r="H26" s="77"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="C27" s="42" t="s">
         <v>437</v>
       </c>
-      <c r="C27" s="42" t="s">
-        <v>430</v>
-      </c>
       <c r="D27" s="76" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E27" s="76"/>
       <c r="F27" s="77" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="43" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D28" s="76" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E28" s="76"/>
       <c r="F28" s="77" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="G28" s="77"/>
       <c r="H28" s="77"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="43" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D29" s="76" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="E29" s="76"/>
       <c r="F29" s="77" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G29" s="77"/>
       <c r="H29" s="77"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="43" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D30" s="76" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E30" s="76"/>
       <c r="F30" s="77" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="G30" s="77"/>
       <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="43" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="D31" s="76" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="E31" s="76"/>
       <c r="F31" s="77" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="43" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -7844,7 +7865,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="79" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C35" s="79"/>
       <c r="D35" s="79"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="463">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1328,6 +1328,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -7301,7 +7304,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7716,170 +7719,191 @@
         <v>431</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C23" s="74">
+        <v>20</v>
+      </c>
+      <c r="D23" s="70">
+        <v>108</v>
+      </c>
+      <c r="E23" s="70">
+        <v>330</v>
+      </c>
+      <c r="F23" s="70">
+        <v>641</v>
+      </c>
+      <c r="G23" s="70">
+        <v>1015</v>
+      </c>
+      <c r="H23" s="69" t="s">
         <v>432</v>
       </c>
-      <c r="C24" s="19" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="C25" s="19" t="s">
         <v>434</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>435</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="43" t="s">
+      <c r="E25" s="19"/>
+      <c r="F25" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="C25" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="D25" s="76" t="s">
-        <v>438</v>
-      </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77" t="s">
-        <v>439</v>
-      </c>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="43" t="s">
-        <v>440</v>
-      </c>
-      <c r="C26" s="78" t="s">
-        <v>441</v>
+        <v>437</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>438</v>
       </c>
       <c r="D26" s="76" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E26" s="76"/>
       <c r="F26" s="77" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G26" s="77"/>
       <c r="H26" s="77"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="43" t="s">
-        <v>444</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>437</v>
+        <v>441</v>
+      </c>
+      <c r="C27" s="78" t="s">
+        <v>442</v>
       </c>
       <c r="D27" s="76" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E27" s="76"/>
       <c r="F27" s="77" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G27" s="77"/>
       <c r="H27" s="77"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="43" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D28" s="76" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E28" s="76"/>
       <c r="F28" s="77" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G28" s="77"/>
       <c r="H28" s="77"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="43" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D29" s="76" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E29" s="76"/>
       <c r="F29" s="77" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G29" s="77"/>
       <c r="H29" s="77"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="43" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D30" s="76" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E30" s="76"/>
       <c r="F30" s="77" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G30" s="77"/>
       <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="43" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D31" s="76" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E31" s="76"/>
       <c r="F31" s="77" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="43" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="D32" s="76" t="s">
+        <v>458</v>
+      </c>
+      <c r="E32" s="76"/>
+      <c r="F32" s="77" t="s">
         <v>459</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="43" t="s">
         <v>460</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="79" t="s">
+      <c r="C34" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="79" t="s">
+        <v>462</v>
+      </c>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -7894,8 +7918,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="467">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1292,6 +1292,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1664,7 +1676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1771,6 +1783,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7304,7 +7325,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7553,365 +7574,440 @@
         <v>419</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" s="70">
+        <v>11087.474534573557</v>
+      </c>
+      <c r="D16" s="70">
+        <v>8929.649354077466</v>
+      </c>
+      <c r="E16" s="70">
+        <v>6781.251362051644</v>
+      </c>
+      <c r="F16" s="70">
+        <v>5740.405768873734</v>
+      </c>
+      <c r="G16" s="70">
+        <v>5143.734896603028</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="C16" s="65">
-        <v>0.6624059405940593</v>
-      </c>
-      <c r="D16" s="66">
-        <v>0.4265746639547223</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0.29503973402336425</v>
-      </c>
-      <c r="F16" s="66">
-        <v>0.22731523300861284</v>
-      </c>
-      <c r="G16" s="66">
-        <v>0.18506529677129674</v>
-      </c>
-      <c r="H16" s="69" t="s">
+      <c r="C17" s="62">
+        <v>650</v>
+      </c>
+      <c r="D17" s="62">
+        <v>669.5</v>
+      </c>
+      <c r="E17" s="62">
+        <v>689.5849999999999</v>
+      </c>
+      <c r="F17" s="62">
+        <v>710.27255</v>
+      </c>
+      <c r="G17" s="62">
+        <v>731.5807265000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="67">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="68">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="68">
+        <v>1138.6993333333332</v>
+      </c>
+      <c r="F18" s="68">
+        <v>879.645235</v>
+      </c>
+      <c r="G18" s="68">
+        <v>724.8276736400001</v>
+      </c>
+      <c r="H18" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="C17" s="65">
-        <v>0.27326732673267323</v>
-      </c>
-      <c r="D17" s="66">
-        <v>0.14664839051998585</v>
-      </c>
-      <c r="E17" s="66">
-        <v>0.1014291419299191</v>
-      </c>
-      <c r="F17" s="66">
-        <v>0.07814672524697092</v>
-      </c>
-      <c r="G17" s="66">
-        <v>0.06362198744062038</v>
-      </c>
-      <c r="H17" s="69" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="C18" s="65">
-        <v>-0.08956294200848645</v>
-      </c>
-      <c r="D18" s="66">
-        <v>0.23094213830916166</v>
-      </c>
-      <c r="E18" s="66">
-        <v>0.40980776290727494</v>
-      </c>
-      <c r="F18" s="66">
-        <v>0.5003846870935568</v>
-      </c>
-      <c r="G18" s="66">
-        <v>0.5566926610396014</v>
-      </c>
-      <c r="H18" s="69" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C19" s="70">
-        <v>3</v>
-      </c>
-      <c r="D19" s="70">
-        <v>3</v>
-      </c>
-      <c r="E19" s="70">
-        <v>3</v>
-      </c>
-      <c r="F19" s="70">
-        <v>3</v>
-      </c>
-      <c r="G19" s="70">
-        <v>3</v>
-      </c>
-      <c r="H19" s="69" t="s">
-        <v>427</v>
+      <c r="C19" s="71">
+        <v>-1768.0300901291116</v>
+      </c>
+      <c r="D19" s="72">
+        <v>2278.350645922532</v>
+      </c>
+      <c r="E19" s="72">
+        <v>4361.965304615022</v>
+      </c>
+      <c r="F19" s="72">
+        <v>5490.923043626268</v>
+      </c>
+      <c r="G19" s="72">
+        <v>6228.988009396972</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C20" s="71">
-        <v>-2.2633099754482346</v>
-      </c>
-      <c r="D20" s="72">
-        <v>11.201250281006729</v>
-      </c>
-      <c r="E20" s="72">
-        <v>29.600242813611526</v>
-      </c>
-      <c r="F20" s="72">
-        <v>48.31792731679209</v>
-      </c>
-      <c r="G20" s="72">
-        <v>68.00808688171976</v>
+        <v>424</v>
+      </c>
+      <c r="C20" s="65">
+        <v>0.6624059405940593</v>
+      </c>
+      <c r="D20" s="66">
+        <v>0.4265746639547223</v>
+      </c>
+      <c r="E20" s="66">
+        <v>0.29503973402336425</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0.22731523300861284</v>
+      </c>
+      <c r="G20" s="66">
+        <v>0.18506529677129674</v>
       </c>
       <c r="H20" s="69" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C21" s="65">
+        <v>0.27326732673267323</v>
+      </c>
+      <c r="D21" s="66">
+        <v>0.14664839051998585</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.1014291419299191</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0.07814672524697092</v>
+      </c>
+      <c r="G21" s="66">
+        <v>0.06362198744062038</v>
+      </c>
+      <c r="H21" s="69" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C22" s="65">
+        <v>-0.08956294200848645</v>
+      </c>
+      <c r="D22" s="66">
+        <v>0.23094213830916166</v>
+      </c>
+      <c r="E22" s="66">
+        <v>0.40980776290727494</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0.5003846870935568</v>
+      </c>
+      <c r="G22" s="66">
+        <v>0.5566926610396014</v>
+      </c>
+      <c r="H22" s="69" t="s">
         <v>429</v>
       </c>
-      <c r="C21" s="73" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C23" s="73">
+        <v>3</v>
+      </c>
+      <c r="D23" s="73">
+        <v>3</v>
+      </c>
+      <c r="E23" s="73">
+        <v>3</v>
+      </c>
+      <c r="F23" s="73">
+        <v>3</v>
+      </c>
+      <c r="G23" s="73">
+        <v>3</v>
+      </c>
+      <c r="H23" s="69" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="74">
+        <v>-2.2633099754482346</v>
+      </c>
+      <c r="D24" s="75">
+        <v>11.201250281006729</v>
+      </c>
+      <c r="E24" s="75">
+        <v>29.600242813611526</v>
+      </c>
+      <c r="F24" s="75">
+        <v>48.31792731679209</v>
+      </c>
+      <c r="G24" s="75">
+        <v>68.00808688171976</v>
+      </c>
+      <c r="H24" s="69" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C25" s="76" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="42" t="str">
+      <c r="D25" s="42" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="73" t="str">
+      <c r="E25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="73" t="str">
+      <c r="F25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="73" t="str">
+      <c r="G25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="69" t="s">
+      <c r="H25" s="69" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="C22" s="74">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="C26" s="77">
         <v>1</v>
       </c>
-      <c r="D22" s="74">
+      <c r="D26" s="77">
         <v>4</v>
       </c>
-      <c r="E22" s="74">
+      <c r="E26" s="77">
         <v>11</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F26" s="78">
         <v>21</v>
       </c>
-      <c r="G22" s="70">
+      <c r="G26" s="73">
         <v>33</v>
       </c>
-      <c r="H22" s="69" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="H26" s="69" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="C23" s="74">
+      <c r="C27" s="77">
         <v>20</v>
       </c>
-      <c r="D23" s="70">
+      <c r="D27" s="73">
         <v>108</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E27" s="73">
         <v>330</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F27" s="73">
         <v>641</v>
       </c>
-      <c r="G23" s="70">
+      <c r="G27" s="73">
         <v>1015</v>
       </c>
-      <c r="H23" s="69" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19" t="s">
+      <c r="H27" s="69" t="s">
         <v>436</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="43" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C29" s="19" t="s">
         <v>438</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D29" s="19" t="s">
         <v>439</v>
       </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="43" t="s">
-        <v>441</v>
-      </c>
-      <c r="C27" s="78" t="s">
-        <v>442</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>443</v>
-      </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77" t="s">
-        <v>444</v>
-      </c>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="43" t="s">
-        <v>445</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="D28" s="76" t="s">
-        <v>446</v>
-      </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="77" t="s">
-        <v>447</v>
-      </c>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="43" t="s">
-        <v>448</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="D29" s="76" t="s">
-        <v>449</v>
-      </c>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77" t="s">
-        <v>450</v>
-      </c>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="43" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>452</v>
-      </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77" t="s">
-        <v>453</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+        <v>442</v>
+      </c>
+      <c r="D30" s="79" t="s">
+        <v>443</v>
+      </c>
+      <c r="E30" s="79"/>
+      <c r="F30" s="80" t="s">
+        <v>444</v>
+      </c>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="43" t="s">
-        <v>454</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>455</v>
-      </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77" t="s">
-        <v>456</v>
-      </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
+        <v>445</v>
+      </c>
+      <c r="C31" s="81" t="s">
+        <v>446</v>
+      </c>
+      <c r="D31" s="79" t="s">
+        <v>447</v>
+      </c>
+      <c r="E31" s="79"/>
+      <c r="F31" s="80" t="s">
+        <v>448</v>
+      </c>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="43" t="s">
+        <v>449</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D32" s="79" t="s">
+        <v>450</v>
+      </c>
+      <c r="E32" s="79"/>
+      <c r="F32" s="80" t="s">
+        <v>451</v>
+      </c>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="43" t="s">
+        <v>452</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D33" s="79" t="s">
+        <v>453</v>
+      </c>
+      <c r="E33" s="79"/>
+      <c r="F33" s="80" t="s">
+        <v>454</v>
+      </c>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="43" t="s">
+        <v>455</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D34" s="79" t="s">
+        <v>456</v>
+      </c>
+      <c r="E34" s="79"/>
+      <c r="F34" s="80" t="s">
         <v>457</v>
       </c>
-      <c r="C32" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="D32" s="76" t="s">
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="E32" s="76"/>
-      <c r="F32" s="77" t="s">
+      <c r="C35" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D35" s="79" t="s">
         <v>459</v>
       </c>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="43" t="s">
+      <c r="E35" s="79"/>
+      <c r="F35" s="80" t="s">
         <v>460</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="43" t="s">
         <v>461</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="79" t="s">
+      <c r="C36" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D36" s="79" t="s">
         <v>462</v>
       </c>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
       <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
+      <c r="F36" s="80" t="s">
+        <v>463</v>
+      </c>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="43" t="s">
+        <v>464</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="82" t="s">
+        <v>466</v>
+      </c>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -7920,8 +8016,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7967,48 +8071,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="462">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1294,18 +1294,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1340,9 +1328,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1676,7 +1661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1783,15 +1768,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7325,7 +7301,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7574,458 +7550,352 @@
         <v>419</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C16" s="70">
-        <v>11087.474534573557</v>
-      </c>
-      <c r="D16" s="70">
-        <v>8929.649354077466</v>
-      </c>
-      <c r="E16" s="70">
-        <v>6781.251362051644</v>
-      </c>
-      <c r="F16" s="70">
-        <v>5740.405768873734</v>
-      </c>
-      <c r="G16" s="70">
-        <v>5143.734896603028</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="C17" s="62">
-        <v>650</v>
-      </c>
-      <c r="D17" s="62">
-        <v>669.5</v>
-      </c>
-      <c r="E17" s="62">
-        <v>689.5849999999999</v>
-      </c>
-      <c r="F17" s="62">
-        <v>710.27255</v>
-      </c>
-      <c r="G17" s="62">
-        <v>731.5807265000001</v>
+      <c r="C16" s="65">
+        <v>0.6624059405940593</v>
+      </c>
+      <c r="D16" s="66">
+        <v>0.4265746639547223</v>
+      </c>
+      <c r="E16" s="66">
+        <v>0.29503973402336425</v>
+      </c>
+      <c r="F16" s="66">
+        <v>0.22731523300861284</v>
+      </c>
+      <c r="G16" s="66">
+        <v>0.18506529677129674</v>
+      </c>
+      <c r="H16" s="69" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="C17" s="65">
+        <v>0.27326732673267323</v>
+      </c>
+      <c r="D17" s="66">
+        <v>0.14664839051998585</v>
+      </c>
+      <c r="E17" s="66">
+        <v>0.1014291419299191</v>
+      </c>
+      <c r="F17" s="66">
+        <v>0.07814672524697092</v>
+      </c>
+      <c r="G17" s="66">
+        <v>0.06362198744062038</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="C18" s="67">
-        <v>2683.3333333333335</v>
-      </c>
-      <c r="D18" s="68">
-        <v>1658.3</v>
-      </c>
-      <c r="E18" s="68">
-        <v>1138.6993333333332</v>
-      </c>
-      <c r="F18" s="68">
-        <v>879.645235</v>
-      </c>
-      <c r="G18" s="68">
-        <v>724.8276736400001</v>
+      <c r="B18" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C18" s="65">
+        <v>-0.08956294200848645</v>
+      </c>
+      <c r="D18" s="66">
+        <v>0.23094213830916166</v>
+      </c>
+      <c r="E18" s="66">
+        <v>0.40980776290727494</v>
+      </c>
+      <c r="F18" s="66">
+        <v>0.5003846870935568</v>
+      </c>
+      <c r="G18" s="66">
+        <v>0.5566926610396014</v>
       </c>
       <c r="H18" s="69" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" s="71">
-        <v>-1768.0300901291116</v>
-      </c>
-      <c r="D19" s="72">
-        <v>2278.350645922532</v>
-      </c>
-      <c r="E19" s="72">
-        <v>4361.965304615022</v>
-      </c>
-      <c r="F19" s="72">
-        <v>5490.923043626268</v>
-      </c>
-      <c r="G19" s="72">
-        <v>6228.988009396972</v>
+        <v>426</v>
+      </c>
+      <c r="C19" s="70">
+        <v>3</v>
+      </c>
+      <c r="D19" s="70">
+        <v>3</v>
+      </c>
+      <c r="E19" s="70">
+        <v>3</v>
+      </c>
+      <c r="F19" s="70">
+        <v>3</v>
+      </c>
+      <c r="G19" s="70">
+        <v>3</v>
+      </c>
+      <c r="H19" s="69" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="C20" s="65">
-        <v>0.6624059405940593</v>
-      </c>
-      <c r="D20" s="66">
-        <v>0.4265746639547223</v>
-      </c>
-      <c r="E20" s="66">
-        <v>0.29503973402336425</v>
-      </c>
-      <c r="F20" s="66">
-        <v>0.22731523300861284</v>
-      </c>
-      <c r="G20" s="66">
-        <v>0.18506529677129674</v>
+        <v>363</v>
+      </c>
+      <c r="C20" s="71">
+        <v>-2.2633099754482346</v>
+      </c>
+      <c r="D20" s="72">
+        <v>11.201250281006729</v>
+      </c>
+      <c r="E20" s="72">
+        <v>29.600242813611526</v>
+      </c>
+      <c r="F20" s="72">
+        <v>48.31792731679209</v>
+      </c>
+      <c r="G20" s="72">
+        <v>68.00808688171976</v>
       </c>
       <c r="H20" s="69" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C21" s="65">
-        <v>0.27326732673267323</v>
-      </c>
-      <c r="D21" s="66">
-        <v>0.14664839051998585</v>
-      </c>
-      <c r="E21" s="66">
-        <v>0.1014291419299191</v>
-      </c>
-      <c r="F21" s="66">
-        <v>0.07814672524697092</v>
-      </c>
-      <c r="G21" s="66">
-        <v>0.06362198744062038</v>
+        <v>429</v>
+      </c>
+      <c r="C21" s="73" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="42" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="E21" s="73" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="73" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="73" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="69" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="C22" s="65">
-        <v>-0.08956294200848645</v>
-      </c>
-      <c r="D22" s="66">
-        <v>0.23094213830916166</v>
-      </c>
-      <c r="E22" s="66">
-        <v>0.40980776290727494</v>
-      </c>
-      <c r="F22" s="66">
-        <v>0.5003846870935568</v>
-      </c>
-      <c r="G22" s="66">
-        <v>0.5566926610396014</v>
+        <v>430</v>
+      </c>
+      <c r="C22" s="74">
+        <v>1</v>
+      </c>
+      <c r="D22" s="74">
+        <v>4</v>
+      </c>
+      <c r="E22" s="74">
+        <v>11</v>
+      </c>
+      <c r="F22" s="75">
+        <v>21</v>
+      </c>
+      <c r="G22" s="70">
+        <v>33</v>
       </c>
       <c r="H22" s="69" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="C23" s="73">
-        <v>3</v>
-      </c>
-      <c r="D23" s="73">
-        <v>3</v>
-      </c>
-      <c r="E23" s="73">
-        <v>3</v>
-      </c>
-      <c r="F23" s="73">
-        <v>3</v>
-      </c>
-      <c r="G23" s="73">
-        <v>3</v>
-      </c>
-      <c r="H23" s="69" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C24" s="74">
-        <v>-2.2633099754482346</v>
-      </c>
-      <c r="D24" s="75">
-        <v>11.201250281006729</v>
-      </c>
-      <c r="E24" s="75">
-        <v>29.600242813611526</v>
-      </c>
-      <c r="F24" s="75">
-        <v>48.31792731679209</v>
-      </c>
-      <c r="G24" s="75">
-        <v>68.00808688171976</v>
-      </c>
-      <c r="H24" s="69" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
+      <c r="C24" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="C25" s="76" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="42" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="E25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="69" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
+      <c r="D24" s="19" t="s">
         <v>434</v>
       </c>
-      <c r="C26" s="77">
-        <v>1</v>
-      </c>
-      <c r="D26" s="77">
-        <v>4</v>
-      </c>
-      <c r="E26" s="77">
-        <v>11</v>
-      </c>
-      <c r="F26" s="78">
-        <v>21</v>
-      </c>
-      <c r="G26" s="73">
-        <v>33</v>
-      </c>
-      <c r="H26" s="69" t="s">
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="C27" s="77">
-        <v>20</v>
-      </c>
-      <c r="D27" s="73">
-        <v>108</v>
-      </c>
-      <c r="E27" s="73">
-        <v>330</v>
-      </c>
-      <c r="F27" s="73">
-        <v>641</v>
-      </c>
-      <c r="G27" s="73">
-        <v>1015</v>
-      </c>
-      <c r="H27" s="69" t="s">
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="43" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
+      <c r="C25" s="42" t="s">
         <v>437</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="D25" s="76" t="s">
         <v>438</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="E25" s="76"/>
+      <c r="F25" s="77" t="s">
         <v>439</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="43" t="s">
         <v>440</v>
       </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
+      <c r="C26" s="78" t="s">
+        <v>441</v>
+      </c>
+      <c r="D26" s="76" t="s">
+        <v>442</v>
+      </c>
+      <c r="E26" s="76"/>
+      <c r="F26" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D27" s="76" t="s">
+        <v>445</v>
+      </c>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77" t="s">
+        <v>446</v>
+      </c>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="43" t="s">
+        <v>447</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D28" s="76" t="s">
+        <v>448</v>
+      </c>
+      <c r="E28" s="76"/>
+      <c r="F28" s="77" t="s">
+        <v>449</v>
+      </c>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="43" t="s">
+        <v>450</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D29" s="76" t="s">
+        <v>451</v>
+      </c>
+      <c r="E29" s="76"/>
+      <c r="F29" s="77" t="s">
+        <v>452</v>
+      </c>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="43" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D30" s="79" t="s">
-        <v>443</v>
-      </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="80" t="s">
-        <v>444</v>
-      </c>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
+        <v>437</v>
+      </c>
+      <c r="D30" s="76" t="s">
+        <v>454</v>
+      </c>
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
+        <v>455</v>
+      </c>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="43" t="s">
-        <v>445</v>
-      </c>
-      <c r="C31" s="81" t="s">
-        <v>446</v>
-      </c>
-      <c r="D31" s="79" t="s">
-        <v>447</v>
-      </c>
-      <c r="E31" s="79"/>
-      <c r="F31" s="80" t="s">
-        <v>448</v>
-      </c>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="43" t="s">
-        <v>449</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D32" s="79" t="s">
-        <v>450</v>
-      </c>
-      <c r="E32" s="79"/>
-      <c r="F32" s="80" t="s">
-        <v>451</v>
-      </c>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D31" s="76" t="s">
+        <v>457</v>
+      </c>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
+        <v>458</v>
+      </c>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="43" t="s">
-        <v>452</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D33" s="79" t="s">
-        <v>453</v>
-      </c>
-      <c r="E33" s="79"/>
-      <c r="F33" s="80" t="s">
-        <v>454</v>
-      </c>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="43" t="s">
-        <v>455</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D34" s="79" t="s">
-        <v>456</v>
-      </c>
-      <c r="E34" s="79"/>
-      <c r="F34" s="80" t="s">
-        <v>457</v>
-      </c>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="43" t="s">
-        <v>458</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D35" s="79" t="s">
         <v>459</v>
       </c>
+      <c r="C33" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="79" t="s">
+        <v>461</v>
+      </c>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
       <c r="E35" s="79"/>
-      <c r="F35" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="43" t="s">
-        <v>461</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D36" s="79" t="s">
-        <v>462</v>
-      </c>
-      <c r="E36" s="79"/>
-      <c r="F36" s="80" t="s">
-        <v>463</v>
-      </c>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="43" t="s">
-        <v>464</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="82" t="s">
-        <v>466</v>
-      </c>
-      <c r="C40" s="82"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="82"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8071,48 +7941,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="467">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1294,6 +1294,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1328,6 +1340,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1661,7 +1676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1768,6 +1783,15 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7301,7 +7325,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7550,352 +7574,458 @@
         <v>419</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" s="70">
+        <v>11087.474534573557</v>
+      </c>
+      <c r="D16" s="70">
+        <v>8929.649354077466</v>
+      </c>
+      <c r="E16" s="70">
+        <v>6781.251362051644</v>
+      </c>
+      <c r="F16" s="70">
+        <v>5740.405768873734</v>
+      </c>
+      <c r="G16" s="70">
+        <v>5143.734896603028</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="C16" s="65">
-        <v>0.6624059405940593</v>
-      </c>
-      <c r="D16" s="66">
-        <v>0.4265746639547223</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0.29503973402336425</v>
-      </c>
-      <c r="F16" s="66">
-        <v>0.22731523300861284</v>
-      </c>
-      <c r="G16" s="66">
-        <v>0.18506529677129674</v>
-      </c>
-      <c r="H16" s="69" t="s">
+      <c r="C17" s="62">
+        <v>650</v>
+      </c>
+      <c r="D17" s="62">
+        <v>669.5</v>
+      </c>
+      <c r="E17" s="62">
+        <v>689.5849999999999</v>
+      </c>
+      <c r="F17" s="62">
+        <v>710.27255</v>
+      </c>
+      <c r="G17" s="62">
+        <v>731.5807265000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="67">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="68">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="68">
+        <v>1138.6993333333332</v>
+      </c>
+      <c r="F18" s="68">
+        <v>879.645235</v>
+      </c>
+      <c r="G18" s="68">
+        <v>724.8276736400001</v>
+      </c>
+      <c r="H18" s="69" t="s">
         <v>422</v>
       </c>
-      <c r="C17" s="65">
-        <v>0.27326732673267323</v>
-      </c>
-      <c r="D17" s="66">
-        <v>0.14664839051998585</v>
-      </c>
-      <c r="E17" s="66">
-        <v>0.1014291419299191</v>
-      </c>
-      <c r="F17" s="66">
-        <v>0.07814672524697092</v>
-      </c>
-      <c r="G17" s="66">
-        <v>0.06362198744062038</v>
-      </c>
-      <c r="H17" s="69" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="C18" s="65">
-        <v>-0.08956294200848645</v>
-      </c>
-      <c r="D18" s="66">
-        <v>0.23094213830916166</v>
-      </c>
-      <c r="E18" s="66">
-        <v>0.40980776290727494</v>
-      </c>
-      <c r="F18" s="66">
-        <v>0.5003846870935568</v>
-      </c>
-      <c r="G18" s="66">
-        <v>0.5566926610396014</v>
-      </c>
-      <c r="H18" s="69" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C19" s="70">
-        <v>3</v>
-      </c>
-      <c r="D19" s="70">
-        <v>3</v>
-      </c>
-      <c r="E19" s="70">
-        <v>3</v>
-      </c>
-      <c r="F19" s="70">
-        <v>3</v>
-      </c>
-      <c r="G19" s="70">
-        <v>3</v>
-      </c>
-      <c r="H19" s="69" t="s">
-        <v>427</v>
+      <c r="C19" s="71">
+        <v>-1768.0300901291116</v>
+      </c>
+      <c r="D19" s="72">
+        <v>2278.350645922532</v>
+      </c>
+      <c r="E19" s="72">
+        <v>4361.965304615022</v>
+      </c>
+      <c r="F19" s="72">
+        <v>5490.923043626268</v>
+      </c>
+      <c r="G19" s="72">
+        <v>6228.988009396972</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C20" s="71">
-        <v>-2.2633099754482346</v>
-      </c>
-      <c r="D20" s="72">
-        <v>11.201250281006729</v>
-      </c>
-      <c r="E20" s="72">
-        <v>29.600242813611526</v>
-      </c>
-      <c r="F20" s="72">
-        <v>48.31792731679209</v>
-      </c>
-      <c r="G20" s="72">
-        <v>68.00808688171976</v>
+        <v>424</v>
+      </c>
+      <c r="C20" s="65">
+        <v>0.6624059405940593</v>
+      </c>
+      <c r="D20" s="66">
+        <v>0.4265746639547223</v>
+      </c>
+      <c r="E20" s="66">
+        <v>0.29503973402336425</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0.22731523300861284</v>
+      </c>
+      <c r="G20" s="66">
+        <v>0.18506529677129674</v>
       </c>
       <c r="H20" s="69" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C21" s="65">
+        <v>0.27326732673267323</v>
+      </c>
+      <c r="D21" s="66">
+        <v>0.14664839051998585</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.1014291419299191</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0.07814672524697092</v>
+      </c>
+      <c r="G21" s="66">
+        <v>0.06362198744062038</v>
+      </c>
+      <c r="H21" s="69" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C22" s="65">
+        <v>-0.08956294200848645</v>
+      </c>
+      <c r="D22" s="66">
+        <v>0.23094213830916166</v>
+      </c>
+      <c r="E22" s="66">
+        <v>0.40980776290727494</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0.5003846870935568</v>
+      </c>
+      <c r="G22" s="66">
+        <v>0.5566926610396014</v>
+      </c>
+      <c r="H22" s="69" t="s">
         <v>429</v>
       </c>
-      <c r="C21" s="73" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C23" s="73">
+        <v>3</v>
+      </c>
+      <c r="D23" s="73">
+        <v>3</v>
+      </c>
+      <c r="E23" s="73">
+        <v>3</v>
+      </c>
+      <c r="F23" s="73">
+        <v>3</v>
+      </c>
+      <c r="G23" s="73">
+        <v>3</v>
+      </c>
+      <c r="H23" s="69" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="74">
+        <v>-2.2633099754482346</v>
+      </c>
+      <c r="D24" s="75">
+        <v>11.201250281006729</v>
+      </c>
+      <c r="E24" s="75">
+        <v>29.600242813611526</v>
+      </c>
+      <c r="F24" s="75">
+        <v>48.31792731679209</v>
+      </c>
+      <c r="G24" s="75">
+        <v>68.00808688171976</v>
+      </c>
+      <c r="H24" s="69" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C25" s="76" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="42" t="str">
+      <c r="D25" s="42" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E21" s="73" t="str">
+      <c r="E25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="73" t="str">
+      <c r="F25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="73" t="str">
+      <c r="G25" s="76" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="69" t="s">
+      <c r="H25" s="69" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="C22" s="74">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="C26" s="77">
         <v>1</v>
       </c>
-      <c r="D22" s="74">
+      <c r="D26" s="77">
         <v>4</v>
       </c>
-      <c r="E22" s="74">
+      <c r="E26" s="77">
         <v>11</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F26" s="78">
         <v>21</v>
       </c>
-      <c r="G22" s="70">
+      <c r="G26" s="73">
         <v>33</v>
       </c>
-      <c r="H22" s="69" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
-        <v>432</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="H26" s="69" t="s">
         <v>435</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="43" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C27" s="77">
+        <v>20</v>
+      </c>
+      <c r="D27" s="73">
+        <v>108</v>
+      </c>
+      <c r="E27" s="73">
+        <v>330</v>
+      </c>
+      <c r="F27" s="73">
+        <v>641</v>
+      </c>
+      <c r="G27" s="73">
+        <v>1015</v>
+      </c>
+      <c r="H27" s="69" t="s">
         <v>436</v>
       </c>
-      <c r="C25" s="42" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="D25" s="76" t="s">
+      <c r="C29" s="19" t="s">
         <v>438</v>
       </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77" t="s">
+      <c r="D29" s="19" t="s">
         <v>439</v>
       </c>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="43" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="C26" s="78" t="s">
-        <v>441</v>
-      </c>
-      <c r="D26" s="76" t="s">
-        <v>442</v>
-      </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77" t="s">
-        <v>443</v>
-      </c>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="43" t="s">
-        <v>444</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>445</v>
-      </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77" t="s">
-        <v>446</v>
-      </c>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="43" t="s">
-        <v>447</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="D28" s="76" t="s">
-        <v>448</v>
-      </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="77" t="s">
-        <v>449</v>
-      </c>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="43" t="s">
-        <v>450</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="D29" s="76" t="s">
-        <v>451</v>
-      </c>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77" t="s">
-        <v>452</v>
-      </c>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="43" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>454</v>
-      </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77" t="s">
-        <v>455</v>
-      </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+        <v>442</v>
+      </c>
+      <c r="D30" s="79" t="s">
+        <v>443</v>
+      </c>
+      <c r="E30" s="79"/>
+      <c r="F30" s="80" t="s">
+        <v>444</v>
+      </c>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="C31" s="81" t="s">
+        <v>446</v>
+      </c>
+      <c r="D31" s="79" t="s">
+        <v>447</v>
+      </c>
+      <c r="E31" s="79"/>
+      <c r="F31" s="80" t="s">
+        <v>448</v>
+      </c>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="43" t="s">
+        <v>449</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D32" s="79" t="s">
+        <v>450</v>
+      </c>
+      <c r="E32" s="79"/>
+      <c r="F32" s="80" t="s">
+        <v>451</v>
+      </c>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="43" t="s">
+        <v>452</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D33" s="79" t="s">
+        <v>453</v>
+      </c>
+      <c r="E33" s="79"/>
+      <c r="F33" s="80" t="s">
+        <v>454</v>
+      </c>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="43" t="s">
+        <v>455</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D34" s="79" t="s">
         <v>456</v>
       </c>
-      <c r="C31" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="D31" s="76" t="s">
+      <c r="E34" s="79"/>
+      <c r="F34" s="80" t="s">
         <v>457</v>
       </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77" t="s">
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="43" t="s">
+      <c r="C35" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D35" s="79" t="s">
         <v>459</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="E35" s="79"/>
+      <c r="F35" s="80" t="s">
         <v>460</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="79" t="s">
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="43" t="s">
         <v>461</v>
       </c>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
+      <c r="C36" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="D36" s="79" t="s">
+        <v>462</v>
+      </c>
+      <c r="E36" s="79"/>
+      <c r="F36" s="80" t="s">
+        <v>463</v>
+      </c>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="43" t="s">
+        <v>464</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="82" t="s">
+        <v>466</v>
+      </c>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7941,48 +8071,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -26,13 +26,15 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="505">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -40,7 +42,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +162,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -310,6 +312,12 @@
     <t>Financial Health</t>
   </si>
   <si>
+    <t>23.</t>
+  </si>
+  <si>
+    <t>Budget Narrative</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -376,6 +384,9 @@
     <t>Escalation %</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
     <t>State Per-Pupil Funding</t>
   </si>
   <si>
@@ -385,6 +396,9 @@
     <t>Per Student</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
     <t>Federal Title I</t>
   </si>
   <si>
@@ -562,6 +576,48 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>Enrollment Growth Rate</t>
+  </si>
+  <si>
+    <t>Rent Escalation Rate</t>
+  </si>
+  <si>
+    <t>Tuition Escalation Rate</t>
+  </si>
+  <si>
+    <t>Default Benefits Rate</t>
+  </si>
+  <si>
+    <t>Default Payroll Tax Rate</t>
+  </si>
+  <si>
+    <t>Student Retention Rate</t>
+  </si>
+  <si>
+    <t>REVENUE COLLECTION DEFAULTS</t>
+  </si>
+  <si>
+    <t>Default Billing Months</t>
+  </si>
+  <si>
+    <t>10 months (Aug-May)</t>
+  </si>
+  <si>
+    <t>Default Collection Method</t>
+  </si>
+  <si>
+    <t>Autopay</t>
+  </si>
+  <si>
+    <t>Default Collection Rate</t>
+  </si>
+  <si>
+    <t>Default Collection Delay</t>
+  </si>
+  <si>
+    <t>0 days</t>
+  </si>
+  <si>
     <t>CHARTER FUNDING DETAILS</t>
   </si>
   <si>
@@ -667,9 +723,6 @@
     <t>Capacity Utilization</t>
   </si>
   <si>
-    <t>Enrollment Growth Rate</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -703,6 +756,9 @@
     <t>Loaded Cost</t>
   </si>
   <si>
+    <t>Rates</t>
+  </si>
+  <si>
     <t>5-YEAR TOTAL PERSONNEL COST</t>
   </si>
   <si>
@@ -1021,12 +1077,24 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
+    <t>Cash Trough: July (Month 1)</t>
+  </si>
+  <si>
+    <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
+  </si>
+  <si>
     <t>Heritage Academy Charter - 5-Year Operating Statement</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>Capital &amp; Debt Service</t>
   </si>
   <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
     <t>BOTTOM LINE</t>
   </si>
   <si>
@@ -1081,7 +1149,7 @@
     <t>Accounts Receivable</t>
   </si>
   <si>
-    <t>Fixed Assets</t>
+    <t>Fixed Assets (Net of Depreciation)</t>
   </si>
   <si>
     <t>Other Assets</t>
@@ -1120,7 +1188,16 @@
     <t>Revenue</t>
   </si>
   <si>
-    <t>CFADS (Rev - Pers - OpEx)</t>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Depreciation Add-Back</t>
+  </si>
+  <si>
+    <t>Debt Service (Loan)</t>
+  </si>
+  <si>
+    <t>CFADS (NI + Depr + DS)</t>
   </si>
   <si>
     <t>DSCR</t>
@@ -1165,6 +1242,9 @@
     <t>Positive Net Income</t>
   </si>
   <si>
+    <t>Current Ratio ≥ 1.1x</t>
+  </si>
+  <si>
     <t>Capacity ≥ 7000%</t>
   </si>
   <si>
@@ -1255,7 +1335,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1288,9 +1368,6 @@
     <t>Benchmark</t>
   </si>
   <si>
-    <t>Net Income</t>
-  </si>
-  <si>
     <t>≥ $10,000</t>
   </si>
   <si>
@@ -1375,7 +1452,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -1433,6 +1510,45 @@
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Enrollment Strategy</t>
+  </si>
+  <si>
+    <t>(Not provided)</t>
+  </si>
+  <si>
+    <t>Retention Plan</t>
+  </si>
+  <si>
+    <t>Risk Mitigation</t>
+  </si>
+  <si>
+    <t>Mission &amp; Vision</t>
+  </si>
+  <si>
+    <t>Revenue Assumptions</t>
+  </si>
+  <si>
+    <t>Staffing Philosophy</t>
+  </si>
+  <si>
+    <t>Expense Assumptions</t>
+  </si>
+  <si>
+    <t>Growth Strategy</t>
+  </si>
+  <si>
+    <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1562,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1537,6 +1653,18 @@
       <i/>
       <color rgb="FF808080"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1676,7 +1804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1725,25 +1853,27 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1751,10 +1881,10 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1782,7 +1912,7 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1813,14 +1943,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2539,7 +2678,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2552,24 +2691,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B4" s="37">
         <v>120</v>
@@ -2589,7 +2728,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2599,7 +2738,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="31">
         <v>969000</v>
@@ -2619,7 +2758,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B8" s="31">
         <v>90000</v>
@@ -2639,7 +2778,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" s="31">
         <v>132000</v>
@@ -2659,7 +2798,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B10" s="31">
         <v>150000</v>
@@ -2679,7 +2818,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B11" s="31">
         <v>25000</v>
@@ -2699,7 +2838,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B12" s="31">
         <v>48000</v>
@@ -2719,7 +2858,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B13" s="33">
         <f>SUM(B7:B12)</f>
@@ -2744,7 +2883,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B15" s="31">
         <v>11783</v>
@@ -2788,7 +2927,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2801,24 +2940,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2828,7 +2967,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B5" s="31">
         <v>278438</v>
@@ -2848,7 +2987,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B6" s="31">
         <v>59029</v>
@@ -2868,7 +3007,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B7" s="31">
         <v>87955</v>
@@ -2888,7 +3027,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
@@ -2913,7 +3052,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -2923,7 +3062,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B10" s="31">
         <v>116944</v>
@@ -2943,7 +3082,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B11" s="31">
         <v>91328</v>
@@ -2963,7 +3102,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
@@ -2988,7 +3127,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -2998,7 +3137,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B14" s="31">
         <v>69053</v>
@@ -3018,7 +3157,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="B15" s="32">
         <f>SUM(B14:B14)</f>
@@ -3043,7 +3182,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -3053,7 +3192,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B17" s="31">
         <v>77790</v>
@@ -3073,7 +3212,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B18" s="32">
         <f>SUM(B17:B17)</f>
@@ -3098,7 +3237,7 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B20" s="33">
         <f>B8+B12+B15+B18</f>
@@ -3147,7 +3286,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3160,24 +3299,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -3187,7 +3326,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B5" s="31">
         <v>807500</v>
@@ -3207,7 +3346,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="B6" s="31">
         <v>75000</v>
@@ -3227,7 +3366,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B7" s="31">
         <v>110000</v>
@@ -3247,7 +3386,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="B8" s="31">
         <v>125000</v>
@@ -3267,7 +3406,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B9" s="31">
         <v>20833</v>
@@ -3287,7 +3426,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B10" s="31">
         <v>40000</v>
@@ -3307,7 +3446,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B11" s="32">
         <f>SUM(B5:B10)</f>
@@ -3332,7 +3471,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -3342,7 +3481,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B14" s="31">
         <v>116944</v>
@@ -3362,7 +3501,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B15" s="31">
         <v>91328</v>
@@ -3382,7 +3521,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B16" s="31">
         <v>278438</v>
@@ -3402,7 +3541,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B17" s="31">
         <v>59029</v>
@@ -3422,7 +3561,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B18" s="31">
         <v>87955</v>
@@ -3442,7 +3581,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B19" s="31">
         <v>69053</v>
@@ -3462,7 +3601,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B20" s="31">
         <v>77790</v>
@@ -3482,7 +3621,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B21" s="32">
         <f>SUM(B14:B20)</f>
@@ -3507,7 +3646,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -3517,12 +3656,12 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B25" s="31">
         <v>65000</v>
@@ -3542,12 +3681,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B27" s="31">
         <v>45000</v>
@@ -3567,12 +3706,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B29" s="31">
         <v>220000</v>
@@ -3592,7 +3731,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="B30" s="31">
         <v>30000</v>
@@ -3612,7 +3751,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="B31" s="31">
         <v>18333</v>
@@ -3632,7 +3771,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B32" s="32">
         <f>SUM(B29:B31)</f>
@@ -3657,12 +3796,12 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="38" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B34" s="31">
         <v>25000</v>
@@ -3682,7 +3821,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B35" s="31">
         <v>10000</v>
@@ -3702,7 +3841,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B36" s="31">
         <v>15000</v>
@@ -3722,7 +3861,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B37" s="31">
         <v>75000</v>
@@ -3742,7 +3881,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B38" s="32">
         <f>SUM(B34:B37)</f>
@@ -3767,7 +3906,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B39" s="32">
         <f>B25+B27+B32+B38</f>
@@ -3792,7 +3931,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -3802,7 +3941,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="B42" s="31">
         <v>46629</v>
@@ -3822,7 +3961,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B43" s="31">
         <v>60000</v>
@@ -3842,7 +3981,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="B44" s="32">
         <f>SUM(B42:B43)</f>
@@ -3891,7 +4030,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3904,24 +4043,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B4" s="34">
         <f>'Budget Detail'!B11</f>
@@ -3946,7 +4085,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
@@ -3971,7 +4110,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
@@ -3996,7 +4135,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
@@ -4021,7 +4160,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
@@ -4046,7 +4185,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -4056,7 +4195,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B11" s="33">
         <f>B4-B8</f>
@@ -4081,7 +4220,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -4106,7 +4245,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B13" s="31">
         <v>-212164</v>
@@ -4126,7 +4265,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B14" s="31">
         <v>9819</v>
@@ -4146,7 +4285,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B15" s="31">
         <v>11587</v>
@@ -4181,7 +4320,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4191,7 +4330,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4212,48 +4351,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -4271,7 +4410,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B4" s="32">
         <v>146500</v>
@@ -4316,7 +4455,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4334,7 +4473,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B7" s="31">
         <v>78054</v>
@@ -4379,7 +4518,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="B8" s="31">
         <v>50333</v>
@@ -4424,7 +4563,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B9" s="31">
         <v>8886</v>
@@ -4469,7 +4608,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4487,7 +4626,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -4544,7 +4683,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -4601,7 +4740,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="B14" s="39">
         <f>B17+B13</f>
@@ -4658,14 +4797,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B17" s="23">
         <v>0</v>
@@ -4673,7 +4812,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="B18" s="39">
         <f>M14</f>
@@ -4682,16 +4821,40 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
         <v>9227</v>
       </c>
     </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="40" t="s">
+        <v>348</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4706,7 +4869,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4715,7 +4878,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4723,29 +4886,39 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+    </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4754,8 +4927,8 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>272</v>
+      <c r="A5" s="42" t="s">
+        <v>290</v>
       </c>
       <c r="B5" s="32">
         <v>1178333</v>
@@ -4775,7 +4948,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4785,7 +4958,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B8" s="34">
         <v>780535</v>
@@ -4805,7 +4978,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="B9" s="34">
         <v>503333</v>
@@ -4825,7 +4998,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="B10" s="34">
         <v>106629</v>
@@ -4844,138 +5017,159 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
-        <v>299</v>
-      </c>
-      <c r="B11" s="32">
-        <f>SUM(B8:B10)</f>
+      <c r="A11" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B11" s="34">
+        <v>0</v>
+      </c>
+      <c r="C11" s="34">
+        <v>0</v>
+      </c>
+      <c r="D11" s="34">
+        <v>0</v>
+      </c>
+      <c r="E11" s="34">
+        <v>0</v>
+      </c>
+      <c r="F11" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="B12" s="32">
+        <f>SUM(B8:B11)</f>
         <v>1390497</v>
       </c>
-      <c r="C11" s="32">
-        <f>SUM(C8:C10)</f>
+      <c r="C12" s="32">
+        <f>SUM(C8:C11)</f>
         <v>1805930</v>
       </c>
-      <c r="D11" s="32">
-        <f>SUM(D8:D10)</f>
+      <c r="D12" s="32">
+        <f>SUM(D8:D11)</f>
         <v>2059375</v>
       </c>
-      <c r="E11" s="32">
-        <f>SUM(E8:E10)</f>
+      <c r="E12" s="32">
+        <f>SUM(E8:E11)</f>
         <v>2306162</v>
       </c>
-      <c r="F11" s="32">
-        <f>SUM(F8:F10)</f>
+      <c r="F12" s="32">
+        <f>SUM(F8:F11)</f>
         <v>2581867</v>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
-        <v>301</v>
-      </c>
-      <c r="B14" s="33">
-        <f>B5-B11</f>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="B15" s="33">
+        <f>B5-B12</f>
         <v>-212164</v>
       </c>
-      <c r="C14" s="33">
-        <f>C5-C11</f>
+      <c r="C15" s="33">
+        <f>C5-C12</f>
         <v>455670</v>
       </c>
-      <c r="D14" s="33">
-        <f>D5-D11</f>
+      <c r="D15" s="33">
+        <f>D5-D12</f>
         <v>1308590</v>
       </c>
-      <c r="E14" s="33">
-        <f>E5-E11</f>
+      <c r="E15" s="33">
+        <f>E5-E12</f>
         <v>2196369</v>
       </c>
-      <c r="F14" s="33">
-        <f>F5-F11</f>
+      <c r="F15" s="33">
+        <f>F5-F12</f>
         <v>3114494</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B15" s="30">
-        <f>IF(B5=0,0,B14/B5)</f>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B16" s="30">
+        <f>IF(B5=0,0,B15/B5)</f>
         <v>-0.18005398</v>
       </c>
-      <c r="C15" s="30">
-        <f>IF(C5=0,0,C14/C5)</f>
+      <c r="C16" s="30">
+        <f>IF(C5=0,0,C15/C5)</f>
         <v>0.20148131</v>
       </c>
-      <c r="D15" s="30">
-        <f>IF(D5=0,0,D14/D5)</f>
+      <c r="D16" s="30">
+        <f>IF(D5=0,0,D15/D5)</f>
         <v>0.38854014</v>
       </c>
-      <c r="E15" s="30">
-        <f>IF(E5=0,0,E14/E5)</f>
+      <c r="E16" s="30">
+        <f>IF(E5=0,0,E15/E5)</f>
         <v>0.48780763</v>
       </c>
-      <c r="F15" s="30">
-        <f>IF(F5=0,0,F14/F5)</f>
+      <c r="F16" s="30">
+        <f>IF(F5=0,0,F15/F5)</f>
         <v>0.54675147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="B16" s="34">
-        <f>B14</f>
-        <v>-212164</v>
-      </c>
-      <c r="C16" s="34">
-        <f>B16+C14</f>
-        <v>243507</v>
-      </c>
-      <c r="D16" s="34">
-        <f>C16+D14</f>
-        <v>1552096</v>
-      </c>
-      <c r="E16" s="34">
-        <f>D16+E14</f>
-        <v>3748465</v>
-      </c>
-      <c r="F16" s="34">
-        <f>E16+F14</f>
-        <v>6862959</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="B17" s="41" t="s">
+        <v>354</v>
+      </c>
+      <c r="B17" s="34">
+        <f>B15</f>
+        <v>-212164</v>
+      </c>
+      <c r="C17" s="34">
+        <f>B17+C15</f>
+        <v>243507</v>
+      </c>
+      <c r="D17" s="34">
+        <f>C17+D15</f>
+        <v>1552096</v>
+      </c>
+      <c r="E17" s="34">
+        <f>D17+E15</f>
+        <v>3748465</v>
+      </c>
+      <c r="F17" s="34">
+        <f>E17+F15</f>
+        <v>6862959</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="42" t="s">
-        <v>334</v>
-      </c>
-      <c r="D17" s="41" t="s">
+      <c r="C18" s="44" t="s">
+        <v>356</v>
+      </c>
+      <c r="D18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F18" s="43" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5012,24 +5206,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5038,25 +5232,25 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>336</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>337</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>338</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>243</v>
+      <c r="A5" s="45" t="s">
+        <v>358</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>359</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B6" s="23">
         <v>350000</v>
@@ -5074,7 +5268,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -5084,7 +5278,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="B9" s="31">
         <f>B6</f>
@@ -5109,7 +5303,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5134,7 +5328,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5159,7 +5353,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -5184,7 +5378,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B13" s="39">
         <f>MAX(0,B9-B11)</f>
@@ -5233,7 +5427,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5246,24 +5440,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5273,52 +5467,52 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B5" s="46">
+        <v>369</v>
+      </c>
+      <c r="B5" s="48">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>74498</v>
       </c>
-      <c r="C5" s="46">
-        <f>B5+'5-Year Operating Stmt'!C14</f>
+      <c r="C5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15</f>
         <v>530168</v>
       </c>
-      <c r="D5" s="46">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
+      <c r="D5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
         <v>1838758</v>
       </c>
-      <c r="E5" s="46">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
+      <c r="E5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
         <v>4035127</v>
       </c>
-      <c r="F5" s="46">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
+      <c r="F5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
         <v>7149621</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="B6" s="31">
-        <v>0</v>
+        <v>67795</v>
       </c>
       <c r="C6" s="31">
-        <v>0</v>
+        <v>130119</v>
       </c>
       <c r="D6" s="31">
-        <v>0</v>
+        <v>193773</v>
       </c>
       <c r="E6" s="31">
-        <v>0</v>
+        <v>259050</v>
       </c>
       <c r="F6" s="31">
-        <v>0</v>
+        <v>327736</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B7" s="31">
         <v>0</v>
@@ -5338,7 +5532,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B8" s="31">
         <v>0</v>
@@ -5358,32 +5552,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
-        <v>74498</v>
+        <v>142293</v>
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>530168</v>
+        <v>660288</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>1838758</v>
+        <v>2032531</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>4035127</v>
+        <v>4294177</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>7149621</v>
+        <v>7477357</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5393,7 +5587,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B12" s="31">
         <v>0</v>
@@ -5413,7 +5607,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
@@ -5438,7 +5632,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
@@ -5463,7 +5657,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5473,50 +5667,50 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
-        <v>-249157</v>
+        <v>-181362</v>
       </c>
       <c r="C17" s="33">
         <f>C9-C14</f>
-        <v>234484</v>
+        <v>364603</v>
       </c>
       <c r="D17" s="33">
         <f>D9-D14</f>
-        <v>1572769</v>
+        <v>1766542</v>
       </c>
       <c r="E17" s="33">
         <f>E9-E14</f>
-        <v>3800665</v>
+        <v>4059714</v>
       </c>
       <c r="F17" s="33">
         <f>F9-F14</f>
-        <v>6948630</v>
+        <v>7276366</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B19" s="47" t="str">
+        <v>380</v>
+      </c>
+      <c r="B19" s="49" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="49" t="str">
         <f>C9-C14-C17</f>
-        <v>-1</v>
-      </c>
-      <c r="D19" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="D19" s="49" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="47" t="str">
+      <c r="E19" s="50">
         <f>E9-E14-E17</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="47" t="str">
+        <v>1</v>
+      </c>
+      <c r="F19" s="49" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -5538,7 +5732,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5547,7 +5741,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5560,24 +5754,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5587,7 +5781,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B5" s="31">
         <v>1178333</v>
@@ -5607,7 +5801,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B6" s="31">
         <v>780535</v>
@@ -5627,7 +5821,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="B7" s="31">
         <v>503333</v>
@@ -5647,372 +5841,432 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="B8" s="34">
-        <f>B5-B6-B7</f>
-        <v>-105535</v>
+        <v>-212164</v>
       </c>
       <c r="C8" s="34">
-        <f>C5-C6-C7</f>
-        <v>522299</v>
+        <v>455670</v>
       </c>
       <c r="D8" s="34">
-        <f>D5-D6-D7</f>
-        <v>1380218</v>
+        <v>1308590</v>
       </c>
       <c r="E8" s="34">
-        <f>E5-E6-E7</f>
-        <v>2252998</v>
+        <v>2196369</v>
       </c>
       <c r="F8" s="34">
-        <f>F5-F6-F7</f>
-        <v>3171123</v>
+        <v>3114494</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>322</v>
+        <v>385</v>
       </c>
       <c r="B9" s="31">
+        <v>0</v>
+      </c>
+      <c r="C9" s="31">
+        <v>0</v>
+      </c>
+      <c r="D9" s="31">
+        <v>0</v>
+      </c>
+      <c r="E9" s="31">
+        <v>0</v>
+      </c>
+      <c r="F9" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="31">
         <v>46629</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C10" s="31">
         <v>46629</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D10" s="31">
         <v>46629</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E10" s="31">
         <v>46629</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F10" s="31">
         <v>46629</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="B10" s="49">
-        <f>IF(B9=0,"N/A",B8/B9)</f>
-        <v>-2.26</v>
-      </c>
-      <c r="C10" s="49">
-        <f>IF(C9=0,"N/A",C8/C9)</f>
-        <v>11.2</v>
-      </c>
-      <c r="D10" s="49">
-        <f>IF(D9=0,"N/A",D8/D9)</f>
-        <v>29.6</v>
-      </c>
-      <c r="E10" s="49">
-        <f>IF(E9=0,"N/A",E8/E9)</f>
-        <v>48.32</v>
-      </c>
-      <c r="F10" s="49">
-        <f>IF(F9=0,"N/A",F8/F9)</f>
-        <v>68.01</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="B13" s="31">
-        <v>74498</v>
-      </c>
-      <c r="C13" s="31">
-        <v>530168</v>
-      </c>
-      <c r="D13" s="31">
-        <v>1838758</v>
-      </c>
-      <c r="E13" s="31">
-        <v>4035127</v>
-      </c>
-      <c r="F13" s="31">
-        <v>7149621</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="B14" s="36">
-        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>20</v>
-      </c>
-      <c r="C14" s="36">
-        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>108</v>
-      </c>
-      <c r="D14" s="36">
-        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>330</v>
-      </c>
-      <c r="E14" s="36">
-        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>641</v>
-      </c>
-      <c r="F14" s="36">
-        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>1015</v>
-      </c>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B11" s="34">
+        <f>B8+B9+B10</f>
+        <v>-165535</v>
+      </c>
+      <c r="C11" s="34">
+        <f>C8+C9+C10</f>
+        <v>502299</v>
+      </c>
+      <c r="D11" s="34">
+        <f>D8+D9+D10</f>
+        <v>1355218</v>
+      </c>
+      <c r="E11" s="34">
+        <f>E8+E9+E10</f>
+        <v>2242998</v>
+      </c>
+      <c r="F11" s="34">
+        <f>F8+F9+F10</f>
+        <v>3161123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="51">
+        <f>IF(B10=0,"N/A",B11/B10)</f>
+        <v>-3.55</v>
+      </c>
+      <c r="C12" s="51">
+        <f>IF(C10=0,"N/A",C11/C10)</f>
+        <v>10.77</v>
+      </c>
+      <c r="D12" s="51">
+        <f>IF(D10=0,"N/A",D11/D10)</f>
+        <v>29.06</v>
+      </c>
+      <c r="E12" s="51">
+        <f>IF(E10=0,"N/A",E11/E10)</f>
+        <v>48.1</v>
+      </c>
+      <c r="F12" s="51">
+        <f>IF(F10=0,"N/A",F11/F10)</f>
+        <v>67.79</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="B15" s="35">
-        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>0.7</v>
-      </c>
-      <c r="C15" s="35">
-        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>3.6</v>
-      </c>
-      <c r="D15" s="35">
-        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>10.8</v>
-      </c>
-      <c r="E15" s="35">
-        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>21.1</v>
-      </c>
-      <c r="F15" s="35">
-        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>33.4</v>
+        <v>390</v>
+      </c>
+      <c r="B15" s="31">
+        <v>74498</v>
+      </c>
+      <c r="C15" s="31">
+        <v>530168</v>
+      </c>
+      <c r="D15" s="31">
+        <v>1838758</v>
+      </c>
+      <c r="E15" s="31">
+        <v>4035127</v>
+      </c>
+      <c r="F15" s="31">
+        <v>7149621</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="B16" s="30">
+        <v>391</v>
+      </c>
+      <c r="B16" s="36">
+        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
+        <v>20</v>
+      </c>
+      <c r="C16" s="36">
+        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
+        <v>107</v>
+      </c>
+      <c r="D16" s="36">
+        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
+        <v>326</v>
+      </c>
+      <c r="E16" s="36">
+        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
+        <v>639</v>
+      </c>
+      <c r="F16" s="36">
+        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B17" s="35">
+        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="35">
+        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
+        <v>3.5</v>
+      </c>
+      <c r="D17" s="35">
+        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
+        <v>10.7</v>
+      </c>
+      <c r="E17" s="35">
+        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
+        <v>21</v>
+      </c>
+      <c r="F17" s="35">
+        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="30">
         <v>0.2</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C18" s="30">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D18" s="30">
         <v>0.5</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E18" s="30">
         <v>0.6666666666666666</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F18" s="30">
         <v>0.8333333333333334</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B19" s="31">
-        <v>9819</v>
-      </c>
-      <c r="C19" s="31">
-        <v>11308</v>
-      </c>
-      <c r="D19" s="31">
-        <v>11227</v>
-      </c>
-      <c r="E19" s="31">
-        <v>11256</v>
-      </c>
-      <c r="F19" s="31">
-        <v>11393</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="B20" s="31">
-        <v>827164</v>
-      </c>
-      <c r="C20" s="31">
-        <v>1011370</v>
-      </c>
-      <c r="D20" s="31">
-        <v>1040312</v>
-      </c>
-      <c r="E20" s="31">
-        <v>1070123</v>
-      </c>
-      <c r="F20" s="31">
-        <v>1100827</v>
-      </c>
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>370</v>
+        <v>268</v>
       </c>
       <c r="B21" s="31">
+        <v>9819</v>
+      </c>
+      <c r="C21" s="31">
+        <v>11308</v>
+      </c>
+      <c r="D21" s="31">
+        <v>11227</v>
+      </c>
+      <c r="E21" s="31">
+        <v>11256</v>
+      </c>
+      <c r="F21" s="31">
+        <v>11393</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="B22" s="31">
+        <v>827164</v>
+      </c>
+      <c r="C22" s="31">
+        <v>1011370</v>
+      </c>
+      <c r="D22" s="31">
+        <v>1040312</v>
+      </c>
+      <c r="E22" s="31">
+        <v>1070123</v>
+      </c>
+      <c r="F22" s="31">
+        <v>1100827</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B23" s="31">
         <v>4194</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C23" s="31">
         <v>3873</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D23" s="31">
         <v>3314</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E23" s="31">
         <v>3065</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F23" s="31">
         <v>2942</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="B22" s="50">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B24" s="52">
         <v>148</v>
       </c>
-      <c r="C22" s="50">
+      <c r="C24" s="52">
         <v>137</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D24" s="52">
         <v>132</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E24" s="52">
         <v>131</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F24" s="52">
         <v>131</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="D25" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="E25" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="F25" s="52" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="D26" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="E26" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="F26" s="52" t="s">
-        <v>375</v>
-      </c>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="B27" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>374</v>
+        <v>398</v>
+      </c>
+      <c r="B27" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="C27" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="D27" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="E27" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C28" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="D28" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="E28" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="F28" s="52" t="s">
-        <v>375</v>
+        <v>401</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="D28" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="E28" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="F28" s="54" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>379</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="D29" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="F29" s="52" t="s">
-        <v>375</v>
+        <v>402</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="E31" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="54" t="s">
+        <v>400</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -6052,28 +6306,28 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
-        <v>380</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>381</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>112</v>
+      <c r="A3" s="55" t="s">
+        <v>406</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>407</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B4" s="31">
         <v>350000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="E4" s="31">
         <v>250000</v>
@@ -6081,13 +6335,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="B5" s="31">
         <v>150000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E5" s="31">
         <v>60000</v>
@@ -6095,7 +6349,7 @@
     </row>
     <row r="6" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D6" s="11" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="E6" s="31">
         <v>50000</v>
@@ -6103,7 +6357,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="E7" s="31">
         <v>140000</v>
@@ -6111,13 +6365,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="B9" s="33">
         <v>500000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="E9" s="33">
         <v>500000</v>
@@ -6125,9 +6379,9 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="B10" s="47">
+        <v>414</v>
+      </c>
+      <c r="B10" s="49">
         <v>0</v>
       </c>
     </row>
@@ -6148,7 +6402,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C43"/>
+  <dimension ref="B3:C44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6414,18 +6668,26 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="14" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="14"/>
+      <c r="C41" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -6450,6 +6712,7 @@
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
+    <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6473,7 +6736,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6483,7 +6746,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6493,7 +6756,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6501,24 +6764,24 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B6" s="31">
         <v>1178333</v>
@@ -6538,7 +6801,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B7" s="31">
         <v>1330497</v>
@@ -6558,7 +6821,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B8" s="33">
         <v>-152164</v>
@@ -6578,7 +6841,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B9" s="30">
         <v>-0.12913460606689658</v>
@@ -6598,27 +6861,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B10" s="54">
+        <v>388</v>
+      </c>
+      <c r="B10" s="56">
         <v>-2.26</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="56">
         <v>11.2</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="56">
         <v>29.6</v>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="56">
         <v>48.32</v>
       </c>
-      <c r="F10" s="54">
+      <c r="F10" s="56">
         <v>68.01</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="B11" s="36">
         <v>148</v>
@@ -6638,7 +6901,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6648,7 +6911,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6656,24 +6919,24 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B16" s="31">
         <v>1001583</v>
@@ -6693,7 +6956,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B17" s="31">
         <v>1330497</v>
@@ -6713,7 +6976,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B18" s="33">
         <v>-328914</v>
@@ -6733,7 +6996,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B19" s="30">
         <v>-0.32839365419634886</v>
@@ -6753,27 +7016,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B20" s="54">
+        <v>388</v>
+      </c>
+      <c r="B20" s="56">
         <v>-6.05</v>
       </c>
-      <c r="C20" s="54">
+      <c r="C20" s="56">
         <v>3.93</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="56">
         <v>18.77</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="56">
         <v>33.83</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="56">
         <v>49.68</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="B21" s="36">
         <v>170</v>
@@ -6793,7 +7056,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6803,7 +7066,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6811,24 +7074,24 @@
         <v>7</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="B26" s="31">
         <v>1084067</v>
@@ -6848,7 +7111,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B27" s="31">
         <v>1330497</v>
@@ -6868,7 +7131,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B28" s="33">
         <v>-246430</v>
@@ -6888,7 +7151,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B29" s="30">
         <v>-0.2273202239857572</v>
@@ -6908,27 +7171,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B30" s="54">
+        <v>388</v>
+      </c>
+      <c r="B30" s="56">
         <v>-4.28</v>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="56">
         <v>7.32</v>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="56">
         <v>23.82</v>
       </c>
-      <c r="E30" s="54">
+      <c r="E30" s="56">
         <v>40.59</v>
       </c>
-      <c r="F30" s="54">
+      <c r="F30" s="56">
         <v>58.23</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="B31" s="36">
         <v>171</v>
@@ -6974,7 +7237,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6986,7 +7249,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -7000,7 +7263,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -7008,7 +7271,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -7032,7 +7295,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -7040,7 +7303,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -7060,25 +7323,25 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="55" t="s">
+      <c r="D12" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="55" t="s">
+      <c r="E12" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="55" t="s">
+      <c r="F12" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="D13" s="31">
         <v>1178333</v>
@@ -7098,7 +7361,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="D14" s="31">
         <v>1330497</v>
@@ -7118,7 +7381,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D15" s="31">
         <v>-212164</v>
@@ -7138,7 +7401,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="D16" s="31">
         <v>74498</v>
@@ -7158,7 +7421,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="D17" s="31">
         <v>323655</v>
@@ -7178,7 +7441,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7198,25 +7461,25 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="55" t="s">
+      <c r="D20" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="55" t="s">
+      <c r="E20" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="55" t="s">
+      <c r="F20" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G20" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="D21" s="30">
         <v>-0.18005398371894768</v>
@@ -7236,27 +7499,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="D22" s="54">
-        <v>-2.26</v>
-      </c>
-      <c r="E22" s="54">
-        <v>11.2</v>
-      </c>
-      <c r="F22" s="54">
-        <v>29.6</v>
-      </c>
-      <c r="G22" s="54">
-        <v>48.32</v>
-      </c>
-      <c r="H22" s="54">
-        <v>68.01</v>
+        <v>388</v>
+      </c>
+      <c r="D22" s="56">
+        <v>-3.55</v>
+      </c>
+      <c r="E22" s="56">
+        <v>10.77</v>
+      </c>
+      <c r="F22" s="56">
+        <v>29.06</v>
+      </c>
+      <c r="G22" s="56">
+        <v>48.1</v>
+      </c>
+      <c r="H22" s="56">
+        <v>67.79</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="D23" s="30">
         <v>0.2</v>
@@ -7276,7 +7539,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="D24" s="36">
         <v>120</v>
@@ -7296,7 +7559,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7337,7 +7600,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7347,662 +7610,662 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="56" t="s">
-        <v>407</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="B3" s="58" t="s">
+        <v>433</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="57" t="s">
-        <v>408</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>409</v>
-      </c>
-      <c r="F4" s="59" t="s">
-        <v>410</v>
+      <c r="B4" s="59" t="s">
+        <v>434</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>435</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>411</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>412</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>413</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>414</v>
-      </c>
-      <c r="F6" s="60" t="s">
-        <v>415</v>
-      </c>
-      <c r="G6" s="60" t="s">
-        <v>416</v>
-      </c>
-      <c r="H6" s="60" t="s">
-        <v>417</v>
+        <v>437</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>438</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>440</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>441</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>442</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="C7" s="61">
+        <v>430</v>
+      </c>
+      <c r="C7" s="63">
         <v>120</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="63">
         <v>200</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="63">
         <v>300</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="63">
         <v>400</v>
       </c>
-      <c r="G7" s="61">
+      <c r="G7" s="63">
         <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="C8" s="62">
+        <v>383</v>
+      </c>
+      <c r="C8" s="64">
         <v>1178333.3333333335</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="64">
         <v>2261600</v>
       </c>
-      <c r="E8" s="62">
+      <c r="E8" s="64">
         <v>3367965</v>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="64">
         <v>4502531.525</v>
       </c>
-      <c r="G8" s="62">
+      <c r="G8" s="64">
         <v>5696361.453</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" s="62">
+        <v>338</v>
+      </c>
+      <c r="C9" s="64">
         <v>780535</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="64">
         <v>964741.26</v>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="64">
         <v>993683.4978</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="64">
         <v>1023494.002734</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="64">
         <v>1054198.82281602</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C10" s="62">
+        <v>339</v>
+      </c>
+      <c r="C10" s="64">
         <v>503333.3333333334</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="64">
         <v>774560</v>
       </c>
-      <c r="E10" s="62">
+      <c r="E10" s="64">
         <v>994063.2999999999</v>
       </c>
-      <c r="F10" s="62">
+      <c r="F10" s="64">
         <v>1226039.6940000001</v>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="64">
         <v>1471040.01467</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="C11" s="62">
+        <v>340</v>
+      </c>
+      <c r="C11" s="64">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="64">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="62">
+      <c r="E11" s="64">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="62">
+      <c r="F11" s="64">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="64">
         <v>46628.6108154935</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C12" s="63">
+        <v>384</v>
+      </c>
+      <c r="C12" s="65">
         <v>-212163.6108154934</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="66">
         <v>455670.12918450637</v>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="66">
         <v>1308589.5913845068</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="66">
         <v>2196369.217450507</v>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="66">
         <v>3114494.004698486</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="C13" s="64">
+        <v>390</v>
+      </c>
+      <c r="C13" s="66">
         <v>74498</v>
       </c>
-      <c r="D13" s="64">
+      <c r="D13" s="66">
         <v>530168.1291845064</v>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="66">
         <v>1838757.7205690132</v>
       </c>
-      <c r="F13" s="64">
+      <c r="F13" s="66">
         <v>4035126.93801952</v>
       </c>
-      <c r="G13" s="64">
+      <c r="G13" s="66">
         <v>7149620.942718007</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="C14" s="65">
+        <v>429</v>
+      </c>
+      <c r="C14" s="67">
         <v>-0.18005398371894768</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D14" s="68">
         <v>0.20148130933167066</v>
       </c>
-      <c r="E14" s="66">
+      <c r="E14" s="68">
         <v>0.38854013963461814</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="68">
         <v>0.48780762672183775</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="68">
         <v>0.54675147116204</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="C15" s="67">
+        <v>268</v>
+      </c>
+      <c r="C15" s="69">
         <v>9819.444444444445</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="70">
         <v>11308</v>
       </c>
-      <c r="E15" s="68">
+      <c r="E15" s="70">
         <v>11226.55</v>
       </c>
-      <c r="F15" s="68">
+      <c r="F15" s="70">
         <v>11256.328812500002</v>
       </c>
-      <c r="G15" s="68">
+      <c r="G15" s="70">
         <v>11392.722905999999</v>
       </c>
-      <c r="H15" s="69" t="s">
-        <v>419</v>
+      <c r="H15" s="71" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C16" s="70">
+        <v>322</v>
+      </c>
+      <c r="C16" s="72">
         <v>11087.474534573557</v>
       </c>
-      <c r="D16" s="70">
+      <c r="D16" s="72">
         <v>8929.649354077466</v>
       </c>
-      <c r="E16" s="70">
+      <c r="E16" s="72">
         <v>6781.251362051644</v>
       </c>
-      <c r="F16" s="70">
+      <c r="F16" s="72">
         <v>5740.405768873734</v>
       </c>
-      <c r="G16" s="70">
+      <c r="G16" s="72">
         <v>5143.734896603028</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="C17" s="62">
+        <v>445</v>
+      </c>
+      <c r="C17" s="64">
         <v>650</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="64">
         <v>669.5</v>
       </c>
-      <c r="E17" s="62">
+      <c r="E17" s="64">
         <v>689.5849999999999</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="64">
         <v>710.27255</v>
       </c>
-      <c r="G17" s="62">
+      <c r="G17" s="64">
         <v>731.5807265000001</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="C18" s="67">
+        <v>446</v>
+      </c>
+      <c r="C18" s="69">
         <v>2683.3333333333335</v>
       </c>
-      <c r="D18" s="68">
+      <c r="D18" s="70">
         <v>1658.3</v>
       </c>
-      <c r="E18" s="68">
+      <c r="E18" s="70">
         <v>1138.6993333333332</v>
       </c>
-      <c r="F18" s="68">
+      <c r="F18" s="70">
         <v>879.645235</v>
       </c>
-      <c r="G18" s="68">
+      <c r="G18" s="70">
         <v>724.8276736400001</v>
       </c>
-      <c r="H18" s="69" t="s">
-        <v>422</v>
+      <c r="H18" s="71" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C19" s="71">
+        <v>448</v>
+      </c>
+      <c r="C19" s="73">
         <v>-1768.0300901291116</v>
       </c>
-      <c r="D19" s="72">
+      <c r="D19" s="74">
         <v>2278.350645922532</v>
       </c>
-      <c r="E19" s="72">
+      <c r="E19" s="74">
         <v>4361.965304615022</v>
       </c>
-      <c r="F19" s="72">
+      <c r="F19" s="74">
         <v>5490.923043626268</v>
       </c>
-      <c r="G19" s="72">
+      <c r="G19" s="74">
         <v>6228.988009396972</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="C20" s="65">
+        <v>449</v>
+      </c>
+      <c r="C20" s="67">
         <v>0.6624059405940593</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="68">
         <v>0.4265746639547223</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="68">
         <v>0.29503973402336425</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="68">
         <v>0.22731523300861284</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="68">
         <v>0.18506529677129674</v>
       </c>
-      <c r="H20" s="69" t="s">
-        <v>425</v>
+      <c r="H20" s="71" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C21" s="65">
+        <v>451</v>
+      </c>
+      <c r="C21" s="67">
         <v>0.27326732673267323</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="68">
         <v>0.14664839051998585</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="68">
         <v>0.1014291419299191</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="68">
         <v>0.07814672524697092</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G21" s="68">
         <v>0.06362198744062038</v>
       </c>
-      <c r="H21" s="69" t="s">
-        <v>427</v>
+      <c r="H21" s="71" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="C22" s="65">
+        <v>453</v>
+      </c>
+      <c r="C22" s="67">
         <v>-0.08956294200848645</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="68">
         <v>0.23094213830916166</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="68">
         <v>0.40980776290727494</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="68">
         <v>0.5003846870935568</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G22" s="68">
         <v>0.5566926610396014</v>
       </c>
-      <c r="H22" s="69" t="s">
-        <v>429</v>
+      <c r="H22" s="71" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="C23" s="73">
+        <v>455</v>
+      </c>
+      <c r="C23" s="75">
         <v>3</v>
       </c>
-      <c r="D23" s="73">
+      <c r="D23" s="75">
         <v>3</v>
       </c>
-      <c r="E23" s="73">
+      <c r="E23" s="75">
         <v>3</v>
       </c>
-      <c r="F23" s="73">
+      <c r="F23" s="75">
         <v>3</v>
       </c>
-      <c r="G23" s="73">
+      <c r="G23" s="75">
         <v>3</v>
       </c>
-      <c r="H23" s="69" t="s">
-        <v>431</v>
+      <c r="H23" s="71" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C24" s="74">
+        <v>388</v>
+      </c>
+      <c r="C24" s="76">
         <v>-2.2633099754482346</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D24" s="77">
         <v>11.201250281006729</v>
       </c>
-      <c r="E24" s="75">
+      <c r="E24" s="77">
         <v>29.600242813611526</v>
       </c>
-      <c r="F24" s="75">
+      <c r="F24" s="77">
         <v>48.31792731679209</v>
       </c>
-      <c r="G24" s="75">
+      <c r="G24" s="77">
         <v>68.00808688171976</v>
       </c>
-      <c r="H24" s="69" t="s">
-        <v>432</v>
+      <c r="H24" s="71" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="C25" s="76" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>458</v>
+      </c>
+      <c r="C25" s="78" t="str">
+        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="42" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+      <c r="D25" s="44" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="E25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+      <c r="E25" s="78" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+      <c r="F25" s="78" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="76" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+      <c r="G25" s="78" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="69" t="s">
-        <v>412</v>
+      <c r="H25" s="71" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="C26" s="77">
+        <v>459</v>
+      </c>
+      <c r="C26" s="79">
         <v>1</v>
       </c>
-      <c r="D26" s="77">
+      <c r="D26" s="79">
         <v>4</v>
       </c>
-      <c r="E26" s="77">
+      <c r="E26" s="79">
         <v>11</v>
       </c>
-      <c r="F26" s="78">
+      <c r="F26" s="80">
         <v>21</v>
       </c>
-      <c r="G26" s="73">
+      <c r="G26" s="75">
         <v>33</v>
       </c>
-      <c r="H26" s="69" t="s">
-        <v>435</v>
+      <c r="H26" s="71" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="C27" s="77">
+        <v>391</v>
+      </c>
+      <c r="C27" s="79">
         <v>20</v>
       </c>
-      <c r="D27" s="73">
+      <c r="D27" s="75">
         <v>108</v>
       </c>
-      <c r="E27" s="73">
+      <c r="E27" s="75">
         <v>330</v>
       </c>
-      <c r="F27" s="73">
+      <c r="F27" s="75">
         <v>641</v>
       </c>
-      <c r="G27" s="73">
+      <c r="G27" s="75">
         <v>1015</v>
       </c>
-      <c r="H27" s="69" t="s">
-        <v>436</v>
+      <c r="H27" s="71" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="43" t="s">
-        <v>441</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D30" s="79" t="s">
-        <v>443</v>
-      </c>
-      <c r="E30" s="79"/>
-      <c r="F30" s="80" t="s">
-        <v>444</v>
-      </c>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
+      <c r="B30" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D30" s="81" t="s">
+        <v>468</v>
+      </c>
+      <c r="E30" s="81"/>
+      <c r="F30" s="82" t="s">
+        <v>469</v>
+      </c>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="43" t="s">
-        <v>445</v>
-      </c>
-      <c r="C31" s="81" t="s">
-        <v>446</v>
-      </c>
-      <c r="D31" s="79" t="s">
-        <v>447</v>
-      </c>
-      <c r="E31" s="79"/>
-      <c r="F31" s="80" t="s">
-        <v>448</v>
-      </c>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
+      <c r="B31" s="45" t="s">
+        <v>470</v>
+      </c>
+      <c r="C31" s="83" t="s">
+        <v>471</v>
+      </c>
+      <c r="D31" s="81" t="s">
+        <v>472</v>
+      </c>
+      <c r="E31" s="81"/>
+      <c r="F31" s="82" t="s">
+        <v>473</v>
+      </c>
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="43" t="s">
-        <v>449</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D32" s="79" t="s">
-        <v>450</v>
-      </c>
-      <c r="E32" s="79"/>
-      <c r="F32" s="80" t="s">
-        <v>451</v>
-      </c>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
+      <c r="B32" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D32" s="81" t="s">
+        <v>475</v>
+      </c>
+      <c r="E32" s="81"/>
+      <c r="F32" s="82" t="s">
+        <v>476</v>
+      </c>
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="43" t="s">
-        <v>452</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D33" s="79" t="s">
-        <v>453</v>
-      </c>
-      <c r="E33" s="79"/>
-      <c r="F33" s="80" t="s">
-        <v>454</v>
-      </c>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
+      <c r="B33" s="45" t="s">
+        <v>477</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>478</v>
+      </c>
+      <c r="E33" s="81"/>
+      <c r="F33" s="82" t="s">
+        <v>479</v>
+      </c>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="43" t="s">
-        <v>455</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D34" s="79" t="s">
-        <v>456</v>
-      </c>
-      <c r="E34" s="79"/>
-      <c r="F34" s="80" t="s">
-        <v>457</v>
-      </c>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
+      <c r="B34" s="45" t="s">
+        <v>480</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D34" s="81" t="s">
+        <v>481</v>
+      </c>
+      <c r="E34" s="81"/>
+      <c r="F34" s="82" t="s">
+        <v>482</v>
+      </c>
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="43" t="s">
-        <v>458</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D35" s="79" t="s">
-        <v>459</v>
-      </c>
-      <c r="E35" s="79"/>
-      <c r="F35" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
+      <c r="B35" s="45" t="s">
+        <v>483</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D35" s="81" t="s">
+        <v>484</v>
+      </c>
+      <c r="E35" s="81"/>
+      <c r="F35" s="82" t="s">
+        <v>485</v>
+      </c>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="43" t="s">
-        <v>461</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="D36" s="79" t="s">
-        <v>462</v>
-      </c>
-      <c r="E36" s="79"/>
-      <c r="F36" s="80" t="s">
-        <v>463</v>
-      </c>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
+      <c r="B36" s="45" t="s">
+        <v>486</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="D36" s="81" t="s">
+        <v>487</v>
+      </c>
+      <c r="E36" s="81"/>
+      <c r="F36" s="82" t="s">
+        <v>488</v>
+      </c>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="43" t="s">
-        <v>464</v>
+      <c r="B38" s="45" t="s">
+        <v>489</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="82" t="s">
-        <v>466</v>
-      </c>
-      <c r="C40" s="82"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="82"/>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="82"/>
+      <c r="B40" s="84" t="s">
+        <v>491</v>
+      </c>
+      <c r="C40" s="84"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
+      <c r="G40" s="84"/>
+      <c r="H40" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -8109,12 +8372,225 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="21"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B4" s="85"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B7" s="85"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="B9" s="19"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B10" s="85"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B13" s="85"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B16" s="85"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="B18" s="19"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B19" s="85"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="B21" s="19"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B22" s="85"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B24" s="19"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B25" s="85"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="B27" s="19"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="B28" s="85"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="86" t="s">
+        <v>503</v>
+      </c>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="87" t="s">
+        <v>504</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -8128,7 +8604,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -8138,7 +8614,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8152,18 +8628,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8206,10 +8682,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -8230,7 +8706,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -8238,7 +8714,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="20">
         <v>600</v>
@@ -8246,7 +8722,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -8260,24 +8736,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B17" s="22">
         <v>120</v>
@@ -8297,7 +8773,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -8306,32 +8782,35 @@
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" s="23">
         <v>8500</v>
@@ -8339,16 +8818,19 @@
       <c r="E21" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>750</v>
@@ -8356,16 +8838,19 @@
       <c r="E22" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>115</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D23" s="23">
         <v>1100</v>
@@ -8373,16 +8858,19 @@
       <c r="E23" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D24" s="23">
         <v>150000</v>
@@ -8390,16 +8878,19 @@
       <c r="E24" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D25" s="23">
         <v>25000</v>
@@ -8407,16 +8898,19 @@
       <c r="E25" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D26" s="23">
         <v>400</v>
@@ -8424,10 +8918,13 @@
       <c r="E26" s="24">
         <v>0</v>
       </c>
+      <c r="F26" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -8438,36 +8935,36 @@
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D30" s="25">
         <v>1</v>
@@ -8484,13 +8981,13 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D31" s="25">
         <v>1</v>
@@ -8507,13 +9004,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D32" s="25">
         <v>5</v>
@@ -8530,13 +9027,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="D33" s="25">
         <v>1</v>
@@ -8553,13 +9050,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D34" s="25">
         <v>3</v>
@@ -8576,13 +9073,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D35" s="25">
         <v>1</v>
@@ -8599,13 +9096,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D36" s="25">
         <v>2</v>
@@ -8622,7 +9119,7 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -8633,30 +9130,30 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D40" s="23">
         <v>22000</v>
@@ -8667,13 +9164,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D41" s="23">
         <v>3000</v>
@@ -8684,13 +9181,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D42" s="23">
         <v>22000</v>
@@ -8701,13 +9198,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D43" s="23">
         <v>650</v>
@@ -8718,13 +9215,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D44" s="23">
         <v>450</v>
@@ -8735,13 +9232,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D45" s="23">
         <v>30000</v>
@@ -8752,13 +9249,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D46" s="23">
         <v>12000</v>
@@ -8769,13 +9266,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D47" s="23">
         <v>18000</v>
@@ -8786,13 +9283,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D48" s="23">
         <v>750</v>
@@ -8803,7 +9300,7 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -8814,27 +9311,27 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C52" s="23">
         <v>350000</v>
@@ -8848,10 +9345,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C53" s="23">
         <v>60000</v>
@@ -8865,7 +9362,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -8876,29 +9373,29 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B56" s="24">
         <v>0.03</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B57" s="24">
         <v>0.03</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B58" s="25">
         <v>0.8333333333333334</v>
@@ -8906,7 +9403,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B59" s="23">
         <v>0</v>
@@ -8914,168 +9411,259 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B62" s="24">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>178</v>
+        <v>182</v>
+      </c>
+      <c r="B63" s="24">
+        <v>0.03</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>147</v>
+        <v>183</v>
+      </c>
+      <c r="B64" s="24">
+        <v>0.25</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B65" s="22">
-        <v>0</v>
+        <v>184</v>
+      </c>
+      <c r="B65" s="24">
+        <v>0.08</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B66" s="22">
+        <v>185</v>
+      </c>
+      <c r="B66" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B71" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B76" s="20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B77" s="22">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B67" s="27">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B79" s="27">
         <v>0.95</v>
       </c>
     </row>
-    <row r="69" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B70" s="23">
+    <row r="81" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B82" s="23">
         <v>8200</v>
       </c>
-      <c r="C70" s="23">
+      <c r="C82" s="23">
         <v>9100</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D82" s="23">
         <v>10500</v>
       </c>
     </row>
-    <row r="72" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B72" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D72" s="21" t="s">
+    <row r="84" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B84" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="E72" s="21" t="s">
+      <c r="C84" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F72" s="21" t="s">
+      <c r="D84" s="21" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="B73" s="22">
+      <c r="E84" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B85" s="22">
         <v>80</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C85" s="22">
         <v>130</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D85" s="22">
         <v>180</v>
       </c>
-      <c r="E73" s="22">
+      <c r="E85" s="22">
         <v>230</v>
       </c>
-      <c r="F73" s="22">
+      <c r="F85" s="22">
         <v>260</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B74" s="22">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B86" s="22">
         <v>40</v>
       </c>
-      <c r="C74" s="22">
+      <c r="C86" s="22">
         <v>70</v>
       </c>
-      <c r="D74" s="22">
+      <c r="D86" s="22">
         <v>100</v>
       </c>
-      <c r="E74" s="22">
+      <c r="E86" s="22">
         <v>120</v>
       </c>
-      <c r="F74" s="22">
+      <c r="F86" s="22">
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="B75" s="22">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B87" s="22">
         <v>0</v>
       </c>
-      <c r="C75" s="22">
+      <c r="C87" s="22">
         <v>0</v>
       </c>
-      <c r="D75" s="22">
+      <c r="D87" s="22">
         <v>20</v>
       </c>
-      <c r="E75" s="22">
+      <c r="E87" s="22">
         <v>50</v>
       </c>
-      <c r="F75" s="22">
+      <c r="F87" s="22">
         <v>100</v>
       </c>
     </row>
@@ -9111,10 +9699,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -9135,10 +9723,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -9151,7 +9739,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -9159,66 +9747,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -9261,24 +9849,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -9288,7 +9876,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="28">
         <v>120</v>
@@ -9308,7 +9896,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="22">
         <v>600</v>
@@ -9316,7 +9904,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B8" s="29">
         <f>B6/$B$7</f>
@@ -9341,10 +9929,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C10" s="30">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
@@ -9389,7 +9977,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9402,24 +9990,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9429,7 +10017,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B5" s="31">
         <v>969000</v>
@@ -9449,7 +10037,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B6" s="31">
         <v>90000</v>
@@ -9469,7 +10057,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B7" s="31">
         <v>132000</v>
@@ -9489,7 +10077,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5,B6,B7)</f>
@@ -9514,7 +10102,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -9524,7 +10112,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B10" s="23">
         <v>150000</v>
@@ -9544,7 +10132,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B11" s="23">
         <v>25000</v>
@@ -9564,7 +10152,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="B12" s="32">
         <f>SUM(B10,B11)</f>
@@ -9589,7 +10177,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -9599,7 +10187,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B14" s="31">
         <v>48000</v>
@@ -9619,7 +10207,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="B15" s="32">
         <f>SUM(B14)</f>
@@ -9644,7 +10232,7 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="B17" s="33">
         <f>SUM(B8,B12,B15)</f>
@@ -9684,7 +10272,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -9693,9 +10281,10 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>61</v>
       </c>
@@ -9705,36 +10294,40 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C4" s="25">
         <v>1</v>
@@ -9751,13 +10344,16 @@
       <c r="G4" s="34">
         <v>140333</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C5" s="25">
         <v>1</v>
@@ -9774,13 +10370,16 @@
       <c r="G5" s="34">
         <v>109593</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C6" s="25">
         <v>5</v>
@@ -9797,13 +10396,16 @@
       <c r="G6" s="34">
         <v>334125</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C7" s="25">
         <v>1</v>
@@ -9820,13 +10422,16 @@
       <c r="G7" s="34">
         <v>70835</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C8" s="25">
         <v>3</v>
@@ -9843,13 +10448,16 @@
       <c r="G8" s="34">
         <v>105546</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C9" s="25">
         <v>1</v>
@@ -9866,13 +10474,16 @@
       <c r="G9" s="34">
         <v>82863</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C10" s="25">
         <v>2</v>
@@ -9889,10 +10500,13 @@
       <c r="G10" s="34">
         <v>93348</v>
       </c>
+      <c r="H10" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -9906,24 +10520,24 @@
         <v>7</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B14" s="33">
         <v>780535</v>
@@ -9943,7 +10557,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B15" s="30">
         <v>0.5520049504950495</v>
@@ -9963,7 +10577,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B16" s="35">
         <v>8.6</v>
@@ -9983,7 +10597,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -10007,7 +10621,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -10020,24 +10634,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -10047,7 +10661,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B5" s="31">
         <v>78000</v>
@@ -10067,7 +10681,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
@@ -10092,7 +10706,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -10102,7 +10716,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B8" s="31">
         <v>54000</v>
@@ -10122,7 +10736,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
@@ -10147,7 +10761,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -10157,7 +10771,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B11" s="31">
         <v>264000</v>
@@ -10177,7 +10791,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B12" s="31">
         <v>36000</v>
@@ -10197,7 +10811,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B13" s="31">
         <v>22000</v>
@@ -10217,7 +10831,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B11:B13)</f>
@@ -10242,7 +10856,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -10252,7 +10866,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B16" s="31">
         <v>30000</v>
@@ -10272,7 +10886,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B17" s="31">
         <v>12000</v>
@@ -10292,7 +10906,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B18" s="31">
         <v>18000</v>
@@ -10312,7 +10926,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B19" s="31">
         <v>90000</v>
@@ -10332,7 +10946,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B20" s="32">
         <f>SUM(B16:B19)</f>
@@ -10357,7 +10971,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B22" s="33">
         <f>B6+B9+B14+B20</f>
@@ -10407,7 +11021,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -10417,30 +11031,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C4" s="23">
         <v>350000</v>
@@ -10457,10 +11071,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C5" s="23">
         <v>60000</v>
@@ -10477,7 +11091,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="F7" s="33">
         <v>46629</v>
@@ -10485,7 +11099,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="F8" s="32">
         <v>350000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -27,14 +27,15 @@
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
+    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="508">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -42,7 +43,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -162,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1335,7 +1336,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1540,6 +1541,15 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Assumptions Memo</t>
+  </si>
+  <si>
+    <t>Founder-supplied reasoning for each assumption captured during the wizard. Empty when no rationale was entered for that area.</t>
+  </si>
+  <si>
+    <t>No founder rationale captured.</t>
   </si>
   <si>
     <t>Decision History</t>
@@ -1562,7 +1572,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1709,6 +1719,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1804,7 +1819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1955,6 +1970,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -8536,6 +8555,54 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="86" t="s">
+        <v>503</v>
+      </c>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="87" t="s">
+        <v>504</v>
+      </c>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8554,7 +8621,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -8564,26 +8631,26 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="86" t="s">
-        <v>503</v>
-      </c>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
+      <c r="B2" s="88" t="s">
+        <v>506</v>
+      </c>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="87" t="s">
-        <v>504</v>
-      </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
+      <c r="B4" s="89" t="s">
+        <v>507</v>
+      </c>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Charter_ADA_Grade-Band.xlsx
@@ -43,7 +43,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -163,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1336,7 +1336,7 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1444,7 +1444,7 @@
     <t>The model reaches net income early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1462,7 +1462,7 @@
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 19% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 18% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1480,7 +1480,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 68.01x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 72.19x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1498,7 +1498,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>33.4 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>35.5 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1882,7 +1882,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1921,9 +1920,6 @@
     <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1931,10 +1927,16 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3469,23 +3471,23 @@
       </c>
       <c r="B11" s="32">
         <f>SUM(B5:B10)</f>
-        <v>1178333</v>
+        <v>1220833</v>
       </c>
       <c r="C11" s="32">
         <f>SUM(C5:C10)</f>
-        <v>2261600</v>
+        <v>2328800</v>
       </c>
       <c r="D11" s="32">
         <f>SUM(D5:D10)</f>
-        <v>3367965</v>
+        <v>3452300</v>
       </c>
       <c r="E11" s="32">
         <f>SUM(E5:E10)</f>
-        <v>4502532</v>
+        <v>4623000</v>
       </c>
       <c r="F11" s="32">
         <f>SUM(F5:F10)</f>
-        <v>5696361</v>
+        <v>5891500</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4083,23 +4085,23 @@
       </c>
       <c r="B4" s="34">
         <f>'Budget Detail'!B11</f>
-        <v>1178333</v>
+        <v>1220833</v>
       </c>
       <c r="C4" s="34">
         <f>'Budget Detail'!C11</f>
-        <v>2261600</v>
+        <v>2328800</v>
       </c>
       <c r="D4" s="34">
         <f>'Budget Detail'!D11</f>
-        <v>3367965</v>
+        <v>3452300</v>
       </c>
       <c r="E4" s="34">
         <f>'Budget Detail'!E11</f>
-        <v>4502532</v>
+        <v>4623000</v>
       </c>
       <c r="F4" s="34">
         <f>'Budget Detail'!F11</f>
-        <v>5696361</v>
+        <v>5891500</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4218,23 +4220,23 @@
       </c>
       <c r="B11" s="33">
         <f>B4-B8</f>
-        <v>-212164</v>
+        <v>-169664</v>
       </c>
       <c r="C11" s="33">
         <f>C4-C8</f>
-        <v>455670</v>
+        <v>522870</v>
       </c>
       <c r="D11" s="33">
         <f>D4-D8</f>
-        <v>1308590</v>
+        <v>1392925</v>
       </c>
       <c r="E11" s="33">
         <f>E4-E8</f>
-        <v>2196369</v>
+        <v>2316838</v>
       </c>
       <c r="F11" s="33">
         <f>F4-F8</f>
-        <v>3114494</v>
+        <v>3309633</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4243,23 +4245,23 @@
       </c>
       <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
-        <v>-0.18005398</v>
+        <v>-0.13897361</v>
       </c>
       <c r="C12" s="30">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.20148131</v>
+        <v>0.22452342</v>
       </c>
       <c r="D12" s="30">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.38854014</v>
+        <v>0.40347727</v>
       </c>
       <c r="E12" s="30">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.48780763</v>
+        <v>0.50115459</v>
       </c>
       <c r="F12" s="30">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.54675147</v>
+        <v>0.56176399</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4267,19 +4269,19 @@
         <v>321</v>
       </c>
       <c r="B13" s="31">
-        <v>-212164</v>
+        <v>-169664</v>
       </c>
       <c r="C13" s="31">
-        <v>243507</v>
+        <v>353207</v>
       </c>
       <c r="D13" s="31">
-        <v>1552096</v>
+        <v>1746131</v>
       </c>
       <c r="E13" s="31">
-        <v>3748465</v>
+        <v>4062969</v>
       </c>
       <c r="F13" s="31">
-        <v>6862959</v>
+        <v>7372601</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4287,19 +4289,19 @@
         <v>268</v>
       </c>
       <c r="B14" s="31">
-        <v>9819</v>
+        <v>10174</v>
       </c>
       <c r="C14" s="31">
-        <v>11308</v>
+        <v>11644</v>
       </c>
       <c r="D14" s="31">
-        <v>11227</v>
+        <v>11508</v>
       </c>
       <c r="E14" s="31">
-        <v>11256</v>
+        <v>11558</v>
       </c>
       <c r="F14" s="31">
-        <v>11393</v>
+        <v>11783</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4950,19 +4952,19 @@
         <v>290</v>
       </c>
       <c r="B5" s="32">
-        <v>1178333</v>
+        <v>1220833</v>
       </c>
       <c r="C5" s="32">
-        <v>2261600</v>
+        <v>2328800</v>
       </c>
       <c r="D5" s="32">
-        <v>3367965</v>
+        <v>3452300</v>
       </c>
       <c r="E5" s="32">
-        <v>4502532</v>
+        <v>4623000</v>
       </c>
       <c r="F5" s="32">
-        <v>5696361</v>
+        <v>5891500</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5096,23 +5098,23 @@
       </c>
       <c r="B15" s="33">
         <f>B5-B12</f>
-        <v>-212164</v>
+        <v>-169664</v>
       </c>
       <c r="C15" s="33">
         <f>C5-C12</f>
-        <v>455670</v>
+        <v>522870</v>
       </c>
       <c r="D15" s="33">
         <f>D5-D12</f>
-        <v>1308590</v>
+        <v>1392925</v>
       </c>
       <c r="E15" s="33">
         <f>E5-E12</f>
-        <v>2196369</v>
+        <v>2316838</v>
       </c>
       <c r="F15" s="33">
         <f>F5-F12</f>
-        <v>3114494</v>
+        <v>3309633</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5121,23 +5123,23 @@
       </c>
       <c r="B16" s="30">
         <f>IF(B5=0,0,B15/B5)</f>
-        <v>-0.18005398</v>
+        <v>-0.13897361</v>
       </c>
       <c r="C16" s="30">
         <f>IF(C5=0,0,C15/C5)</f>
-        <v>0.20148131</v>
+        <v>0.22452342</v>
       </c>
       <c r="D16" s="30">
         <f>IF(D5=0,0,D15/D5)</f>
-        <v>0.38854014</v>
+        <v>0.40347727</v>
       </c>
       <c r="E16" s="30">
         <f>IF(E5=0,0,E15/E5)</f>
-        <v>0.48780763</v>
+        <v>0.50115459</v>
       </c>
       <c r="F16" s="30">
         <f>IF(F5=0,0,F15/F5)</f>
-        <v>0.54675147</v>
+        <v>0.56176399</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5146,23 +5148,23 @@
       </c>
       <c r="B17" s="34">
         <f>B15</f>
-        <v>-212164</v>
+        <v>-169664</v>
       </c>
       <c r="C17" s="34">
         <f>B17+C15</f>
-        <v>243507</v>
+        <v>353207</v>
       </c>
       <c r="D17" s="34">
         <f>C17+D15</f>
-        <v>1552096</v>
+        <v>1746131</v>
       </c>
       <c r="E17" s="34">
         <f>D17+E15</f>
-        <v>3748465</v>
+        <v>4062969</v>
       </c>
       <c r="F17" s="34">
         <f>E17+F15</f>
-        <v>6862959</v>
+        <v>7372601</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5494,19 +5496,19 @@
       </c>
       <c r="C5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15</f>
-        <v>530168</v>
+        <v>597368</v>
       </c>
       <c r="D5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
-        <v>1838758</v>
+        <v>1990293</v>
       </c>
       <c r="E5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
-        <v>4035127</v>
+        <v>4307130</v>
       </c>
       <c r="F5" s="48">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
-        <v>7149621</v>
+        <v>7616763</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5514,19 +5516,19 @@
         <v>370</v>
       </c>
       <c r="B6" s="31">
-        <v>67795</v>
+        <v>70240</v>
       </c>
       <c r="C6" s="31">
-        <v>130119</v>
+        <v>133986</v>
       </c>
       <c r="D6" s="31">
-        <v>193773</v>
+        <v>198625</v>
       </c>
       <c r="E6" s="31">
-        <v>259050</v>
+        <v>265981</v>
       </c>
       <c r="F6" s="31">
-        <v>327736</v>
+        <v>338963</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5575,23 +5577,23 @@
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
-        <v>142293</v>
+        <v>144738</v>
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>660288</v>
+        <v>731354</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>2032531</v>
+        <v>2188918</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>4294177</v>
+        <v>4573111</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>7477357</v>
+        <v>7955726</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5690,23 +5692,23 @@
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
-        <v>-181362</v>
+        <v>-178917</v>
       </c>
       <c r="C17" s="33">
         <f>C9-C14</f>
-        <v>364603</v>
+        <v>435669</v>
       </c>
       <c r="D17" s="33">
         <f>D9-D14</f>
-        <v>1766542</v>
+        <v>1922929</v>
       </c>
       <c r="E17" s="33">
         <f>E9-E14</f>
-        <v>4059714</v>
+        <v>4338649</v>
       </c>
       <c r="F17" s="33">
         <f>F9-F14</f>
-        <v>7276366</v>
+        <v>7754735</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5725,9 +5727,9 @@
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="49" t="str">
         <f>E9-E14-E17</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="49" t="str">
         <f>F9-F14-F17</f>
@@ -5803,19 +5805,19 @@
         <v>383</v>
       </c>
       <c r="B5" s="31">
-        <v>1178333</v>
+        <v>1220833</v>
       </c>
       <c r="C5" s="31">
-        <v>2261600</v>
+        <v>2328800</v>
       </c>
       <c r="D5" s="31">
-        <v>3367965</v>
+        <v>3452300</v>
       </c>
       <c r="E5" s="31">
-        <v>4502532</v>
+        <v>4623000</v>
       </c>
       <c r="F5" s="31">
-        <v>5696361</v>
+        <v>5891500</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5863,19 +5865,19 @@
         <v>384</v>
       </c>
       <c r="B8" s="34">
-        <v>-212164</v>
+        <v>-169664</v>
       </c>
       <c r="C8" s="34">
-        <v>455670</v>
+        <v>522870</v>
       </c>
       <c r="D8" s="34">
-        <v>1308590</v>
+        <v>1392925</v>
       </c>
       <c r="E8" s="34">
-        <v>2196369</v>
+        <v>2316838</v>
       </c>
       <c r="F8" s="34">
-        <v>3114494</v>
+        <v>3309633</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5924,48 +5926,48 @@
       </c>
       <c r="B11" s="34">
         <f>B8+B9+B10</f>
-        <v>-165535</v>
+        <v>-123035</v>
       </c>
       <c r="C11" s="34">
         <f>C8+C9+C10</f>
-        <v>502299</v>
+        <v>569499</v>
       </c>
       <c r="D11" s="34">
         <f>D8+D9+D10</f>
-        <v>1355218</v>
+        <v>1439553</v>
       </c>
       <c r="E11" s="34">
         <f>E8+E9+E10</f>
-        <v>2242998</v>
+        <v>2363466</v>
       </c>
       <c r="F11" s="34">
         <f>F8+F9+F10</f>
-        <v>3161123</v>
+        <v>3356261</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="B12" s="51">
+      <c r="B12" s="50">
         <f>IF(B10=0,"N/A",B11/B10)</f>
-        <v>-3.55</v>
-      </c>
-      <c r="C12" s="51">
+        <v>-2.64</v>
+      </c>
+      <c r="C12" s="50">
         <f>IF(C10=0,"N/A",C11/C10)</f>
-        <v>10.77</v>
-      </c>
-      <c r="D12" s="51">
+        <v>12.21</v>
+      </c>
+      <c r="D12" s="50">
         <f>IF(D10=0,"N/A",D11/D10)</f>
-        <v>29.06</v>
-      </c>
-      <c r="E12" s="51">
+        <v>30.87</v>
+      </c>
+      <c r="E12" s="50">
         <f>IF(E10=0,"N/A",E11/E10)</f>
-        <v>48.1</v>
-      </c>
-      <c r="F12" s="51">
+        <v>50.69</v>
+      </c>
+      <c r="F12" s="50">
         <f>IF(F10=0,"N/A",F11/F10)</f>
-        <v>67.79</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5986,16 +5988,16 @@
         <v>74498</v>
       </c>
       <c r="C15" s="31">
-        <v>530168</v>
+        <v>597368</v>
       </c>
       <c r="D15" s="31">
-        <v>1838758</v>
+        <v>1990293</v>
       </c>
       <c r="E15" s="31">
-        <v>4035127</v>
+        <v>4307130</v>
       </c>
       <c r="F15" s="31">
-        <v>7149621</v>
+        <v>7616763</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6008,19 +6010,19 @@
       </c>
       <c r="C16" s="36">
         <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D16" s="36">
         <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="E16" s="36">
         <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>639</v>
+        <v>682</v>
       </c>
       <c r="F16" s="36">
         <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>1011</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6033,19 +6035,19 @@
       </c>
       <c r="C17" s="35">
         <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="35">
         <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>10.7</v>
+        <v>11.6</v>
       </c>
       <c r="E17" s="35">
         <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>21</v>
+        <v>22.4</v>
       </c>
       <c r="F17" s="35">
         <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>33.2</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6083,19 +6085,19 @@
         <v>268</v>
       </c>
       <c r="B21" s="31">
-        <v>9819</v>
+        <v>10174</v>
       </c>
       <c r="C21" s="31">
-        <v>11308</v>
+        <v>11644</v>
       </c>
       <c r="D21" s="31">
-        <v>11227</v>
+        <v>11508</v>
       </c>
       <c r="E21" s="31">
-        <v>11256</v>
+        <v>11558</v>
       </c>
       <c r="F21" s="31">
-        <v>11393</v>
+        <v>11783</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6142,20 +6144,20 @@
       <c r="A24" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="B24" s="52">
-        <v>148</v>
-      </c>
-      <c r="C24" s="52">
-        <v>137</v>
-      </c>
-      <c r="D24" s="52">
-        <v>132</v>
-      </c>
-      <c r="E24" s="52">
+      <c r="B24" s="51">
+        <v>139</v>
+      </c>
+      <c r="C24" s="51">
         <v>131</v>
       </c>
-      <c r="F24" s="52">
-        <v>131</v>
+      <c r="D24" s="51">
+        <v>127</v>
+      </c>
+      <c r="E24" s="51">
+        <v>127</v>
+      </c>
+      <c r="F24" s="51">
+        <v>125</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6172,19 +6174,19 @@
       <c r="A27" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="C27" s="54" t="s">
+      <c r="C27" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="D27" s="54" t="s">
+      <c r="D27" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="E27" s="54" t="s">
+      <c r="E27" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="F27" s="54" t="s">
+      <c r="F27" s="53" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6192,19 +6194,19 @@
       <c r="A28" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="B28" s="53" t="s">
+      <c r="B28" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="C28" s="54" t="s">
+      <c r="C28" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="D28" s="54" t="s">
+      <c r="D28" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="E28" s="54" t="s">
+      <c r="E28" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="F28" s="54" t="s">
+      <c r="F28" s="53" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6212,19 +6214,19 @@
       <c r="A29" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="D29" s="54" t="s">
+      <c r="D29" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="E29" s="54" t="s">
+      <c r="E29" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="F29" s="54" t="s">
+      <c r="F29" s="53" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6232,19 +6234,19 @@
       <c r="A30" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="E30" s="53" t="s">
+      <c r="E30" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="52" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6252,19 +6254,19 @@
       <c r="A31" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="C31" s="54" t="s">
+      <c r="C31" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="D31" s="54" t="s">
+      <c r="D31" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="E31" s="54" t="s">
+      <c r="E31" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="F31" s="54" t="s">
+      <c r="F31" s="53" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6272,19 +6274,19 @@
       <c r="A32" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="52" t="s">
         <v>399</v>
       </c>
-      <c r="C32" s="54" t="s">
+      <c r="C32" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="D32" s="54" t="s">
+      <c r="D32" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="E32" s="54" t="s">
+      <c r="E32" s="53" t="s">
         <v>400</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="F32" s="53" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6325,16 +6327,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="54" t="s">
         <v>406</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="54" t="s">
         <v>407</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="54" t="s">
         <v>114</v>
       </c>
     </row>
@@ -6803,19 +6805,19 @@
         <v>383</v>
       </c>
       <c r="B6" s="31">
-        <v>1178333</v>
+        <v>1220833</v>
       </c>
       <c r="C6" s="31">
-        <v>2261600</v>
+        <v>2328800</v>
       </c>
       <c r="D6" s="31">
-        <v>3367965</v>
+        <v>3452300</v>
       </c>
       <c r="E6" s="31">
-        <v>4502532</v>
+        <v>4623000</v>
       </c>
       <c r="F6" s="31">
-        <v>5696361</v>
+        <v>5891500</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6843,19 +6845,19 @@
         <v>319</v>
       </c>
       <c r="B8" s="33">
-        <v>-152164</v>
+        <v>-109664</v>
       </c>
       <c r="C8" s="33">
-        <v>475670</v>
+        <v>542870</v>
       </c>
       <c r="D8" s="33">
-        <v>1333590</v>
+        <v>1417925</v>
       </c>
       <c r="E8" s="33">
-        <v>2206369</v>
+        <v>2326838</v>
       </c>
       <c r="F8" s="33">
-        <v>3124494</v>
+        <v>3319633</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6863,39 +6865,39 @@
         <v>320</v>
       </c>
       <c r="B9" s="30">
-        <v>-0.12913460606689658</v>
+        <v>-0.08982684844955091</v>
       </c>
       <c r="C9" s="30">
-        <v>0.21032460611271073</v>
+        <v>0.23311152919293482</v>
       </c>
       <c r="D9" s="30">
-        <v>0.39596301962297903</v>
+        <v>0.41071882263549125</v>
       </c>
       <c r="E9" s="30">
-        <v>0.49002859951113986</v>
+        <v>0.5033176925049766</v>
       </c>
       <c r="F9" s="30">
-        <v>0.5485069777397931</v>
+        <v>0.5634613513873353</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="B10" s="56">
-        <v>-2.26</v>
-      </c>
-      <c r="C10" s="56">
-        <v>11.2</v>
-      </c>
-      <c r="D10" s="56">
-        <v>29.6</v>
-      </c>
-      <c r="E10" s="56">
-        <v>48.32</v>
-      </c>
-      <c r="F10" s="56">
-        <v>68.01</v>
+      <c r="B10" s="55">
+        <v>-1.35</v>
+      </c>
+      <c r="C10" s="55">
+        <v>12.64</v>
+      </c>
+      <c r="D10" s="55">
+        <v>31.41</v>
+      </c>
+      <c r="E10" s="55">
+        <v>50.9</v>
+      </c>
+      <c r="F10" s="55">
+        <v>72.19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6903,19 +6905,19 @@
         <v>396</v>
       </c>
       <c r="B11" s="36">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C11" s="36">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D11" s="36">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E11" s="36">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F11" s="36">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6958,19 +6960,19 @@
         <v>383</v>
       </c>
       <c r="B16" s="31">
-        <v>1001583</v>
+        <v>1037708</v>
       </c>
       <c r="C16" s="31">
-        <v>1922360</v>
+        <v>1979480</v>
       </c>
       <c r="D16" s="31">
-        <v>2862770</v>
+        <v>2934455</v>
       </c>
       <c r="E16" s="31">
-        <v>3827152</v>
+        <v>3929550</v>
       </c>
       <c r="F16" s="31">
-        <v>4841907</v>
+        <v>5007775</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6998,19 +7000,19 @@
         <v>319</v>
       </c>
       <c r="B18" s="33">
-        <v>-328914</v>
+        <v>-292789</v>
       </c>
       <c r="C18" s="33">
-        <v>136430</v>
+        <v>193550</v>
       </c>
       <c r="D18" s="33">
-        <v>828395</v>
+        <v>900080</v>
       </c>
       <c r="E18" s="33">
-        <v>1530989</v>
+        <v>1633388</v>
       </c>
       <c r="F18" s="33">
-        <v>2270040</v>
+        <v>2435908</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -7018,39 +7020,39 @@
         <v>320</v>
       </c>
       <c r="B19" s="30">
-        <v>-0.32839365419634886</v>
+        <v>-0.2821492334700599</v>
       </c>
       <c r="C19" s="30">
-        <v>0.07097012483848322</v>
+        <v>0.09777826963874685</v>
       </c>
       <c r="D19" s="30">
-        <v>0.2893682583799753</v>
+        <v>0.30672802662998977</v>
       </c>
       <c r="E19" s="30">
-        <v>0.40003364648369394</v>
+        <v>0.4156678735352665</v>
       </c>
       <c r="F19" s="30">
-        <v>0.46883173851740356</v>
+        <v>0.48642511927921805</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="B20" s="56">
-        <v>-6.05</v>
-      </c>
-      <c r="C20" s="56">
-        <v>3.93</v>
-      </c>
-      <c r="D20" s="56">
-        <v>18.77</v>
-      </c>
-      <c r="E20" s="56">
-        <v>33.83</v>
-      </c>
-      <c r="F20" s="56">
-        <v>49.68</v>
+      <c r="B20" s="55">
+        <v>-5.28</v>
+      </c>
+      <c r="C20" s="55">
+        <v>5.15</v>
+      </c>
+      <c r="D20" s="55">
+        <v>20.3</v>
+      </c>
+      <c r="E20" s="55">
+        <v>36.03</v>
+      </c>
+      <c r="F20" s="55">
+        <v>53.24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -7058,19 +7060,19 @@
         <v>396</v>
       </c>
       <c r="B21" s="36">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C21" s="36">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D21" s="36">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E21" s="36">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F21" s="36">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7113,19 +7115,19 @@
         <v>383</v>
       </c>
       <c r="B26" s="31">
-        <v>1084067</v>
+        <v>1123167</v>
       </c>
       <c r="C26" s="31">
-        <v>2080672</v>
+        <v>2142496</v>
       </c>
       <c r="D26" s="31">
-        <v>3098528</v>
+        <v>3176116</v>
       </c>
       <c r="E26" s="31">
-        <v>4142329</v>
+        <v>4253160</v>
       </c>
       <c r="F26" s="31">
-        <v>5240653</v>
+        <v>5420180</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -7153,19 +7155,19 @@
         <v>319</v>
       </c>
       <c r="B28" s="33">
-        <v>-246430</v>
+        <v>-207330</v>
       </c>
       <c r="C28" s="33">
-        <v>294742</v>
+        <v>356566</v>
       </c>
       <c r="D28" s="33">
-        <v>1064152</v>
+        <v>1141741</v>
       </c>
       <c r="E28" s="33">
-        <v>1846167</v>
+        <v>1956998</v>
       </c>
       <c r="F28" s="33">
-        <v>2668785</v>
+        <v>2848313</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -7173,39 +7175,39 @@
         <v>320</v>
       </c>
       <c r="B29" s="30">
-        <v>-0.2273202239857572</v>
+        <v>-0.18459440048864212</v>
       </c>
       <c r="C29" s="30">
-        <v>0.1416571805572943</v>
+        <v>0.16642557520971177</v>
       </c>
       <c r="D29" s="30">
-        <v>0.34343806480758593</v>
+        <v>0.359476981125534</v>
       </c>
       <c r="E29" s="30">
-        <v>0.4456832603381955</v>
+        <v>0.46012792663584406</v>
       </c>
       <c r="F29" s="30">
-        <v>0.5092467149345576</v>
+        <v>0.5255014688992776</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="B30" s="56">
-        <v>-4.28</v>
-      </c>
-      <c r="C30" s="56">
-        <v>7.32</v>
-      </c>
-      <c r="D30" s="56">
-        <v>23.82</v>
-      </c>
-      <c r="E30" s="56">
-        <v>40.59</v>
-      </c>
-      <c r="F30" s="56">
-        <v>58.23</v>
+      <c r="B30" s="55">
+        <v>-3.45</v>
+      </c>
+      <c r="C30" s="55">
+        <v>8.65</v>
+      </c>
+      <c r="D30" s="55">
+        <v>25.49</v>
+      </c>
+      <c r="E30" s="55">
+        <v>42.97</v>
+      </c>
+      <c r="F30" s="55">
+        <v>62.09</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -7213,19 +7215,19 @@
         <v>396</v>
       </c>
       <c r="B31" s="36">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C31" s="36">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D31" s="36">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E31" s="36">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F31" s="36">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7342,19 +7344,19 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="F12" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="57" t="s">
+      <c r="G12" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="57" t="s">
+      <c r="H12" s="56" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7363,19 +7365,19 @@
         <v>383</v>
       </c>
       <c r="D13" s="31">
-        <v>1178333</v>
+        <v>1220833</v>
       </c>
       <c r="E13" s="31">
-        <v>2261600</v>
+        <v>2328800</v>
       </c>
       <c r="F13" s="31">
-        <v>3367965</v>
+        <v>3452300</v>
       </c>
       <c r="G13" s="31">
-        <v>4502532</v>
+        <v>4623000</v>
       </c>
       <c r="H13" s="31">
-        <v>5696361</v>
+        <v>5891500</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -7403,19 +7405,19 @@
         <v>319</v>
       </c>
       <c r="D15" s="31">
-        <v>-212164</v>
+        <v>-169664</v>
       </c>
       <c r="E15" s="31">
-        <v>455670</v>
+        <v>522870</v>
       </c>
       <c r="F15" s="31">
-        <v>1308590</v>
+        <v>1392925</v>
       </c>
       <c r="G15" s="31">
-        <v>2196369</v>
+        <v>2316838</v>
       </c>
       <c r="H15" s="31">
-        <v>3114494</v>
+        <v>3309633</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -7426,16 +7428,16 @@
         <v>74498</v>
       </c>
       <c r="E16" s="31">
-        <v>530168</v>
+        <v>597368</v>
       </c>
       <c r="F16" s="31">
-        <v>1838758</v>
+        <v>1990293</v>
       </c>
       <c r="G16" s="31">
-        <v>4035127</v>
+        <v>4307130</v>
       </c>
       <c r="H16" s="31">
-        <v>7149621</v>
+        <v>7616763</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7480,19 +7482,19 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="57" t="s">
+      <c r="F20" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="57" t="s">
+      <c r="G20" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="57" t="s">
+      <c r="H20" s="56" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7501,39 +7503,39 @@
         <v>429</v>
       </c>
       <c r="D21" s="30">
-        <v>-0.18005398371894768</v>
+        <v>-0.138973606128732</v>
       </c>
       <c r="E21" s="30">
-        <v>0.20148130933167066</v>
+        <v>0.22452341514278013</v>
       </c>
       <c r="F21" s="30">
-        <v>0.38854013963461814</v>
+        <v>0.40347727352330515</v>
       </c>
       <c r="G21" s="30">
-        <v>0.48780762672183775</v>
+        <v>0.5011545949492768</v>
       </c>
       <c r="H21" s="30">
-        <v>0.54675147116204</v>
+        <v>0.561763990783075</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="D22" s="56">
-        <v>-3.55</v>
-      </c>
-      <c r="E22" s="56">
-        <v>10.77</v>
-      </c>
-      <c r="F22" s="56">
-        <v>29.06</v>
-      </c>
-      <c r="G22" s="56">
-        <v>48.1</v>
-      </c>
-      <c r="H22" s="56">
-        <v>67.79</v>
+      <c r="D22" s="55">
+        <v>-2.64</v>
+      </c>
+      <c r="E22" s="55">
+        <v>12.21</v>
+      </c>
+      <c r="F22" s="55">
+        <v>30.87</v>
+      </c>
+      <c r="G22" s="55">
+        <v>50.69</v>
+      </c>
+      <c r="H22" s="55">
+        <v>71.98</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7607,7 +7609,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7617,7 +7619,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>432</v>
       </c>
@@ -7627,26 +7629,28 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="58" t="s">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="57" t="s">
         <v>433</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="58" t="s">
         <v>434</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="59" t="s">
         <v>435</v>
       </c>
-      <c r="F4" s="61" t="s">
+      <c r="F4" s="60" t="s">
         <v>436</v>
       </c>
     </row>
@@ -7654,22 +7658,22 @@
       <c r="B6" s="19" t="s">
         <v>437</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="61" t="s">
         <v>438</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="61" t="s">
         <v>439</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="61" t="s">
         <v>440</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="61" t="s">
         <v>441</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="61" t="s">
         <v>442</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="61" t="s">
         <v>443</v>
       </c>
     </row>
@@ -7677,19 +7681,19 @@
       <c r="B7" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="62">
         <v>120</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="62">
         <v>200</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="62">
         <v>300</v>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="62">
         <v>400</v>
       </c>
-      <c r="G7" s="63">
+      <c r="G7" s="62">
         <v>500</v>
       </c>
     </row>
@@ -7697,39 +7701,39 @@
       <c r="B8" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="C8" s="64">
-        <v>1178333.3333333335</v>
-      </c>
-      <c r="D8" s="64">
-        <v>2261600</v>
-      </c>
-      <c r="E8" s="64">
-        <v>3367965</v>
-      </c>
-      <c r="F8" s="64">
-        <v>4502531.525</v>
-      </c>
-      <c r="G8" s="64">
-        <v>5696361.453</v>
+      <c r="C8" s="63">
+        <v>1220833.3333333333</v>
+      </c>
+      <c r="D8" s="63">
+        <v>2328800</v>
+      </c>
+      <c r="E8" s="63">
+        <v>3452300</v>
+      </c>
+      <c r="F8" s="63">
+        <v>4623000</v>
+      </c>
+      <c r="G8" s="63">
+        <v>5891500</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C9" s="64">
+      <c r="C9" s="63">
         <v>780535</v>
       </c>
-      <c r="D9" s="64">
+      <c r="D9" s="63">
         <v>964741.26</v>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="63">
         <v>993683.4978</v>
       </c>
-      <c r="F9" s="64">
-        <v>1023494.002734</v>
-      </c>
-      <c r="G9" s="64">
+      <c r="F9" s="63">
+        <v>1023494.0027339999</v>
+      </c>
+      <c r="G9" s="63">
         <v>1054198.82281602</v>
       </c>
     </row>
@@ -7737,39 +7741,39 @@
       <c r="B10" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="C10" s="64">
-        <v>503333.3333333334</v>
-      </c>
-      <c r="D10" s="64">
+      <c r="C10" s="63">
+        <v>503333.3333333333</v>
+      </c>
+      <c r="D10" s="63">
         <v>774560</v>
       </c>
-      <c r="E10" s="64">
-        <v>994063.2999999999</v>
-      </c>
-      <c r="F10" s="64">
-        <v>1226039.6940000001</v>
-      </c>
-      <c r="G10" s="64">
-        <v>1471040.01467</v>
+      <c r="E10" s="63">
+        <v>994063.3</v>
+      </c>
+      <c r="F10" s="63">
+        <v>1226039.694</v>
+      </c>
+      <c r="G10" s="63">
+        <v>1471040.0146700002</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="C11" s="64">
+      <c r="C11" s="63">
         <v>46628.6108154935</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="63">
         <v>46628.6108154935</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="63">
         <v>46628.6108154935</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="63">
         <v>46628.6108154935</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="63">
         <v>46628.6108154935</v>
       </c>
     </row>
@@ -7777,82 +7781,82 @@
       <c r="B12" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="C12" s="65">
-        <v>-212163.6108154934</v>
-      </c>
-      <c r="D12" s="66">
-        <v>455670.12918450637</v>
-      </c>
-      <c r="E12" s="66">
-        <v>1308589.5913845068</v>
-      </c>
-      <c r="F12" s="66">
-        <v>2196369.217450507</v>
-      </c>
-      <c r="G12" s="66">
-        <v>3114494.004698486</v>
+      <c r="C12" s="64">
+        <v>-169663.61081549362</v>
+      </c>
+      <c r="D12" s="65">
+        <v>522870.12918450637</v>
+      </c>
+      <c r="E12" s="65">
+        <v>1392924.5913845063</v>
+      </c>
+      <c r="F12" s="65">
+        <v>2316837.6924505066</v>
+      </c>
+      <c r="G12" s="65">
+        <v>3309632.5516984863</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="C13" s="66">
+      <c r="C13" s="65">
         <v>74498</v>
       </c>
-      <c r="D13" s="66">
-        <v>530168.1291845064</v>
-      </c>
-      <c r="E13" s="66">
-        <v>1838757.7205690132</v>
-      </c>
-      <c r="F13" s="66">
-        <v>4035126.93801952</v>
-      </c>
-      <c r="G13" s="66">
-        <v>7149620.942718007</v>
+      <c r="D13" s="65">
+        <v>597368.1291845064</v>
+      </c>
+      <c r="E13" s="65">
+        <v>1990292.7205690127</v>
+      </c>
+      <c r="F13" s="65">
+        <v>4307130.413019519</v>
+      </c>
+      <c r="G13" s="65">
+        <v>7616762.964718006</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="C14" s="67">
-        <v>-0.18005398371894768</v>
-      </c>
-      <c r="D14" s="68">
-        <v>0.20148130933167066</v>
-      </c>
-      <c r="E14" s="68">
-        <v>0.38854013963461814</v>
-      </c>
-      <c r="F14" s="68">
-        <v>0.48780762672183775</v>
-      </c>
-      <c r="G14" s="68">
-        <v>0.54675147116204</v>
+      <c r="C14" s="66">
+        <v>-0.138973606128732</v>
+      </c>
+      <c r="D14" s="67">
+        <v>0.22452341514278013</v>
+      </c>
+      <c r="E14" s="67">
+        <v>0.40347727352330515</v>
+      </c>
+      <c r="F14" s="67">
+        <v>0.5011545949492768</v>
+      </c>
+      <c r="G14" s="67">
+        <v>0.561763990783075</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="C15" s="69">
-        <v>9819.444444444445</v>
-      </c>
-      <c r="D15" s="70">
-        <v>11308</v>
-      </c>
-      <c r="E15" s="70">
-        <v>11226.55</v>
-      </c>
-      <c r="F15" s="70">
-        <v>11256.328812500002</v>
-      </c>
-      <c r="G15" s="70">
-        <v>11392.722905999999</v>
-      </c>
-      <c r="H15" s="71" t="s">
+      <c r="C15" s="68">
+        <v>10173.611111111111</v>
+      </c>
+      <c r="D15" s="68">
+        <v>11644</v>
+      </c>
+      <c r="E15" s="68">
+        <v>11507.666666666666</v>
+      </c>
+      <c r="F15" s="68">
+        <v>11557.5</v>
+      </c>
+      <c r="G15" s="68">
+        <v>11783</v>
+      </c>
+      <c r="H15" s="69" t="s">
         <v>444</v>
       </c>
     </row>
@@ -7860,19 +7864,19 @@
       <c r="B16" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C16" s="72">
-        <v>11087.474534573557</v>
-      </c>
-      <c r="D16" s="72">
+      <c r="C16" s="70">
+        <v>11087.474534573556</v>
+      </c>
+      <c r="D16" s="70">
         <v>8929.649354077466</v>
       </c>
-      <c r="E16" s="72">
-        <v>6781.251362051644</v>
-      </c>
-      <c r="F16" s="72">
+      <c r="E16" s="70">
+        <v>6781.251362051645</v>
+      </c>
+      <c r="F16" s="70">
         <v>5740.405768873734</v>
       </c>
-      <c r="G16" s="72">
+      <c r="G16" s="70">
         <v>5143.734896603028</v>
       </c>
     </row>
@@ -7880,19 +7884,19 @@
       <c r="B17" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="C17" s="64">
+      <c r="C17" s="63">
         <v>650</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="63">
         <v>669.5</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="63">
         <v>689.5849999999999</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="63">
         <v>710.27255</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="63">
         <v>731.5807265000001</v>
       </c>
     </row>
@@ -7900,22 +7904,22 @@
       <c r="B18" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="C18" s="69">
+      <c r="C18" s="71">
         <v>2683.3333333333335</v>
       </c>
-      <c r="D18" s="70">
+      <c r="D18" s="68">
         <v>1658.3</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="68">
         <v>1138.6993333333332</v>
       </c>
-      <c r="F18" s="70">
+      <c r="F18" s="68">
         <v>879.645235</v>
       </c>
-      <c r="G18" s="70">
+      <c r="G18" s="68">
         <v>724.8276736400001</v>
       </c>
-      <c r="H18" s="71" t="s">
+      <c r="H18" s="69" t="s">
         <v>447</v>
       </c>
     </row>
@@ -7923,42 +7927,42 @@
       <c r="B19" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="C19" s="73">
-        <v>-1768.0300901291116</v>
-      </c>
-      <c r="D19" s="74">
-        <v>2278.350645922532</v>
-      </c>
-      <c r="E19" s="74">
-        <v>4361.965304615022</v>
-      </c>
-      <c r="F19" s="74">
-        <v>5490.923043626268</v>
-      </c>
-      <c r="G19" s="74">
-        <v>6228.988009396972</v>
+      <c r="C19" s="72">
+        <v>-1413.863423462447</v>
+      </c>
+      <c r="D19" s="73">
+        <v>2614.350645922532</v>
+      </c>
+      <c r="E19" s="73">
+        <v>4643.081971281687</v>
+      </c>
+      <c r="F19" s="73">
+        <v>5792.094231126266</v>
+      </c>
+      <c r="G19" s="73">
+        <v>6619.265103396972</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="C20" s="67">
-        <v>0.6624059405940593</v>
-      </c>
-      <c r="D20" s="68">
-        <v>0.4265746639547223</v>
-      </c>
-      <c r="E20" s="68">
-        <v>0.29503973402336425</v>
-      </c>
-      <c r="F20" s="68">
-        <v>0.22731523300861284</v>
-      </c>
-      <c r="G20" s="68">
-        <v>0.18506529677129674</v>
-      </c>
-      <c r="H20" s="71" t="s">
+      <c r="C20" s="74">
+        <v>0.6393460750853243</v>
+      </c>
+      <c r="D20" s="67">
+        <v>0.4142653984884919</v>
+      </c>
+      <c r="E20" s="67">
+        <v>0.2878323140515019</v>
+      </c>
+      <c r="F20" s="67">
+        <v>0.22139173755872807</v>
+      </c>
+      <c r="G20" s="67">
+        <v>0.1789355550905576</v>
+      </c>
+      <c r="H20" s="69" t="s">
         <v>450</v>
       </c>
     </row>
@@ -7966,22 +7970,22 @@
       <c r="B21" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="C21" s="67">
-        <v>0.27326732673267323</v>
-      </c>
-      <c r="D21" s="68">
-        <v>0.14664839051998585</v>
-      </c>
-      <c r="E21" s="68">
-        <v>0.1014291419299191</v>
-      </c>
-      <c r="F21" s="68">
-        <v>0.07814672524697092</v>
-      </c>
-      <c r="G21" s="68">
-        <v>0.06362198744062038</v>
-      </c>
-      <c r="H21" s="71" t="s">
+      <c r="C21" s="66">
+        <v>0.26375426621160414</v>
+      </c>
+      <c r="D21" s="67">
+        <v>0.1424166952937135</v>
+      </c>
+      <c r="E21" s="67">
+        <v>0.09895136575616255</v>
+      </c>
+      <c r="F21" s="67">
+        <v>0.0761103383084577</v>
+      </c>
+      <c r="G21" s="67">
+        <v>0.061514696905711624</v>
+      </c>
+      <c r="H21" s="69" t="s">
         <v>452</v>
       </c>
     </row>
@@ -7989,22 +7993,22 @@
       <c r="B22" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="C22" s="67">
-        <v>-0.08956294200848645</v>
-      </c>
-      <c r="D22" s="68">
-        <v>0.23094213830916166</v>
-      </c>
-      <c r="E22" s="68">
-        <v>0.40980776290727494</v>
-      </c>
-      <c r="F22" s="68">
-        <v>0.5003846870935568</v>
-      </c>
-      <c r="G22" s="68">
-        <v>0.5566926610396014</v>
-      </c>
-      <c r="H22" s="71" t="s">
+      <c r="C22" s="66">
+        <v>-0.051632764505119506</v>
+      </c>
+      <c r="D22" s="67">
+        <v>0.25313412057712126</v>
+      </c>
+      <c r="E22" s="67">
+        <v>0.4242253576456275</v>
+      </c>
+      <c r="F22" s="67">
+        <v>0.5134039159130435</v>
+      </c>
+      <c r="G22" s="67">
+        <v>0.5713759080902961</v>
+      </c>
+      <c r="H22" s="69" t="s">
         <v>454</v>
       </c>
     </row>
@@ -8027,7 +8031,7 @@
       <c r="G23" s="75">
         <v>3</v>
       </c>
-      <c r="H23" s="71" t="s">
+      <c r="H23" s="69" t="s">
         <v>456</v>
       </c>
     </row>
@@ -8036,21 +8040,21 @@
         <v>388</v>
       </c>
       <c r="C24" s="76">
-        <v>-2.2633099754482346</v>
+        <v>-1.3518524120185698</v>
       </c>
       <c r="D24" s="77">
-        <v>11.201250281006729</v>
+        <v>12.642425534241406</v>
       </c>
       <c r="E24" s="77">
-        <v>29.600242813611526</v>
+        <v>31.408896310360724</v>
       </c>
       <c r="F24" s="77">
-        <v>48.31792731679209</v>
+        <v>50.90150149781768</v>
       </c>
       <c r="G24" s="77">
-        <v>68.00808688171976</v>
-      </c>
-      <c r="H24" s="71" t="s">
+        <v>72.19303993065684</v>
+      </c>
+      <c r="H24" s="69" t="s">
         <v>457</v>
       </c>
     </row>
@@ -8078,7 +8082,7 @@
         <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="71" t="s">
+      <c r="H25" s="69" t="s">
         <v>438</v>
       </c>
     </row>
@@ -8092,16 +8096,16 @@
       <c r="D26" s="79">
         <v>4</v>
       </c>
-      <c r="E26" s="79">
-        <v>11</v>
+      <c r="E26" s="80">
+        <v>12</v>
       </c>
       <c r="F26" s="80">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G26" s="75">
-        <v>33</v>
-      </c>
-      <c r="H26" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="69" t="s">
         <v>460</v>
       </c>
     </row>
@@ -8113,22 +8117,22 @@
         <v>20</v>
       </c>
       <c r="D27" s="75">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E27" s="75">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="F27" s="75">
-        <v>641</v>
+        <v>685</v>
       </c>
       <c r="G27" s="75">
-        <v>1015</v>
-      </c>
-      <c r="H27" s="71" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H27" s="69" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>462</v>
       </c>
@@ -8144,8 +8148,9 @@
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="45" t="s">
         <v>466</v>
       </c>
@@ -8161,8 +8166,9 @@
       </c>
       <c r="G30" s="82"/>
       <c r="H30" s="82"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="82"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="45" t="s">
         <v>470</v>
       </c>
@@ -8178,8 +8184,9 @@
       </c>
       <c r="G31" s="82"/>
       <c r="H31" s="82"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="82"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="45" t="s">
         <v>474</v>
       </c>
@@ -8195,8 +8202,9 @@
       </c>
       <c r="G32" s="82"/>
       <c r="H32" s="82"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="82"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="45" t="s">
         <v>477</v>
       </c>
@@ -8212,8 +8220,9 @@
       </c>
       <c r="G33" s="82"/>
       <c r="H33" s="82"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="82"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="45" t="s">
         <v>480</v>
       </c>
@@ -8229,8 +8238,9 @@
       </c>
       <c r="G34" s="82"/>
       <c r="H34" s="82"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="82"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="45" t="s">
         <v>483</v>
       </c>
@@ -8246,8 +8256,9 @@
       </c>
       <c r="G35" s="82"/>
       <c r="H35" s="82"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="82"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="45" t="s">
         <v>486</v>
       </c>
@@ -8263,6 +8274,7 @@
       </c>
       <c r="G36" s="82"/>
       <c r="H36" s="82"/>
+      <c r="I36" s="82"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="45" t="s">
@@ -8275,7 +8287,7 @@
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="84" t="s">
         <v>491</v>
       </c>
@@ -8285,29 +8297,30 @@
       <c r="F40" s="84"/>
       <c r="G40" s="84"/>
       <c r="H40" s="84"/>
+      <c r="I40" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8787,7 +8800,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>103</v>
       </c>
@@ -8796,7 +8809,6 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -10039,7 +10051,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10571,7 +10583,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>241</v>
       </c>
@@ -10580,7 +10592,6 @@
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
@@ -10683,7 +10694,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
